--- a/input/ES/reg_home_ownership.xlsx
+++ b/input/ES/reg_home_ownership.xlsx
@@ -53,7 +53,7 @@
     <t>Have combined dhhtp_c4 and lessp_c3 into a single variable with 8 cateogries, dhhtp_c8</t>
   </si>
   <si>
-    <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES5 =  Sur , ES5 = ,  Canarias.</t>
+    <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES6=  Sur , ES7 = ,  Canarias.</t>
   </si>
   <si>
     <t>Estimated on the sample of benefit unit heads.</t>
@@ -360,7 +360,7 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.82527764862821207</v>
+        <v>0.82527868238661584</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -368,7 +368,7 @@
         <v>22</v>
       </c>
       <c r="F5">
-        <v>34641.609700401503</v>
+        <v>34641.743101335895</v>
       </c>
     </row>
     <row r="6">
@@ -376,7 +376,7 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>178069</v>
+        <v>178071</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -384,7 +384,7 @@
         <v>23</v>
       </c>
       <c r="F6">
-        <v>-21003588.814084016</v>
+        <v>-21003652.813034989</v>
       </c>
     </row>
   </sheetData>
@@ -514,112 +514,112 @@
         <v>26</v>
       </c>
       <c r="B2">
-        <v>0.026883115152069433</v>
+        <v>0.026895337107439264</v>
       </c>
       <c r="C2">
-        <v>0.0004559747218091649</v>
+        <v>0.00045598098670887225</v>
       </c>
       <c r="D2">
-        <v>3.6242021476330278e-06</v>
+        <v>3.6215291549113554e-06</v>
       </c>
       <c r="E2">
-        <v>-7.4736878992871302e-09</v>
+        <v>-7.4480976254347049e-09</v>
       </c>
       <c r="F2">
-        <v>6.729506504589151e-05</v>
+        <v>6.7268826536586617e-05</v>
       </c>
       <c r="G2">
-        <v>-7.7622022958695488e-05</v>
+        <v>-7.76349176659076e-05</v>
       </c>
       <c r="H2">
-        <v>3.3335838907160016e-06</v>
+        <v>3.3341554446164095e-06</v>
       </c>
       <c r="I2">
-        <v>-9.6576786167536471e-05</v>
+        <v>-9.6585898395810108e-05</v>
       </c>
       <c r="J2">
-        <v>-9.6713508606986016e-05</v>
+        <v>-9.6715316770636358e-05</v>
       </c>
       <c r="K2">
-        <v>0.00013304687546415061</v>
+        <v>0.00013304390576172323</v>
       </c>
       <c r="L2">
-        <v>0.00022011010259935789</v>
+        <v>0.00022012041977361829</v>
       </c>
       <c r="M2">
-        <v>3.1021431459994536e-05</v>
+        <v>3.0999900657781177e-05</v>
       </c>
       <c r="N2">
-        <v>-0.00010284487799181759</v>
+        <v>-0.00010287980318271373</v>
       </c>
       <c r="O2">
-        <v>-6.2230380287060094e-05</v>
+        <v>-6.2240004934265684e-05</v>
       </c>
       <c r="P2">
-        <v>-4.2743199445159099e-05</v>
+        <v>-4.2742447953118519e-05</v>
       </c>
       <c r="Q2">
-        <v>-7.1669919744395317e-05</v>
+        <v>-7.1684750782153312e-05</v>
       </c>
       <c r="R2">
-        <v>0.00013420566143491886</v>
+        <v>0.0001342129335474713</v>
       </c>
       <c r="S2">
-        <v>-3.4921551950940357e-05</v>
+        <v>-3.492902222563712e-05</v>
       </c>
       <c r="T2">
-        <v>-3.5548423043606316e-05</v>
+        <v>-3.5571747157914926e-05</v>
       </c>
       <c r="U2">
-        <v>-8.4529721572964401e-05</v>
+        <v>-8.4545928728930157e-05</v>
       </c>
       <c r="V2">
-        <v>-1.4813620219372844e-06</v>
+        <v>-1.5333079626743306e-06</v>
       </c>
       <c r="W2">
-        <v>1.7352256984078351e-05</v>
+        <v>1.7320127798754005e-05</v>
       </c>
       <c r="X2">
-        <v>-2.7548024030372515e-05</v>
+        <v>-2.7578672969093225e-05</v>
       </c>
       <c r="Y2">
-        <v>-9.7104411995299622e-05</v>
+        <v>-9.7140136555206414e-05</v>
       </c>
       <c r="Z2">
-        <v>-1.3078918440939959e-06</v>
+        <v>-1.3032057519368863e-06</v>
       </c>
       <c r="AA2">
-        <v>-3.7839195947584752e-05</v>
+        <v>-3.7841443168210034e-05</v>
       </c>
       <c r="AB2">
-        <v>-8.321893980225406e-05</v>
+        <v>-8.3220926574514197e-05</v>
       </c>
       <c r="AC2">
-        <v>-8.9065044076384702e-05</v>
+        <v>-8.906949029818085e-05</v>
       </c>
       <c r="AD2">
-        <v>-9.2779629768422294e-05</v>
+        <v>-9.2826737795602955e-05</v>
       </c>
       <c r="AE2">
-        <v>-0.00010770340055663942</v>
+        <v>-0.00010770278311922061</v>
       </c>
       <c r="AF2">
-        <v>-6.8490860444218293e-05</v>
+        <v>-6.848526538045293e-05</v>
       </c>
       <c r="AG2">
-        <v>2.2238731019172593e-06</v>
+        <v>2.2275491929254512e-06</v>
       </c>
       <c r="AH2">
-        <v>-2.7857809298481919e-06</v>
+        <v>-2.7855725170312608e-06</v>
       </c>
       <c r="AI2">
-        <v>8.9130519989634747e-05</v>
+        <v>8.915465808709844e-05</v>
       </c>
       <c r="AJ2">
-        <v>1.1049385443962807e-05</v>
+        <v>1.1057416584411131e-05</v>
       </c>
       <c r="AK2">
-        <v>-0.00018440944934257808</v>
+        <v>-0.00018429143249133056</v>
       </c>
     </row>
     <row r="3">
@@ -627,112 +627,112 @@
         <v>27</v>
       </c>
       <c r="B3">
-        <v>-0.0008090090456259007</v>
+        <v>-0.00080459157607772579</v>
       </c>
       <c r="C3">
-        <v>3.6242021476330278e-06</v>
+        <v>3.6215291549113554e-06</v>
       </c>
       <c r="D3">
-        <v>1.2118005580314373e-05</v>
+        <v>1.211723183217659e-05</v>
       </c>
       <c r="E3">
-        <v>-1.1047932550441516e-07</v>
+        <v>-1.1047162587412689e-07</v>
       </c>
       <c r="F3">
-        <v>2.6677204931288101e-05</v>
+        <v>2.6670843332077363e-05</v>
       </c>
       <c r="G3">
-        <v>3.3881584904706412e-06</v>
+        <v>3.3874334153264149e-06</v>
       </c>
       <c r="H3">
-        <v>-6.2523532159829248e-06</v>
+        <v>-6.25223592107784e-06</v>
       </c>
       <c r="I3">
-        <v>4.2543252737847173e-06</v>
+        <v>4.2537987613986187e-06</v>
       </c>
       <c r="J3">
-        <v>-6.9328261188962532e-06</v>
+        <v>-6.9309431216146215e-06</v>
       </c>
       <c r="K3">
-        <v>2.6321121076365047e-05</v>
+        <v>2.6319770202980336e-05</v>
       </c>
       <c r="L3">
-        <v>2.8637152737352788e-06</v>
+        <v>2.8641344872958962e-06</v>
       </c>
       <c r="M3">
-        <v>5.755988843460683e-05</v>
+        <v>5.7557596450142848e-05</v>
       </c>
       <c r="N3">
-        <v>1.2001458455157771e-05</v>
+        <v>1.1994460097592127e-05</v>
       </c>
       <c r="O3">
-        <v>1.849540546058624e-05</v>
+        <v>1.8493161870515433e-05</v>
       </c>
       <c r="P3">
-        <v>3.2424186703479025e-06</v>
+        <v>3.243644708268023e-06</v>
       </c>
       <c r="Q3">
-        <v>-3.2440327681688612e-06</v>
+        <v>-3.2481501141426011e-06</v>
       </c>
       <c r="R3">
-        <v>2.0386837988315136e-05</v>
+        <v>2.03879574622578e-05</v>
       </c>
       <c r="S3">
-        <v>-3.6214124445822153e-07</v>
+        <v>-3.6424690642633323e-07</v>
       </c>
       <c r="T3">
-        <v>2.9838937459911776e-06</v>
+        <v>2.9768829863696834e-06</v>
       </c>
       <c r="U3">
-        <v>1.0296429700273896e-05</v>
+        <v>1.0292432767799328e-05</v>
       </c>
       <c r="V3">
-        <v>5.4938493318870571e-06</v>
+        <v>5.478910716750254e-06</v>
       </c>
       <c r="W3">
-        <v>3.6309692420625767e-06</v>
+        <v>3.6238612205948006e-06</v>
       </c>
       <c r="X3">
-        <v>7.3174811776762199e-06</v>
+        <v>7.3128771778003263e-06</v>
       </c>
       <c r="Y3">
-        <v>-6.0449240535131489e-06</v>
+        <v>-6.051814695894758e-06</v>
       </c>
       <c r="Z3">
-        <v>-1.0064813404940604e-06</v>
+        <v>-1.005130469697827e-06</v>
       </c>
       <c r="AA3">
-        <v>-2.125484830955518e-06</v>
+        <v>-2.1263051652331842e-06</v>
       </c>
       <c r="AB3">
-        <v>-4.9015448977291778e-06</v>
+        <v>-4.9021878271057989e-06</v>
       </c>
       <c r="AC3">
-        <v>-1.940549386887625e-07</v>
+        <v>-1.9514781448637993e-07</v>
       </c>
       <c r="AD3">
-        <v>6.2856319531107434e-07</v>
+        <v>6.1513538738070233e-07</v>
       </c>
       <c r="AE3">
-        <v>-1.4176370058927804e-06</v>
+        <v>-1.4172083583867813e-06</v>
       </c>
       <c r="AF3">
-        <v>-5.3264824558947837e-07</v>
+        <v>-5.3222697295533773e-07</v>
       </c>
       <c r="AG3">
-        <v>-3.0057981496875799e-06</v>
+        <v>-3.0054686833840975e-06</v>
       </c>
       <c r="AH3">
-        <v>-6.7295998727717456e-07</v>
+        <v>-6.7275357072985575e-07</v>
       </c>
       <c r="AI3">
-        <v>-5.6677662949906763e-06</v>
+        <v>-5.6633420541665563e-06</v>
       </c>
       <c r="AJ3">
-        <v>-1.0040630381399728e-05</v>
+        <v>-1.003814833831166e-05</v>
       </c>
       <c r="AK3">
-        <v>-0.00030419755771113051</v>
+        <v>-0.00030416812978090462</v>
       </c>
     </row>
     <row r="4">
@@ -740,112 +740,112 @@
         <v>28</v>
       </c>
       <c r="B4">
-        <v>6.5238955972800284e-05</v>
+        <v>6.5199379026281929e-05</v>
       </c>
       <c r="C4">
-        <v>-7.4736878992871302e-09</v>
+        <v>-7.4480976254347049e-09</v>
       </c>
       <c r="D4">
-        <v>-1.1047932550441516e-07</v>
+        <v>-1.1047162587412689e-07</v>
       </c>
       <c r="E4">
-        <v>1.0573396940360165e-09</v>
+        <v>1.0572636626675565e-09</v>
       </c>
       <c r="F4">
-        <v>-2.3548679739243457e-07</v>
+        <v>-2.354277399472372e-07</v>
       </c>
       <c r="G4">
-        <v>-7.1895800622494002e-08</v>
+        <v>-7.1884982986310097e-08</v>
       </c>
       <c r="H4">
-        <v>6.6528812303699037e-08</v>
+        <v>6.6527950715626985e-08</v>
       </c>
       <c r="I4">
-        <v>-2.3298145549925339e-08</v>
+        <v>-2.3294099055857732e-08</v>
       </c>
       <c r="J4">
-        <v>7.9841145316131466e-08</v>
+        <v>7.9823238894101803e-08</v>
       </c>
       <c r="K4">
-        <v>-2.1280722072831973e-07</v>
+        <v>-2.1279393631650998e-07</v>
       </c>
       <c r="L4">
-        <v>6.0010689024517214e-08</v>
+        <v>6.0006056155785776e-08</v>
       </c>
       <c r="M4">
-        <v>-5.1690039741706562e-07</v>
+        <v>-5.1687671150398904e-07</v>
       </c>
       <c r="N4">
-        <v>-2.2827853745737478e-07</v>
+        <v>-2.282167931725598e-07</v>
       </c>
       <c r="O4">
-        <v>-1.7802073679945095e-07</v>
+        <v>-1.7800012130098569e-07</v>
       </c>
       <c r="P4">
-        <v>-4.1789753539437336e-08</v>
+        <v>-4.180119020685555e-08</v>
       </c>
       <c r="Q4">
-        <v>-1.8293831883355746e-08</v>
+        <v>-1.8257074853130559e-08</v>
       </c>
       <c r="R4">
-        <v>-2.3307329415924923e-07</v>
+        <v>-2.3308044762955454e-07</v>
       </c>
       <c r="S4">
-        <v>-1.7935383711011097e-08</v>
+        <v>-1.7919896359651921e-08</v>
       </c>
       <c r="T4">
-        <v>-7.7066021856421626e-09</v>
+        <v>-7.6404521593637758e-09</v>
       </c>
       <c r="U4">
-        <v>-6.537596477961261e-08</v>
+        <v>-6.533851256180072e-08</v>
       </c>
       <c r="V4">
-        <v>-5.1451220615427808e-08</v>
+        <v>-5.131731462441057e-08</v>
       </c>
       <c r="W4">
-        <v>-8.4585824596336219e-08</v>
+        <v>-8.4522838499709036e-08</v>
       </c>
       <c r="X4">
-        <v>-1.1268753893109769e-07</v>
+        <v>-1.126472656274382e-07</v>
       </c>
       <c r="Y4">
-        <v>-1.6968589260686767e-08</v>
+        <v>-1.690835330445087e-08</v>
       </c>
       <c r="Z4">
-        <v>6.8879643726840316e-09</v>
+        <v>6.8760027504605691e-09</v>
       </c>
       <c r="AA4">
-        <v>6.4156154457390736e-09</v>
+        <v>6.422796339319445e-09</v>
       </c>
       <c r="AB4">
-        <v>4.9284408428887805e-08</v>
+        <v>4.9290414321812228e-08</v>
       </c>
       <c r="AC4">
-        <v>7.231931649447275e-09</v>
+        <v>7.2420227277417834e-09</v>
       </c>
       <c r="AD4">
-        <v>-2.8375157172594823e-09</v>
+        <v>-2.7174720676790462e-09</v>
       </c>
       <c r="AE4">
-        <v>2.3278842565938673e-08</v>
+        <v>2.3275186937323524e-08</v>
       </c>
       <c r="AF4">
-        <v>4.8747638591450779e-09</v>
+        <v>4.869925171155404e-09</v>
       </c>
       <c r="AG4">
-        <v>4.6015714018561087e-08</v>
+        <v>4.6013643849496761e-08</v>
       </c>
       <c r="AH4">
-        <v>4.5848603360447901e-09</v>
+        <v>4.5830711267215435e-09</v>
       </c>
       <c r="AI4">
-        <v>6.6903421873668923e-08</v>
+        <v>6.6863409455461351e-08</v>
       </c>
       <c r="AJ4">
-        <v>8.9063978609485001e-08</v>
+        <v>8.9041164065659396e-08</v>
       </c>
       <c r="AK4">
-        <v>2.731377679922013e-06</v>
+        <v>2.7310916419036542e-06</v>
       </c>
     </row>
     <row r="5">
@@ -853,112 +853,112 @@
         <v>29</v>
       </c>
       <c r="B5">
-        <v>0.20597350606953221</v>
+        <v>0.20597873718441592</v>
       </c>
       <c r="C5">
-        <v>6.729506504589151e-05</v>
+        <v>6.7268826536586617e-05</v>
       </c>
       <c r="D5">
-        <v>2.6677204931288101e-05</v>
+        <v>2.6670843332077363e-05</v>
       </c>
       <c r="E5">
-        <v>-2.3548679739243457e-07</v>
+        <v>-2.354277399472372e-07</v>
       </c>
       <c r="F5">
-        <v>0.13553151444033346</v>
+        <v>0.13553132341881574</v>
       </c>
       <c r="G5">
-        <v>0.0020379441910741863</v>
+        <v>0.0020380260055970602</v>
       </c>
       <c r="H5">
-        <v>0.0016734538064952431</v>
+        <v>0.001673492339514706</v>
       </c>
       <c r="I5">
-        <v>0.0023906059299763035</v>
+        <v>0.0023906395269241093</v>
       </c>
       <c r="J5">
-        <v>0.0020654118059609677</v>
+        <v>0.0020654718840749796</v>
       </c>
       <c r="K5">
-        <v>0.0020026753603981967</v>
+        <v>0.0020026998232934986</v>
       </c>
       <c r="L5">
-        <v>0.0020711991975545228</v>
+        <v>0.0020712387838376337</v>
       </c>
       <c r="M5">
-        <v>0.00017108290561129291</v>
+        <v>0.00017105498378687696</v>
       </c>
       <c r="N5">
-        <v>0.00024595180386376993</v>
+        <v>0.00024591485347891197</v>
       </c>
       <c r="O5">
-        <v>0.00029836823804563575</v>
+        <v>0.00029837182396270402</v>
       </c>
       <c r="P5">
-        <v>3.827277481463807e-05</v>
+        <v>3.8287409453310363e-05</v>
       </c>
       <c r="Q5">
-        <v>0.0001619552673622247</v>
+        <v>0.00016194203110046258</v>
       </c>
       <c r="R5">
-        <v>0.00022837758340651807</v>
+        <v>0.00022838431649253518</v>
       </c>
       <c r="S5">
-        <v>0.00020243608162499871</v>
+        <v>0.00020243144669056809</v>
       </c>
       <c r="T5">
-        <v>0.0001496439366933754</v>
+        <v>0.00014961023123421049</v>
       </c>
       <c r="U5">
-        <v>0.00038256576570248749</v>
+        <v>0.00038255499253252179</v>
       </c>
       <c r="V5">
-        <v>4.2466494095345865e-05</v>
+        <v>4.2393983027296228e-05</v>
       </c>
       <c r="W5">
-        <v>6.7039399235246065e-05</v>
+        <v>6.7013509459798448e-05</v>
       </c>
       <c r="X5">
-        <v>0.00041791432293122833</v>
+        <v>0.00041790608657136272</v>
       </c>
       <c r="Y5">
-        <v>0.00082094867511977622</v>
+        <v>0.00082093055223320935</v>
       </c>
       <c r="Z5">
-        <v>-2.9385190883117859e-05</v>
+        <v>-2.9380921477202878e-05</v>
       </c>
       <c r="AA5">
-        <v>0.00035993203788987124</v>
+        <v>0.00035992754909626565</v>
       </c>
       <c r="AB5">
-        <v>0.00017088454794393572</v>
+        <v>0.00017089336480977861</v>
       </c>
       <c r="AC5">
-        <v>0.0010396525872968484</v>
+        <v>0.0010396622006849535</v>
       </c>
       <c r="AD5">
-        <v>0.0007230071151432039</v>
+        <v>0.00072293055582634642</v>
       </c>
       <c r="AE5">
-        <v>0.00014512202767931839</v>
+        <v>0.00014512559808635612</v>
       </c>
       <c r="AF5">
-        <v>0.0001400488397701584</v>
+        <v>0.00014004760693710243</v>
       </c>
       <c r="AG5">
-        <v>2.1573923662473755e-05</v>
+        <v>2.1591697983216096e-05</v>
       </c>
       <c r="AH5">
-        <v>-1.0577415409203473e-05</v>
+        <v>-1.0575696445527265e-05</v>
       </c>
       <c r="AI5">
-        <v>-1.0605757314727758e-05</v>
+        <v>-1.0610707155621259e-05</v>
       </c>
       <c r="AJ5">
-        <v>0.0013384228419809558</v>
+        <v>0.0013384388536105847</v>
       </c>
       <c r="AK5">
-        <v>-0.0036322712391759562</v>
+        <v>-0.0036321204845852118</v>
       </c>
     </row>
     <row r="6">
@@ -966,112 +966,112 @@
         <v>30</v>
       </c>
       <c r="B6">
-        <v>-0.0065339102496650052</v>
+        <v>-0.0065648356212262733</v>
       </c>
       <c r="C6">
-        <v>-7.7622022958695488e-05</v>
+        <v>-7.76349176659076e-05</v>
       </c>
       <c r="D6">
-        <v>3.3881584904706412e-06</v>
+        <v>3.3874334153264149e-06</v>
       </c>
       <c r="E6">
-        <v>-7.1895800622494002e-08</v>
+        <v>-7.1884982986310097e-08</v>
       </c>
       <c r="F6">
-        <v>0.0020379441910741863</v>
+        <v>0.0020380260055970602</v>
       </c>
       <c r="G6">
-        <v>0.0026285987112459265</v>
+        <v>0.0026286647044102243</v>
       </c>
       <c r="H6">
-        <v>0.0017707386413929474</v>
+        <v>0.00177079404857823</v>
       </c>
       <c r="I6">
-        <v>0.0019980356952356286</v>
+        <v>0.001998110088060025</v>
       </c>
       <c r="J6">
-        <v>0.0020434133816835537</v>
+        <v>0.0020434787245531788</v>
       </c>
       <c r="K6">
-        <v>0.0020473334591842112</v>
+        <v>0.0020473901228867473</v>
       </c>
       <c r="L6">
-        <v>0.0019960537777912969</v>
+        <v>0.0019961017245598818</v>
       </c>
       <c r="M6">
-        <v>2.8213742492335867e-05</v>
+        <v>2.8223029018945413e-05</v>
       </c>
       <c r="N6">
-        <v>1.6465966131722271e-05</v>
+        <v>1.6490432075175307e-05</v>
       </c>
       <c r="O6">
-        <v>0.00012622871584825821</v>
+        <v>0.00012623894597151562</v>
       </c>
       <c r="P6">
-        <v>0.00014563558546464451</v>
+        <v>0.00014563989567054775</v>
       </c>
       <c r="Q6">
-        <v>0.00013240951091894772</v>
+        <v>0.00013243328503286059</v>
       </c>
       <c r="R6">
-        <v>0.00028019533833558742</v>
+        <v>0.00028018013986952893</v>
       </c>
       <c r="S6">
-        <v>9.1795808582042452e-05</v>
+        <v>9.1832062200270675e-05</v>
       </c>
       <c r="T6">
-        <v>5.7532952177817066e-05</v>
+        <v>5.7560987659392487e-05</v>
       </c>
       <c r="U6">
-        <v>0.00010405091912444849</v>
+        <v>0.00010408204210283025</v>
       </c>
       <c r="V6">
-        <v>7.6858848076335383e-05</v>
+        <v>7.6936626433448784e-05</v>
       </c>
       <c r="W6">
-        <v>0.00013047642463277222</v>
+        <v>0.000130512544865558</v>
       </c>
       <c r="X6">
-        <v>0.00027331608494886458</v>
+        <v>0.00027336396351494187</v>
       </c>
       <c r="Y6">
-        <v>0.00076472299585248057</v>
+        <v>0.0007647872838871736</v>
       </c>
       <c r="Z6">
-        <v>-2.9287183641041694e-05</v>
+        <v>-2.9295868871452031e-05</v>
       </c>
       <c r="AA6">
-        <v>-5.4327580794293583e-05</v>
+        <v>-5.4323734239563628e-05</v>
       </c>
       <c r="AB6">
-        <v>0.00010551725724153695</v>
+        <v>0.00010552169516705925</v>
       </c>
       <c r="AC6">
-        <v>8.4362077400489816e-05</v>
+        <v>8.4368794715609105e-05</v>
       </c>
       <c r="AD6">
-        <v>0.00010126219746218242</v>
+        <v>0.00010134094841438446</v>
       </c>
       <c r="AE6">
-        <v>3.1849970326139994e-05</v>
+        <v>3.1844229894414759e-05</v>
       </c>
       <c r="AF6">
-        <v>6.3114505588942043e-05</v>
+        <v>6.3109637921800286e-05</v>
       </c>
       <c r="AG6">
-        <v>-1.6873910236692917e-05</v>
+        <v>-1.6876315326658318e-05</v>
       </c>
       <c r="AH6">
-        <v>6.8038155865142409e-06</v>
+        <v>6.8023772104693964e-06</v>
       </c>
       <c r="AI6">
-        <v>-4.2446913073927901e-05</v>
+        <v>-4.2492166427976746e-05</v>
       </c>
       <c r="AJ6">
-        <v>4.1344977390652912e-05</v>
+        <v>4.1329387394248513e-05</v>
       </c>
       <c r="AK6">
-        <v>-0.0024304373710473618</v>
+        <v>-0.0024305356388305312</v>
       </c>
     </row>
     <row r="7">
@@ -1079,112 +1079,112 @@
         <v>31</v>
       </c>
       <c r="B7">
-        <v>-0.039677728320830066</v>
+        <v>-0.03967914324928206</v>
       </c>
       <c r="C7">
-        <v>3.3335838907160016e-06</v>
+        <v>3.3341554446164095e-06</v>
       </c>
       <c r="D7">
-        <v>-6.2523532159829248e-06</v>
+        <v>-6.25223592107784e-06</v>
       </c>
       <c r="E7">
-        <v>6.6528812303699037e-08</v>
+        <v>6.6527950715626985e-08</v>
       </c>
       <c r="F7">
-        <v>0.0016734538064952431</v>
+        <v>0.001673492339514706</v>
       </c>
       <c r="G7">
-        <v>0.0017707386413929474</v>
+        <v>0.00177079404857823</v>
       </c>
       <c r="H7">
-        <v>0.0028768274117340377</v>
+        <v>0.0028769200432114737</v>
       </c>
       <c r="I7">
-        <v>0.0018570161660647014</v>
+        <v>0.0018570623259393472</v>
       </c>
       <c r="J7">
-        <v>0.0018212189645804714</v>
+        <v>0.001821266881503312</v>
       </c>
       <c r="K7">
-        <v>0.0017680039034498037</v>
+        <v>0.0017680507784060937</v>
       </c>
       <c r="L7">
-        <v>0.0017493087233110809</v>
+        <v>0.0017493554418150405</v>
       </c>
       <c r="M7">
-        <v>6.6519254582384814e-05</v>
+        <v>6.6514188150040626e-05</v>
       </c>
       <c r="N7">
-        <v>6.1715989478061553e-05</v>
+        <v>6.170849700752178e-05</v>
       </c>
       <c r="O7">
-        <v>7.7048327174811032e-05</v>
+        <v>7.7049602391855406e-05</v>
       </c>
       <c r="P7">
-        <v>0.0001305610373722979</v>
+        <v>0.00013056106850083636</v>
       </c>
       <c r="Q7">
-        <v>0.00010424295910005168</v>
+        <v>0.00010424122871433243</v>
       </c>
       <c r="R7">
-        <v>1.1697323578276661e-05</v>
+        <v>1.1699965530151488e-05</v>
       </c>
       <c r="S7">
-        <v>2.6618447836996391e-05</v>
+        <v>2.661754862446318e-05</v>
       </c>
       <c r="T7">
-        <v>2.518802711129356e-06</v>
+        <v>2.5215092514105841e-06</v>
       </c>
       <c r="U7">
-        <v>8.7756474835707027e-06</v>
+        <v>8.7750778236801545e-06</v>
       </c>
       <c r="V7">
-        <v>2.5076923450845958e-05</v>
+        <v>2.5072607670293513e-05</v>
       </c>
       <c r="W7">
-        <v>2.793574316478024e-05</v>
+        <v>2.7925235297103024e-05</v>
       </c>
       <c r="X7">
-        <v>4.9530687024611567e-05</v>
+        <v>4.9524922024530302e-05</v>
       </c>
       <c r="Y7">
-        <v>0.00031936743496319554</v>
+        <v>0.00031935560965139686</v>
       </c>
       <c r="Z7">
-        <v>-8.9263416154587796e-06</v>
+        <v>-8.9246904624852345e-06</v>
       </c>
       <c r="AA7">
-        <v>-4.9650473414267302e-05</v>
+        <v>-4.9655501839485723e-05</v>
       </c>
       <c r="AB7">
-        <v>0.00010618075421804023</v>
+        <v>0.00010618260158602776</v>
       </c>
       <c r="AC7">
-        <v>-2.5267151641799202e-06</v>
+        <v>-2.5287817091834003e-06</v>
       </c>
       <c r="AD7">
-        <v>3.619505802813605e-05</v>
+        <v>3.6201780308259225e-05</v>
       </c>
       <c r="AE7">
-        <v>-3.4556101347137319e-05</v>
+        <v>-3.4557675597660662e-05</v>
       </c>
       <c r="AF7">
-        <v>-2.8031077380931662e-05</v>
+        <v>-2.8034532334489664e-05</v>
       </c>
       <c r="AG7">
-        <v>-6.9766609789192037e-05</v>
+        <v>-6.975746189792013e-05</v>
       </c>
       <c r="AH7">
-        <v>2.6253152083416357e-06</v>
+        <v>2.6249090092077162e-06</v>
       </c>
       <c r="AI7">
-        <v>0.00012237466566103689</v>
+        <v>0.00012237409901647987</v>
       </c>
       <c r="AJ7">
-        <v>8.4057494262503117e-05</v>
+        <v>8.4058184719090962e-05</v>
       </c>
       <c r="AK7">
-        <v>-0.0018467793899298772</v>
+        <v>-0.001846817251595371</v>
       </c>
     </row>
     <row r="8">
@@ -1192,112 +1192,112 @@
         <v>32</v>
       </c>
       <c r="B8">
-        <v>0.032125195484017599</v>
+        <v>0.032127306932461242</v>
       </c>
       <c r="C8">
-        <v>-9.6576786167536471e-05</v>
+        <v>-9.6585898395810108e-05</v>
       </c>
       <c r="D8">
-        <v>4.2543252737847173e-06</v>
+        <v>4.2537987613986187e-06</v>
       </c>
       <c r="E8">
-        <v>-2.3298145549925339e-08</v>
+        <v>-2.3294099055857732e-08</v>
       </c>
       <c r="F8">
-        <v>0.0023906059299763035</v>
+        <v>0.0023906395269241093</v>
       </c>
       <c r="G8">
-        <v>0.0019980356952356286</v>
+        <v>0.001998110088060025</v>
       </c>
       <c r="H8">
-        <v>0.0018570161660647014</v>
+        <v>0.0018570623259393472</v>
       </c>
       <c r="I8">
-        <v>0.043333343956813035</v>
+        <v>0.043335027730543881</v>
       </c>
       <c r="J8">
-        <v>0.0022296604721420742</v>
+        <v>0.0022297171573666089</v>
       </c>
       <c r="K8">
-        <v>0.001964729675575966</v>
+        <v>0.0019647733387385511</v>
       </c>
       <c r="L8">
-        <v>0.0020922679338160749</v>
+        <v>0.0020923181677727732</v>
       </c>
       <c r="M8">
-        <v>0.00049574936951798064</v>
+        <v>0.0004957537782104113</v>
       </c>
       <c r="N8">
-        <v>0.00038151436665666229</v>
+        <v>0.00038151294888219008</v>
       </c>
       <c r="O8">
-        <v>0.00016345047982942737</v>
+        <v>0.0001634579299751185</v>
       </c>
       <c r="P8">
-        <v>0.0002199443317413354</v>
+        <v>0.00021995600760838719</v>
       </c>
       <c r="Q8">
-        <v>0.00021976745877755203</v>
+        <v>0.00021977304420419899</v>
       </c>
       <c r="R8">
-        <v>-4.2164400749345084e-05</v>
+        <v>-4.2162219541459116e-05</v>
       </c>
       <c r="S8">
-        <v>6.0484176166268611e-05</v>
+        <v>6.0483320952118896e-05</v>
       </c>
       <c r="T8">
-        <v>-4.3114087389519687e-05</v>
+        <v>-4.3118920600893561e-05</v>
       </c>
       <c r="U8">
-        <v>5.4132469581722386e-05</v>
+        <v>5.4137266248193631e-05</v>
       </c>
       <c r="V8">
-        <v>0.00011978362656084126</v>
+        <v>0.00011977695022078335</v>
       </c>
       <c r="W8">
-        <v>0.00018705615237387145</v>
+        <v>0.00018705243795518194</v>
       </c>
       <c r="X8">
-        <v>0.00049134187229104144</v>
+        <v>0.0004913479309294731</v>
       </c>
       <c r="Y8">
-        <v>0.0010978307885125265</v>
+        <v>0.0010978483904407641</v>
       </c>
       <c r="Z8">
-        <v>-4.5222535412690761e-05</v>
+        <v>-4.522272122790604e-05</v>
       </c>
       <c r="AA8">
-        <v>8.033842417980012e-05</v>
+        <v>8.0340995526613057e-05</v>
       </c>
       <c r="AB8">
-        <v>0.00019838439079984259</v>
+        <v>0.00019839081252925948</v>
       </c>
       <c r="AC8">
-        <v>0.00011279309646676267</v>
+        <v>0.00011279705654526346</v>
       </c>
       <c r="AD8">
-        <v>0.00012740170804045165</v>
+        <v>0.00012739588607572666</v>
       </c>
       <c r="AE8">
-        <v>6.2410531796767152e-05</v>
+        <v>6.2411795254526141e-05</v>
       </c>
       <c r="AF8">
-        <v>3.0201280062958167e-05</v>
+        <v>3.0199903768108759e-05</v>
       </c>
       <c r="AG8">
-        <v>-4.7528422924719764e-05</v>
+        <v>-4.7522259414865033e-05</v>
       </c>
       <c r="AH8">
-        <v>7.3387070253574463e-06</v>
+        <v>7.3389126967648348e-06</v>
       </c>
       <c r="AI8">
-        <v>-2.5262519972187123e-05</v>
+        <v>-2.5280771717804598e-05</v>
       </c>
       <c r="AJ8">
-        <v>0.00012366908819771007</v>
+        <v>0.00012367372499727611</v>
       </c>
       <c r="AK8">
-        <v>-0.0029055770861499907</v>
+        <v>-0.0029056184140483078</v>
       </c>
     </row>
     <row r="9">
@@ -1305,112 +1305,112 @@
         <v>33</v>
       </c>
       <c r="B9">
-        <v>-0.19047343844762652</v>
+        <v>-0.19048767406637981</v>
       </c>
       <c r="C9">
-        <v>-9.6713508606986016e-05</v>
+        <v>-9.6715316770636358e-05</v>
       </c>
       <c r="D9">
-        <v>-6.9328261188962532e-06</v>
+        <v>-6.9309431216146215e-06</v>
       </c>
       <c r="E9">
-        <v>7.9841145316131466e-08</v>
+        <v>7.9823238894101803e-08</v>
       </c>
       <c r="F9">
-        <v>0.0020654118059609677</v>
+        <v>0.0020654718840749796</v>
       </c>
       <c r="G9">
-        <v>0.0020434133816835537</v>
+        <v>0.0020434787245531788</v>
       </c>
       <c r="H9">
-        <v>0.0018212189645804714</v>
+        <v>0.001821266881503312</v>
       </c>
       <c r="I9">
-        <v>0.0022296604721420742</v>
+        <v>0.0022297171573666089</v>
       </c>
       <c r="J9">
-        <v>0.0031092586691221624</v>
+        <v>0.0031093298681548667</v>
       </c>
       <c r="K9">
-        <v>0.0019790192490285468</v>
+        <v>0.001979074737966699</v>
       </c>
       <c r="L9">
-        <v>0.0020944977876566355</v>
+        <v>0.0020945452316248319</v>
       </c>
       <c r="M9">
-        <v>0.00035539938667742701</v>
+        <v>0.00035541435441676468</v>
       </c>
       <c r="N9">
-        <v>0.00032578343631377478</v>
+        <v>0.00032580038708374928</v>
       </c>
       <c r="O9">
-        <v>0.0001019365135082567</v>
+        <v>0.00010194590320954794</v>
       </c>
       <c r="P9">
-        <v>0.00016665242253161662</v>
+        <v>0.00016665881505841174</v>
       </c>
       <c r="Q9">
-        <v>9.2304215324873481e-05</v>
+        <v>9.2319156419083586e-05</v>
       </c>
       <c r="R9">
-        <v>-6.7695892935032117e-06</v>
+        <v>-6.7707757489979346e-06</v>
       </c>
       <c r="S9">
-        <v>-8.1225892030046924e-06</v>
+        <v>-8.1208873535783353e-06</v>
       </c>
       <c r="T9">
-        <v>-3.0729418641468995e-05</v>
+        <v>-3.0715747977917837e-05</v>
       </c>
       <c r="U9">
-        <v>3.2129803071658208e-05</v>
+        <v>3.2143550216585069e-05</v>
       </c>
       <c r="V9">
-        <v>0.00011957118330981418</v>
+        <v>0.00011960556855189529</v>
       </c>
       <c r="W9">
-        <v>0.00011894559471515664</v>
+        <v>0.00011896340925752569</v>
       </c>
       <c r="X9">
-        <v>0.00048693274213967722</v>
+        <v>0.00048695453163207381</v>
       </c>
       <c r="Y9">
-        <v>0.001017453600681351</v>
+        <v>0.0010174882548330177</v>
       </c>
       <c r="Z9">
-        <v>-2.401288961297145e-05</v>
+        <v>-2.4016397220903199e-05</v>
       </c>
       <c r="AA9">
-        <v>-1.9660996630426148e-05</v>
+        <v>-1.9662175965197534e-05</v>
       </c>
       <c r="AB9">
-        <v>0.00023229232820717871</v>
+        <v>0.00023229934460498262</v>
       </c>
       <c r="AC9">
-        <v>0.00015046153509580421</v>
+        <v>0.00015046715161416485</v>
       </c>
       <c r="AD9">
-        <v>0.00017379390005154284</v>
+        <v>0.00017382373752403732</v>
       </c>
       <c r="AE9">
-        <v>9.8721498721418078e-05</v>
+        <v>9.8726304086698682e-05</v>
       </c>
       <c r="AF9">
-        <v>0.00010977055225061365</v>
+        <v>0.00010976484539881637</v>
       </c>
       <c r="AG9">
-        <v>1.6268992807537842e-05</v>
+        <v>1.6276962793432672e-05</v>
       </c>
       <c r="AH9">
-        <v>1.392162477322366e-05</v>
+        <v>1.3921870275758492e-05</v>
       </c>
       <c r="AI9">
-        <v>-6.9376751859976087e-05</v>
+        <v>-6.9409204249576764e-05</v>
       </c>
       <c r="AJ9">
-        <v>7.879179419844869e-05</v>
+        <v>7.8782802852043641e-05</v>
       </c>
       <c r="AK9">
-        <v>-0.002656321101019021</v>
+        <v>-0.0026564637035712568</v>
       </c>
     </row>
     <row r="10">
@@ -1418,112 +1418,112 @@
         <v>34</v>
       </c>
       <c r="B10">
-        <v>-0.11959219826474067</v>
+        <v>-0.11958090783573948</v>
       </c>
       <c r="C10">
-        <v>0.00013304687546415061</v>
+        <v>0.00013304390576172323</v>
       </c>
       <c r="D10">
-        <v>2.6321121076365047e-05</v>
+        <v>2.6319770202980336e-05</v>
       </c>
       <c r="E10">
-        <v>-2.1280722072831973e-07</v>
+        <v>-2.1279393631650998e-07</v>
       </c>
       <c r="F10">
-        <v>0.0020026753603981967</v>
+        <v>0.0020026998232934986</v>
       </c>
       <c r="G10">
-        <v>0.0020473334591842112</v>
+        <v>0.0020473901228867473</v>
       </c>
       <c r="H10">
-        <v>0.0017680039034498037</v>
+        <v>0.0017680507784060937</v>
       </c>
       <c r="I10">
-        <v>0.001964729675575966</v>
+        <v>0.0019647733387385511</v>
       </c>
       <c r="J10">
-        <v>0.0019790192490285468</v>
+        <v>0.001979074737966699</v>
       </c>
       <c r="K10">
-        <v>0.002385317777460707</v>
+        <v>0.0023853786545902757</v>
       </c>
       <c r="L10">
-        <v>0.0021633061731016431</v>
+        <v>0.0021633622334578245</v>
       </c>
       <c r="M10">
-        <v>5.1507694799198759e-05</v>
+        <v>5.1497033762574725e-05</v>
       </c>
       <c r="N10">
-        <v>-9.0833229448591328e-05</v>
+        <v>-9.0866635729285018e-05</v>
       </c>
       <c r="O10">
-        <v>0.00012338849215694421</v>
+        <v>0.00012338939884368378</v>
       </c>
       <c r="P10">
-        <v>0.00012829048939733118</v>
+        <v>0.00012830323147817313</v>
       </c>
       <c r="Q10">
-        <v>0.00010544591470862338</v>
+        <v>0.00010543891706890313</v>
       </c>
       <c r="R10">
-        <v>0.00012678847762746619</v>
+        <v>0.00012679830056682806</v>
       </c>
       <c r="S10">
-        <v>-1.185739986945167e-05</v>
+        <v>-1.1876330806251606e-05</v>
       </c>
       <c r="T10">
-        <v>3.9611480137141577e-06</v>
+        <v>3.9338056891625398e-06</v>
       </c>
       <c r="U10">
-        <v>5.6135453318191053e-06</v>
+        <v>5.6008102751753256e-06</v>
       </c>
       <c r="V10">
-        <v>9.8062603679315545e-05</v>
+        <v>9.7996192177115843e-05</v>
       </c>
       <c r="W10">
-        <v>0.00021084417722837972</v>
+        <v>0.00021082050307295311</v>
       </c>
       <c r="X10">
-        <v>0.00034670368532950069</v>
+        <v>0.00034669342221652424</v>
       </c>
       <c r="Y10">
-        <v>0.00071296069461482909</v>
+        <v>0.00071294432274992669</v>
       </c>
       <c r="Z10">
-        <v>-3.8096571245856515e-05</v>
+        <v>-3.8092029488725583e-05</v>
       </c>
       <c r="AA10">
-        <v>-9.5343896151411445e-05</v>
+        <v>-9.5348212475492803e-05</v>
       </c>
       <c r="AB10">
-        <v>4.9043072589556461e-05</v>
+        <v>4.9044470238045592e-05</v>
       </c>
       <c r="AC10">
-        <v>3.0489284273914168e-05</v>
+        <v>3.0487672599616676e-05</v>
       </c>
       <c r="AD10">
-        <v>5.0030039650950011e-05</v>
+        <v>4.9970620505085557e-05</v>
       </c>
       <c r="AE10">
-        <v>-1.991636919297787e-05</v>
+        <v>-1.9916388888269491e-05</v>
       </c>
       <c r="AF10">
-        <v>2.3806793720527748e-05</v>
+        <v>2.3812120986320905e-05</v>
       </c>
       <c r="AG10">
-        <v>3.5788346830092292e-05</v>
+        <v>3.5794081858431996e-05</v>
       </c>
       <c r="AH10">
-        <v>9.1396972887454833e-07</v>
+        <v>9.1424478038541258e-07</v>
       </c>
       <c r="AI10">
-        <v>2.2824839855722576e-06</v>
+        <v>2.2814609825895851e-06</v>
       </c>
       <c r="AJ10">
-        <v>3.2261107812278644e-05</v>
+        <v>3.2271928767388684e-05</v>
       </c>
       <c r="AK10">
-        <v>-0.0030800343277878339</v>
+        <v>-0.0030800114156639652</v>
       </c>
     </row>
     <row r="11">
@@ -1531,112 +1531,112 @@
         <v>35</v>
       </c>
       <c r="B11">
-        <v>-0.2899752725463205</v>
+        <v>-0.28997947227204102</v>
       </c>
       <c r="C11">
-        <v>0.00022011010259935789</v>
+        <v>0.00022012041977361829</v>
       </c>
       <c r="D11">
-        <v>2.8637152737352788e-06</v>
+        <v>2.8641344872958962e-06</v>
       </c>
       <c r="E11">
-        <v>6.0010689024517214e-08</v>
+        <v>6.0006056155785776e-08</v>
       </c>
       <c r="F11">
-        <v>0.0020711991975545228</v>
+        <v>0.0020712387838376337</v>
       </c>
       <c r="G11">
-        <v>0.0019960537777912969</v>
+        <v>0.0019961017245598818</v>
       </c>
       <c r="H11">
-        <v>0.0017493087233110809</v>
+        <v>0.0017493554418150405</v>
       </c>
       <c r="I11">
-        <v>0.0020922679338160749</v>
+        <v>0.0020923181677727732</v>
       </c>
       <c r="J11">
-        <v>0.0020944977876566355</v>
+        <v>0.0020945452316248319</v>
       </c>
       <c r="K11">
-        <v>0.0021633061731016431</v>
+        <v>0.0021633622334578245</v>
       </c>
       <c r="L11">
-        <v>0.0043980781579875091</v>
+        <v>0.0043981795838537409</v>
       </c>
       <c r="M11">
-        <v>0.00021169178151447376</v>
+        <v>0.00021169738376874492</v>
       </c>
       <c r="N11">
-        <v>-0.00014891078970252064</v>
+        <v>-0.00014891080533422984</v>
       </c>
       <c r="O11">
-        <v>3.3290537761394932e-05</v>
+        <v>3.3295891704159973e-05</v>
       </c>
       <c r="P11">
-        <v>2.6359258611128656e-05</v>
+        <v>2.6368182619703785e-05</v>
       </c>
       <c r="Q11">
-        <v>-1.5497968678253107e-05</v>
+        <v>-1.5488279850675116e-05</v>
       </c>
       <c r="R11">
-        <v>0.00015180337019379006</v>
+        <v>0.00015181253655580996</v>
       </c>
       <c r="S11">
-        <v>6.2222772827284279e-05</v>
+        <v>6.2227471161098728e-05</v>
       </c>
       <c r="T11">
-        <v>6.9005235723320333e-05</v>
+        <v>6.9006974218798443e-05</v>
       </c>
       <c r="U11">
-        <v>4.5739347489597688e-05</v>
+        <v>4.574616360110851e-05</v>
       </c>
       <c r="V11">
-        <v>5.2692789592910359e-05</v>
+        <v>5.2687433501897525e-05</v>
       </c>
       <c r="W11">
-        <v>3.7361488613367293e-06</v>
+        <v>3.737803418578595e-06</v>
       </c>
       <c r="X11">
-        <v>0.00036018859480426205</v>
+        <v>0.00036019533200513454</v>
       </c>
       <c r="Y11">
-        <v>0.000633808018733031</v>
+        <v>0.00063382182572373994</v>
       </c>
       <c r="Z11">
-        <v>-3.9085044861963709e-05</v>
+        <v>-3.9087122093091754e-05</v>
       </c>
       <c r="AA11">
-        <v>-4.1283644658945127e-05</v>
+        <v>-4.1284254635589463e-05</v>
       </c>
       <c r="AB11">
-        <v>0.0001531971084146105</v>
+        <v>0.00015320647609406166</v>
       </c>
       <c r="AC11">
-        <v>0.0001270410718614127</v>
+        <v>0.00012705031902480557</v>
       </c>
       <c r="AD11">
-        <v>7.0728087837666547e-05</v>
+        <v>7.0737092000580518e-05</v>
       </c>
       <c r="AE11">
-        <v>7.9753303428038453e-05</v>
+        <v>7.975825688759635e-05</v>
       </c>
       <c r="AF11">
-        <v>0.00016116144006006049</v>
+        <v>0.00016117107222544724</v>
       </c>
       <c r="AG11">
-        <v>4.7928043876269757e-05</v>
+        <v>4.7937875782734567e-05</v>
       </c>
       <c r="AH11">
-        <v>-5.6363336602679515e-07</v>
+        <v>-5.6423937115830138e-07</v>
       </c>
       <c r="AI11">
-        <v>0.00018717311068847846</v>
+        <v>0.00018715727023934812</v>
       </c>
       <c r="AJ11">
-        <v>-2.0543834528382633e-05</v>
+        <v>-2.0544762476647953e-05</v>
       </c>
       <c r="AK11">
-        <v>-0.0027187827216915298</v>
+        <v>-0.0027188541205461492</v>
       </c>
     </row>
     <row r="12">
@@ -1644,112 +1644,112 @@
         <v>36</v>
       </c>
       <c r="B12">
-        <v>0.19244294246965798</v>
+        <v>0.19246220580884188</v>
       </c>
       <c r="C12">
-        <v>3.1021431459994536e-05</v>
+        <v>3.0999900657781177e-05</v>
       </c>
       <c r="D12">
-        <v>5.755988843460683e-05</v>
+        <v>5.7557596450142848e-05</v>
       </c>
       <c r="E12">
-        <v>-5.1690039741706562e-07</v>
+        <v>-5.1687671150398904e-07</v>
       </c>
       <c r="F12">
-        <v>0.00017108290561129291</v>
+        <v>0.00017105498378687696</v>
       </c>
       <c r="G12">
-        <v>2.8213742492335867e-05</v>
+        <v>2.8223029018945413e-05</v>
       </c>
       <c r="H12">
-        <v>6.6519254582384814e-05</v>
+        <v>6.6514188150040626e-05</v>
       </c>
       <c r="I12">
-        <v>0.00049574936951798064</v>
+        <v>0.0004957537782104113</v>
       </c>
       <c r="J12">
-        <v>0.00035539938667742701</v>
+        <v>0.00035541435441676468</v>
       </c>
       <c r="K12">
-        <v>5.1507694799198759e-05</v>
+        <v>5.1497033762574725e-05</v>
       </c>
       <c r="L12">
-        <v>0.00021169178151447376</v>
+        <v>0.00021169738376874492</v>
       </c>
       <c r="M12">
-        <v>0.0074923242899299792</v>
+        <v>0.0074923034310951453</v>
       </c>
       <c r="N12">
-        <v>0.0031866630863742656</v>
+        <v>0.0031866363209568289</v>
       </c>
       <c r="O12">
-        <v>-0.0039024839201533893</v>
+        <v>-0.0039024694826555063</v>
       </c>
       <c r="P12">
-        <v>9.2350131216029736e-05</v>
+        <v>9.2356351574602257e-05</v>
       </c>
       <c r="Q12">
-        <v>0.00013049601598286157</v>
+        <v>0.00013048030078558449</v>
       </c>
       <c r="R12">
-        <v>0.00040034826651316464</v>
+        <v>0.00040036659471146116</v>
       </c>
       <c r="S12">
-        <v>7.0188535707875737e-05</v>
+        <v>7.0190594616147259e-05</v>
       </c>
       <c r="T12">
-        <v>5.5146278714787418e-05</v>
+        <v>5.5124142924785216e-05</v>
       </c>
       <c r="U12">
-        <v>0.00019182793736752181</v>
+        <v>0.00019182119029518847</v>
       </c>
       <c r="V12">
-        <v>0.00065136072350025615</v>
+        <v>0.0006513196185803673</v>
       </c>
       <c r="W12">
-        <v>0.0031556215148482387</v>
+        <v>0.0031556052964034076</v>
       </c>
       <c r="X12">
-        <v>0.0036333808813741476</v>
+        <v>0.0036333819257838018</v>
       </c>
       <c r="Y12">
-        <v>0.0038086382056721608</v>
+        <v>0.0038086350141968688</v>
       </c>
       <c r="Z12">
-        <v>-0.00016793227152801755</v>
+        <v>-0.00016792801303399941</v>
       </c>
       <c r="AA12">
-        <v>2.3583005607361453e-05</v>
+        <v>2.3582936305882834e-05</v>
       </c>
       <c r="AB12">
-        <v>0.00017708004432941951</v>
+        <v>0.0001770860584250889</v>
       </c>
       <c r="AC12">
-        <v>0.00012066406113529641</v>
+        <v>0.00012066737429660291</v>
       </c>
       <c r="AD12">
-        <v>9.3980802410449302e-05</v>
+        <v>9.3938644631497929e-05</v>
       </c>
       <c r="AE12">
-        <v>0.00016404978519658688</v>
+        <v>0.00016406673375481216</v>
       </c>
       <c r="AF12">
-        <v>0.00035967662001975956</v>
+        <v>0.00035967883933484685</v>
       </c>
       <c r="AG12">
-        <v>0.00021697857664566172</v>
+        <v>0.00021698156621521262</v>
       </c>
       <c r="AH12">
-        <v>-3.6098291435469106e-06</v>
+        <v>-3.6083818067304883e-06</v>
       </c>
       <c r="AI12">
-        <v>0.00035750023934170636</v>
+        <v>0.00035750766520286238</v>
       </c>
       <c r="AJ12">
-        <v>-0.00014044840666929681</v>
+        <v>-0.00014043889582977332</v>
       </c>
       <c r="AK12">
-        <v>-0.0053790277856958606</v>
+        <v>-0.005378962444420857</v>
       </c>
     </row>
     <row r="13">
@@ -1757,112 +1757,112 @@
         <v>37</v>
       </c>
       <c r="B13">
-        <v>-0.016931840207822693</v>
+        <v>-0.016906123795864349</v>
       </c>
       <c r="C13">
-        <v>-0.00010284487799181759</v>
+        <v>-0.00010287980318271373</v>
       </c>
       <c r="D13">
-        <v>1.2001458455157771e-05</v>
+        <v>1.1994460097592127e-05</v>
       </c>
       <c r="E13">
-        <v>-2.2827853745737478e-07</v>
+        <v>-2.282167931725598e-07</v>
       </c>
       <c r="F13">
-        <v>0.00024595180386376993</v>
+        <v>0.00024591485347891197</v>
       </c>
       <c r="G13">
-        <v>1.6465966131722271e-05</v>
+        <v>1.6490432075175307e-05</v>
       </c>
       <c r="H13">
-        <v>6.1715989478061553e-05</v>
+        <v>6.170849700752178e-05</v>
       </c>
       <c r="I13">
-        <v>0.00038151436665666229</v>
+        <v>0.00038151294888219008</v>
       </c>
       <c r="J13">
-        <v>0.00032578343631377478</v>
+        <v>0.00032580038708374928</v>
       </c>
       <c r="K13">
-        <v>-9.0833229448591328e-05</v>
+        <v>-9.0866635729285018e-05</v>
       </c>
       <c r="L13">
-        <v>-0.00014891078970252064</v>
+        <v>-0.00014891080533422984</v>
       </c>
       <c r="M13">
-        <v>0.0031866630863742656</v>
+        <v>0.0031866363209568289</v>
       </c>
       <c r="N13">
-        <v>0.0033101646212255627</v>
+        <v>0.0033101474778905182</v>
       </c>
       <c r="O13">
-        <v>-0.00037534663656049044</v>
+        <v>-0.00037535719091312406</v>
       </c>
       <c r="P13">
-        <v>0.00018422635349997404</v>
+        <v>0.00018423641443473117</v>
       </c>
       <c r="Q13">
-        <v>0.00017832114300707114</v>
+        <v>0.00017829896758694483</v>
       </c>
       <c r="R13">
-        <v>0.00038060181975724185</v>
+        <v>0.00038062178990733468</v>
       </c>
       <c r="S13">
-        <v>0.00019662642067314246</v>
+        <v>0.00019663832564372776</v>
       </c>
       <c r="T13">
-        <v>0.00021037711093222628</v>
+        <v>0.00021035101059134161</v>
       </c>
       <c r="U13">
-        <v>0.0003725195176027484</v>
+        <v>0.00037251560686469925</v>
       </c>
       <c r="V13">
-        <v>0.00047858650291903468</v>
+        <v>0.00047851206798052014</v>
       </c>
       <c r="W13">
-        <v>0.0027092676205075685</v>
+        <v>0.0027092356933511616</v>
       </c>
       <c r="X13">
-        <v>0.0031294321984750985</v>
+        <v>0.0031294106327237835</v>
       </c>
       <c r="Y13">
-        <v>0.0034072188462806437</v>
+        <v>0.0034072040684542042</v>
       </c>
       <c r="Z13">
-        <v>-0.00014092467059130019</v>
+        <v>-0.00014091800407097161</v>
       </c>
       <c r="AA13">
-        <v>6.7131760883186919e-05</v>
+        <v>6.7132284963779482e-05</v>
       </c>
       <c r="AB13">
-        <v>5.0295069978107624e-05</v>
+        <v>5.0297396159034759e-05</v>
       </c>
       <c r="AC13">
-        <v>-3.4868050018369186e-05</v>
+        <v>-3.4870515197211495e-05</v>
       </c>
       <c r="AD13">
-        <v>-1.1210550792164261e-05</v>
+        <v>-1.1278162757271618e-05</v>
       </c>
       <c r="AE13">
-        <v>2.8728365879227523e-05</v>
+        <v>2.8744723553628723e-05</v>
       </c>
       <c r="AF13">
-        <v>0.00012682358669003778</v>
+        <v>0.00012682828905954903</v>
       </c>
       <c r="AG13">
-        <v>-8.0198346687011151e-05</v>
+        <v>-8.0194557288379138e-05</v>
       </c>
       <c r="AH13">
-        <v>1.4010040916725638e-05</v>
+        <v>1.4011853674495702e-05</v>
       </c>
       <c r="AI13">
-        <v>2.2497273758510881e-05</v>
+        <v>2.2514017574319558e-05</v>
       </c>
       <c r="AJ13">
-        <v>-1.7642350327369766e-05</v>
+        <v>-1.7625645102796765e-05</v>
       </c>
       <c r="AK13">
-        <v>-0.0037283434415254571</v>
+        <v>-0.0037281263337097595</v>
       </c>
     </row>
     <row r="14">
@@ -1870,112 +1870,112 @@
         <v>38</v>
       </c>
       <c r="B14">
-        <v>-0.05152273796127882</v>
+        <v>-0.051514847756305979</v>
       </c>
       <c r="C14">
-        <v>-6.2230380287060094e-05</v>
+        <v>-6.2240004934265684e-05</v>
       </c>
       <c r="D14">
-        <v>1.849540546058624e-05</v>
+        <v>1.8493161870515433e-05</v>
       </c>
       <c r="E14">
-        <v>-1.7802073679945095e-07</v>
+        <v>-1.7800012130098569e-07</v>
       </c>
       <c r="F14">
-        <v>0.00029836823804563575</v>
+        <v>0.00029837182396270402</v>
       </c>
       <c r="G14">
-        <v>0.00012622871584825821</v>
+        <v>0.00012623894597151562</v>
       </c>
       <c r="H14">
-        <v>7.7048327174811032e-05</v>
+        <v>7.7049602391855406e-05</v>
       </c>
       <c r="I14">
-        <v>0.00016345047982942737</v>
+        <v>0.0001634579299751185</v>
       </c>
       <c r="J14">
-        <v>0.0001019365135082567</v>
+        <v>0.00010194590320954794</v>
       </c>
       <c r="K14">
-        <v>0.00012338849215694421</v>
+        <v>0.00012338939884368378</v>
       </c>
       <c r="L14">
-        <v>3.3290537761394932e-05</v>
+        <v>3.3295891704159973e-05</v>
       </c>
       <c r="M14">
-        <v>-0.0039024839201533893</v>
+        <v>-0.0039024694826555063</v>
       </c>
       <c r="N14">
-        <v>-0.00037534663656049044</v>
+        <v>-0.00037535719091312406</v>
       </c>
       <c r="O14">
-        <v>0.0055419405291165175</v>
+        <v>0.0055419269637901371</v>
       </c>
       <c r="P14">
-        <v>0.00053477469754197526</v>
+        <v>0.00053479029744423184</v>
       </c>
       <c r="Q14">
-        <v>0.00040863378201786891</v>
+        <v>0.00040864257732344179</v>
       </c>
       <c r="R14">
-        <v>0.00017344257762705746</v>
+        <v>0.00017345002455418764</v>
       </c>
       <c r="S14">
-        <v>7.5393389499131422e-05</v>
+        <v>7.539192396890037e-05</v>
       </c>
       <c r="T14">
-        <v>8.2266326846122407e-05</v>
+        <v>8.225903245233162e-05</v>
       </c>
       <c r="U14">
-        <v>7.6724180258661316e-05</v>
+        <v>7.6712840879963147e-05</v>
       </c>
       <c r="V14">
-        <v>-0.00020575246722271101</v>
+        <v>-0.00020577290392620511</v>
       </c>
       <c r="W14">
-        <v>-0.00054619469812332701</v>
+        <v>-0.00054620077739307054</v>
       </c>
       <c r="X14">
-        <v>-0.00044372446158519367</v>
+        <v>-0.00044372109775907888</v>
       </c>
       <c r="Y14">
-        <v>-0.0003347383240470281</v>
+        <v>-0.00033472777077171392</v>
       </c>
       <c r="Z14">
-        <v>1.1140767805429049e-05</v>
+        <v>1.1142088365938665e-05</v>
       </c>
       <c r="AA14">
-        <v>-3.6248053603790307e-07</v>
+        <v>-3.6176184143933189e-07</v>
       </c>
       <c r="AB14">
-        <v>5.7766035196025458e-06</v>
+        <v>5.7726246558616754e-06</v>
       </c>
       <c r="AC14">
-        <v>-4.2566943769912439e-05</v>
+        <v>-4.2572121139827388e-05</v>
       </c>
       <c r="AD14">
-        <v>3.0942762292997012e-05</v>
+        <v>3.0913068517185124e-05</v>
       </c>
       <c r="AE14">
-        <v>-2.4394353489169262e-05</v>
+        <v>-2.4403755522718325e-05</v>
       </c>
       <c r="AF14">
-        <v>-7.0865269281933482e-05</v>
+        <v>-7.0864633063615599e-05</v>
       </c>
       <c r="AG14">
-        <v>-0.0001419765316418533</v>
+        <v>-0.00014196893536984535</v>
       </c>
       <c r="AH14">
-        <v>1.3672397677193627e-05</v>
+        <v>1.3672779687304104e-05</v>
       </c>
       <c r="AI14">
-        <v>-0.0003203966071602951</v>
+        <v>-0.00032039198444023365</v>
       </c>
       <c r="AJ14">
-        <v>-5.0527274971843878e-05</v>
+        <v>-5.052634472419023e-05</v>
       </c>
       <c r="AK14">
-        <v>-0.00059342837293038927</v>
+        <v>-0.00059337538449408516</v>
       </c>
     </row>
     <row r="15">
@@ -1983,112 +1983,112 @@
         <v>39</v>
       </c>
       <c r="B15">
-        <v>-0.082551690372539136</v>
+        <v>-0.082553486754600044</v>
       </c>
       <c r="C15">
-        <v>-4.2743199445159099e-05</v>
+        <v>-4.2742447953118519e-05</v>
       </c>
       <c r="D15">
-        <v>3.2424186703479025e-06</v>
+        <v>3.243644708268023e-06</v>
       </c>
       <c r="E15">
-        <v>-4.1789753539437336e-08</v>
+        <v>-4.180119020685555e-08</v>
       </c>
       <c r="F15">
-        <v>3.827277481463807e-05</v>
+        <v>3.8287409453310363e-05</v>
       </c>
       <c r="G15">
-        <v>0.00014563558546464451</v>
+        <v>0.00014563989567054775</v>
       </c>
       <c r="H15">
-        <v>0.0001305610373722979</v>
+        <v>0.00013056106850083636</v>
       </c>
       <c r="I15">
-        <v>0.0002199443317413354</v>
+        <v>0.00021995600760838719</v>
       </c>
       <c r="J15">
-        <v>0.00016665242253161662</v>
+        <v>0.00016665881505841174</v>
       </c>
       <c r="K15">
-        <v>0.00012829048939733118</v>
+        <v>0.00012830323147817313</v>
       </c>
       <c r="L15">
-        <v>2.6359258611128656e-05</v>
+        <v>2.6368182619703785e-05</v>
       </c>
       <c r="M15">
-        <v>9.2350131216029736e-05</v>
+        <v>9.2356351574602257e-05</v>
       </c>
       <c r="N15">
-        <v>0.00018422635349997404</v>
+        <v>0.00018423641443473117</v>
       </c>
       <c r="O15">
-        <v>0.00053477469754197526</v>
+        <v>0.00053479029744423184</v>
       </c>
       <c r="P15">
-        <v>0.00085212607516859632</v>
+        <v>0.00085214717192500455</v>
       </c>
       <c r="Q15">
-        <v>0.0004271578403558092</v>
+        <v>0.00042717301835042229</v>
       </c>
       <c r="R15">
-        <v>0.00022830699261457173</v>
+        <v>0.00022831574977796531</v>
       </c>
       <c r="S15">
-        <v>3.3016110453642811e-05</v>
+        <v>3.3016835274407607e-05</v>
       </c>
       <c r="T15">
-        <v>-3.0656344798475903e-05</v>
+        <v>-3.0651886088650264e-05</v>
       </c>
       <c r="U15">
-        <v>2.8757679846070955e-05</v>
+        <v>2.876497494133594e-05</v>
       </c>
       <c r="V15">
-        <v>-1.933401039301713e-05</v>
+        <v>-1.9320896881787098e-05</v>
       </c>
       <c r="W15">
-        <v>0.00015475424456343876</v>
+        <v>0.00015476411292640716</v>
       </c>
       <c r="X15">
-        <v>0.00025002282833821256</v>
+        <v>0.0002500355632349666</v>
       </c>
       <c r="Y15">
-        <v>0.00044896262577068816</v>
+        <v>0.0004489876661003785</v>
       </c>
       <c r="Z15">
-        <v>-8.7107838624458297e-06</v>
+        <v>-8.7127622993345505e-06</v>
       </c>
       <c r="AA15">
-        <v>3.1801073212105326e-06</v>
+        <v>3.181593351948706e-06</v>
       </c>
       <c r="AB15">
-        <v>4.0227291794956463e-05</v>
+        <v>4.0226663270417082e-05</v>
       </c>
       <c r="AC15">
-        <v>2.1457238077300504e-05</v>
+        <v>2.1456531395724183e-05</v>
       </c>
       <c r="AD15">
-        <v>1.1421144050133758e-05</v>
+        <v>1.1429507838074302e-05</v>
       </c>
       <c r="AE15">
-        <v>2.3670129780542536e-05</v>
+        <v>2.3669353205774937e-05</v>
       </c>
       <c r="AF15">
-        <v>1.8140719347580349e-05</v>
+        <v>1.8138429968336334e-05</v>
       </c>
       <c r="AG15">
-        <v>-1.8293545756455215e-05</v>
+        <v>-1.8294509765440727e-05</v>
       </c>
       <c r="AH15">
-        <v>5.9740567592712043e-06</v>
+        <v>5.9739552814932e-06</v>
       </c>
       <c r="AI15">
-        <v>-9.9362207800476996e-05</v>
+        <v>-9.9376228560866013e-05</v>
       </c>
       <c r="AJ15">
-        <v>-3.6940638418842269e-05</v>
+        <v>-3.6944388681503179e-05</v>
       </c>
       <c r="AK15">
-        <v>-0.00088753503768827368</v>
+        <v>-0.00088759852567903456</v>
       </c>
     </row>
     <row r="16">
@@ -2096,112 +2096,112 @@
         <v>40</v>
       </c>
       <c r="B16">
-        <v>-0.057781194908145379</v>
+        <v>-0.057766580112118583</v>
       </c>
       <c r="C16">
-        <v>-7.1669919744395317e-05</v>
+        <v>-7.1684750782153312e-05</v>
       </c>
       <c r="D16">
-        <v>-3.2440327681688612e-06</v>
+        <v>-3.2481501141426011e-06</v>
       </c>
       <c r="E16">
-        <v>-1.8293831883355746e-08</v>
+        <v>-1.8257074853130559e-08</v>
       </c>
       <c r="F16">
-        <v>0.0001619552673622247</v>
+        <v>0.00016194203110046258</v>
       </c>
       <c r="G16">
-        <v>0.00013240951091894772</v>
+        <v>0.00013243328503286059</v>
       </c>
       <c r="H16">
-        <v>0.00010424295910005168</v>
+        <v>0.00010424122871433243</v>
       </c>
       <c r="I16">
-        <v>0.00021976745877755203</v>
+        <v>0.00021977304420419899</v>
       </c>
       <c r="J16">
-        <v>9.2304215324873481e-05</v>
+        <v>9.2319156419083586e-05</v>
       </c>
       <c r="K16">
-        <v>0.00010544591470862338</v>
+        <v>0.00010543891706890313</v>
       </c>
       <c r="L16">
-        <v>-1.5497968678253107e-05</v>
+        <v>-1.5488279850675116e-05</v>
       </c>
       <c r="M16">
-        <v>0.00013049601598286157</v>
+        <v>0.00013048030078558449</v>
       </c>
       <c r="N16">
-        <v>0.00017832114300707114</v>
+        <v>0.00017829896758694483</v>
       </c>
       <c r="O16">
-        <v>0.00040863378201786891</v>
+        <v>0.00040864257732344179</v>
       </c>
       <c r="P16">
-        <v>0.0004271578403558092</v>
+        <v>0.00042717301835042229</v>
       </c>
       <c r="Q16">
-        <v>0.00081042706077744868</v>
+        <v>0.00081044016801293001</v>
       </c>
       <c r="R16">
-        <v>5.0616526959522152e-05</v>
+        <v>5.0624637336585182e-05</v>
       </c>
       <c r="S16">
-        <v>0.00012371357558828067</v>
+        <v>0.00012371502958618926</v>
       </c>
       <c r="T16">
-        <v>0.000174030323683663</v>
+        <v>0.00017401398144694147</v>
       </c>
       <c r="U16">
-        <v>0.00024760783753635809</v>
+        <v>0.00024760958492600247</v>
       </c>
       <c r="V16">
-        <v>3.0193827943864015e-05</v>
+        <v>3.0141678541860193e-05</v>
       </c>
       <c r="W16">
-        <v>0.00021947670711863082</v>
+        <v>0.00021945842890863947</v>
       </c>
       <c r="X16">
-        <v>0.0003233767068380332</v>
+        <v>0.00032337329010795313</v>
       </c>
       <c r="Y16">
-        <v>0.00055503544742020673</v>
+        <v>0.00055503397386503595</v>
       </c>
       <c r="Z16">
-        <v>-8.1373156770862186e-06</v>
+        <v>-8.1337547318097298e-06</v>
       </c>
       <c r="AA16">
-        <v>1.7333481452116894e-05</v>
+        <v>1.7334835094153639e-05</v>
       </c>
       <c r="AB16">
-        <v>8.0576268154295707e-05</v>
+        <v>8.0581684497851988e-05</v>
       </c>
       <c r="AC16">
-        <v>8.3804712631863065e-05</v>
+        <v>8.3807967486456704e-05</v>
       </c>
       <c r="AD16">
-        <v>0.00010136890377841057</v>
+        <v>0.00010132380066673349</v>
       </c>
       <c r="AE16">
-        <v>1.3748227545033872e-05</v>
+        <v>1.3751992204978332e-05</v>
       </c>
       <c r="AF16">
-        <v>6.772115567816514e-05</v>
+        <v>6.7733099180269083e-05</v>
       </c>
       <c r="AG16">
-        <v>6.9525296452413042e-07</v>
+        <v>6.9540725960201121e-07</v>
       </c>
       <c r="AH16">
-        <v>1.118089007127762e-05</v>
+        <v>1.118153308104632e-05</v>
       </c>
       <c r="AI16">
-        <v>-9.6750022121993521e-05</v>
+        <v>-9.6747092675855922e-05</v>
       </c>
       <c r="AJ16">
-        <v>-6.6639733347515591e-05</v>
+        <v>-6.6631928615452647e-05</v>
       </c>
       <c r="AK16">
-        <v>-0.0010158069852433725</v>
+        <v>-0.0010156987188927886</v>
       </c>
     </row>
     <row r="17">
@@ -2209,112 +2209,112 @@
         <v>41</v>
       </c>
       <c r="B17">
-        <v>-0.10450925133560861</v>
+        <v>-0.10450723923137492</v>
       </c>
       <c r="C17">
-        <v>0.00013420566143491886</v>
+        <v>0.0001342129335474713</v>
       </c>
       <c r="D17">
-        <v>2.0386837988315136e-05</v>
+        <v>2.03879574622578e-05</v>
       </c>
       <c r="E17">
-        <v>-2.3307329415924923e-07</v>
+        <v>-2.3308044762955454e-07</v>
       </c>
       <c r="F17">
-        <v>0.00022837758340651807</v>
+        <v>0.00022838431649253518</v>
       </c>
       <c r="G17">
-        <v>0.00028019533833558742</v>
+        <v>0.00028018013986952893</v>
       </c>
       <c r="H17">
-        <v>1.1697323578276661e-05</v>
+        <v>1.1699965530151488e-05</v>
       </c>
       <c r="I17">
-        <v>-4.2164400749345084e-05</v>
+        <v>-4.2162219541459116e-05</v>
       </c>
       <c r="J17">
-        <v>-6.7695892935032117e-06</v>
+        <v>-6.7707757489979346e-06</v>
       </c>
       <c r="K17">
-        <v>0.00012678847762746619</v>
+        <v>0.00012679830056682806</v>
       </c>
       <c r="L17">
-        <v>0.00015180337019379006</v>
+        <v>0.00015181253655580996</v>
       </c>
       <c r="M17">
-        <v>0.00040034826651316464</v>
+        <v>0.00040036659471146116</v>
       </c>
       <c r="N17">
-        <v>0.00038060181975724185</v>
+        <v>0.00038062178990733468</v>
       </c>
       <c r="O17">
-        <v>0.00017344257762705746</v>
+        <v>0.00017345002455418764</v>
       </c>
       <c r="P17">
-        <v>0.00022830699261457173</v>
+        <v>0.00022831574977796531</v>
       </c>
       <c r="Q17">
-        <v>5.0616526959522152e-05</v>
+        <v>5.0624637336585182e-05</v>
       </c>
       <c r="R17">
-        <v>0.0096314813873918329</v>
+        <v>0.0096316733954500151</v>
       </c>
       <c r="S17">
-        <v>0.0069603863164168327</v>
+        <v>0.006960530824811368</v>
       </c>
       <c r="T17">
-        <v>0.0068800840852735207</v>
+        <v>0.006880229585386052</v>
       </c>
       <c r="U17">
-        <v>0.0068629803929895292</v>
+        <v>0.0068631250994986778</v>
       </c>
       <c r="V17">
-        <v>-0.00011633069352961155</v>
+        <v>-0.00011630626322391521</v>
       </c>
       <c r="W17">
-        <v>0.00037058340889709355</v>
+        <v>0.00037061157523519354</v>
       </c>
       <c r="X17">
-        <v>0.00053352859280354596</v>
+        <v>0.00053355947791007205</v>
       </c>
       <c r="Y17">
-        <v>0.00043498186638154038</v>
+        <v>0.00043500993381972563</v>
       </c>
       <c r="Z17">
-        <v>-2.6947999711512017e-05</v>
+        <v>-2.6951325317340401e-05</v>
       </c>
       <c r="AA17">
-        <v>-0.00012141883029646405</v>
+        <v>-0.00012142235918183677</v>
       </c>
       <c r="AB17">
-        <v>0.00015721557200828237</v>
+        <v>0.00015721225935875181</v>
       </c>
       <c r="AC17">
-        <v>0.00022045477681207574</v>
+        <v>0.00022045493845321632</v>
       </c>
       <c r="AD17">
-        <v>0.00021136950546718925</v>
+        <v>0.00021139810342213176</v>
       </c>
       <c r="AE17">
-        <v>0.00015404301536331693</v>
+        <v>0.00015404135002411445</v>
       </c>
       <c r="AF17">
-        <v>0.00026288990610466535</v>
+        <v>0.00026289074750658766</v>
       </c>
       <c r="AG17">
-        <v>0.00042198338766060817</v>
+        <v>0.0004219850881182784</v>
       </c>
       <c r="AH17">
-        <v>6.3094041663496901e-06</v>
+        <v>6.3090179502545336e-06</v>
       </c>
       <c r="AI17">
-        <v>3.2985664300947716e-05</v>
+        <v>3.2992963550648041e-05</v>
       </c>
       <c r="AJ17">
-        <v>-3.3357670150407307e-05</v>
+        <v>-3.3360425697209761e-05</v>
       </c>
       <c r="AK17">
-        <v>-0.0082140119343833331</v>
+        <v>-0.0082142232681731674</v>
       </c>
     </row>
     <row r="18">
@@ -2322,112 +2322,112 @@
         <v>42</v>
       </c>
       <c r="B18">
-        <v>-0.075528085976167891</v>
+        <v>-0.075518641858778352</v>
       </c>
       <c r="C18">
-        <v>-3.4921551950940357e-05</v>
+        <v>-3.492902222563712e-05</v>
       </c>
       <c r="D18">
-        <v>-3.6214124445822153e-07</v>
+        <v>-3.6424690642633323e-07</v>
       </c>
       <c r="E18">
-        <v>-1.7935383711011097e-08</v>
+        <v>-1.7919896359651921e-08</v>
       </c>
       <c r="F18">
-        <v>0.00020243608162499871</v>
+        <v>0.00020243144669056809</v>
       </c>
       <c r="G18">
-        <v>9.1795808582042452e-05</v>
+        <v>9.1832062200270675e-05</v>
       </c>
       <c r="H18">
-        <v>2.6618447836996391e-05</v>
+        <v>2.661754862446318e-05</v>
       </c>
       <c r="I18">
-        <v>6.0484176166268611e-05</v>
+        <v>6.0483320952118896e-05</v>
       </c>
       <c r="J18">
-        <v>-8.1225892030046924e-06</v>
+        <v>-8.1208873535783353e-06</v>
       </c>
       <c r="K18">
-        <v>-1.185739986945167e-05</v>
+        <v>-1.1876330806251606e-05</v>
       </c>
       <c r="L18">
-        <v>6.2222772827284279e-05</v>
+        <v>6.2227471161098728e-05</v>
       </c>
       <c r="M18">
-        <v>7.0188535707875737e-05</v>
+        <v>7.0190594616147259e-05</v>
       </c>
       <c r="N18">
-        <v>0.00019662642067314246</v>
+        <v>0.00019663832564372776</v>
       </c>
       <c r="O18">
-        <v>7.5393389499131422e-05</v>
+        <v>7.539192396890037e-05</v>
       </c>
       <c r="P18">
-        <v>3.3016110453642811e-05</v>
+        <v>3.3016835274407607e-05</v>
       </c>
       <c r="Q18">
-        <v>0.00012371357558828067</v>
+        <v>0.00012371502958618926</v>
       </c>
       <c r="R18">
-        <v>0.0069603863164168327</v>
+        <v>0.006960530824811368</v>
       </c>
       <c r="S18">
-        <v>0.0074751884736742307</v>
+        <v>0.007475332021060585</v>
       </c>
       <c r="T18">
-        <v>0.007126200314555263</v>
+        <v>0.0071263396898190792</v>
       </c>
       <c r="U18">
-        <v>0.0071391230930635428</v>
+        <v>0.0071392658714457963</v>
       </c>
       <c r="V18">
-        <v>-0.00019811970557464026</v>
+        <v>-0.00019814679312695627</v>
       </c>
       <c r="W18">
-        <v>-1.7936533909374257e-05</v>
+        <v>-1.7942532772350067e-05</v>
       </c>
       <c r="X18">
-        <v>-4.2465109285256403e-05</v>
+        <v>-4.2471438949593342e-05</v>
       </c>
       <c r="Y18">
-        <v>-2.803836075114096e-06</v>
+        <v>-2.8065318577845389e-06</v>
       </c>
       <c r="Z18">
-        <v>-1.3605355056044755e-05</v>
+        <v>-1.3604001049854248e-05</v>
       </c>
       <c r="AA18">
-        <v>-2.7501105139336344e-05</v>
+        <v>-2.7502158129465463e-05</v>
       </c>
       <c r="AB18">
-        <v>0.00043790842602804692</v>
+        <v>0.00043792243425426741</v>
       </c>
       <c r="AC18">
-        <v>0.00044951602127424849</v>
+        <v>0.00044953031904174882</v>
       </c>
       <c r="AD18">
-        <v>0.00044366143414337981</v>
+        <v>0.00044366328659484807</v>
       </c>
       <c r="AE18">
-        <v>0.0003685897313903232</v>
+        <v>0.00036860541209909198</v>
       </c>
       <c r="AF18">
-        <v>0.00045106378006006301</v>
+        <v>0.00045108047264597604</v>
       </c>
       <c r="AG18">
-        <v>0.00040656128482668389</v>
+        <v>0.00040657107945525444</v>
       </c>
       <c r="AH18">
-        <v>3.9477254569432376e-07</v>
+        <v>3.9528066487977713e-07</v>
       </c>
       <c r="AI18">
-        <v>6.2748640235272407e-05</v>
+        <v>6.2750748413151203e-05</v>
       </c>
       <c r="AJ18">
-        <v>3.6756520083021556e-05</v>
+        <v>3.6761823225330524e-05</v>
       </c>
       <c r="AK18">
-        <v>-0.0075311052027089509</v>
+        <v>-0.0075311980341891197</v>
       </c>
     </row>
     <row r="19">
@@ -2435,112 +2435,112 @@
         <v>43</v>
       </c>
       <c r="B19">
-        <v>-0.013365352090778517</v>
+        <v>-0.013338457624871319</v>
       </c>
       <c r="C19">
-        <v>-3.5548423043606316e-05</v>
+        <v>-3.5571747157914926e-05</v>
       </c>
       <c r="D19">
-        <v>2.9838937459911776e-06</v>
+        <v>2.9768829863696834e-06</v>
       </c>
       <c r="E19">
-        <v>-7.7066021856421626e-09</v>
+        <v>-7.6404521593637758e-09</v>
       </c>
       <c r="F19">
-        <v>0.0001496439366933754</v>
+        <v>0.00014961023123421049</v>
       </c>
       <c r="G19">
-        <v>5.7532952177817066e-05</v>
+        <v>5.7560987659392487e-05</v>
       </c>
       <c r="H19">
-        <v>2.518802711129356e-06</v>
+        <v>2.5215092514105841e-06</v>
       </c>
       <c r="I19">
-        <v>-4.3114087389519687e-05</v>
+        <v>-4.3118920600893561e-05</v>
       </c>
       <c r="J19">
-        <v>-3.0729418641468995e-05</v>
+        <v>-3.0715747977917837e-05</v>
       </c>
       <c r="K19">
-        <v>3.9611480137141577e-06</v>
+        <v>3.9338056891625398e-06</v>
       </c>
       <c r="L19">
-        <v>6.9005235723320333e-05</v>
+        <v>6.9006974218798443e-05</v>
       </c>
       <c r="M19">
-        <v>5.5146278714787418e-05</v>
+        <v>5.5124142924785216e-05</v>
       </c>
       <c r="N19">
-        <v>0.00021037711093222628</v>
+        <v>0.00021035101059134161</v>
       </c>
       <c r="O19">
-        <v>8.2266326846122407e-05</v>
+        <v>8.225903245233162e-05</v>
       </c>
       <c r="P19">
-        <v>-3.0656344798475903e-05</v>
+        <v>-3.0651886088650264e-05</v>
       </c>
       <c r="Q19">
-        <v>0.000174030323683663</v>
+        <v>0.00017401398144694147</v>
       </c>
       <c r="R19">
-        <v>0.0068800840852735207</v>
+        <v>0.006880229585386052</v>
       </c>
       <c r="S19">
-        <v>0.007126200314555263</v>
+        <v>0.0071263396898190792</v>
       </c>
       <c r="T19">
-        <v>0.007439803499887797</v>
+        <v>0.0074399238777659513</v>
       </c>
       <c r="U19">
-        <v>0.0072869263547294411</v>
+        <v>0.0072870594713744987</v>
       </c>
       <c r="V19">
-        <v>-0.00016181961638011091</v>
+        <v>-0.00016190740334869234</v>
       </c>
       <c r="W19">
-        <v>1.0615446783957764e-05</v>
+        <v>1.0578835977466308e-05</v>
       </c>
       <c r="X19">
-        <v>-5.8561330038135219e-05</v>
+        <v>-5.859065101626159e-05</v>
       </c>
       <c r="Y19">
-        <v>-1.6490486110466197e-05</v>
+        <v>-1.6522378890875856e-05</v>
       </c>
       <c r="Z19">
-        <v>-1.5527168124512727e-05</v>
+        <v>-1.5519833150295023e-05</v>
       </c>
       <c r="AA19">
-        <v>-4.5180700695797308e-05</v>
+        <v>-4.5184850812885835e-05</v>
       </c>
       <c r="AB19">
-        <v>0.00047454632816830347</v>
+        <v>0.00047455826863080416</v>
       </c>
       <c r="AC19">
-        <v>0.00045514427693892773</v>
+        <v>0.00045515397205222151</v>
       </c>
       <c r="AD19">
-        <v>0.00044584842290995314</v>
+        <v>0.00044579472625172131</v>
       </c>
       <c r="AE19">
-        <v>0.00037201559848097469</v>
+        <v>0.00037203166613365528</v>
       </c>
       <c r="AF19">
-        <v>0.00044704731658186023</v>
+        <v>0.0004470645319115639</v>
       </c>
       <c r="AG19">
-        <v>0.00046031712819683516</v>
+        <v>0.00046032666736534544</v>
       </c>
       <c r="AH19">
-        <v>2.9033242832995768e-06</v>
+        <v>2.9048955028014134e-06</v>
       </c>
       <c r="AI19">
-        <v>6.6048570054214745e-05</v>
+        <v>6.6076337071089772e-05</v>
       </c>
       <c r="AJ19">
-        <v>2.7265126406627194e-05</v>
+        <v>2.7281207194245795e-05</v>
       </c>
       <c r="AK19">
-        <v>-0.0078957048946451738</v>
+        <v>-0.0078956453265367523</v>
       </c>
     </row>
     <row r="20">
@@ -2548,112 +2548,112 @@
         <v>44</v>
       </c>
       <c r="B20">
-        <v>-0.042669097870340747</v>
+        <v>-0.04264819766323568</v>
       </c>
       <c r="C20">
-        <v>-8.4529721572964401e-05</v>
+        <v>-8.4545928728930157e-05</v>
       </c>
       <c r="D20">
-        <v>1.0296429700273896e-05</v>
+        <v>1.0292432767799328e-05</v>
       </c>
       <c r="E20">
-        <v>-6.537596477961261e-08</v>
+        <v>-6.533851256180072e-08</v>
       </c>
       <c r="F20">
-        <v>0.00038256576570248749</v>
+        <v>0.00038255499253252179</v>
       </c>
       <c r="G20">
-        <v>0.00010405091912444849</v>
+        <v>0.00010408204210283025</v>
       </c>
       <c r="H20">
-        <v>8.7756474835707027e-06</v>
+        <v>8.7750778236801545e-06</v>
       </c>
       <c r="I20">
-        <v>5.4132469581722386e-05</v>
+        <v>5.4137266248193631e-05</v>
       </c>
       <c r="J20">
-        <v>3.2129803071658208e-05</v>
+        <v>3.2143550216585069e-05</v>
       </c>
       <c r="K20">
-        <v>5.6135453318191053e-06</v>
+        <v>5.6008102751753256e-06</v>
       </c>
       <c r="L20">
-        <v>4.5739347489597688e-05</v>
+        <v>4.574616360110851e-05</v>
       </c>
       <c r="M20">
-        <v>0.00019182793736752181</v>
+        <v>0.00019182119029518847</v>
       </c>
       <c r="N20">
-        <v>0.0003725195176027484</v>
+        <v>0.00037251560686469925</v>
       </c>
       <c r="O20">
-        <v>7.6724180258661316e-05</v>
+        <v>7.6712840879963147e-05</v>
       </c>
       <c r="P20">
-        <v>2.8757679846070955e-05</v>
+        <v>2.876497494133594e-05</v>
       </c>
       <c r="Q20">
-        <v>0.00024760783753635809</v>
+        <v>0.00024760958492600247</v>
       </c>
       <c r="R20">
-        <v>0.0068629803929895292</v>
+        <v>0.0068631250994986778</v>
       </c>
       <c r="S20">
-        <v>0.0071391230930635428</v>
+        <v>0.0071392658714457963</v>
       </c>
       <c r="T20">
-        <v>0.0072869263547294411</v>
+        <v>0.0072870594713744987</v>
       </c>
       <c r="U20">
-        <v>0.0078869342705864265</v>
+        <v>0.0078871029018913099</v>
       </c>
       <c r="V20">
-        <v>-0.00020865552379749225</v>
+        <v>-0.00020871349241464665</v>
       </c>
       <c r="W20">
-        <v>9.647182247711104e-05</v>
+        <v>9.6452086689876541e-05</v>
       </c>
       <c r="X20">
-        <v>7.7201130822303343e-05</v>
+        <v>7.7192051089696942e-05</v>
       </c>
       <c r="Y20">
-        <v>0.00015215192336604996</v>
+        <v>0.00015214063173027079</v>
       </c>
       <c r="Z20">
-        <v>-1.4997094774375731e-05</v>
+        <v>-1.4993509390343136e-05</v>
       </c>
       <c r="AA20">
-        <v>-2.1732523540068721e-05</v>
+        <v>-2.1733090131611501e-05</v>
       </c>
       <c r="AB20">
-        <v>0.00055390881857341357</v>
+        <v>0.00055392495136093352</v>
       </c>
       <c r="AC20">
-        <v>0.00050831370349618387</v>
+        <v>0.00050832725165993794</v>
       </c>
       <c r="AD20">
-        <v>0.00050853877760929228</v>
+        <v>0.00050851898057002048</v>
       </c>
       <c r="AE20">
-        <v>0.00044165846089542701</v>
+        <v>0.00044167620340231171</v>
       </c>
       <c r="AF20">
-        <v>0.00054347568782368004</v>
+        <v>0.00054349859132573459</v>
       </c>
       <c r="AG20">
-        <v>0.00037320853590305629</v>
+        <v>0.00037321764746299301</v>
       </c>
       <c r="AH20">
-        <v>4.8924266332218264e-06</v>
+        <v>4.8929705299049164e-06</v>
       </c>
       <c r="AI20">
-        <v>6.6267106489470082e-05</v>
+        <v>6.6273869017443449e-05</v>
       </c>
       <c r="AJ20">
-        <v>7.739509810262982e-05</v>
+        <v>7.7407651909492357e-05</v>
       </c>
       <c r="AK20">
-        <v>-0.0084047148033068626</v>
+        <v>-0.0084047649127244502</v>
       </c>
     </row>
     <row r="21">
@@ -2661,112 +2661,112 @@
         <v>45</v>
       </c>
       <c r="B21">
-        <v>0.18581672506193331</v>
+        <v>0.18587288408909039</v>
       </c>
       <c r="C21">
-        <v>-1.4813620219372844e-06</v>
+        <v>-1.5333079626743306e-06</v>
       </c>
       <c r="D21">
-        <v>5.4938493318870571e-06</v>
+        <v>5.478910716750254e-06</v>
       </c>
       <c r="E21">
-        <v>-5.1451220615427808e-08</v>
+        <v>-5.131731462441057e-08</v>
       </c>
       <c r="F21">
-        <v>4.2466494095345865e-05</v>
+        <v>4.2393983027296228e-05</v>
       </c>
       <c r="G21">
-        <v>7.6858848076335383e-05</v>
+        <v>7.6936626433448784e-05</v>
       </c>
       <c r="H21">
-        <v>2.5076923450845958e-05</v>
+        <v>2.5072607670293513e-05</v>
       </c>
       <c r="I21">
-        <v>0.00011978362656084126</v>
+        <v>0.00011977695022078335</v>
       </c>
       <c r="J21">
-        <v>0.00011957118330981418</v>
+        <v>0.00011960556855189529</v>
       </c>
       <c r="K21">
-        <v>9.8062603679315545e-05</v>
+        <v>9.7996192177115843e-05</v>
       </c>
       <c r="L21">
-        <v>5.2692789592910359e-05</v>
+        <v>5.2687433501897525e-05</v>
       </c>
       <c r="M21">
-        <v>0.00065136072350025615</v>
+        <v>0.0006513196185803673</v>
       </c>
       <c r="N21">
-        <v>0.00047858650291903468</v>
+        <v>0.00047851206798052014</v>
       </c>
       <c r="O21">
-        <v>-0.00020575246722271101</v>
+        <v>-0.00020577290392620511</v>
       </c>
       <c r="P21">
-        <v>-1.933401039301713e-05</v>
+        <v>-1.9320896881787098e-05</v>
       </c>
       <c r="Q21">
-        <v>3.0193827943864015e-05</v>
+        <v>3.0141678541860193e-05</v>
       </c>
       <c r="R21">
-        <v>-0.00011633069352961155</v>
+        <v>-0.00011630626322391521</v>
       </c>
       <c r="S21">
-        <v>-0.00019811970557464026</v>
+        <v>-0.00019814679312695627</v>
       </c>
       <c r="T21">
-        <v>-0.00016181961638011091</v>
+        <v>-0.00016190740334869234</v>
       </c>
       <c r="U21">
-        <v>-0.00020865552379749225</v>
+        <v>-0.00020871349241464665</v>
       </c>
       <c r="V21">
-        <v>0.0010881138356200885</v>
+        <v>0.0010879734232769349</v>
       </c>
       <c r="W21">
-        <v>0.00096500355076953662</v>
+        <v>0.00096492220489102559</v>
       </c>
       <c r="X21">
-        <v>0.0010060687184385443</v>
+        <v>0.0010060107628910462</v>
       </c>
       <c r="Y21">
-        <v>0.0010987470605070687</v>
+        <v>0.0010986902141187286</v>
       </c>
       <c r="Z21">
-        <v>-9.7750833826045432e-05</v>
+        <v>-9.7735378788608415e-05</v>
       </c>
       <c r="AA21">
-        <v>8.4349652446997418e-06</v>
+        <v>8.430203632331238e-06</v>
       </c>
       <c r="AB21">
-        <v>6.2213354989718917e-05</v>
+        <v>6.2215016927632811e-05</v>
       </c>
       <c r="AC21">
-        <v>5.5517202497956382e-05</v>
+        <v>5.551159091172304e-05</v>
       </c>
       <c r="AD21">
-        <v>2.5586899086530563e-05</v>
+        <v>2.5427207967291783e-05</v>
       </c>
       <c r="AE21">
-        <v>3.5358664222996574e-05</v>
+        <v>3.5370838212990833e-05</v>
       </c>
       <c r="AF21">
-        <v>2.1860475353110699e-05</v>
+        <v>2.186656129644343e-05</v>
       </c>
       <c r="AG21">
-        <v>0.00011342840730378033</v>
+        <v>0.00011343594944440005</v>
       </c>
       <c r="AH21">
-        <v>-3.2089001525624134e-06</v>
+        <v>-3.2051049512609733e-06</v>
       </c>
       <c r="AI21">
-        <v>-0.00014346109081114094</v>
+        <v>-0.00014341427858625163</v>
       </c>
       <c r="AJ21">
-        <v>-5.5767442248278495e-05</v>
+        <v>-5.5734186276285567e-05</v>
       </c>
       <c r="AK21">
-        <v>-0.00087090108422831474</v>
+        <v>-0.00087039852192216031</v>
       </c>
     </row>
     <row r="22">
@@ -2774,112 +2774,112 @@
         <v>46</v>
       </c>
       <c r="B22">
-        <v>0.060753739800239952</v>
+        <v>0.060779790579179357</v>
       </c>
       <c r="C22">
-        <v>1.7352256984078351e-05</v>
+        <v>1.7320127798754005e-05</v>
       </c>
       <c r="D22">
-        <v>3.6309692420625767e-06</v>
+        <v>3.6238612205948006e-06</v>
       </c>
       <c r="E22">
-        <v>-8.4585824596336219e-08</v>
+        <v>-8.4522838499709036e-08</v>
       </c>
       <c r="F22">
-        <v>6.7039399235246065e-05</v>
+        <v>6.7013509459798448e-05</v>
       </c>
       <c r="G22">
-        <v>0.00013047642463277222</v>
+        <v>0.000130512544865558</v>
       </c>
       <c r="H22">
-        <v>2.793574316478024e-05</v>
+        <v>2.7925235297103024e-05</v>
       </c>
       <c r="I22">
-        <v>0.00018705615237387145</v>
+        <v>0.00018705243795518194</v>
       </c>
       <c r="J22">
-        <v>0.00011894559471515664</v>
+        <v>0.00011896340925752569</v>
       </c>
       <c r="K22">
-        <v>0.00021084417722837972</v>
+        <v>0.00021082050307295311</v>
       </c>
       <c r="L22">
-        <v>3.7361488613367293e-06</v>
+        <v>3.737803418578595e-06</v>
       </c>
       <c r="M22">
-        <v>0.0031556215148482387</v>
+        <v>0.0031556052964034076</v>
       </c>
       <c r="N22">
-        <v>0.0027092676205075685</v>
+        <v>0.0027092356933511616</v>
       </c>
       <c r="O22">
-        <v>-0.00054619469812332701</v>
+        <v>-0.00054620077739307054</v>
       </c>
       <c r="P22">
-        <v>0.00015475424456343876</v>
+        <v>0.00015476411292640716</v>
       </c>
       <c r="Q22">
-        <v>0.00021947670711863082</v>
+        <v>0.00021945842890863947</v>
       </c>
       <c r="R22">
-        <v>0.00037058340889709355</v>
+        <v>0.00037061157523519354</v>
       </c>
       <c r="S22">
-        <v>-1.7936533909374257e-05</v>
+        <v>-1.7942532772350067e-05</v>
       </c>
       <c r="T22">
-        <v>1.0615446783957764e-05</v>
+        <v>1.0578835977466308e-05</v>
       </c>
       <c r="U22">
-        <v>9.647182247711104e-05</v>
+        <v>9.6452086689876541e-05</v>
       </c>
       <c r="V22">
-        <v>0.00096500355076953662</v>
+        <v>0.00096492220489102559</v>
       </c>
       <c r="W22">
-        <v>0.0035235923191966482</v>
+        <v>0.0035235765768407623</v>
       </c>
       <c r="X22">
-        <v>0.0033564498323355244</v>
+        <v>0.0033564437282770543</v>
       </c>
       <c r="Y22">
-        <v>0.0036511532688898837</v>
+        <v>0.0036511541137874536</v>
       </c>
       <c r="Z22">
-        <v>-0.00020362892724945386</v>
+        <v>-0.00020362293739623115</v>
       </c>
       <c r="AA22">
-        <v>3.5513179620983056e-05</v>
+        <v>3.5515039328621321e-05</v>
       </c>
       <c r="AB22">
-        <v>4.9100618034042184e-05</v>
+        <v>4.9105307281538564e-05</v>
       </c>
       <c r="AC22">
-        <v>-4.7253264226984615e-06</v>
+        <v>-4.7251357243268712e-06</v>
       </c>
       <c r="AD22">
-        <v>-1.8520172109935196e-05</v>
+        <v>-1.8605951851966268e-05</v>
       </c>
       <c r="AE22">
-        <v>2.2287889056261077e-05</v>
+        <v>2.2304809881174177e-05</v>
       </c>
       <c r="AF22">
-        <v>0.00011836176834439726</v>
+        <v>0.00011837024832619996</v>
       </c>
       <c r="AG22">
-        <v>8.2306099945634052e-05</v>
+        <v>8.2314725543089447e-05</v>
       </c>
       <c r="AH22">
-        <v>6.2388234138415226e-06</v>
+        <v>6.2405451611873328e-06</v>
       </c>
       <c r="AI22">
-        <v>-3.4061938609403469e-05</v>
+        <v>-3.4047526304822797e-05</v>
       </c>
       <c r="AJ22">
-        <v>-5.7148638478477908e-05</v>
+        <v>-5.7130189632925753e-05</v>
       </c>
       <c r="AK22">
-        <v>-0.0035897040150082459</v>
+        <v>-0.0035894863773359397</v>
       </c>
     </row>
     <row r="23">
@@ -2887,112 +2887,112 @@
         <v>47</v>
       </c>
       <c r="B23">
-        <v>0.17597498553155375</v>
+        <v>0.17599427622298103</v>
       </c>
       <c r="C23">
-        <v>-2.7548024030372515e-05</v>
+        <v>-2.7578672969093225e-05</v>
       </c>
       <c r="D23">
-        <v>7.3174811776762199e-06</v>
+        <v>7.3128771778003263e-06</v>
       </c>
       <c r="E23">
-        <v>-1.1268753893109769e-07</v>
+        <v>-1.126472656274382e-07</v>
       </c>
       <c r="F23">
-        <v>0.00041791432293122833</v>
+        <v>0.00041790608657136272</v>
       </c>
       <c r="G23">
-        <v>0.00027331608494886458</v>
+        <v>0.00027336396351494187</v>
       </c>
       <c r="H23">
-        <v>4.9530687024611567e-05</v>
+        <v>4.9524922024530302e-05</v>
       </c>
       <c r="I23">
-        <v>0.00049134187229104144</v>
+        <v>0.0004913479309294731</v>
       </c>
       <c r="J23">
-        <v>0.00048693274213967722</v>
+        <v>0.00048695453163207381</v>
       </c>
       <c r="K23">
-        <v>0.00034670368532950069</v>
+        <v>0.00034669342221652424</v>
       </c>
       <c r="L23">
-        <v>0.00036018859480426205</v>
+        <v>0.00036019533200513454</v>
       </c>
       <c r="M23">
-        <v>0.0036333808813741476</v>
+        <v>0.0036333819257838018</v>
       </c>
       <c r="N23">
-        <v>0.0031294321984750985</v>
+        <v>0.0031294106327237835</v>
       </c>
       <c r="O23">
-        <v>-0.00044372446158519367</v>
+        <v>-0.00044372109775907888</v>
       </c>
       <c r="P23">
-        <v>0.00025002282833821256</v>
+        <v>0.0002500355632349666</v>
       </c>
       <c r="Q23">
-        <v>0.0003233767068380332</v>
+        <v>0.00032337329010795313</v>
       </c>
       <c r="R23">
-        <v>0.00053352859280354596</v>
+        <v>0.00053355947791007205</v>
       </c>
       <c r="S23">
-        <v>-4.2465109285256403e-05</v>
+        <v>-4.2471438949593342e-05</v>
       </c>
       <c r="T23">
-        <v>-5.8561330038135219e-05</v>
+        <v>-5.859065101626159e-05</v>
       </c>
       <c r="U23">
-        <v>7.7201130822303343e-05</v>
+        <v>7.7192051089696942e-05</v>
       </c>
       <c r="V23">
-        <v>0.0010060687184385443</v>
+        <v>0.0010060107628910462</v>
       </c>
       <c r="W23">
-        <v>0.0033564498323355244</v>
+        <v>0.0033564437282770543</v>
       </c>
       <c r="X23">
-        <v>0.0044514440079025993</v>
+        <v>0.0044514737926923311</v>
       </c>
       <c r="Y23">
-        <v>0.0042273941172363376</v>
+        <v>0.0042274158152500524</v>
       </c>
       <c r="Z23">
-        <v>-0.00020800310355676004</v>
+        <v>-0.0002080005552566935</v>
       </c>
       <c r="AA23">
-        <v>3.8051693381254098e-05</v>
+        <v>3.8055925120422164e-05</v>
       </c>
       <c r="AB23">
-        <v>0.00010993476809554453</v>
+        <v>0.000109941145362372</v>
       </c>
       <c r="AC23">
-        <v>2.3097686720350424e-05</v>
+        <v>2.3099686328289723e-05</v>
       </c>
       <c r="AD23">
-        <v>5.2452107729939693e-05</v>
+        <v>5.238172533216694e-05</v>
       </c>
       <c r="AE23">
-        <v>9.3578681102805643e-05</v>
+        <v>9.3594557088700053e-05</v>
       </c>
       <c r="AF23">
-        <v>0.00020359729260564232</v>
+        <v>0.00020361227965020592</v>
       </c>
       <c r="AG23">
-        <v>0.00021553150864596707</v>
+        <v>0.00021554429213088209</v>
       </c>
       <c r="AH23">
-        <v>1.0350152968928601e-05</v>
+        <v>1.0351104190018683e-05</v>
       </c>
       <c r="AI23">
-        <v>9.7635099104415209e-05</v>
+        <v>9.7645302096884337e-05</v>
       </c>
       <c r="AJ23">
-        <v>-8.563530496687329e-05</v>
+        <v>-8.5620284228440056e-05</v>
       </c>
       <c r="AK23">
-        <v>-0.0044937115429248562</v>
+        <v>-0.0044935850989067851</v>
       </c>
     </row>
     <row r="24">
@@ -3000,112 +3000,112 @@
         <v>48</v>
       </c>
       <c r="B24">
-        <v>0.19728973538206351</v>
+        <v>0.19730644786845025</v>
       </c>
       <c r="C24">
-        <v>-9.7104411995299622e-05</v>
+        <v>-9.7140136555206414e-05</v>
       </c>
       <c r="D24">
-        <v>-6.0449240535131489e-06</v>
+        <v>-6.051814695894758e-06</v>
       </c>
       <c r="E24">
-        <v>-1.6968589260686767e-08</v>
+        <v>-1.690835330445087e-08</v>
       </c>
       <c r="F24">
-        <v>0.00082094867511977622</v>
+        <v>0.00082093055223320935</v>
       </c>
       <c r="G24">
-        <v>0.00076472299585248057</v>
+        <v>0.0007647872838871736</v>
       </c>
       <c r="H24">
-        <v>0.00031936743496319554</v>
+        <v>0.00031935560965139686</v>
       </c>
       <c r="I24">
-        <v>0.0010978307885125265</v>
+        <v>0.0010978483904407641</v>
       </c>
       <c r="J24">
-        <v>0.001017453600681351</v>
+        <v>0.0010174882548330177</v>
       </c>
       <c r="K24">
-        <v>0.00071296069461482909</v>
+        <v>0.00071294432274992669</v>
       </c>
       <c r="L24">
-        <v>0.000633808018733031</v>
+        <v>0.00063382182572373994</v>
       </c>
       <c r="M24">
-        <v>0.0038086382056721608</v>
+        <v>0.0038086350141968688</v>
       </c>
       <c r="N24">
-        <v>0.0034072188462806437</v>
+        <v>0.0034072040684542042</v>
       </c>
       <c r="O24">
-        <v>-0.0003347383240470281</v>
+        <v>-0.00033472777077171392</v>
       </c>
       <c r="P24">
-        <v>0.00044896262577068816</v>
+        <v>0.0004489876661003785</v>
       </c>
       <c r="Q24">
-        <v>0.00055503544742020673</v>
+        <v>0.00055503397386503595</v>
       </c>
       <c r="R24">
-        <v>0.00043498186638154038</v>
+        <v>0.00043500993381972563</v>
       </c>
       <c r="S24">
-        <v>-2.803836075114096e-06</v>
+        <v>-2.8065318577845389e-06</v>
       </c>
       <c r="T24">
-        <v>-1.6490486110466197e-05</v>
+        <v>-1.6522378890875856e-05</v>
       </c>
       <c r="U24">
-        <v>0.00015215192336604996</v>
+        <v>0.00015214063173027079</v>
       </c>
       <c r="V24">
-        <v>0.0010987470605070687</v>
+        <v>0.0010986902141187286</v>
       </c>
       <c r="W24">
-        <v>0.0036511532688898837</v>
+        <v>0.0036511541137874536</v>
       </c>
       <c r="X24">
-        <v>0.0042273941172363376</v>
+        <v>0.0042274158152500524</v>
       </c>
       <c r="Y24">
-        <v>0.0054436138896379908</v>
+        <v>0.0054436772202071226</v>
       </c>
       <c r="Z24">
-        <v>-0.00024475866744502202</v>
+        <v>-0.0002447574363151083</v>
       </c>
       <c r="AA24">
-        <v>4.574509799763803e-05</v>
+        <v>4.5752712847904001e-05</v>
       </c>
       <c r="AB24">
-        <v>0.00018970132034961318</v>
+        <v>0.00018971010605313291</v>
       </c>
       <c r="AC24">
-        <v>4.8847752252468082e-05</v>
+        <v>4.8850147306897605e-05</v>
       </c>
       <c r="AD24">
-        <v>7.2867634338611483e-05</v>
+        <v>7.2796011310754822e-05</v>
       </c>
       <c r="AE24">
-        <v>0.00014539768845387791</v>
+        <v>0.00014541651187611679</v>
       </c>
       <c r="AF24">
-        <v>0.00021084669154244169</v>
+        <v>0.00021085587420886527</v>
       </c>
       <c r="AG24">
-        <v>0.0001488490302762206</v>
+        <v>0.00014886355641468603</v>
       </c>
       <c r="AH24">
-        <v>1.463197315066788e-05</v>
+        <v>1.4633362057436353e-05</v>
       </c>
       <c r="AI24">
-        <v>-0.00017669991184134093</v>
+        <v>-0.00017670710869012625</v>
       </c>
       <c r="AJ24">
-        <v>-0.000116603795565878</v>
+        <v>-0.00011658928202047648</v>
       </c>
       <c r="AK24">
-        <v>-0.0049900702767961286</v>
+        <v>-0.0049899018761898149</v>
       </c>
     </row>
     <row r="25">
@@ -3113,112 +3113,112 @@
         <v>49</v>
       </c>
       <c r="B25">
-        <v>0.014243488188918501</v>
+        <v>0.014239308773784565</v>
       </c>
       <c r="C25">
-        <v>-1.3078918440939959e-06</v>
+        <v>-1.3032057519368863e-06</v>
       </c>
       <c r="D25">
-        <v>-1.0064813404940604e-06</v>
+        <v>-1.005130469697827e-06</v>
       </c>
       <c r="E25">
-        <v>6.8879643726840316e-09</v>
+        <v>6.8760027504605691e-09</v>
       </c>
       <c r="F25">
-        <v>-2.9385190883117859e-05</v>
+        <v>-2.9380921477202878e-05</v>
       </c>
       <c r="G25">
-        <v>-2.9287183641041694e-05</v>
+        <v>-2.9295868871452031e-05</v>
       </c>
       <c r="H25">
-        <v>-8.9263416154587796e-06</v>
+        <v>-8.9246904624852345e-06</v>
       </c>
       <c r="I25">
-        <v>-4.5222535412690761e-05</v>
+        <v>-4.522272122790604e-05</v>
       </c>
       <c r="J25">
-        <v>-2.401288961297145e-05</v>
+        <v>-2.4016397220903199e-05</v>
       </c>
       <c r="K25">
-        <v>-3.8096571245856515e-05</v>
+        <v>-3.8092029488725583e-05</v>
       </c>
       <c r="L25">
-        <v>-3.9085044861963709e-05</v>
+        <v>-3.9087122093091754e-05</v>
       </c>
       <c r="M25">
-        <v>-0.00016793227152801755</v>
+        <v>-0.00016792801303399941</v>
       </c>
       <c r="N25">
-        <v>-0.00014092467059130019</v>
+        <v>-0.00014091800407097161</v>
       </c>
       <c r="O25">
-        <v>1.1140767805429049e-05</v>
+        <v>1.1142088365938665e-05</v>
       </c>
       <c r="P25">
-        <v>-8.7107838624458297e-06</v>
+        <v>-8.7127622993345505e-06</v>
       </c>
       <c r="Q25">
-        <v>-8.1373156770862186e-06</v>
+        <v>-8.1337547318097298e-06</v>
       </c>
       <c r="R25">
-        <v>-2.6947999711512017e-05</v>
+        <v>-2.6951325317340401e-05</v>
       </c>
       <c r="S25">
-        <v>-1.3605355056044755e-05</v>
+        <v>-1.3604001049854248e-05</v>
       </c>
       <c r="T25">
-        <v>-1.5527168124512727e-05</v>
+        <v>-1.5519833150295023e-05</v>
       </c>
       <c r="U25">
-        <v>-1.4997094774375731e-05</v>
+        <v>-1.4993509390343136e-05</v>
       </c>
       <c r="V25">
-        <v>-9.7750833826045432e-05</v>
+        <v>-9.7735378788608415e-05</v>
       </c>
       <c r="W25">
-        <v>-0.00020362892724945386</v>
+        <v>-0.00020362293739623115</v>
       </c>
       <c r="X25">
-        <v>-0.00020800310355676004</v>
+        <v>-0.0002080005552566935</v>
       </c>
       <c r="Y25">
-        <v>-0.00024475866744502202</v>
+        <v>-0.0002447574363151083</v>
       </c>
       <c r="Z25">
-        <v>3.5730585604776868e-05</v>
+        <v>3.572969261520134e-05</v>
       </c>
       <c r="AA25">
-        <v>-4.6240447318630316e-06</v>
+        <v>-4.6243367574907948e-06</v>
       </c>
       <c r="AB25">
-        <v>-1.634198135269149e-05</v>
+        <v>-1.6342250942130411e-05</v>
       </c>
       <c r="AC25">
-        <v>-1.5100108534370755e-05</v>
+        <v>-1.5099728936074261e-05</v>
       </c>
       <c r="AD25">
-        <v>-8.9446291190543246e-06</v>
+        <v>-8.9277565666271954e-06</v>
       </c>
       <c r="AE25">
-        <v>-1.3548074859630132e-05</v>
+        <v>-1.3549173748914008e-05</v>
       </c>
       <c r="AF25">
-        <v>-9.7793678748603509e-06</v>
+        <v>-9.7813632305206431e-06</v>
       </c>
       <c r="AG25">
-        <v>-1.7716850429115815e-05</v>
+        <v>-1.7717223407969519e-05</v>
       </c>
       <c r="AH25">
-        <v>2.0841021875454969e-06</v>
+        <v>2.0838513120365381e-06</v>
       </c>
       <c r="AI25">
-        <v>3.0132228729184073e-05</v>
+        <v>3.0127887298176141e-05</v>
       </c>
       <c r="AJ25">
-        <v>-5.5393497825243719e-06</v>
+        <v>-5.5428478897691602e-06</v>
       </c>
       <c r="AK25">
-        <v>0.00021096325430880713</v>
+        <v>0.00021091908774728004</v>
       </c>
     </row>
     <row r="26">
@@ -3226,112 +3226,112 @@
         <v>50</v>
       </c>
       <c r="B26">
-        <v>3.8787117593871985</v>
+        <v>3.8787235130671189</v>
       </c>
       <c r="C26">
-        <v>-3.7839195947584752e-05</v>
+        <v>-3.7841443168210034e-05</v>
       </c>
       <c r="D26">
-        <v>-2.125484830955518e-06</v>
+        <v>-2.1263051652331842e-06</v>
       </c>
       <c r="E26">
-        <v>6.4156154457390736e-09</v>
+        <v>6.422796339319445e-09</v>
       </c>
       <c r="F26">
-        <v>0.00035993203788987124</v>
+        <v>0.00035992754909626565</v>
       </c>
       <c r="G26">
-        <v>-5.4327580794293583e-05</v>
+        <v>-5.4323734239563628e-05</v>
       </c>
       <c r="H26">
-        <v>-4.9650473414267302e-05</v>
+        <v>-4.9655501839485723e-05</v>
       </c>
       <c r="I26">
-        <v>8.033842417980012e-05</v>
+        <v>8.0340995526613057e-05</v>
       </c>
       <c r="J26">
-        <v>-1.9660996630426148e-05</v>
+        <v>-1.9662175965197534e-05</v>
       </c>
       <c r="K26">
-        <v>-9.5343896151411445e-05</v>
+        <v>-9.5348212475492803e-05</v>
       </c>
       <c r="L26">
-        <v>-4.1283644658945127e-05</v>
+        <v>-4.1284254635589463e-05</v>
       </c>
       <c r="M26">
-        <v>2.3583005607361453e-05</v>
+        <v>2.3582936305882834e-05</v>
       </c>
       <c r="N26">
-        <v>6.7131760883186919e-05</v>
+        <v>6.7132284963779482e-05</v>
       </c>
       <c r="O26">
-        <v>-3.6248053603790307e-07</v>
+        <v>-3.6176184143933189e-07</v>
       </c>
       <c r="P26">
-        <v>3.1801073212105326e-06</v>
+        <v>3.181593351948706e-06</v>
       </c>
       <c r="Q26">
-        <v>1.7333481452116894e-05</v>
+        <v>1.7334835094153639e-05</v>
       </c>
       <c r="R26">
-        <v>-0.00012141883029646405</v>
+        <v>-0.00012142235918183677</v>
       </c>
       <c r="S26">
-        <v>-2.7501105139336344e-05</v>
+        <v>-2.7502158129465463e-05</v>
       </c>
       <c r="T26">
-        <v>-4.5180700695797308e-05</v>
+        <v>-4.5184850812885835e-05</v>
       </c>
       <c r="U26">
-        <v>-2.1732523540068721e-05</v>
+        <v>-2.1733090131611501e-05</v>
       </c>
       <c r="V26">
-        <v>8.4349652446997418e-06</v>
+        <v>8.430203632331238e-06</v>
       </c>
       <c r="W26">
-        <v>3.5513179620983056e-05</v>
+        <v>3.5515039328621321e-05</v>
       </c>
       <c r="X26">
-        <v>3.8051693381254098e-05</v>
+        <v>3.8055925120422164e-05</v>
       </c>
       <c r="Y26">
-        <v>4.574509799763803e-05</v>
+        <v>4.5752712847904001e-05</v>
       </c>
       <c r="Z26">
-        <v>-4.6240447318630316e-06</v>
+        <v>-4.6243367574907948e-06</v>
       </c>
       <c r="AA26">
-        <v>0.00046983571436057372</v>
+        <v>0.0004698381381528199</v>
       </c>
       <c r="AB26">
-        <v>-9.5160493587699552e-06</v>
+        <v>-9.5157637410631557e-06</v>
       </c>
       <c r="AC26">
-        <v>2.7938300041489622e-05</v>
+        <v>2.7938140835760225e-05</v>
       </c>
       <c r="AD26">
-        <v>-8.4643356937314581e-06</v>
+        <v>-8.4700965027039316e-06</v>
       </c>
       <c r="AE26">
-        <v>-2.3683155429950821e-06</v>
+        <v>-2.3695392562908703e-06</v>
       </c>
       <c r="AF26">
-        <v>9.403123090444973e-06</v>
+        <v>9.4052218660299923e-06</v>
       </c>
       <c r="AG26">
-        <v>-4.6754872345085924e-05</v>
+        <v>-4.6754991388016934e-05</v>
       </c>
       <c r="AH26">
-        <v>3.238703458800489e-07</v>
+        <v>3.237116744580379e-07</v>
       </c>
       <c r="AI26">
-        <v>-0.00010533555266603045</v>
+        <v>-0.00010533869536918442</v>
       </c>
       <c r="AJ26">
-        <v>3.1082918101691153e-05</v>
+        <v>3.1083917251401773e-05</v>
       </c>
       <c r="AK26">
-        <v>-0.00011010593494362019</v>
+        <v>-0.0001100793555372636</v>
       </c>
     </row>
     <row r="27">
@@ -3339,112 +3339,112 @@
         <v>51</v>
       </c>
       <c r="B27">
-        <v>0.077786472751133207</v>
+        <v>0.077787627733398201</v>
       </c>
       <c r="C27">
-        <v>-8.321893980225406e-05</v>
+        <v>-8.3220926574514197e-05</v>
       </c>
       <c r="D27">
-        <v>-4.9015448977291778e-06</v>
+        <v>-4.9021878271057989e-06</v>
       </c>
       <c r="E27">
-        <v>4.9284408428887805e-08</v>
+        <v>4.9290414321812228e-08</v>
       </c>
       <c r="F27">
-        <v>0.00017088454794393572</v>
+        <v>0.00017089336480977861</v>
       </c>
       <c r="G27">
-        <v>0.00010551725724153695</v>
+        <v>0.00010552169516705925</v>
       </c>
       <c r="H27">
-        <v>0.00010618075421804023</v>
+        <v>0.00010618260158602776</v>
       </c>
       <c r="I27">
-        <v>0.00019838439079984259</v>
+        <v>0.00019839081252925948</v>
       </c>
       <c r="J27">
-        <v>0.00023229232820717871</v>
+        <v>0.00023229934460498262</v>
       </c>
       <c r="K27">
-        <v>4.9043072589556461e-05</v>
+        <v>4.9044470238045592e-05</v>
       </c>
       <c r="L27">
-        <v>0.0001531971084146105</v>
+        <v>0.00015320647609406166</v>
       </c>
       <c r="M27">
-        <v>0.00017708004432941951</v>
+        <v>0.0001770860584250889</v>
       </c>
       <c r="N27">
-        <v>5.0295069978107624e-05</v>
+        <v>5.0297396159034759e-05</v>
       </c>
       <c r="O27">
-        <v>5.7766035196025458e-06</v>
+        <v>5.7726246558616754e-06</v>
       </c>
       <c r="P27">
-        <v>4.0227291794956463e-05</v>
+        <v>4.0226663270417082e-05</v>
       </c>
       <c r="Q27">
-        <v>8.0576268154295707e-05</v>
+        <v>8.0581684497851988e-05</v>
       </c>
       <c r="R27">
-        <v>0.00015721557200828237</v>
+        <v>0.00015721225935875181</v>
       </c>
       <c r="S27">
-        <v>0.00043790842602804692</v>
+        <v>0.00043792243425426741</v>
       </c>
       <c r="T27">
-        <v>0.00047454632816830347</v>
+        <v>0.00047455826863080416</v>
       </c>
       <c r="U27">
-        <v>0.00055390881857341357</v>
+        <v>0.00055392495136093352</v>
       </c>
       <c r="V27">
-        <v>6.2213354989718917e-05</v>
+        <v>6.2215016927632811e-05</v>
       </c>
       <c r="W27">
-        <v>4.9100618034042184e-05</v>
+        <v>4.9105307281538564e-05</v>
       </c>
       <c r="X27">
-        <v>0.00010993476809554453</v>
+        <v>0.000109941145362372</v>
       </c>
       <c r="Y27">
-        <v>0.00018970132034961318</v>
+        <v>0.00018971010605313291</v>
       </c>
       <c r="Z27">
-        <v>-1.634198135269149e-05</v>
+        <v>-1.6342250942130411e-05</v>
       </c>
       <c r="AA27">
-        <v>-9.5160493587699552e-06</v>
+        <v>-9.5157637410631557e-06</v>
       </c>
       <c r="AB27">
-        <v>0.0031190950742089078</v>
+        <v>0.0031191578122552349</v>
       </c>
       <c r="AC27">
-        <v>0.0024615016733367918</v>
+        <v>0.0024615492144343292</v>
       </c>
       <c r="AD27">
-        <v>0.0024487960514349852</v>
+        <v>0.0024488437454076809</v>
       </c>
       <c r="AE27">
-        <v>0.0024652553304338838</v>
+        <v>0.0024653027195969237</v>
       </c>
       <c r="AF27">
-        <v>0.0024650369759858051</v>
+        <v>0.0024650856877057167</v>
       </c>
       <c r="AG27">
-        <v>0.0024490828286697123</v>
+        <v>0.0024491287077466947</v>
       </c>
       <c r="AH27">
-        <v>4.63145584620678e-06</v>
+        <v>4.6315409095330833e-06</v>
       </c>
       <c r="AI27">
-        <v>-0.0001066261803923255</v>
+        <v>-0.00010663134530288594</v>
       </c>
       <c r="AJ27">
-        <v>-7.4616263061845966e-05</v>
+        <v>-7.4617209358636568e-05</v>
       </c>
       <c r="AK27">
-        <v>-0.0030390993999282541</v>
+        <v>-0.0030391536449426407</v>
       </c>
     </row>
     <row r="28">
@@ -3452,112 +3452,112 @@
         <v>52</v>
       </c>
       <c r="B28">
-        <v>0.10214149443780199</v>
+        <v>0.10214527809118833</v>
       </c>
       <c r="C28">
-        <v>-8.9065044076384702e-05</v>
+        <v>-8.906949029818085e-05</v>
       </c>
       <c r="D28">
-        <v>-1.940549386887625e-07</v>
+        <v>-1.9514781448637993e-07</v>
       </c>
       <c r="E28">
-        <v>7.231931649447275e-09</v>
+        <v>7.2420227277417834e-09</v>
       </c>
       <c r="F28">
-        <v>0.0010396525872968484</v>
+        <v>0.0010396622006849535</v>
       </c>
       <c r="G28">
-        <v>8.4362077400489816e-05</v>
+        <v>8.4368794715609105e-05</v>
       </c>
       <c r="H28">
-        <v>-2.5267151641799202e-06</v>
+        <v>-2.5287817091834003e-06</v>
       </c>
       <c r="I28">
-        <v>0.00011279309646676267</v>
+        <v>0.00011279705654526346</v>
       </c>
       <c r="J28">
-        <v>0.00015046153509580421</v>
+        <v>0.00015046715161416485</v>
       </c>
       <c r="K28">
-        <v>3.0489284273914168e-05</v>
+        <v>3.0487672599616676e-05</v>
       </c>
       <c r="L28">
-        <v>0.0001270410718614127</v>
+        <v>0.00012705031902480557</v>
       </c>
       <c r="M28">
-        <v>0.00012066406113529641</v>
+        <v>0.00012066737429660291</v>
       </c>
       <c r="N28">
-        <v>-3.4868050018369186e-05</v>
+        <v>-3.4870515197211495e-05</v>
       </c>
       <c r="O28">
-        <v>-4.2566943769912439e-05</v>
+        <v>-4.2572121139827388e-05</v>
       </c>
       <c r="P28">
-        <v>2.1457238077300504e-05</v>
+        <v>2.1456531395724183e-05</v>
       </c>
       <c r="Q28">
-        <v>8.3804712631863065e-05</v>
+        <v>8.3807967486456704e-05</v>
       </c>
       <c r="R28">
-        <v>0.00022045477681207574</v>
+        <v>0.00022045493845321632</v>
       </c>
       <c r="S28">
-        <v>0.00044951602127424849</v>
+        <v>0.00044953031904174882</v>
       </c>
       <c r="T28">
-        <v>0.00045514427693892773</v>
+        <v>0.00045515397205222151</v>
       </c>
       <c r="U28">
-        <v>0.00050831370349618387</v>
+        <v>0.00050832725165993794</v>
       </c>
       <c r="V28">
-        <v>5.5517202497956382e-05</v>
+        <v>5.551159091172304e-05</v>
       </c>
       <c r="W28">
-        <v>-4.7253264226984615e-06</v>
+        <v>-4.7251357243268712e-06</v>
       </c>
       <c r="X28">
-        <v>2.3097686720350424e-05</v>
+        <v>2.3099686328289723e-05</v>
       </c>
       <c r="Y28">
-        <v>4.8847752252468082e-05</v>
+        <v>4.8850147306897605e-05</v>
       </c>
       <c r="Z28">
-        <v>-1.5100108534370755e-05</v>
+        <v>-1.5099728936074261e-05</v>
       </c>
       <c r="AA28">
-        <v>2.7938300041489622e-05</v>
+        <v>2.7938140835760225e-05</v>
       </c>
       <c r="AB28">
-        <v>0.0024615016733367918</v>
+        <v>0.0024615492144343292</v>
       </c>
       <c r="AC28">
-        <v>0.003161656531438213</v>
+        <v>0.0031617186933199136</v>
       </c>
       <c r="AD28">
-        <v>0.0024431055649184572</v>
+        <v>0.0024431470469142647</v>
       </c>
       <c r="AE28">
-        <v>0.0024517394340161985</v>
+        <v>0.002451786944779519</v>
       </c>
       <c r="AF28">
-        <v>0.0024560753636708454</v>
+        <v>0.002456123938966397</v>
       </c>
       <c r="AG28">
-        <v>0.0024444052553283268</v>
+        <v>0.0024444506879656787</v>
       </c>
       <c r="AH28">
-        <v>5.0668050914396705e-06</v>
+        <v>5.06704063144684e-06</v>
       </c>
       <c r="AI28">
-        <v>-0.0001036889974872098</v>
+        <v>-0.00010368989030267979</v>
       </c>
       <c r="AJ28">
-        <v>-1.6168897166982197e-05</v>
+        <v>-1.616832719370789e-05</v>
       </c>
       <c r="AK28">
-        <v>-0.0030386154645466062</v>
+        <v>-0.0030386505253575426</v>
       </c>
     </row>
     <row r="29">
@@ -3565,112 +3565,112 @@
         <v>53</v>
       </c>
       <c r="B29">
-        <v>-0.056567755319741529</v>
+        <v>-0.056508206108460045</v>
       </c>
       <c r="C29">
-        <v>-9.2779629768422294e-05</v>
+        <v>-9.2826737795602955e-05</v>
       </c>
       <c r="D29">
-        <v>6.2856319531107434e-07</v>
+        <v>6.1513538738070233e-07</v>
       </c>
       <c r="E29">
-        <v>-2.8375157172594823e-09</v>
+        <v>-2.7174720676790462e-09</v>
       </c>
       <c r="F29">
-        <v>0.0007230071151432039</v>
+        <v>0.00072293055582634642</v>
       </c>
       <c r="G29">
-        <v>0.00010126219746218242</v>
+        <v>0.00010134094841438446</v>
       </c>
       <c r="H29">
-        <v>3.619505802813605e-05</v>
+        <v>3.6201780308259225e-05</v>
       </c>
       <c r="I29">
-        <v>0.00012740170804045165</v>
+        <v>0.00012739588607572666</v>
       </c>
       <c r="J29">
-        <v>0.00017379390005154284</v>
+        <v>0.00017382373752403732</v>
       </c>
       <c r="K29">
-        <v>5.0030039650950011e-05</v>
+        <v>4.9970620505085557e-05</v>
       </c>
       <c r="L29">
-        <v>7.0728087837666547e-05</v>
+        <v>7.0737092000580518e-05</v>
       </c>
       <c r="M29">
-        <v>9.3980802410449302e-05</v>
+        <v>9.3938644631497929e-05</v>
       </c>
       <c r="N29">
-        <v>-1.1210550792164261e-05</v>
+        <v>-1.1278162757271618e-05</v>
       </c>
       <c r="O29">
-        <v>3.0942762292997012e-05</v>
+        <v>3.0913068517185124e-05</v>
       </c>
       <c r="P29">
-        <v>1.1421144050133758e-05</v>
+        <v>1.1429507838074302e-05</v>
       </c>
       <c r="Q29">
-        <v>0.00010136890377841057</v>
+        <v>0.00010132380066673349</v>
       </c>
       <c r="R29">
-        <v>0.00021136950546718925</v>
+        <v>0.00021139810342213176</v>
       </c>
       <c r="S29">
-        <v>0.00044366143414337981</v>
+        <v>0.00044366328659484807</v>
       </c>
       <c r="T29">
-        <v>0.00044584842290995314</v>
+        <v>0.00044579472625172131</v>
       </c>
       <c r="U29">
-        <v>0.00050853877760929228</v>
+        <v>0.00050851898057002048</v>
       </c>
       <c r="V29">
-        <v>2.5586899086530563e-05</v>
+        <v>2.5427207967291783e-05</v>
       </c>
       <c r="W29">
-        <v>-1.8520172109935196e-05</v>
+        <v>-1.8605951851966268e-05</v>
       </c>
       <c r="X29">
-        <v>5.2452107729939693e-05</v>
+        <v>5.238172533216694e-05</v>
       </c>
       <c r="Y29">
-        <v>7.2867634338611483e-05</v>
+        <v>7.2796011310754822e-05</v>
       </c>
       <c r="Z29">
-        <v>-8.9446291190543246e-06</v>
+        <v>-8.9277565666271954e-06</v>
       </c>
       <c r="AA29">
-        <v>-8.4643356937314581e-06</v>
+        <v>-8.4700965027039316e-06</v>
       </c>
       <c r="AB29">
-        <v>0.0024487960514349852</v>
+        <v>0.0024488437454076809</v>
       </c>
       <c r="AC29">
-        <v>0.0024431055649184572</v>
+        <v>0.0024431470469142647</v>
       </c>
       <c r="AD29">
-        <v>0.0029521982810279635</v>
+        <v>0.0029521486895823226</v>
       </c>
       <c r="AE29">
-        <v>0.0024386697782569581</v>
+        <v>0.0024387267736864955</v>
       </c>
       <c r="AF29">
-        <v>0.0024389224885327222</v>
+        <v>0.0024389757691829321</v>
       </c>
       <c r="AG29">
-        <v>0.0024378746947479272</v>
+        <v>0.0024379177749221988</v>
       </c>
       <c r="AH29">
-        <v>1.9566230662405214e-06</v>
+        <v>1.9600508353146852e-06</v>
       </c>
       <c r="AI29">
-        <v>-8.5283316818115813e-05</v>
+        <v>-8.5239957407083709e-05</v>
       </c>
       <c r="AJ29">
-        <v>-0.00010136400901270242</v>
+        <v>-0.00010133362225287065</v>
       </c>
       <c r="AK29">
-        <v>-0.0029958964299309143</v>
+        <v>-0.0029955110811089739</v>
       </c>
     </row>
     <row r="30">
@@ -3678,112 +3678,112 @@
         <v>54</v>
       </c>
       <c r="B30">
-        <v>0.043340245697031377</v>
+        <v>0.043341630929584853</v>
       </c>
       <c r="C30">
-        <v>-0.00010770340055663942</v>
+        <v>-0.00010770278311922061</v>
       </c>
       <c r="D30">
-        <v>-1.4176370058927804e-06</v>
+        <v>-1.4172083583867813e-06</v>
       </c>
       <c r="E30">
-        <v>2.3278842565938673e-08</v>
+        <v>2.3275186937323524e-08</v>
       </c>
       <c r="F30">
-        <v>0.00014512202767931839</v>
+        <v>0.00014512559808635612</v>
       </c>
       <c r="G30">
-        <v>3.1849970326139994e-05</v>
+        <v>3.1844229894414759e-05</v>
       </c>
       <c r="H30">
-        <v>-3.4556101347137319e-05</v>
+        <v>-3.4557675597660662e-05</v>
       </c>
       <c r="I30">
-        <v>6.2410531796767152e-05</v>
+        <v>6.2411795254526141e-05</v>
       </c>
       <c r="J30">
-        <v>9.8721498721418078e-05</v>
+        <v>9.8726304086698682e-05</v>
       </c>
       <c r="K30">
-        <v>-1.991636919297787e-05</v>
+        <v>-1.9916388888269491e-05</v>
       </c>
       <c r="L30">
-        <v>7.9753303428038453e-05</v>
+        <v>7.975825688759635e-05</v>
       </c>
       <c r="M30">
-        <v>0.00016404978519658688</v>
+        <v>0.00016406673375481216</v>
       </c>
       <c r="N30">
-        <v>2.8728365879227523e-05</v>
+        <v>2.8744723553628723e-05</v>
       </c>
       <c r="O30">
-        <v>-2.4394353489169262e-05</v>
+        <v>-2.4403755522718325e-05</v>
       </c>
       <c r="P30">
-        <v>2.3670129780542536e-05</v>
+        <v>2.3669353205774937e-05</v>
       </c>
       <c r="Q30">
-        <v>1.3748227545033872e-05</v>
+        <v>1.3751992204978332e-05</v>
       </c>
       <c r="R30">
-        <v>0.00015404301536331693</v>
+        <v>0.00015404135002411445</v>
       </c>
       <c r="S30">
-        <v>0.0003685897313903232</v>
+        <v>0.00036860541209909198</v>
       </c>
       <c r="T30">
-        <v>0.00037201559848097469</v>
+        <v>0.00037203166613365528</v>
       </c>
       <c r="U30">
-        <v>0.00044165846089542701</v>
+        <v>0.00044167620340231171</v>
       </c>
       <c r="V30">
-        <v>3.5358664222996574e-05</v>
+        <v>3.5370838212990833e-05</v>
       </c>
       <c r="W30">
-        <v>2.2287889056261077e-05</v>
+        <v>2.2304809881174177e-05</v>
       </c>
       <c r="X30">
-        <v>9.3578681102805643e-05</v>
+        <v>9.3594557088700053e-05</v>
       </c>
       <c r="Y30">
-        <v>0.00014539768845387791</v>
+        <v>0.00014541651187611679</v>
       </c>
       <c r="Z30">
-        <v>-1.3548074859630132e-05</v>
+        <v>-1.3549173748914008e-05</v>
       </c>
       <c r="AA30">
-        <v>-2.3683155429950821e-06</v>
+        <v>-2.3695392562908703e-06</v>
       </c>
       <c r="AB30">
-        <v>0.0024652553304338838</v>
+        <v>0.0024653027195969237</v>
       </c>
       <c r="AC30">
-        <v>0.0024517394340161985</v>
+        <v>0.002451786944779519</v>
       </c>
       <c r="AD30">
-        <v>0.0024386697782569581</v>
+        <v>0.0024387267736864955</v>
       </c>
       <c r="AE30">
-        <v>0.0030162173493615795</v>
+        <v>0.0030162686506356477</v>
       </c>
       <c r="AF30">
-        <v>0.0024576158030740519</v>
+        <v>0.0024576626423326664</v>
       </c>
       <c r="AG30">
-        <v>0.00245684783073269</v>
+        <v>0.0024568943830358997</v>
       </c>
       <c r="AH30">
-        <v>5.1926736026641941e-06</v>
+        <v>5.1927534039564299e-06</v>
       </c>
       <c r="AI30">
-        <v>-8.9424393463073595e-05</v>
+        <v>-8.9430173679340159e-05</v>
       </c>
       <c r="AJ30">
-        <v>-6.4097213237671925e-05</v>
+        <v>-6.4100404898649859e-05</v>
       </c>
       <c r="AK30">
-        <v>-0.0029048864581103276</v>
+        <v>-0.0029049788151290796</v>
       </c>
     </row>
     <row r="31">
@@ -3791,112 +3791,112 @@
         <v>55</v>
       </c>
       <c r="B31">
-        <v>-0.08831930778457138</v>
+        <v>-0.088320160860836272</v>
       </c>
       <c r="C31">
-        <v>-6.8490860444218293e-05</v>
+        <v>-6.848526538045293e-05</v>
       </c>
       <c r="D31">
-        <v>-5.3264824558947837e-07</v>
+        <v>-5.3222697295533773e-07</v>
       </c>
       <c r="E31">
-        <v>4.8747638591450779e-09</v>
+        <v>4.869925171155404e-09</v>
       </c>
       <c r="F31">
-        <v>0.0001400488397701584</v>
+        <v>0.00014004760693710243</v>
       </c>
       <c r="G31">
-        <v>6.3114505588942043e-05</v>
+        <v>6.3109637921800286e-05</v>
       </c>
       <c r="H31">
-        <v>-2.8031077380931662e-05</v>
+        <v>-2.8034532334489664e-05</v>
       </c>
       <c r="I31">
-        <v>3.0201280062958167e-05</v>
+        <v>3.0199903768108759e-05</v>
       </c>
       <c r="J31">
-        <v>0.00010977055225061365</v>
+        <v>0.00010976484539881637</v>
       </c>
       <c r="K31">
-        <v>2.3806793720527748e-05</v>
+        <v>2.3812120986320905e-05</v>
       </c>
       <c r="L31">
-        <v>0.00016116144006006049</v>
+        <v>0.00016117107222544724</v>
       </c>
       <c r="M31">
-        <v>0.00035967662001975956</v>
+        <v>0.00035967883933484685</v>
       </c>
       <c r="N31">
-        <v>0.00012682358669003778</v>
+        <v>0.00012682828905954903</v>
       </c>
       <c r="O31">
-        <v>-7.0865269281933482e-05</v>
+        <v>-7.0864633063615599e-05</v>
       </c>
       <c r="P31">
-        <v>1.8140719347580349e-05</v>
+        <v>1.8138429968336334e-05</v>
       </c>
       <c r="Q31">
-        <v>6.772115567816514e-05</v>
+        <v>6.7733099180269083e-05</v>
       </c>
       <c r="R31">
-        <v>0.00026288990610466535</v>
+        <v>0.00026289074750658766</v>
       </c>
       <c r="S31">
-        <v>0.00045106378006006301</v>
+        <v>0.00045108047264597604</v>
       </c>
       <c r="T31">
-        <v>0.00044704731658186023</v>
+        <v>0.0004470645319115639</v>
       </c>
       <c r="U31">
-        <v>0.00054347568782368004</v>
+        <v>0.00054349859132573459</v>
       </c>
       <c r="V31">
-        <v>2.1860475353110699e-05</v>
+        <v>2.186656129644343e-05</v>
       </c>
       <c r="W31">
-        <v>0.00011836176834439726</v>
+        <v>0.00011837024832619996</v>
       </c>
       <c r="X31">
-        <v>0.00020359729260564232</v>
+        <v>0.00020361227965020592</v>
       </c>
       <c r="Y31">
-        <v>0.00021084669154244169</v>
+        <v>0.00021085587420886527</v>
       </c>
       <c r="Z31">
-        <v>-9.7793678748603509e-06</v>
+        <v>-9.7813632305206431e-06</v>
       </c>
       <c r="AA31">
-        <v>9.403123090444973e-06</v>
+        <v>9.4052218660299923e-06</v>
       </c>
       <c r="AB31">
-        <v>0.0024650369759858051</v>
+        <v>0.0024650856877057167</v>
       </c>
       <c r="AC31">
-        <v>0.0024560753636708454</v>
+        <v>0.002456123938966397</v>
       </c>
       <c r="AD31">
-        <v>0.0024389224885327222</v>
+        <v>0.0024389757691829321</v>
       </c>
       <c r="AE31">
-        <v>0.0024576158030740519</v>
+        <v>0.0024576626423326664</v>
       </c>
       <c r="AF31">
-        <v>0.0028360081868872853</v>
+        <v>0.0028360734200607602</v>
       </c>
       <c r="AG31">
-        <v>0.0024555236094775004</v>
+        <v>0.002455569014236571</v>
       </c>
       <c r="AH31">
-        <v>1.1140113677038125e-06</v>
+        <v>1.112915820024626e-06</v>
       </c>
       <c r="AI31">
-        <v>4.4511831371199864e-05</v>
+        <v>4.4512379639054592e-05</v>
       </c>
       <c r="AJ31">
-        <v>-3.4832369199632287e-05</v>
+        <v>-3.4834226891073935e-05</v>
       </c>
       <c r="AK31">
-        <v>-0.003118613227807817</v>
+        <v>-0.0031186835463261585</v>
       </c>
     </row>
     <row r="32">
@@ -3904,112 +3904,112 @@
         <v>56</v>
       </c>
       <c r="B32">
-        <v>0.065430070892483982</v>
+        <v>0.065431214866320711</v>
       </c>
       <c r="C32">
-        <v>2.2238731019172593e-06</v>
+        <v>2.2275491929254512e-06</v>
       </c>
       <c r="D32">
-        <v>-3.0057981496875799e-06</v>
+        <v>-3.0054686833840975e-06</v>
       </c>
       <c r="E32">
-        <v>4.6015714018561087e-08</v>
+        <v>4.6013643849496761e-08</v>
       </c>
       <c r="F32">
-        <v>2.1573923662473755e-05</v>
+        <v>2.1591697983216096e-05</v>
       </c>
       <c r="G32">
-        <v>-1.6873910236692917e-05</v>
+        <v>-1.6876315326658318e-05</v>
       </c>
       <c r="H32">
-        <v>-6.9766609789192037e-05</v>
+        <v>-6.975746189792013e-05</v>
       </c>
       <c r="I32">
-        <v>-4.7528422924719764e-05</v>
+        <v>-4.7522259414865033e-05</v>
       </c>
       <c r="J32">
-        <v>1.6268992807537842e-05</v>
+        <v>1.6276962793432672e-05</v>
       </c>
       <c r="K32">
-        <v>3.5788346830092292e-05</v>
+        <v>3.5794081858431996e-05</v>
       </c>
       <c r="L32">
-        <v>4.7928043876269757e-05</v>
+        <v>4.7937875782734567e-05</v>
       </c>
       <c r="M32">
-        <v>0.00021697857664566172</v>
+        <v>0.00021698156621521262</v>
       </c>
       <c r="N32">
-        <v>-8.0198346687011151e-05</v>
+        <v>-8.0194557288379138e-05</v>
       </c>
       <c r="O32">
-        <v>-0.0001419765316418533</v>
+        <v>-0.00014196893536984535</v>
       </c>
       <c r="P32">
-        <v>-1.8293545756455215e-05</v>
+        <v>-1.8294509765440727e-05</v>
       </c>
       <c r="Q32">
-        <v>6.9525296452413042e-07</v>
+        <v>6.9540725960201121e-07</v>
       </c>
       <c r="R32">
-        <v>0.00042198338766060817</v>
+        <v>0.0004219850881182784</v>
       </c>
       <c r="S32">
-        <v>0.00040656128482668389</v>
+        <v>0.00040657107945525444</v>
       </c>
       <c r="T32">
-        <v>0.00046031712819683516</v>
+        <v>0.00046032666736534544</v>
       </c>
       <c r="U32">
-        <v>0.00037320853590305629</v>
+        <v>0.00037321764746299301</v>
       </c>
       <c r="V32">
-        <v>0.00011342840730378033</v>
+        <v>0.00011343594944440005</v>
       </c>
       <c r="W32">
-        <v>8.2306099945634052e-05</v>
+        <v>8.2314725543089447e-05</v>
       </c>
       <c r="X32">
-        <v>0.00021553150864596707</v>
+        <v>0.00021554429213088209</v>
       </c>
       <c r="Y32">
-        <v>0.0001488490302762206</v>
+        <v>0.00014886355641468603</v>
       </c>
       <c r="Z32">
-        <v>-1.7716850429115815e-05</v>
+        <v>-1.7717223407969519e-05</v>
       </c>
       <c r="AA32">
-        <v>-4.6754872345085924e-05</v>
+        <v>-4.6754991388016934e-05</v>
       </c>
       <c r="AB32">
-        <v>0.0024490828286697123</v>
+        <v>0.0024491287077466947</v>
       </c>
       <c r="AC32">
-        <v>0.0024444052553283268</v>
+        <v>0.0024444506879656787</v>
       </c>
       <c r="AD32">
-        <v>0.0024378746947479272</v>
+        <v>0.0024379177749221988</v>
       </c>
       <c r="AE32">
-        <v>0.00245684783073269</v>
+        <v>0.0024568943830358997</v>
       </c>
       <c r="AF32">
-        <v>0.0024555236094775004</v>
+        <v>0.002455569014236571</v>
       </c>
       <c r="AG32">
-        <v>0.0030746134974204515</v>
+        <v>0.0030746667522620849</v>
       </c>
       <c r="AH32">
-        <v>2.6585612763727851e-06</v>
+        <v>2.6586276749018822e-06</v>
       </c>
       <c r="AI32">
-        <v>-1.8209457757887085e-05</v>
+        <v>-1.8214574711171352e-05</v>
       </c>
       <c r="AJ32">
-        <v>-9.8875690219375799e-05</v>
+        <v>-9.8878405566171735e-05</v>
       </c>
       <c r="AK32">
-        <v>-0.0029429015216106049</v>
+        <v>-0.0029429837293659545</v>
       </c>
     </row>
     <row r="33">
@@ -4017,112 +4017,112 @@
         <v>57</v>
       </c>
       <c r="B33">
-        <v>-0.00028517854839236106</v>
+        <v>-0.00028612342360396305</v>
       </c>
       <c r="C33">
-        <v>-2.7857809298481919e-06</v>
+        <v>-2.7855725170312608e-06</v>
       </c>
       <c r="D33">
-        <v>-6.7295998727717456e-07</v>
+        <v>-6.7275357072985575e-07</v>
       </c>
       <c r="E33">
-        <v>4.5848603360447901e-09</v>
+        <v>4.5830711267215435e-09</v>
       </c>
       <c r="F33">
-        <v>-1.0577415409203473e-05</v>
+        <v>-1.0575696445527265e-05</v>
       </c>
       <c r="G33">
-        <v>6.8038155865142409e-06</v>
+        <v>6.8023772104693964e-06</v>
       </c>
       <c r="H33">
-        <v>2.6253152083416357e-06</v>
+        <v>2.6249090092077162e-06</v>
       </c>
       <c r="I33">
-        <v>7.3387070253574463e-06</v>
+        <v>7.3389126967648348e-06</v>
       </c>
       <c r="J33">
-        <v>1.392162477322366e-05</v>
+        <v>1.3921870275758492e-05</v>
       </c>
       <c r="K33">
-        <v>9.1396972887454833e-07</v>
+        <v>9.1424478038541258e-07</v>
       </c>
       <c r="L33">
-        <v>-5.6363336602679515e-07</v>
+        <v>-5.6423937115830138e-07</v>
       </c>
       <c r="M33">
-        <v>-3.6098291435469106e-06</v>
+        <v>-3.6083818067304883e-06</v>
       </c>
       <c r="N33">
-        <v>1.4010040916725638e-05</v>
+        <v>1.4011853674495702e-05</v>
       </c>
       <c r="O33">
-        <v>1.3672397677193627e-05</v>
+        <v>1.3672779687304104e-05</v>
       </c>
       <c r="P33">
-        <v>5.9740567592712043e-06</v>
+        <v>5.9739552814932e-06</v>
       </c>
       <c r="Q33">
-        <v>1.118089007127762e-05</v>
+        <v>1.118153308104632e-05</v>
       </c>
       <c r="R33">
-        <v>6.3094041663496901e-06</v>
+        <v>6.3090179502545336e-06</v>
       </c>
       <c r="S33">
-        <v>3.9477254569432376e-07</v>
+        <v>3.9528066487977713e-07</v>
       </c>
       <c r="T33">
-        <v>2.9033242832995768e-06</v>
+        <v>2.9048955028014134e-06</v>
       </c>
       <c r="U33">
-        <v>4.8924266332218264e-06</v>
+        <v>4.8929705299049164e-06</v>
       </c>
       <c r="V33">
-        <v>-3.2089001525624134e-06</v>
+        <v>-3.2051049512609733e-06</v>
       </c>
       <c r="W33">
-        <v>6.2388234138415226e-06</v>
+        <v>6.2405451611873328e-06</v>
       </c>
       <c r="X33">
-        <v>1.0350152968928601e-05</v>
+        <v>1.0351104190018683e-05</v>
       </c>
       <c r="Y33">
-        <v>1.463197315066788e-05</v>
+        <v>1.4633362057436353e-05</v>
       </c>
       <c r="Z33">
-        <v>2.0841021875454969e-06</v>
+        <v>2.0838513120365381e-06</v>
       </c>
       <c r="AA33">
-        <v>3.238703458800489e-07</v>
+        <v>3.237116744580379e-07</v>
       </c>
       <c r="AB33">
-        <v>4.63145584620678e-06</v>
+        <v>4.6315409095330833e-06</v>
       </c>
       <c r="AC33">
-        <v>5.0668050914396705e-06</v>
+        <v>5.06704063144684e-06</v>
       </c>
       <c r="AD33">
-        <v>1.9566230662405214e-06</v>
+        <v>1.9600508353146852e-06</v>
       </c>
       <c r="AE33">
-        <v>5.1926736026641941e-06</v>
+        <v>5.1927534039564299e-06</v>
       </c>
       <c r="AF33">
-        <v>1.1140113677038125e-06</v>
+        <v>1.112915820024626e-06</v>
       </c>
       <c r="AG33">
-        <v>2.6585612763727851e-06</v>
+        <v>2.6586276749018822e-06</v>
       </c>
       <c r="AH33">
-        <v>4.8362065600720093e-06</v>
+        <v>4.8363452685978054e-06</v>
       </c>
       <c r="AI33">
-        <v>-7.6846043188958583e-06</v>
+        <v>-7.6858596764321785e-06</v>
       </c>
       <c r="AJ33">
-        <v>-1.3275073373393845e-05</v>
+        <v>-1.3276019498263992e-05</v>
       </c>
       <c r="AK33">
-        <v>-9.5404012987326163e-05</v>
+        <v>-9.5414755969491113e-05</v>
       </c>
     </row>
     <row r="34">
@@ -4130,112 +4130,112 @@
         <v>58</v>
       </c>
       <c r="B34">
-        <v>-0.15033972883173386</v>
+        <v>-0.15034503538462818</v>
       </c>
       <c r="C34">
-        <v>8.9130519989634747e-05</v>
+        <v>8.915465808709844e-05</v>
       </c>
       <c r="D34">
-        <v>-5.6677662949906763e-06</v>
+        <v>-5.6633420541665563e-06</v>
       </c>
       <c r="E34">
-        <v>6.6903421873668923e-08</v>
+        <v>6.6863409455461351e-08</v>
       </c>
       <c r="F34">
-        <v>-1.0605757314727758e-05</v>
+        <v>-1.0610707155621259e-05</v>
       </c>
       <c r="G34">
-        <v>-4.2446913073927901e-05</v>
+        <v>-4.2492166427976746e-05</v>
       </c>
       <c r="H34">
-        <v>0.00012237466566103689</v>
+        <v>0.00012237409901647987</v>
       </c>
       <c r="I34">
-        <v>-2.5262519972187123e-05</v>
+        <v>-2.5280771717804598e-05</v>
       </c>
       <c r="J34">
-        <v>-6.9376751859976087e-05</v>
+        <v>-6.9409204249576764e-05</v>
       </c>
       <c r="K34">
-        <v>2.2824839855722576e-06</v>
+        <v>2.2814609825895851e-06</v>
       </c>
       <c r="L34">
-        <v>0.00018717311068847846</v>
+        <v>0.00018715727023934812</v>
       </c>
       <c r="M34">
-        <v>0.00035750023934170636</v>
+        <v>0.00035750766520286238</v>
       </c>
       <c r="N34">
-        <v>2.2497273758510881e-05</v>
+        <v>2.2514017574319558e-05</v>
       </c>
       <c r="O34">
-        <v>-0.0003203966071602951</v>
+        <v>-0.00032039198444023365</v>
       </c>
       <c r="P34">
-        <v>-9.9362207800476996e-05</v>
+        <v>-9.9376228560866013e-05</v>
       </c>
       <c r="Q34">
-        <v>-9.6750022121993521e-05</v>
+        <v>-9.6747092675855922e-05</v>
       </c>
       <c r="R34">
-        <v>3.2985664300947716e-05</v>
+        <v>3.2992963550648041e-05</v>
       </c>
       <c r="S34">
-        <v>6.2748640235272407e-05</v>
+        <v>6.2750748413151203e-05</v>
       </c>
       <c r="T34">
-        <v>6.6048570054214745e-05</v>
+        <v>6.6076337071089772e-05</v>
       </c>
       <c r="U34">
-        <v>6.6267106489470082e-05</v>
+        <v>6.6273869017443449e-05</v>
       </c>
       <c r="V34">
-        <v>-0.00014346109081114094</v>
+        <v>-0.00014341427858625163</v>
       </c>
       <c r="W34">
-        <v>-3.4061938609403469e-05</v>
+        <v>-3.4047526304822797e-05</v>
       </c>
       <c r="X34">
-        <v>9.7635099104415209e-05</v>
+        <v>9.7645302096884337e-05</v>
       </c>
       <c r="Y34">
-        <v>-0.00017669991184134093</v>
+        <v>-0.00017670710869012625</v>
       </c>
       <c r="Z34">
-        <v>3.0132228729184073e-05</v>
+        <v>3.0127887298176141e-05</v>
       </c>
       <c r="AA34">
-        <v>-0.00010533555266603045</v>
+        <v>-0.00010533869536918442</v>
       </c>
       <c r="AB34">
-        <v>-0.0001066261803923255</v>
+        <v>-0.00010663134530288594</v>
       </c>
       <c r="AC34">
-        <v>-0.0001036889974872098</v>
+        <v>-0.00010368989030267979</v>
       </c>
       <c r="AD34">
-        <v>-8.5283316818115813e-05</v>
+        <v>-8.5239957407083709e-05</v>
       </c>
       <c r="AE34">
-        <v>-8.9424393463073595e-05</v>
+        <v>-8.9430173679340159e-05</v>
       </c>
       <c r="AF34">
-        <v>4.4511831371199864e-05</v>
+        <v>4.4512379639054592e-05</v>
       </c>
       <c r="AG34">
-        <v>-1.8209457757887085e-05</v>
+        <v>-1.8214574711171352e-05</v>
       </c>
       <c r="AH34">
-        <v>-7.6846043188958583e-06</v>
+        <v>-7.6858596764321785e-06</v>
       </c>
       <c r="AI34">
-        <v>0.0022136601503368277</v>
+        <v>0.0022137049556604062</v>
       </c>
       <c r="AJ34">
-        <v>0.00014432207197130764</v>
+        <v>0.0001443201995180632</v>
       </c>
       <c r="AK34">
-        <v>0.00012355210189410765</v>
+        <v>0.00012343758506881501</v>
       </c>
     </row>
     <row r="35">
@@ -4243,112 +4243,112 @@
         <v>59</v>
       </c>
       <c r="B35">
-        <v>-0.054709267616763549</v>
+        <v>-0.054715726299834171</v>
       </c>
       <c r="C35">
-        <v>1.1049385443962807e-05</v>
+        <v>1.1057416584411131e-05</v>
       </c>
       <c r="D35">
-        <v>-1.0040630381399728e-05</v>
+        <v>-1.003814833831166e-05</v>
       </c>
       <c r="E35">
-        <v>8.9063978609485001e-08</v>
+        <v>8.9041164065659396e-08</v>
       </c>
       <c r="F35">
-        <v>0.0013384228419809558</v>
+        <v>0.0013384388536105847</v>
       </c>
       <c r="G35">
-        <v>4.1344977390652912e-05</v>
+        <v>4.1329387394248513e-05</v>
       </c>
       <c r="H35">
-        <v>8.4057494262503117e-05</v>
+        <v>8.4058184719090962e-05</v>
       </c>
       <c r="I35">
-        <v>0.00012366908819771007</v>
+        <v>0.00012367372499727611</v>
       </c>
       <c r="J35">
-        <v>7.879179419844869e-05</v>
+        <v>7.8782802852043641e-05</v>
       </c>
       <c r="K35">
-        <v>3.2261107812278644e-05</v>
+        <v>3.2271928767388684e-05</v>
       </c>
       <c r="L35">
-        <v>-2.0543834528382633e-05</v>
+        <v>-2.0544762476647953e-05</v>
       </c>
       <c r="M35">
-        <v>-0.00014044840666929681</v>
+        <v>-0.00014043889582977332</v>
       </c>
       <c r="N35">
-        <v>-1.7642350327369766e-05</v>
+        <v>-1.7625645102796765e-05</v>
       </c>
       <c r="O35">
-        <v>-5.0527274971843878e-05</v>
+        <v>-5.052634472419023e-05</v>
       </c>
       <c r="P35">
-        <v>-3.6940638418842269e-05</v>
+        <v>-3.6944388681503179e-05</v>
       </c>
       <c r="Q35">
-        <v>-6.6639733347515591e-05</v>
+        <v>-6.6631928615452647e-05</v>
       </c>
       <c r="R35">
-        <v>-3.3357670150407307e-05</v>
+        <v>-3.3360425697209761e-05</v>
       </c>
       <c r="S35">
-        <v>3.6756520083021556e-05</v>
+        <v>3.6761823225330524e-05</v>
       </c>
       <c r="T35">
-        <v>2.7265126406627194e-05</v>
+        <v>2.7281207194245795e-05</v>
       </c>
       <c r="U35">
-        <v>7.739509810262982e-05</v>
+        <v>7.7407651909492357e-05</v>
       </c>
       <c r="V35">
-        <v>-5.5767442248278495e-05</v>
+        <v>-5.5734186276285567e-05</v>
       </c>
       <c r="W35">
-        <v>-5.7148638478477908e-05</v>
+        <v>-5.7130189632925753e-05</v>
       </c>
       <c r="X35">
-        <v>-8.563530496687329e-05</v>
+        <v>-8.5620284228440056e-05</v>
       </c>
       <c r="Y35">
-        <v>-0.000116603795565878</v>
+        <v>-0.00011658928202047648</v>
       </c>
       <c r="Z35">
-        <v>-5.5393497825243719e-06</v>
+        <v>-5.5428478897691602e-06</v>
       </c>
       <c r="AA35">
-        <v>3.1082918101691153e-05</v>
+        <v>3.1083917251401773e-05</v>
       </c>
       <c r="AB35">
-        <v>-7.4616263061845966e-05</v>
+        <v>-7.4617209358636568e-05</v>
       </c>
       <c r="AC35">
-        <v>-1.6168897166982197e-05</v>
+        <v>-1.616832719370789e-05</v>
       </c>
       <c r="AD35">
-        <v>-0.00010136400901270242</v>
+        <v>-0.00010133362225287065</v>
       </c>
       <c r="AE35">
-        <v>-6.4097213237671925e-05</v>
+        <v>-6.4100404898649859e-05</v>
       </c>
       <c r="AF35">
-        <v>-3.4832369199632287e-05</v>
+        <v>-3.4834226891073935e-05</v>
       </c>
       <c r="AG35">
-        <v>-9.8875690219375799e-05</v>
+        <v>-9.8878405566171735e-05</v>
       </c>
       <c r="AH35">
-        <v>-1.3275073373393845e-05</v>
+        <v>-1.3276019498263992e-05</v>
       </c>
       <c r="AI35">
-        <v>0.00014432207197130764</v>
+        <v>0.0001443201995180632</v>
       </c>
       <c r="AJ35">
-        <v>0.002449055200601233</v>
+        <v>0.0024491015669465288</v>
       </c>
       <c r="AK35">
-        <v>0.00046780281352956941</v>
+        <v>0.0004677202747141088</v>
       </c>
     </row>
     <row r="36">
@@ -4356,112 +4356,112 @@
         <v>60</v>
       </c>
       <c r="B36">
-        <v>-1.6842295054060479</v>
+        <v>-1.6843882547400635</v>
       </c>
       <c r="C36">
-        <v>-0.00018440944934257808</v>
+        <v>-0.00018429143249133056</v>
       </c>
       <c r="D36">
-        <v>-0.00030419755771113051</v>
+        <v>-0.00030416812978090462</v>
       </c>
       <c r="E36">
-        <v>2.731377679922013e-06</v>
+        <v>2.7310916419036542e-06</v>
       </c>
       <c r="F36">
-        <v>-0.0036322712391759562</v>
+        <v>-0.0036321204845852118</v>
       </c>
       <c r="G36">
-        <v>-0.0024304373710473618</v>
+        <v>-0.0024305356388305312</v>
       </c>
       <c r="H36">
-        <v>-0.0018467793899298772</v>
+        <v>-0.001846817251595371</v>
       </c>
       <c r="I36">
-        <v>-0.0029055770861499907</v>
+        <v>-0.0029056184140483078</v>
       </c>
       <c r="J36">
-        <v>-0.002656321101019021</v>
+        <v>-0.0026564637035712568</v>
       </c>
       <c r="K36">
-        <v>-0.0030800343277878339</v>
+        <v>-0.0030800114156639652</v>
       </c>
       <c r="L36">
-        <v>-0.0027187827216915298</v>
+        <v>-0.0027188541205461492</v>
       </c>
       <c r="M36">
-        <v>-0.0053790277856958606</v>
+        <v>-0.005378962444420857</v>
       </c>
       <c r="N36">
-        <v>-0.0037283434415254571</v>
+        <v>-0.0037281263337097595</v>
       </c>
       <c r="O36">
-        <v>-0.00059342837293038927</v>
+        <v>-0.00059337538449408516</v>
       </c>
       <c r="P36">
-        <v>-0.00088753503768827368</v>
+        <v>-0.00088759852567903456</v>
       </c>
       <c r="Q36">
-        <v>-0.0010158069852433725</v>
+        <v>-0.0010156987188927886</v>
       </c>
       <c r="R36">
-        <v>-0.0082140119343833331</v>
+        <v>-0.0082142232681731674</v>
       </c>
       <c r="S36">
-        <v>-0.0075311052027089509</v>
+        <v>-0.0075311980341891197</v>
       </c>
       <c r="T36">
-        <v>-0.0078957048946451738</v>
+        <v>-0.0078956453265367523</v>
       </c>
       <c r="U36">
-        <v>-0.0084047148033068626</v>
+        <v>-0.0084047649127244502</v>
       </c>
       <c r="V36">
-        <v>-0.00087090108422831474</v>
+        <v>-0.00087039852192216031</v>
       </c>
       <c r="W36">
-        <v>-0.0035897040150082459</v>
+        <v>-0.0035894863773359397</v>
       </c>
       <c r="X36">
-        <v>-0.0044937115429248562</v>
+        <v>-0.0044935850989067851</v>
       </c>
       <c r="Y36">
-        <v>-0.0049900702767961286</v>
+        <v>-0.0049899018761898149</v>
       </c>
       <c r="Z36">
-        <v>0.00021096325430880713</v>
+        <v>0.00021091908774728004</v>
       </c>
       <c r="AA36">
-        <v>-0.00011010593494362019</v>
+        <v>-0.0001100793555372636</v>
       </c>
       <c r="AB36">
-        <v>-0.0030390993999282541</v>
+        <v>-0.0030391536449426407</v>
       </c>
       <c r="AC36">
-        <v>-0.0030386154645466062</v>
+        <v>-0.0030386505253575426</v>
       </c>
       <c r="AD36">
-        <v>-0.0029958964299309143</v>
+        <v>-0.0029955110811089739</v>
       </c>
       <c r="AE36">
-        <v>-0.0029048864581103276</v>
+        <v>-0.0029049788151290796</v>
       </c>
       <c r="AF36">
-        <v>-0.003118613227807817</v>
+        <v>-0.0031186835463261585</v>
       </c>
       <c r="AG36">
-        <v>-0.0029429015216106049</v>
+        <v>-0.0029429837293659545</v>
       </c>
       <c r="AH36">
-        <v>-9.5404012987326163e-05</v>
+        <v>-9.5414755969491113e-05</v>
       </c>
       <c r="AI36">
-        <v>0.00012355210189410765</v>
+        <v>0.00012343758506881501</v>
       </c>
       <c r="AJ36">
-        <v>0.00046780281352956941</v>
+        <v>0.0004677202747141088</v>
       </c>
       <c r="AK36">
-        <v>0.02754173849489127</v>
+        <v>0.027541038141718505</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_home_ownership.xlsx
+++ b/input/ES/reg_home_ownership.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="97" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="93" uniqueCount="60">
   <si>
     <t>Description</t>
   </si>
@@ -96,12 +96,6 @@
   </si>
   <si>
     <t>Dgn</t>
-  </si>
-  <si>
-    <t>Dag</t>
-  </si>
-  <si>
-    <t>Dag_sq</t>
   </si>
   <si>
     <t>Dhhtp_c8_2_L1</t>
@@ -360,7 +354,7 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.82527868238661584</v>
+        <v>0.82462702602528459</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -368,7 +362,7 @@
         <v>22</v>
       </c>
       <c r="F5">
-        <v>34641.743101335895</v>
+        <v>34533.017929957103</v>
       </c>
     </row>
     <row r="6">
@@ -376,7 +370,7 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>178071</v>
+        <v>178084</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -384,7 +378,7 @@
         <v>23</v>
       </c>
       <c r="F6">
-        <v>-21003652.813034989</v>
+        <v>-21085708.007565789</v>
       </c>
     </row>
   </sheetData>
@@ -393,7 +387,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK36"/>
+  <dimension ref="A1:AI34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -401,7 +395,7 @@
         <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
         <v>26</v>
@@ -501,12 +495,6 @@
       </c>
       <c r="AI1" t="s">
         <v>58</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2">
@@ -514,112 +502,106 @@
         <v>26</v>
       </c>
       <c r="B2">
-        <v>0.026895337107439264</v>
+        <v>0.0041327587006645666</v>
       </c>
       <c r="C2">
-        <v>0.00045598098670887225</v>
+        <v>0.00044992553030662381</v>
       </c>
       <c r="D2">
-        <v>3.6215291549113554e-06</v>
+        <v>8.5196106026390415e-05</v>
       </c>
       <c r="E2">
-        <v>-7.4480976254347049e-09</v>
+        <v>-6.2828630875756437e-05</v>
       </c>
       <c r="F2">
-        <v>6.7268826536586617e-05</v>
+        <v>-8.4565668852782602e-06</v>
       </c>
       <c r="G2">
-        <v>-7.76349176659076e-05</v>
+        <v>-0.00010843423021864615</v>
       </c>
       <c r="H2">
-        <v>3.3341554446164095e-06</v>
+        <v>-0.00010596516053969346</v>
       </c>
       <c r="I2">
-        <v>-9.6585898395810108e-05</v>
+        <v>0.00011732840928461018</v>
       </c>
       <c r="J2">
-        <v>-9.6715316770636358e-05</v>
+        <v>0.00018803916794095022</v>
       </c>
       <c r="K2">
-        <v>0.00013304390576172323</v>
+        <v>5.1197771764598007e-06</v>
       </c>
       <c r="L2">
-        <v>0.00022012041977361829</v>
+        <v>-4.2400694082288633e-05</v>
       </c>
       <c r="M2">
-        <v>3.0999900657781177e-05</v>
+        <v>-6.0906119824910346e-05</v>
       </c>
       <c r="N2">
-        <v>-0.00010287980318271373</v>
+        <v>-3.361322185230121e-05</v>
       </c>
       <c r="O2">
-        <v>-6.2240004934265684e-05</v>
+        <v>-4.8211227158035332e-05</v>
       </c>
       <c r="P2">
-        <v>-4.2742447953118519e-05</v>
+        <v>0.00015964187899656531</v>
       </c>
       <c r="Q2">
-        <v>-7.1684750782153312e-05</v>
+        <v>-2.9367506558327801e-05</v>
       </c>
       <c r="R2">
-        <v>0.0001342129335474713</v>
+        <v>-5.3783345333062307e-05</v>
       </c>
       <c r="S2">
-        <v>-3.492902222563712e-05</v>
+        <v>-0.00011313088460214999</v>
       </c>
       <c r="T2">
-        <v>-3.5571747157914926e-05</v>
+        <v>3.3585706080962048e-07</v>
       </c>
       <c r="U2">
-        <v>-8.4545928728930157e-05</v>
+        <v>3.897800193710734e-05</v>
       </c>
       <c r="V2">
-        <v>-1.5333079626743306e-06</v>
+        <v>-1.429762836629479e-06</v>
       </c>
       <c r="W2">
-        <v>1.7320127798754005e-05</v>
+        <v>-5.9422502834602001e-05</v>
       </c>
       <c r="X2">
-        <v>-2.7578672969093225e-05</v>
+        <v>-4.802813257907438e-07</v>
       </c>
       <c r="Y2">
-        <v>-9.7140136555206414e-05</v>
+        <v>-3.1834493471115892e-05</v>
       </c>
       <c r="Z2">
-        <v>-1.3032057519368863e-06</v>
+        <v>-8.1085924364915341e-05</v>
       </c>
       <c r="AA2">
-        <v>-3.7841443168210034e-05</v>
+        <v>-8.7021960423897996e-05</v>
       </c>
       <c r="AB2">
-        <v>-8.3220926574514197e-05</v>
+        <v>-9.2596972208624484e-05</v>
       </c>
       <c r="AC2">
-        <v>-8.906949029818085e-05</v>
+        <v>-0.00010856841590938738</v>
       </c>
       <c r="AD2">
-        <v>-9.2826737795602955e-05</v>
+        <v>-6.3819334106375331e-05</v>
       </c>
       <c r="AE2">
-        <v>-0.00010770278311922061</v>
+        <v>-4.7641209485684455e-06</v>
       </c>
       <c r="AF2">
-        <v>-6.848526538045293e-05</v>
+        <v>-1.9497710287320405e-06</v>
       </c>
       <c r="AG2">
-        <v>2.2275491929254512e-06</v>
+        <v>8.2682461790918376e-05</v>
       </c>
       <c r="AH2">
-        <v>-2.7855725170312608e-06</v>
+        <v>1.3097791130418853e-05</v>
       </c>
       <c r="AI2">
-        <v>8.915465808709844e-05</v>
-      </c>
-      <c r="AJ2">
-        <v>1.1057416584411131e-05</v>
-      </c>
-      <c r="AK2">
-        <v>-0.00018429143249133056</v>
+        <v>-7.2034827626274e-05</v>
       </c>
     </row>
     <row r="3">
@@ -627,112 +609,106 @@
         <v>27</v>
       </c>
       <c r="B3">
-        <v>-0.00080459157607772579</v>
+        <v>0.12681895963208956</v>
       </c>
       <c r="C3">
-        <v>3.6215291549113554e-06</v>
+        <v>8.5196106026390415e-05</v>
       </c>
       <c r="D3">
-        <v>1.211723183217659e-05</v>
+        <v>0.15220756463936075</v>
       </c>
       <c r="E3">
-        <v>-1.1047162587412689e-07</v>
+        <v>0.002084396923760304</v>
       </c>
       <c r="F3">
-        <v>2.6670843332077363e-05</v>
+        <v>0.0016882452590596976</v>
       </c>
       <c r="G3">
-        <v>3.3874334153264149e-06</v>
+        <v>0.0024417879512849943</v>
       </c>
       <c r="H3">
-        <v>-6.25223592107784e-06</v>
+        <v>0.0021134510801234059</v>
       </c>
       <c r="I3">
-        <v>4.2537987613986187e-06</v>
+        <v>0.0019828406336588871</v>
       </c>
       <c r="J3">
-        <v>-6.9309431216146215e-06</v>
+        <v>0.0020871683533679178</v>
       </c>
       <c r="K3">
-        <v>2.6319770202980336e-05</v>
+        <v>-2.0115308488022473e-05</v>
       </c>
       <c r="L3">
-        <v>2.8641344872958962e-06</v>
+        <v>0.0001862923207223158</v>
       </c>
       <c r="M3">
-        <v>5.7557596450142848e-05</v>
+        <v>0.00027309987750996157</v>
       </c>
       <c r="N3">
-        <v>1.1994460097592127e-05</v>
+        <v>3.415495757352156e-05</v>
       </c>
       <c r="O3">
-        <v>1.8493161870515433e-05</v>
+        <v>0.00017304750110305124</v>
       </c>
       <c r="P3">
-        <v>3.243644708268023e-06</v>
+        <v>0.00024098226622748672</v>
       </c>
       <c r="Q3">
-        <v>-3.2481501141426011e-06</v>
+        <v>0.0002049088881617481</v>
       </c>
       <c r="R3">
-        <v>2.03879574622578e-05</v>
+        <v>0.00013961429365073885</v>
       </c>
       <c r="S3">
-        <v>-3.6424690642633323e-07</v>
+        <v>0.00035347518107974138</v>
       </c>
       <c r="T3">
-        <v>2.9768829863696834e-06</v>
+        <v>-1.9174180004394734e-05</v>
       </c>
       <c r="U3">
-        <v>1.0292432767799328e-05</v>
+        <v>-3.2793598063826689e-05</v>
       </c>
       <c r="V3">
-        <v>5.478910716750254e-06</v>
+        <v>0.00034904637853419248</v>
       </c>
       <c r="W3">
-        <v>3.6238612205948006e-06</v>
+        <v>0.00080519745304555952</v>
       </c>
       <c r="X3">
-        <v>7.3128771778003263e-06</v>
+        <v>-7.8230614138234162e-06</v>
       </c>
       <c r="Y3">
-        <v>-6.051814695894758e-06</v>
+        <v>0.00033228372241895826</v>
       </c>
       <c r="Z3">
-        <v>-1.005130469697827e-06</v>
+        <v>0.00014280146279554637</v>
       </c>
       <c r="AA3">
-        <v>-2.1263051652331842e-06</v>
+        <v>0.0010716454027064866</v>
       </c>
       <c r="AB3">
-        <v>-4.9021878271057989e-06</v>
+        <v>0.0007563371623317567</v>
       </c>
       <c r="AC3">
-        <v>-1.9514781448637993e-07</v>
+        <v>0.00013931877986970488</v>
       </c>
       <c r="AD3">
-        <v>6.1513538738070233e-07</v>
+        <v>0.00013819997115470237</v>
       </c>
       <c r="AE3">
-        <v>-1.4172083583867813e-06</v>
+        <v>2.6842920995643992e-05</v>
       </c>
       <c r="AF3">
-        <v>-5.3222697295533773e-07</v>
+        <v>-8.510155342639439e-06</v>
       </c>
       <c r="AG3">
-        <v>-3.0054686833840975e-06</v>
+        <v>5.4247913094004809e-05</v>
       </c>
       <c r="AH3">
-        <v>-6.7275357072985575e-07</v>
+        <v>0.0013306349657106415</v>
       </c>
       <c r="AI3">
-        <v>-5.6633420541665563e-06</v>
-      </c>
-      <c r="AJ3">
-        <v>-1.003814833831166e-05</v>
-      </c>
-      <c r="AK3">
-        <v>-0.00030416812978090462</v>
+        <v>-0.0029610538351407139</v>
       </c>
     </row>
     <row r="4">
@@ -740,112 +716,106 @@
         <v>28</v>
       </c>
       <c r="B4">
-        <v>6.5199379026281929e-05</v>
+        <v>0.03595234274131201</v>
       </c>
       <c r="C4">
-        <v>-7.4480976254347049e-09</v>
+        <v>-6.2828630875756437e-05</v>
       </c>
       <c r="D4">
-        <v>-1.1047162587412689e-07</v>
+        <v>0.002084396923760304</v>
       </c>
       <c r="E4">
-        <v>1.0572636626675565e-09</v>
+        <v>0.0026441163376976526</v>
       </c>
       <c r="F4">
-        <v>-2.354277399472372e-07</v>
+        <v>0.0018128197573376338</v>
       </c>
       <c r="G4">
-        <v>-7.1884982986310097e-08</v>
+        <v>0.0020642741812237952</v>
       </c>
       <c r="H4">
-        <v>6.6527950715626985e-08</v>
+        <v>0.0020977832497201653</v>
       </c>
       <c r="I4">
-        <v>-2.3294099055857732e-08</v>
+        <v>0.0021085718188296109</v>
       </c>
       <c r="J4">
-        <v>7.9823238894101803e-08</v>
+        <v>0.0021090443932507389</v>
       </c>
       <c r="K4">
-        <v>-2.1279393631650998e-07</v>
+        <v>1.4118593225045939e-05</v>
       </c>
       <c r="L4">
-        <v>6.0006056155785776e-08</v>
+        <v>-9.3260023870279937e-05</v>
       </c>
       <c r="M4">
-        <v>-5.1687671150398904e-07</v>
+        <v>0.00011537275032906199</v>
       </c>
       <c r="N4">
-        <v>-2.282167931725598e-07</v>
+        <v>0.00013157663846053444</v>
       </c>
       <c r="O4">
-        <v>-1.7800012130098569e-07</v>
+        <v>9.2101658019669966e-05</v>
       </c>
       <c r="P4">
-        <v>-4.180119020685555e-08</v>
+        <v>0.00025685583857601392</v>
       </c>
       <c r="Q4">
-        <v>-1.8257074853130559e-08</v>
+        <v>7.6911989027215739e-05</v>
       </c>
       <c r="R4">
-        <v>-2.3308044762955454e-07</v>
+        <v>5.8410909162380639e-05</v>
       </c>
       <c r="S4">
-        <v>-1.7919896359651921e-08</v>
+        <v>0.00011723908016807649</v>
       </c>
       <c r="T4">
-        <v>-7.6404521593637758e-09</v>
+        <v>7.8675240484065185e-05</v>
       </c>
       <c r="U4">
-        <v>-6.533851256180072e-08</v>
+        <v>9.0123156531705896e-05</v>
       </c>
       <c r="V4">
-        <v>-5.131731462441057e-08</v>
+        <v>0.00023564401616686876</v>
       </c>
       <c r="W4">
-        <v>-8.4522838499709036e-08</v>
+        <v>0.00072939579332476838</v>
       </c>
       <c r="X4">
-        <v>-1.126472656274382e-07</v>
+        <v>-3.1864712784610305e-05</v>
       </c>
       <c r="Y4">
-        <v>-1.690835330445087e-08</v>
+        <v>-6.7136134926304263e-05</v>
       </c>
       <c r="Z4">
-        <v>6.8760027504605691e-09</v>
+        <v>0.00010394145986337652</v>
       </c>
       <c r="AA4">
-        <v>6.422796339319445e-09</v>
+        <v>8.770373819365785e-05</v>
       </c>
       <c r="AB4">
-        <v>4.9290414321812228e-08</v>
+        <v>0.00010743254938749445</v>
       </c>
       <c r="AC4">
-        <v>7.2420227277417834e-09</v>
+        <v>4.3360577271745913e-05</v>
       </c>
       <c r="AD4">
-        <v>-2.7174720676790462e-09</v>
+        <v>6.5902518832273212e-05</v>
       </c>
       <c r="AE4">
-        <v>2.3275186937323524e-08</v>
+        <v>-1.1316323787113696e-05</v>
       </c>
       <c r="AF4">
-        <v>4.869925171155404e-09</v>
+        <v>5.5397297790903439e-06</v>
       </c>
       <c r="AG4">
-        <v>4.6013643849496761e-08</v>
+        <v>-3.4781742681625188e-05</v>
       </c>
       <c r="AH4">
-        <v>4.5830711267215435e-09</v>
+        <v>2.948272168971347e-05</v>
       </c>
       <c r="AI4">
-        <v>6.6863409455461351e-08</v>
-      </c>
-      <c r="AJ4">
-        <v>8.9041164065659396e-08</v>
-      </c>
-      <c r="AK4">
-        <v>2.7310916419036542e-06</v>
+        <v>-0.0024047977311919084</v>
       </c>
     </row>
     <row r="5">
@@ -853,112 +823,106 @@
         <v>29</v>
       </c>
       <c r="B5">
-        <v>0.20597873718441592</v>
+        <v>-0.076810395035844345</v>
       </c>
       <c r="C5">
-        <v>6.7268826536586617e-05</v>
+        <v>-8.4565668852782602e-06</v>
       </c>
       <c r="D5">
-        <v>2.6670843332077363e-05</v>
+        <v>0.0016882452590596976</v>
       </c>
       <c r="E5">
-        <v>-2.354277399472372e-07</v>
+        <v>0.0018128197573376338</v>
       </c>
       <c r="F5">
-        <v>0.13553132341881574</v>
+        <v>0.0028941737281210798</v>
       </c>
       <c r="G5">
-        <v>0.0020380260055970602</v>
+        <v>0.0018612724534218567</v>
       </c>
       <c r="H5">
-        <v>0.001673492339514706</v>
+        <v>0.0018492289694546063</v>
       </c>
       <c r="I5">
-        <v>0.0023906395269241093</v>
+        <v>0.001802882282930145</v>
       </c>
       <c r="J5">
-        <v>0.0020654718840749796</v>
+        <v>0.0017667256002488313</v>
       </c>
       <c r="K5">
-        <v>0.0020026998232934986</v>
+        <v>0.0001037959055400241</v>
       </c>
       <c r="L5">
-        <v>0.0020712387838376337</v>
+        <v>9.6185840505532403e-05</v>
       </c>
       <c r="M5">
-        <v>0.00017105498378687696</v>
+        <v>8.1680466308312917e-05</v>
       </c>
       <c r="N5">
-        <v>0.00024591485347891197</v>
+        <v>0.00012419560983464682</v>
       </c>
       <c r="O5">
-        <v>0.00029837182396270402</v>
+        <v>0.00011222399271491033</v>
       </c>
       <c r="P5">
-        <v>3.8287409453310363e-05</v>
+        <v>2.6036874602798177e-05</v>
       </c>
       <c r="Q5">
-        <v>0.00016194203110046258</v>
+        <v>3.0606587825475549e-05</v>
       </c>
       <c r="R5">
-        <v>0.00022838431649253518</v>
+        <v>-5.2813169843047366e-06</v>
       </c>
       <c r="S5">
-        <v>0.00020243144669056809</v>
+        <v>2.2049062175248733e-05</v>
       </c>
       <c r="T5">
-        <v>0.00014961023123421049</v>
+        <v>3.3185996693455404e-05</v>
       </c>
       <c r="U5">
-        <v>0.00038255499253252179</v>
+        <v>4.759201680919038e-05</v>
       </c>
       <c r="V5">
-        <v>4.2393983027296228e-05</v>
+        <v>6.0529809378991268e-05</v>
       </c>
       <c r="W5">
-        <v>6.7013509459798448e-05</v>
+        <v>0.00035402050081689601</v>
       </c>
       <c r="X5">
-        <v>0.00041790608657136272</v>
+        <v>-1.1239453734116289e-05</v>
       </c>
       <c r="Y5">
-        <v>0.00082093055223320935</v>
+        <v>-4.883454486433441e-05</v>
       </c>
       <c r="Z5">
-        <v>-2.9380921477202878e-05</v>
+        <v>0.00011191749201079561</v>
       </c>
       <c r="AA5">
-        <v>0.00035992754909626565</v>
+        <v>7.3842847933200395e-06</v>
       </c>
       <c r="AB5">
-        <v>0.00017089336480977861</v>
+        <v>5.2590944147562577e-05</v>
       </c>
       <c r="AC5">
-        <v>0.0010396622006849535</v>
+        <v>-2.1056099340477884e-05</v>
       </c>
       <c r="AD5">
-        <v>0.00072293055582634642</v>
+        <v>-5.3059972264982548e-06</v>
       </c>
       <c r="AE5">
-        <v>0.00014512559808635612</v>
+        <v>-7.2812817573096904e-05</v>
       </c>
       <c r="AF5">
-        <v>0.00014004760693710243</v>
+        <v>2.3800320149084932e-06</v>
       </c>
       <c r="AG5">
-        <v>2.1591697983216096e-05</v>
+        <v>0.00011273175229523135</v>
       </c>
       <c r="AH5">
-        <v>-1.0575696445527265e-05</v>
+        <v>7.0103091909831813e-05</v>
       </c>
       <c r="AI5">
-        <v>-1.0610707155621259e-05</v>
-      </c>
-      <c r="AJ5">
-        <v>0.0013384388536105847</v>
-      </c>
-      <c r="AK5">
-        <v>-0.0036321204845852118</v>
+        <v>-0.0020326920215607788</v>
       </c>
     </row>
     <row r="6">
@@ -966,112 +930,106 @@
         <v>30</v>
       </c>
       <c r="B6">
-        <v>-0.0065648356212262733</v>
+        <v>0.16250526351603703</v>
       </c>
       <c r="C6">
-        <v>-7.76349176659076e-05</v>
+        <v>-0.00010843423021864615</v>
       </c>
       <c r="D6">
-        <v>3.3874334153264149e-06</v>
+        <v>0.0024417879512849943</v>
       </c>
       <c r="E6">
-        <v>-7.1884982986310097e-08</v>
+        <v>0.0020642741812237952</v>
       </c>
       <c r="F6">
-        <v>0.0020380260055970602</v>
+        <v>0.0018612724534218567</v>
       </c>
       <c r="G6">
-        <v>0.0026286647044102243</v>
+        <v>0.057488003405249427</v>
       </c>
       <c r="H6">
-        <v>0.00177079404857823</v>
+        <v>0.0022753072320950917</v>
       </c>
       <c r="I6">
-        <v>0.001998110088060025</v>
+        <v>0.001991292999147447</v>
       </c>
       <c r="J6">
-        <v>0.0020434787245531788</v>
+        <v>0.0021086397979223183</v>
       </c>
       <c r="K6">
-        <v>0.0020473901228867473</v>
+        <v>0.000499162153585417</v>
       </c>
       <c r="L6">
-        <v>0.0019961017245598818</v>
+        <v>0.00044981848966821586</v>
       </c>
       <c r="M6">
-        <v>2.8223029018945413e-05</v>
+        <v>0.00018633283427474867</v>
       </c>
       <c r="N6">
-        <v>1.6490432075175307e-05</v>
+        <v>0.00027573964584833103</v>
       </c>
       <c r="O6">
-        <v>0.00012623894597151562</v>
+        <v>0.00028512265825970701</v>
       </c>
       <c r="P6">
-        <v>0.00014563989567054775</v>
+        <v>-5.3984468993179338e-05</v>
       </c>
       <c r="Q6">
-        <v>0.00013243328503286059</v>
+        <v>6.9483088424569491e-05</v>
       </c>
       <c r="R6">
-        <v>0.00028018013986952893</v>
+        <v>-4.2746946247138073e-05</v>
       </c>
       <c r="S6">
-        <v>9.1832062200270675e-05</v>
+        <v>0.0001053769319945768</v>
       </c>
       <c r="T6">
-        <v>5.7560987659392487e-05</v>
+        <v>0.00013915368209563547</v>
       </c>
       <c r="U6">
-        <v>0.00010408204210283025</v>
+        <v>0.00021119581025745267</v>
       </c>
       <c r="V6">
-        <v>7.6936626433448784e-05</v>
+        <v>0.00054653907747107444</v>
       </c>
       <c r="W6">
-        <v>0.000130512544865558</v>
+        <v>0.0012059413454082234</v>
       </c>
       <c r="X6">
-        <v>0.00027336396351494187</v>
+        <v>-4.7557013707125948e-05</v>
       </c>
       <c r="Y6">
-        <v>0.0007647872838871736</v>
+        <v>0.00012877618346038923</v>
       </c>
       <c r="Z6">
-        <v>-2.9295868871452031e-05</v>
+        <v>0.00020423090026065174</v>
       </c>
       <c r="AA6">
-        <v>-5.4323734239563628e-05</v>
+        <v>6.1444208924456853e-05</v>
       </c>
       <c r="AB6">
-        <v>0.00010552169516705925</v>
+        <v>0.0001231085885548299</v>
       </c>
       <c r="AC6">
-        <v>8.4368794715609105e-05</v>
+        <v>6.6073099431141315e-05</v>
       </c>
       <c r="AD6">
-        <v>0.00010134094841438446</v>
+        <v>2.2334027506154791e-05</v>
       </c>
       <c r="AE6">
-        <v>3.1844229894414759e-05</v>
+        <v>-3.5116145501650625e-05</v>
       </c>
       <c r="AF6">
-        <v>6.3109637921800286e-05</v>
+        <v>1.0130120580751479e-05</v>
       </c>
       <c r="AG6">
-        <v>-1.6876315326658318e-05</v>
+        <v>-0.00013755789499182453</v>
       </c>
       <c r="AH6">
-        <v>6.8023772104693964e-06</v>
+        <v>7.9445070357428687e-05</v>
       </c>
       <c r="AI6">
-        <v>-4.2492166427976746e-05</v>
-      </c>
-      <c r="AJ6">
-        <v>4.1329387394248513e-05</v>
-      </c>
-      <c r="AK6">
-        <v>-0.0024305356388305312</v>
+        <v>-0.0029729672163784247</v>
       </c>
     </row>
     <row r="7">
@@ -1079,112 +1037,106 @@
         <v>31</v>
       </c>
       <c r="B7">
-        <v>-0.03967914324928206</v>
+        <v>-0.22492068207238639</v>
       </c>
       <c r="C7">
-        <v>3.3341554446164095e-06</v>
+        <v>-0.00010596516053969346</v>
       </c>
       <c r="D7">
-        <v>-6.25223592107784e-06</v>
+        <v>0.0021134510801234059</v>
       </c>
       <c r="E7">
-        <v>6.6527950715626985e-08</v>
+        <v>0.0020977832497201653</v>
       </c>
       <c r="F7">
-        <v>0.001673492339514706</v>
+        <v>0.0018492289694546063</v>
       </c>
       <c r="G7">
-        <v>0.00177079404857823</v>
+        <v>0.0022753072320950917</v>
       </c>
       <c r="H7">
-        <v>0.0028769200432114737</v>
+        <v>0.0031113177501820512</v>
       </c>
       <c r="I7">
-        <v>0.0018570623259393472</v>
+        <v>0.0020203654061571332</v>
       </c>
       <c r="J7">
-        <v>0.001821266881503312</v>
+        <v>0.0021083988136712008</v>
       </c>
       <c r="K7">
-        <v>0.0017680507784060937</v>
+        <v>0.00039531652231036374</v>
       </c>
       <c r="L7">
-        <v>0.0017493554418150405</v>
+        <v>0.00038087372306953724</v>
       </c>
       <c r="M7">
-        <v>6.6514188150040626e-05</v>
+        <v>0.00011825463761074928</v>
       </c>
       <c r="N7">
-        <v>6.170849700752178e-05</v>
+        <v>0.00016660764644241399</v>
       </c>
       <c r="O7">
-        <v>7.7049602391855406e-05</v>
+        <v>0.00010625670043667456</v>
       </c>
       <c r="P7">
-        <v>0.00013056106850083636</v>
+        <v>2.4952126135451978e-05</v>
       </c>
       <c r="Q7">
-        <v>0.00010424122871433243</v>
+        <v>1.6276286501519304e-06</v>
       </c>
       <c r="R7">
-        <v>1.1699965530151488e-05</v>
+        <v>-3.8034219591053182e-05</v>
       </c>
       <c r="S7">
-        <v>2.661754862446318e-05</v>
+        <v>3.104761253483148e-05</v>
       </c>
       <c r="T7">
-        <v>2.5215092514105841e-06</v>
+        <v>0.00013130352291067067</v>
       </c>
       <c r="U7">
-        <v>8.7750778236801545e-06</v>
+        <v>0.00014664378215088975</v>
       </c>
       <c r="V7">
-        <v>2.5072607670293513e-05</v>
+        <v>0.00051188472275484316</v>
       </c>
       <c r="W7">
-        <v>2.7925235297103024e-05</v>
+        <v>0.001063574258902799</v>
       </c>
       <c r="X7">
-        <v>4.9524922024530302e-05</v>
+        <v>-2.6566527801927502e-05</v>
       </c>
       <c r="Y7">
-        <v>0.00031935560965139686</v>
+        <v>-1.8494888706545559e-05</v>
       </c>
       <c r="Z7">
-        <v>-8.9246904624852345e-06</v>
+        <v>0.00022190153581250639</v>
       </c>
       <c r="AA7">
-        <v>-4.9655501839485723e-05</v>
+        <v>0.00014698745143087479</v>
       </c>
       <c r="AB7">
-        <v>0.00010618260158602776</v>
+        <v>0.00017526084095628117</v>
       </c>
       <c r="AC7">
-        <v>-2.5287817091834003e-06</v>
+        <v>9.9242546054492892e-05</v>
       </c>
       <c r="AD7">
-        <v>3.6201780308259225e-05</v>
+        <v>0.00011251699848729887</v>
       </c>
       <c r="AE7">
-        <v>-3.4557675597660662e-05</v>
+        <v>-6.6641415073845887e-06</v>
       </c>
       <c r="AF7">
-        <v>-2.8034532334489664e-05</v>
+        <v>1.4003597577924943e-05</v>
       </c>
       <c r="AG7">
-        <v>-6.975746189792013e-05</v>
+        <v>-8.6778641401065969e-05</v>
       </c>
       <c r="AH7">
-        <v>2.6249090092077162e-06</v>
+        <v>6.0970632979302688e-05</v>
       </c>
       <c r="AI7">
-        <v>0.00012237409901647987</v>
-      </c>
-      <c r="AJ7">
-        <v>8.4058184719090962e-05</v>
-      </c>
-      <c r="AK7">
-        <v>-0.001846817251595371</v>
+        <v>-0.0028559799727096713</v>
       </c>
     </row>
     <row r="8">
@@ -1192,112 +1144,106 @@
         <v>32</v>
       </c>
       <c r="B8">
-        <v>0.032127306932461242</v>
+        <v>-0.1529704486597758</v>
       </c>
       <c r="C8">
-        <v>-9.6585898395810108e-05</v>
+        <v>0.00011732840928461018</v>
       </c>
       <c r="D8">
-        <v>4.2537987613986187e-06</v>
+        <v>0.0019828406336588871</v>
       </c>
       <c r="E8">
-        <v>-2.3294099055857732e-08</v>
+        <v>0.0021085718188296109</v>
       </c>
       <c r="F8">
-        <v>0.0023906395269241093</v>
+        <v>0.001802882282930145</v>
       </c>
       <c r="G8">
-        <v>0.001998110088060025</v>
+        <v>0.001991292999147447</v>
       </c>
       <c r="H8">
-        <v>0.0018570623259393472</v>
+        <v>0.0020203654061571332</v>
       </c>
       <c r="I8">
-        <v>0.043335027730543881</v>
+        <v>0.0023630518918623398</v>
       </c>
       <c r="J8">
-        <v>0.0022297171573666089</v>
+        <v>0.0021630154235348737</v>
       </c>
       <c r="K8">
-        <v>0.0019647733387385511</v>
+        <v>-9.6477412201960693e-05</v>
       </c>
       <c r="L8">
-        <v>0.0020923181677727732</v>
+        <v>-6.2624319062020188e-05</v>
       </c>
       <c r="M8">
-        <v>0.0004957537782104113</v>
+        <v>8.9623365210410788e-05</v>
       </c>
       <c r="N8">
-        <v>0.00038151294888219008</v>
+        <v>0.00012382017728425647</v>
       </c>
       <c r="O8">
-        <v>0.0001634579299751185</v>
+        <v>0.00012507577302552488</v>
       </c>
       <c r="P8">
-        <v>0.00021995600760838719</v>
+        <v>0.00012121079140615248</v>
       </c>
       <c r="Q8">
-        <v>0.00021977304420419899</v>
+        <v>-5.1614434372137608e-06</v>
       </c>
       <c r="R8">
-        <v>-4.2162219541459116e-05</v>
+        <v>-2.4039909615055483e-05</v>
       </c>
       <c r="S8">
-        <v>6.0483320952118896e-05</v>
+        <v>-3.7246413668003554e-05</v>
       </c>
       <c r="T8">
-        <v>-4.3118920600893561e-05</v>
+        <v>9.1079901964059986e-05</v>
       </c>
       <c r="U8">
-        <v>5.4137266248193631e-05</v>
+        <v>0.00022175602752184205</v>
       </c>
       <c r="V8">
-        <v>0.00011977695022078335</v>
+        <v>0.0003513849927976253</v>
       </c>
       <c r="W8">
-        <v>0.00018705243795518194</v>
+        <v>0.000769543349896985</v>
       </c>
       <c r="X8">
-        <v>0.0004913479309294731</v>
+        <v>-3.6324449322708719e-05</v>
       </c>
       <c r="Y8">
-        <v>0.0010978483904407641</v>
+        <v>-8.8974886706919552e-05</v>
       </c>
       <c r="Z8">
-        <v>-4.522272122790604e-05</v>
+        <v>5.285445932202786e-05</v>
       </c>
       <c r="AA8">
-        <v>8.0340995526613057e-05</v>
+        <v>3.2123447875525299e-05</v>
       </c>
       <c r="AB8">
-        <v>0.00019839081252925948</v>
+        <v>5.362024703079349e-05</v>
       </c>
       <c r="AC8">
-        <v>0.00011279705654526346</v>
+        <v>-1.5459636173135441e-05</v>
       </c>
       <c r="AD8">
-        <v>0.00012739588607572666</v>
+        <v>3.2777159819301132e-05</v>
       </c>
       <c r="AE8">
-        <v>6.2411795254526141e-05</v>
+        <v>2.4805335383795338e-05</v>
       </c>
       <c r="AF8">
-        <v>3.0199903768108759e-05</v>
+        <v>2.8167527087327672e-06</v>
       </c>
       <c r="AG8">
-        <v>-4.7522259414865033e-05</v>
+        <v>4.6806591355737746e-06</v>
       </c>
       <c r="AH8">
-        <v>7.3389126967648348e-06</v>
+        <v>3.7243755954839588e-05</v>
       </c>
       <c r="AI8">
-        <v>-2.5280771717804598e-05</v>
-      </c>
-      <c r="AJ8">
-        <v>0.00012367372499727611</v>
-      </c>
-      <c r="AK8">
-        <v>-0.0029056184140483078</v>
+        <v>-0.0024133870012868893</v>
       </c>
     </row>
     <row r="9">
@@ -1305,112 +1251,106 @@
         <v>33</v>
       </c>
       <c r="B9">
-        <v>-0.19048767406637981</v>
+        <v>-0.36025040732867963</v>
       </c>
       <c r="C9">
-        <v>-9.6715316770636358e-05</v>
+        <v>0.00018803916794095022</v>
       </c>
       <c r="D9">
-        <v>-6.9309431216146215e-06</v>
+        <v>0.0020871683533679178</v>
       </c>
       <c r="E9">
-        <v>7.9823238894101803e-08</v>
+        <v>0.0021090443932507389</v>
       </c>
       <c r="F9">
-        <v>0.0020654718840749796</v>
+        <v>0.0017667256002488313</v>
       </c>
       <c r="G9">
-        <v>0.0020434787245531788</v>
+        <v>0.0021086397979223183</v>
       </c>
       <c r="H9">
-        <v>0.001821266881503312</v>
+        <v>0.0021083988136712008</v>
       </c>
       <c r="I9">
-        <v>0.0022297171573666089</v>
+        <v>0.0021630154235348737</v>
       </c>
       <c r="J9">
-        <v>0.0031093298681548667</v>
+        <v>0.0042791945053281084</v>
       </c>
       <c r="K9">
-        <v>0.001979074737966699</v>
+        <v>0.00017945082029095587</v>
       </c>
       <c r="L9">
-        <v>0.0020945452316248319</v>
+        <v>4.5283576011172862e-05</v>
       </c>
       <c r="M9">
-        <v>0.00035541435441676468</v>
+        <v>4.9604585912203271e-05</v>
       </c>
       <c r="N9">
-        <v>0.00032580038708374928</v>
+        <v>4.7138664410984951e-05</v>
       </c>
       <c r="O9">
-        <v>0.00010194590320954794</v>
+        <v>5.7869774781328644e-05</v>
       </c>
       <c r="P9">
-        <v>0.00016665881505841174</v>
+        <v>0.00020041402999989547</v>
       </c>
       <c r="Q9">
-        <v>9.2319156419083586e-05</v>
+        <v>6.3657106405295766e-05</v>
       </c>
       <c r="R9">
-        <v>-6.7707757489979346e-06</v>
+        <v>-1.090278735531964e-05</v>
       </c>
       <c r="S9">
-        <v>-8.1208873535783353e-06</v>
+        <v>-6.0940037529625996e-05</v>
       </c>
       <c r="T9">
-        <v>-3.0715747977917837e-05</v>
+        <v>6.999213058396495e-05</v>
       </c>
       <c r="U9">
-        <v>3.2143550216585069e-05</v>
+        <v>7.925130788153387e-05</v>
       </c>
       <c r="V9">
-        <v>0.00011960556855189529</v>
+        <v>0.0004394237064820612</v>
       </c>
       <c r="W9">
-        <v>0.00011896340925752569</v>
+        <v>0.00077552129634346251</v>
       </c>
       <c r="X9">
-        <v>0.00048695453163207381</v>
+        <v>-3.8749522387691831e-05</v>
       </c>
       <c r="Y9">
-        <v>0.0010174882548330177</v>
+        <v>-2.3845104977733469e-05</v>
       </c>
       <c r="Z9">
-        <v>-2.4016397220903199e-05</v>
+        <v>0.00014993704661024967</v>
       </c>
       <c r="AA9">
-        <v>-1.9662175965197534e-05</v>
+        <v>0.00012300481935884349</v>
       </c>
       <c r="AB9">
-        <v>0.00023229934460498262</v>
+        <v>7.6264365752959753e-05</v>
       </c>
       <c r="AC9">
-        <v>0.00015046715161416485</v>
+        <v>7.7531048207134723e-05</v>
       </c>
       <c r="AD9">
-        <v>0.00017382373752403732</v>
+        <v>0.00016385404757253771</v>
       </c>
       <c r="AE9">
-        <v>9.8726304086698682e-05</v>
+        <v>1.1865457425506851e-05</v>
       </c>
       <c r="AF9">
-        <v>0.00010976484539881637</v>
+        <v>2.2537754202507757e-06</v>
       </c>
       <c r="AG9">
-        <v>1.6276962793432672e-05</v>
+        <v>0.00015386211925594567</v>
       </c>
       <c r="AH9">
-        <v>1.3921870275758492e-05</v>
+        <v>-2.3520691061540422e-05</v>
       </c>
       <c r="AI9">
-        <v>-6.9409204249576764e-05</v>
-      </c>
-      <c r="AJ9">
-        <v>7.8782802852043641e-05</v>
-      </c>
-      <c r="AK9">
-        <v>-0.0026564637035712568</v>
+        <v>-0.002582096142993707</v>
       </c>
     </row>
     <row r="10">
@@ -1418,112 +1358,106 @@
         <v>34</v>
       </c>
       <c r="B10">
-        <v>-0.11958090783573948</v>
+        <v>0.15737459156980077</v>
       </c>
       <c r="C10">
-        <v>0.00013304390576172323</v>
+        <v>5.1197771764598007e-06</v>
       </c>
       <c r="D10">
-        <v>2.6319770202980336e-05</v>
+        <v>-2.0115308488022473e-05</v>
       </c>
       <c r="E10">
-        <v>-2.1279393631650998e-07</v>
+        <v>1.4118593225045939e-05</v>
       </c>
       <c r="F10">
-        <v>0.0020026998232934986</v>
+        <v>0.0001037959055400241</v>
       </c>
       <c r="G10">
-        <v>0.0020473901228867473</v>
+        <v>0.000499162153585417</v>
       </c>
       <c r="H10">
-        <v>0.0017680507784060937</v>
+        <v>0.00039531652231036374</v>
       </c>
       <c r="I10">
-        <v>0.0019647733387385511</v>
+        <v>-9.6477412201960693e-05</v>
       </c>
       <c r="J10">
-        <v>0.001979074737966699</v>
+        <v>0.00017945082029095587</v>
       </c>
       <c r="K10">
-        <v>0.0023853786545902757</v>
+        <v>0.0074102080942152846</v>
       </c>
       <c r="L10">
-        <v>0.0021633622334578245</v>
+        <v>0.0032290788500811763</v>
       </c>
       <c r="M10">
-        <v>5.1497033762574725e-05</v>
+        <v>-0.0040853893661426562</v>
       </c>
       <c r="N10">
-        <v>-9.0866635729285018e-05</v>
+        <v>7.6384446146617079e-05</v>
       </c>
       <c r="O10">
-        <v>0.00012338939884368378</v>
+        <v>0.00017008274704562862</v>
       </c>
       <c r="P10">
-        <v>0.00012830323147817313</v>
+        <v>0.00034860485841903114</v>
       </c>
       <c r="Q10">
-        <v>0.00010543891706890313</v>
+        <v>9.7647707584599822e-05</v>
       </c>
       <c r="R10">
-        <v>0.00012679830056682806</v>
+        <v>6.1269581888890234e-05</v>
       </c>
       <c r="S10">
-        <v>-1.1876330806251606e-05</v>
+        <v>0.00016744100269595696</v>
       </c>
       <c r="T10">
-        <v>3.9338056891625398e-06</v>
+        <v>0.00063230654186255972</v>
       </c>
       <c r="U10">
-        <v>5.6008102751753256e-06</v>
+        <v>0.0032118980277105877</v>
       </c>
       <c r="V10">
-        <v>9.7996192177115843e-05</v>
+        <v>0.0036789130441664463</v>
       </c>
       <c r="W10">
-        <v>0.00021082050307295311</v>
+        <v>0.0039392190568509015</v>
       </c>
       <c r="X10">
-        <v>0.00034669342221652424</v>
+        <v>-0.00016679003225496483</v>
       </c>
       <c r="Y10">
-        <v>0.00071294432274992669</v>
+        <v>3.7762544182087083e-05</v>
       </c>
       <c r="Z10">
-        <v>-3.8092029488725583e-05</v>
+        <v>0.00018681899800963376</v>
       </c>
       <c r="AA10">
-        <v>-9.5348212475492803e-05</v>
+        <v>0.00010292825587060895</v>
       </c>
       <c r="AB10">
-        <v>4.9044470238045592e-05</v>
+        <v>7.9016028483066278e-05</v>
       </c>
       <c r="AC10">
-        <v>3.0487672599616676e-05</v>
+        <v>0.0001535077105833311</v>
       </c>
       <c r="AD10">
-        <v>4.9970620505085557e-05</v>
+        <v>0.00035701943319050699</v>
       </c>
       <c r="AE10">
-        <v>-1.9916388888269491e-05</v>
+        <v>0.0002187728275894843</v>
       </c>
       <c r="AF10">
-        <v>2.3812120986320905e-05</v>
+        <v>-3.2565980408890923e-07</v>
       </c>
       <c r="AG10">
-        <v>3.5794081858431996e-05</v>
+        <v>0.00037063543131517608</v>
       </c>
       <c r="AH10">
-        <v>9.1424478038541258e-07</v>
+        <v>-9.4744370399680016e-05</v>
       </c>
       <c r="AI10">
-        <v>2.2814609825895851e-06</v>
-      </c>
-      <c r="AJ10">
-        <v>3.2271928767388684e-05</v>
-      </c>
-      <c r="AK10">
-        <v>-0.0030800114156639652</v>
+        <v>-0.0040142065628919503</v>
       </c>
     </row>
     <row r="11">
@@ -1531,112 +1465,106 @@
         <v>35</v>
       </c>
       <c r="B11">
-        <v>-0.28997947227204102</v>
+        <v>0.083971588068680172</v>
       </c>
       <c r="C11">
-        <v>0.00022012041977361829</v>
+        <v>-4.2400694082288633e-05</v>
       </c>
       <c r="D11">
-        <v>2.8641344872958962e-06</v>
+        <v>0.0001862923207223158</v>
       </c>
       <c r="E11">
-        <v>6.0006056155785776e-08</v>
+        <v>-9.3260023870279937e-05</v>
       </c>
       <c r="F11">
-        <v>0.0020712387838376337</v>
+        <v>9.6185840505532403e-05</v>
       </c>
       <c r="G11">
-        <v>0.0019961017245598818</v>
+        <v>0.00044981848966821586</v>
       </c>
       <c r="H11">
-        <v>0.0017493554418150405</v>
+        <v>0.00038087372306953724</v>
       </c>
       <c r="I11">
-        <v>0.0020923181677727732</v>
+        <v>-6.2624319062020188e-05</v>
       </c>
       <c r="J11">
-        <v>0.0020945452316248319</v>
+        <v>4.5283576011172862e-05</v>
       </c>
       <c r="K11">
-        <v>0.0021633622334578245</v>
+        <v>0.0032290788500811763</v>
       </c>
       <c r="L11">
-        <v>0.0043981795838537409</v>
+        <v>0.0031002153941946968</v>
       </c>
       <c r="M11">
-        <v>0.00021169738376874492</v>
+        <v>-0.00041434020189945052</v>
       </c>
       <c r="N11">
-        <v>-0.00014891080533422984</v>
+        <v>0.00015482852411966399</v>
       </c>
       <c r="O11">
-        <v>3.3295891704159973e-05</v>
+        <v>8.2149596255874971e-05</v>
       </c>
       <c r="P11">
-        <v>2.6368182619703785e-05</v>
+        <v>0.00030185717532583457</v>
       </c>
       <c r="Q11">
-        <v>-1.5488279850675116e-05</v>
+        <v>0.00017023512700279297</v>
       </c>
       <c r="R11">
-        <v>0.00015181253655580996</v>
+        <v>0.00028235702247508392</v>
       </c>
       <c r="S11">
-        <v>6.2227471161098728e-05</v>
+        <v>0.00047732123564773365</v>
       </c>
       <c r="T11">
-        <v>6.9006974218798443e-05</v>
+        <v>0.00047289903568890847</v>
       </c>
       <c r="U11">
-        <v>4.574616360110851e-05</v>
+        <v>0.0026454966364136681</v>
       </c>
       <c r="V11">
-        <v>5.2687433501897525e-05</v>
+        <v>0.0030849932598246382</v>
       </c>
       <c r="W11">
-        <v>3.737803418578595e-06</v>
+        <v>0.0033259568499667243</v>
       </c>
       <c r="X11">
-        <v>0.00036019533200513454</v>
+        <v>-0.0001492195673697877</v>
       </c>
       <c r="Y11">
-        <v>0.00063382182572373994</v>
+        <v>4.2739638244125274e-05</v>
       </c>
       <c r="Z11">
-        <v>-3.9087122093091754e-05</v>
+        <v>4.4432803402145657e-05</v>
       </c>
       <c r="AA11">
-        <v>-4.1284254635589463e-05</v>
+        <v>-5.0739540888786183e-05</v>
       </c>
       <c r="AB11">
-        <v>0.00015320647609406166</v>
+        <v>-2.6403228015850705e-05</v>
       </c>
       <c r="AC11">
-        <v>0.00012705031902480557</v>
+        <v>2.9783468960469656e-05</v>
       </c>
       <c r="AD11">
-        <v>7.0737092000580518e-05</v>
+        <v>0.00011865440852693141</v>
       </c>
       <c r="AE11">
-        <v>7.975825688759635e-05</v>
+        <v>-5.003866963365614e-05</v>
       </c>
       <c r="AF11">
-        <v>0.00016117107222544724</v>
+        <v>1.0516857342269178e-05</v>
       </c>
       <c r="AG11">
-        <v>4.7937875782734567e-05</v>
+        <v>5.5955232594965317e-05</v>
       </c>
       <c r="AH11">
-        <v>-5.6423937115830138e-07</v>
+        <v>-2.7635679663996337e-05</v>
       </c>
       <c r="AI11">
-        <v>0.00018715727023934812</v>
-      </c>
-      <c r="AJ11">
-        <v>-2.0544762476647953e-05</v>
-      </c>
-      <c r="AK11">
-        <v>-0.0027188541205461492</v>
+        <v>-0.0036131444182356887</v>
       </c>
     </row>
     <row r="12">
@@ -1644,112 +1572,106 @@
         <v>36</v>
       </c>
       <c r="B12">
-        <v>0.19246220580884188</v>
+        <v>-0.05101015186102266</v>
       </c>
       <c r="C12">
-        <v>3.0999900657781177e-05</v>
+        <v>-6.0906119824910346e-05</v>
       </c>
       <c r="D12">
-        <v>5.7557596450142848e-05</v>
+        <v>0.00027309987750996157</v>
       </c>
       <c r="E12">
-        <v>-5.1687671150398904e-07</v>
+        <v>0.00011537275032906199</v>
       </c>
       <c r="F12">
-        <v>0.00017105498378687696</v>
+        <v>8.1680466308312917e-05</v>
       </c>
       <c r="G12">
-        <v>2.8223029018945413e-05</v>
+        <v>0.00018633283427474867</v>
       </c>
       <c r="H12">
-        <v>6.6514188150040626e-05</v>
+        <v>0.00011825463761074928</v>
       </c>
       <c r="I12">
-        <v>0.0004957537782104113</v>
+        <v>8.9623365210410788e-05</v>
       </c>
       <c r="J12">
-        <v>0.00035541435441676468</v>
+        <v>4.9604585912203271e-05</v>
       </c>
       <c r="K12">
-        <v>5.1497033762574725e-05</v>
+        <v>-0.0040853893661426562</v>
       </c>
       <c r="L12">
-        <v>0.00021169738376874492</v>
+        <v>-0.00041434020189945052</v>
       </c>
       <c r="M12">
-        <v>0.0074923034310951453</v>
+        <v>0.0056550742588793567</v>
       </c>
       <c r="N12">
-        <v>0.0031866363209568289</v>
+        <v>0.00053972298045773537</v>
       </c>
       <c r="O12">
-        <v>-0.0039024694826555063</v>
+        <v>0.00041312332789258054</v>
       </c>
       <c r="P12">
-        <v>9.2356351574602257e-05</v>
+        <v>0.00015702916722206293</v>
       </c>
       <c r="Q12">
-        <v>0.00013048030078558449</v>
+        <v>8.1640007173089296e-05</v>
       </c>
       <c r="R12">
-        <v>0.00040036659471146116</v>
+        <v>8.659241108307745e-05</v>
       </c>
       <c r="S12">
-        <v>7.0190594616147259e-05</v>
+        <v>7.2625568124505723e-05</v>
       </c>
       <c r="T12">
-        <v>5.5124142924785216e-05</v>
+        <v>-0.00021872529679949171</v>
       </c>
       <c r="U12">
-        <v>0.00019182119029518847</v>
+        <v>-0.00055939481065233362</v>
       </c>
       <c r="V12">
-        <v>0.0006513196185803673</v>
+        <v>-0.00045654085313738161</v>
       </c>
       <c r="W12">
-        <v>0.0031556052964034076</v>
+        <v>-0.00033281241228975955</v>
       </c>
       <c r="X12">
-        <v>0.0036333819257838018</v>
+        <v>1.3508018690001934e-05</v>
       </c>
       <c r="Y12">
-        <v>0.0038086350141968688</v>
+        <v>3.3516023083526297e-06</v>
       </c>
       <c r="Z12">
-        <v>-0.00016792801303399941</v>
+        <v>5.3753552470530829e-06</v>
       </c>
       <c r="AA12">
-        <v>2.3582936305882834e-05</v>
+        <v>-4.7040608925575636e-05</v>
       </c>
       <c r="AB12">
-        <v>0.0001770860584250889</v>
+        <v>2.4527032191439961e-05</v>
       </c>
       <c r="AC12">
-        <v>0.00012066737429660291</v>
+        <v>-2.7358458102672961e-05</v>
       </c>
       <c r="AD12">
-        <v>9.3938644631497929e-05</v>
+        <v>-7.4634030212139476e-05</v>
       </c>
       <c r="AE12">
-        <v>0.00016406673375481216</v>
+        <v>-0.00015014202061696563</v>
       </c>
       <c r="AF12">
-        <v>0.00035967883933484685</v>
+        <v>1.4859872921433072e-05</v>
       </c>
       <c r="AG12">
-        <v>0.00021698156621521262</v>
+        <v>-0.00030833222323535297</v>
       </c>
       <c r="AH12">
-        <v>-3.6083818067304883e-06</v>
+        <v>-4.2100416755658121e-05</v>
       </c>
       <c r="AI12">
-        <v>0.00035750766520286238</v>
-      </c>
-      <c r="AJ12">
-        <v>-0.00014043889582977332</v>
-      </c>
-      <c r="AK12">
-        <v>-0.005378962444420857</v>
+        <v>-0.00015965131485163437</v>
       </c>
     </row>
     <row r="13">
@@ -1757,112 +1679,106 @@
         <v>37</v>
       </c>
       <c r="B13">
-        <v>-0.016906123795864349</v>
+        <v>-0.080449105696533005</v>
       </c>
       <c r="C13">
-        <v>-0.00010287980318271373</v>
+        <v>-3.361322185230121e-05</v>
       </c>
       <c r="D13">
-        <v>1.1994460097592127e-05</v>
+        <v>3.415495757352156e-05</v>
       </c>
       <c r="E13">
-        <v>-2.282167931725598e-07</v>
+        <v>0.00013157663846053444</v>
       </c>
       <c r="F13">
-        <v>0.00024591485347891197</v>
+        <v>0.00012419560983464682</v>
       </c>
       <c r="G13">
-        <v>1.6490432075175307e-05</v>
+        <v>0.00027573964584833103</v>
       </c>
       <c r="H13">
-        <v>6.170849700752178e-05</v>
+        <v>0.00016660764644241399</v>
       </c>
       <c r="I13">
-        <v>0.00038151294888219008</v>
+        <v>0.00012382017728425647</v>
       </c>
       <c r="J13">
-        <v>0.00032580038708374928</v>
+        <v>4.7138664410984951e-05</v>
       </c>
       <c r="K13">
-        <v>-9.0866635729285018e-05</v>
+        <v>7.6384446146617079e-05</v>
       </c>
       <c r="L13">
-        <v>-0.00014891080533422984</v>
+        <v>0.00015482852411966399</v>
       </c>
       <c r="M13">
-        <v>0.0031866363209568289</v>
+        <v>0.00053972298045773537</v>
       </c>
       <c r="N13">
-        <v>0.0033101474778905182</v>
+        <v>0.00085714983948552209</v>
       </c>
       <c r="O13">
-        <v>-0.00037535719091312406</v>
+        <v>0.00042212863405599837</v>
       </c>
       <c r="P13">
-        <v>0.00018423641443473117</v>
+        <v>0.00023414186729393713</v>
       </c>
       <c r="Q13">
-        <v>0.00017829896758694483</v>
+        <v>3.9947432961129814e-05</v>
       </c>
       <c r="R13">
-        <v>0.00038062178990733468</v>
+        <v>-1.9673944736484721e-05</v>
       </c>
       <c r="S13">
-        <v>0.00019663832564372776</v>
+        <v>4.0788415143500092e-05</v>
       </c>
       <c r="T13">
-        <v>0.00021035101059134161</v>
+        <v>-2.4394818592365961e-05</v>
       </c>
       <c r="U13">
-        <v>0.00037251560686469925</v>
+        <v>0.00014571898141819267</v>
       </c>
       <c r="V13">
-        <v>0.00047851206798052014</v>
+        <v>0.00024170927075665868</v>
       </c>
       <c r="W13">
-        <v>0.0027092356933511616</v>
+        <v>0.00043867877034087726</v>
       </c>
       <c r="X13">
-        <v>0.0031294106327237835</v>
+        <v>-8.9450452029444165e-06</v>
       </c>
       <c r="Y13">
-        <v>0.0034072040684542042</v>
+        <v>2.5349901746122248e-06</v>
       </c>
       <c r="Z13">
-        <v>-0.00014091800407097161</v>
+        <v>3.176840152891992e-05</v>
       </c>
       <c r="AA13">
-        <v>6.7132284963779482e-05</v>
+        <v>1.4427976619051325e-05</v>
       </c>
       <c r="AB13">
-        <v>5.0297396159034759e-05</v>
+        <v>4.8685890455250794e-06</v>
       </c>
       <c r="AC13">
-        <v>-3.4870515197211495e-05</v>
+        <v>1.6549667470975769e-05</v>
       </c>
       <c r="AD13">
-        <v>-1.1278162757271618e-05</v>
+        <v>1.0462524298719981e-05</v>
       </c>
       <c r="AE13">
-        <v>2.8744723553628723e-05</v>
+        <v>-2.3821879086441338e-05</v>
       </c>
       <c r="AF13">
-        <v>0.00012682828905954903</v>
+        <v>5.616813985184142e-06</v>
       </c>
       <c r="AG13">
-        <v>-8.0194557288379138e-05</v>
+        <v>-9.8069252881486258e-05</v>
       </c>
       <c r="AH13">
-        <v>1.4011853674495702e-05</v>
+        <v>-3.6525377833204319e-05</v>
       </c>
       <c r="AI13">
-        <v>2.2514017574319558e-05</v>
-      </c>
-      <c r="AJ13">
-        <v>-1.7625645102796765e-05</v>
-      </c>
-      <c r="AK13">
-        <v>-0.0037281263337097595</v>
+        <v>-0.00082028153442178608</v>
       </c>
     </row>
     <row r="14">
@@ -1870,112 +1786,106 @@
         <v>38</v>
       </c>
       <c r="B14">
-        <v>-0.051514847756305979</v>
+        <v>-0.028886584725227402</v>
       </c>
       <c r="C14">
-        <v>-6.2240004934265684e-05</v>
+        <v>-4.8211227158035332e-05</v>
       </c>
       <c r="D14">
-        <v>1.8493161870515433e-05</v>
+        <v>0.00017304750110305124</v>
       </c>
       <c r="E14">
-        <v>-1.7800012130098569e-07</v>
+        <v>9.2101658019669966e-05</v>
       </c>
       <c r="F14">
-        <v>0.00029837182396270402</v>
+        <v>0.00011222399271491033</v>
       </c>
       <c r="G14">
-        <v>0.00012623894597151562</v>
+        <v>0.00028512265825970701</v>
       </c>
       <c r="H14">
-        <v>7.7049602391855406e-05</v>
+        <v>0.00010625670043667456</v>
       </c>
       <c r="I14">
-        <v>0.0001634579299751185</v>
+        <v>0.00012507577302552488</v>
       </c>
       <c r="J14">
-        <v>0.00010194590320954794</v>
+        <v>5.7869774781328644e-05</v>
       </c>
       <c r="K14">
-        <v>0.00012338939884368378</v>
+        <v>0.00017008274704562862</v>
       </c>
       <c r="L14">
-        <v>3.3295891704159973e-05</v>
+        <v>8.2149596255874971e-05</v>
       </c>
       <c r="M14">
-        <v>-0.0039024694826555063</v>
+        <v>0.00041312332789258054</v>
       </c>
       <c r="N14">
-        <v>-0.00037535719091312406</v>
+        <v>0.00042212863405599837</v>
       </c>
       <c r="O14">
-        <v>0.0055419269637901371</v>
+        <v>0.00078169302244828506</v>
       </c>
       <c r="P14">
-        <v>0.00053479029744423184</v>
+        <v>3.2044993063426854e-05</v>
       </c>
       <c r="Q14">
-        <v>0.00040864257732344179</v>
+        <v>0.00012321554516546714</v>
       </c>
       <c r="R14">
-        <v>0.00017345002455418764</v>
+        <v>0.00021635474993374584</v>
       </c>
       <c r="S14">
-        <v>7.539192396890037e-05</v>
+        <v>0.00031014633916723653</v>
       </c>
       <c r="T14">
-        <v>8.225903245233162e-05</v>
+        <v>2.4679496354268625e-05</v>
       </c>
       <c r="U14">
-        <v>7.6712840879963147e-05</v>
+        <v>0.00018782629432656083</v>
       </c>
       <c r="V14">
-        <v>-0.00020577290392620511</v>
+        <v>0.00029188576739535427</v>
       </c>
       <c r="W14">
-        <v>-0.00054620077739307054</v>
+        <v>0.00050573604431693045</v>
       </c>
       <c r="X14">
-        <v>-0.00044372109775907888</v>
+        <v>-1.0285577321125531e-05</v>
       </c>
       <c r="Y14">
-        <v>-0.00033472777077171392</v>
+        <v>1.0451598659236535e-05</v>
       </c>
       <c r="Z14">
-        <v>1.1142088365938665e-05</v>
+        <v>7.8399976348818355e-05</v>
       </c>
       <c r="AA14">
-        <v>-3.6176184143933189e-07</v>
+        <v>8.0597869771119454e-05</v>
       </c>
       <c r="AB14">
-        <v>5.7726246558616754e-06</v>
+        <v>0.00010319506017073969</v>
       </c>
       <c r="AC14">
-        <v>-4.2572121139827388e-05</v>
+        <v>1.7201678399737103e-05</v>
       </c>
       <c r="AD14">
-        <v>3.0913068517185124e-05</v>
+        <v>6.7471731706362253e-05</v>
       </c>
       <c r="AE14">
-        <v>-2.4403755522718325e-05</v>
+        <v>1.4188838300472849e-05</v>
       </c>
       <c r="AF14">
-        <v>-7.0864633063615599e-05</v>
+        <v>9.5812939870465262e-06</v>
       </c>
       <c r="AG14">
-        <v>-0.00014196893536984535</v>
+        <v>-8.9809283282528017e-05</v>
       </c>
       <c r="AH14">
-        <v>1.3672779687304104e-05</v>
+        <v>-7.0967816654567714e-05</v>
       </c>
       <c r="AI14">
-        <v>-0.00032039198444023365</v>
-      </c>
-      <c r="AJ14">
-        <v>-5.052634472419023e-05</v>
-      </c>
-      <c r="AK14">
-        <v>-0.00059337538449408516</v>
+        <v>-0.0011770786664807337</v>
       </c>
     </row>
     <row r="15">
@@ -1983,112 +1893,106 @@
         <v>39</v>
       </c>
       <c r="B15">
-        <v>-0.082553486754600044</v>
+        <v>-0.11485641027320445</v>
       </c>
       <c r="C15">
-        <v>-4.2742447953118519e-05</v>
+        <v>0.00015964187899656531</v>
       </c>
       <c r="D15">
-        <v>3.243644708268023e-06</v>
+        <v>0.00024098226622748672</v>
       </c>
       <c r="E15">
-        <v>-4.180119020685555e-08</v>
+        <v>0.00025685583857601392</v>
       </c>
       <c r="F15">
-        <v>3.8287409453310363e-05</v>
+        <v>2.6036874602798177e-05</v>
       </c>
       <c r="G15">
-        <v>0.00014563989567054775</v>
+        <v>-5.3984468993179338e-05</v>
       </c>
       <c r="H15">
-        <v>0.00013056106850083636</v>
+        <v>2.4952126135451978e-05</v>
       </c>
       <c r="I15">
-        <v>0.00021995600760838719</v>
+        <v>0.00012121079140615248</v>
       </c>
       <c r="J15">
-        <v>0.00016665881505841174</v>
+        <v>0.00020041402999989547</v>
       </c>
       <c r="K15">
-        <v>0.00012830323147817313</v>
+        <v>0.00034860485841903114</v>
       </c>
       <c r="L15">
-        <v>2.6368182619703785e-05</v>
+        <v>0.00030185717532583457</v>
       </c>
       <c r="M15">
-        <v>9.2356351574602257e-05</v>
+        <v>0.00015702916722206293</v>
       </c>
       <c r="N15">
-        <v>0.00018423641443473117</v>
+        <v>0.00023414186729393713</v>
       </c>
       <c r="O15">
-        <v>0.00053479029744423184</v>
+        <v>3.2044993063426854e-05</v>
       </c>
       <c r="P15">
-        <v>0.00085214717192500455</v>
+        <v>0.009426341629225508</v>
       </c>
       <c r="Q15">
-        <v>0.00042717301835042229</v>
+        <v>0.0068137726272689426</v>
       </c>
       <c r="R15">
-        <v>0.00022831574977796531</v>
+        <v>0.0067577625961099744</v>
       </c>
       <c r="S15">
-        <v>3.3016835274407607e-05</v>
+        <v>0.0067408136400644997</v>
       </c>
       <c r="T15">
-        <v>-3.0651886088650264e-05</v>
+        <v>-0.00011777917643881022</v>
       </c>
       <c r="U15">
-        <v>2.876497494133594e-05</v>
+        <v>0.00038688893363880315</v>
       </c>
       <c r="V15">
-        <v>-1.9320896881787098e-05</v>
+        <v>0.00055400873771308933</v>
       </c>
       <c r="W15">
-        <v>0.00015476411292640716</v>
+        <v>0.00046371833807942004</v>
       </c>
       <c r="X15">
-        <v>0.0002500355632349666</v>
+        <v>-2.9039404761879379e-05</v>
       </c>
       <c r="Y15">
-        <v>0.0004489876661003785</v>
+        <v>-0.00011733515753141401</v>
       </c>
       <c r="Z15">
-        <v>-8.7127622993345505e-06</v>
+        <v>0.00011420262847560651</v>
       </c>
       <c r="AA15">
-        <v>3.181593351948706e-06</v>
+        <v>0.00016597672273013959</v>
       </c>
       <c r="AB15">
-        <v>4.0226663270417082e-05</v>
+        <v>0.00016024217855355183</v>
       </c>
       <c r="AC15">
-        <v>2.1456531395724183e-05</v>
+        <v>0.00011097867444821892</v>
       </c>
       <c r="AD15">
-        <v>1.1429507838074302e-05</v>
+        <v>0.00021100525375209183</v>
       </c>
       <c r="AE15">
-        <v>2.3669353205774937e-05</v>
+        <v>0.00039010103324478698</v>
       </c>
       <c r="AF15">
-        <v>1.8138429968336334e-05</v>
+        <v>5.7254640730687004e-06</v>
       </c>
       <c r="AG15">
-        <v>-1.8294509765440727e-05</v>
+        <v>1.2088203191898579e-05</v>
       </c>
       <c r="AH15">
-        <v>5.9739552814932e-06</v>
+        <v>-4.9005125978268584e-05</v>
       </c>
       <c r="AI15">
-        <v>-9.9376228560866013e-05</v>
-      </c>
-      <c r="AJ15">
-        <v>-3.6944388681503179e-05</v>
-      </c>
-      <c r="AK15">
-        <v>-0.00088759852567903456</v>
+        <v>-0.007646923409067169</v>
       </c>
     </row>
     <row r="16">
@@ -2096,112 +2000,106 @@
         <v>40</v>
       </c>
       <c r="B16">
-        <v>-0.057766580112118583</v>
+        <v>-0.099438391666721845</v>
       </c>
       <c r="C16">
-        <v>-7.1684750782153312e-05</v>
+        <v>-2.9367506558327801e-05</v>
       </c>
       <c r="D16">
-        <v>-3.2481501141426011e-06</v>
+        <v>0.0002049088881617481</v>
       </c>
       <c r="E16">
-        <v>-1.8257074853130559e-08</v>
+        <v>7.6911989027215739e-05</v>
       </c>
       <c r="F16">
-        <v>0.00016194203110046258</v>
+        <v>3.0606587825475549e-05</v>
       </c>
       <c r="G16">
-        <v>0.00013243328503286059</v>
+        <v>6.9483088424569491e-05</v>
       </c>
       <c r="H16">
-        <v>0.00010424122871433243</v>
+        <v>1.6276286501519304e-06</v>
       </c>
       <c r="I16">
-        <v>0.00021977304420419899</v>
+        <v>-5.1614434372137608e-06</v>
       </c>
       <c r="J16">
-        <v>9.2319156419083586e-05</v>
+        <v>6.3657106405295766e-05</v>
       </c>
       <c r="K16">
-        <v>0.00010543891706890313</v>
+        <v>9.7647707584599822e-05</v>
       </c>
       <c r="L16">
-        <v>-1.5488279850675116e-05</v>
+        <v>0.00017023512700279297</v>
       </c>
       <c r="M16">
-        <v>0.00013048030078558449</v>
+        <v>8.1640007173089296e-05</v>
       </c>
       <c r="N16">
-        <v>0.00017829896758694483</v>
+        <v>3.9947432961129814e-05</v>
       </c>
       <c r="O16">
-        <v>0.00040864257732344179</v>
+        <v>0.00012321554516546714</v>
       </c>
       <c r="P16">
-        <v>0.00042717301835042229</v>
+        <v>0.0068137726272689426</v>
       </c>
       <c r="Q16">
-        <v>0.00081044016801293001</v>
+        <v>0.0073181904543887701</v>
       </c>
       <c r="R16">
-        <v>5.0624637336585182e-05</v>
+        <v>0.0069913547073796947</v>
       </c>
       <c r="S16">
-        <v>0.00012371502958618926</v>
+        <v>0.0070188449262131893</v>
       </c>
       <c r="T16">
-        <v>0.00017401398144694147</v>
+        <v>-0.00019017400239543304</v>
       </c>
       <c r="U16">
-        <v>0.00024760958492600247</v>
+        <v>-2.4202738745484134e-07</v>
       </c>
       <c r="V16">
-        <v>3.0141678541860193e-05</v>
+        <v>-2.6207257167606968e-05</v>
       </c>
       <c r="W16">
-        <v>0.00021945842890863947</v>
+        <v>1.6812808064698651e-05</v>
       </c>
       <c r="X16">
-        <v>0.00032337329010795313</v>
+        <v>-1.5446679067544567e-05</v>
       </c>
       <c r="Y16">
-        <v>0.00055503397386503595</v>
+        <v>-2.0611295039211402e-05</v>
       </c>
       <c r="Z16">
-        <v>-8.1337547318097298e-06</v>
+        <v>0.00039977578339571874</v>
       </c>
       <c r="AA16">
-        <v>1.7334835094153639e-05</v>
+        <v>0.00039619269341183844</v>
       </c>
       <c r="AB16">
-        <v>8.0581684497851988e-05</v>
+        <v>0.00039999263156205271</v>
       </c>
       <c r="AC16">
-        <v>8.3807967486456704e-05</v>
+        <v>0.00032778991844844511</v>
       </c>
       <c r="AD16">
-        <v>0.00010132380066673349</v>
+        <v>0.00040526383753041113</v>
       </c>
       <c r="AE16">
-        <v>1.3751992204978332e-05</v>
+        <v>0.00037619705005900988</v>
       </c>
       <c r="AF16">
-        <v>6.7733099180269083e-05</v>
+        <v>-2.857098044788532e-07</v>
       </c>
       <c r="AG16">
-        <v>6.9540725960201121e-07</v>
+        <v>4.3779515320177889e-05</v>
       </c>
       <c r="AH16">
-        <v>1.118153308104632e-05</v>
+        <v>2.3744716712641081e-05</v>
       </c>
       <c r="AI16">
-        <v>-9.6747092675855922e-05</v>
-      </c>
-      <c r="AJ16">
-        <v>-6.6631928615452647e-05</v>
-      </c>
-      <c r="AK16">
-        <v>-0.0010156987188927886</v>
+        <v>-0.0074153616530795467</v>
       </c>
     </row>
     <row r="17">
@@ -2209,112 +2107,106 @@
         <v>41</v>
       </c>
       <c r="B17">
-        <v>-0.10450723923137492</v>
+        <v>-0.083042836433586745</v>
       </c>
       <c r="C17">
-        <v>0.0001342129335474713</v>
+        <v>-5.3783345333062307e-05</v>
       </c>
       <c r="D17">
-        <v>2.03879574622578e-05</v>
+        <v>0.00013961429365073885</v>
       </c>
       <c r="E17">
-        <v>-2.3308044762955454e-07</v>
+        <v>5.8410909162380639e-05</v>
       </c>
       <c r="F17">
-        <v>0.00022838431649253518</v>
+        <v>-5.2813169843047366e-06</v>
       </c>
       <c r="G17">
-        <v>0.00028018013986952893</v>
+        <v>-4.2746946247138073e-05</v>
       </c>
       <c r="H17">
-        <v>1.1699965530151488e-05</v>
+        <v>-3.8034219591053182e-05</v>
       </c>
       <c r="I17">
-        <v>-4.2162219541459116e-05</v>
+        <v>-2.4039909615055483e-05</v>
       </c>
       <c r="J17">
-        <v>-6.7707757489979346e-06</v>
+        <v>-1.090278735531964e-05</v>
       </c>
       <c r="K17">
-        <v>0.00012679830056682806</v>
+        <v>6.1269581888890234e-05</v>
       </c>
       <c r="L17">
-        <v>0.00015181253655580996</v>
+        <v>0.00028235702247508392</v>
       </c>
       <c r="M17">
-        <v>0.00040036659471146116</v>
+        <v>8.659241108307745e-05</v>
       </c>
       <c r="N17">
-        <v>0.00038062178990733468</v>
+        <v>-1.9673944736484721e-05</v>
       </c>
       <c r="O17">
-        <v>0.00017345002455418764</v>
+        <v>0.00021635474993374584</v>
       </c>
       <c r="P17">
-        <v>0.00022831574977796531</v>
+        <v>0.0067577625961099744</v>
       </c>
       <c r="Q17">
-        <v>5.0624637336585182e-05</v>
+        <v>0.0069913547073796947</v>
       </c>
       <c r="R17">
-        <v>0.0096316733954500151</v>
+        <v>0.0072937728143594328</v>
       </c>
       <c r="S17">
-        <v>0.006960530824811368</v>
+        <v>0.0071502877158113286</v>
       </c>
       <c r="T17">
-        <v>0.006880229585386052</v>
+        <v>-0.00015611331133342095</v>
       </c>
       <c r="U17">
-        <v>0.0068631250994986778</v>
+        <v>6.7493561899841393e-05</v>
       </c>
       <c r="V17">
-        <v>-0.00011630626322391521</v>
+        <v>-1.1335263924642028e-05</v>
       </c>
       <c r="W17">
-        <v>0.00037061157523519354</v>
+        <v>5.8702360032054837e-05</v>
       </c>
       <c r="X17">
-        <v>0.00053355947791007205</v>
+        <v>-1.4914311524460619e-05</v>
       </c>
       <c r="Y17">
-        <v>0.00043500993381972563</v>
+        <v>-2.791809035572186e-05</v>
       </c>
       <c r="Z17">
-        <v>-2.6951325317340401e-05</v>
+        <v>0.00042834881384021077</v>
       </c>
       <c r="AA17">
-        <v>-0.00012142235918183677</v>
+        <v>0.00038964786848787094</v>
       </c>
       <c r="AB17">
-        <v>0.00015721225935875181</v>
+        <v>0.00039390262233660652</v>
       </c>
       <c r="AC17">
-        <v>0.00022045493845321632</v>
+        <v>0.00031836766960773727</v>
       </c>
       <c r="AD17">
-        <v>0.00021139810342213176</v>
+        <v>0.00039693324408751564</v>
       </c>
       <c r="AE17">
-        <v>0.00015404135002411445</v>
+        <v>0.00041366543595435884</v>
       </c>
       <c r="AF17">
-        <v>0.00026289074750658766</v>
+        <v>3.6208117601797146e-06</v>
       </c>
       <c r="AG17">
-        <v>0.0004219850881182784</v>
+        <v>4.5946337358625244e-05</v>
       </c>
       <c r="AH17">
-        <v>6.3090179502545336e-06</v>
+        <v>2.3263439245871376e-05</v>
       </c>
       <c r="AI17">
-        <v>3.2992963550648041e-05</v>
-      </c>
-      <c r="AJ17">
-        <v>-3.3360425697209761e-05</v>
-      </c>
-      <c r="AK17">
-        <v>-0.0082142232681731674</v>
+        <v>-0.0076541926183776501</v>
       </c>
     </row>
     <row r="18">
@@ -2322,112 +2214,106 @@
         <v>42</v>
       </c>
       <c r="B18">
-        <v>-0.075518641858778352</v>
+        <v>-0.13606630682082815</v>
       </c>
       <c r="C18">
-        <v>-3.492902222563712e-05</v>
+        <v>-0.00011313088460214999</v>
       </c>
       <c r="D18">
-        <v>-3.6424690642633323e-07</v>
+        <v>0.00035347518107974138</v>
       </c>
       <c r="E18">
-        <v>-1.7919896359651921e-08</v>
+        <v>0.00011723908016807649</v>
       </c>
       <c r="F18">
-        <v>0.00020243144669056809</v>
+        <v>2.2049062175248733e-05</v>
       </c>
       <c r="G18">
-        <v>9.1832062200270675e-05</v>
+        <v>0.0001053769319945768</v>
       </c>
       <c r="H18">
-        <v>2.661754862446318e-05</v>
+        <v>3.104761253483148e-05</v>
       </c>
       <c r="I18">
-        <v>6.0483320952118896e-05</v>
+        <v>-3.7246413668003554e-05</v>
       </c>
       <c r="J18">
-        <v>-8.1208873535783353e-06</v>
+        <v>-6.0940037529625996e-05</v>
       </c>
       <c r="K18">
-        <v>-1.1876330806251606e-05</v>
+        <v>0.00016744100269595696</v>
       </c>
       <c r="L18">
-        <v>6.2227471161098728e-05</v>
+        <v>0.00047732123564773365</v>
       </c>
       <c r="M18">
-        <v>7.0190594616147259e-05</v>
+        <v>7.2625568124505723e-05</v>
       </c>
       <c r="N18">
-        <v>0.00019663832564372776</v>
+        <v>4.0788415143500092e-05</v>
       </c>
       <c r="O18">
-        <v>7.539192396890037e-05</v>
+        <v>0.00031014633916723653</v>
       </c>
       <c r="P18">
-        <v>3.3016835274407607e-05</v>
+        <v>0.0067408136400644997</v>
       </c>
       <c r="Q18">
-        <v>0.00012371502958618926</v>
+        <v>0.0070188449262131893</v>
       </c>
       <c r="R18">
-        <v>0.006960530824811368</v>
+        <v>0.0071502877158113286</v>
       </c>
       <c r="S18">
-        <v>0.007475332021060585</v>
+        <v>0.0077670221172790868</v>
       </c>
       <c r="T18">
-        <v>0.0071263396898190792</v>
+        <v>-0.00021038681129576778</v>
       </c>
       <c r="U18">
-        <v>0.0071392658714457963</v>
+        <v>0.00017642226562673922</v>
       </c>
       <c r="V18">
-        <v>-0.00019814679312695627</v>
+        <v>0.00013642230501540332</v>
       </c>
       <c r="W18">
-        <v>-1.7942532772350067e-05</v>
+        <v>0.00025997622043381517</v>
       </c>
       <c r="X18">
-        <v>-4.2471438949593342e-05</v>
+        <v>-1.2964826891340041e-05</v>
       </c>
       <c r="Y18">
-        <v>-2.8065318577845389e-06</v>
+        <v>1.2286128425974523e-06</v>
       </c>
       <c r="Z18">
-        <v>-1.3604001049854248e-05</v>
+        <v>0.00050815612522661473</v>
       </c>
       <c r="AA18">
-        <v>-2.7502158129465463e-05</v>
+        <v>0.00043808842808900489</v>
       </c>
       <c r="AB18">
-        <v>0.00043792243425426741</v>
+        <v>0.00045272675287770861</v>
       </c>
       <c r="AC18">
-        <v>0.00044953031904174882</v>
+        <v>0.00038264462745451165</v>
       </c>
       <c r="AD18">
-        <v>0.00044366328659484807</v>
+        <v>0.00049446962267037727</v>
       </c>
       <c r="AE18">
-        <v>0.00036860541209909198</v>
+        <v>0.00032125317013082764</v>
       </c>
       <c r="AF18">
-        <v>0.00045108047264597604</v>
+        <v>6.4351374456237591e-06</v>
       </c>
       <c r="AG18">
-        <v>0.00040657107945525444</v>
+        <v>4.3708144531398943e-05</v>
       </c>
       <c r="AH18">
-        <v>3.9528066487977713e-07</v>
+        <v>7.8244783439976838e-05</v>
       </c>
       <c r="AI18">
-        <v>6.2750748413151203e-05</v>
-      </c>
-      <c r="AJ18">
-        <v>3.6761823225330524e-05</v>
-      </c>
-      <c r="AK18">
-        <v>-0.0075311980341891197</v>
+        <v>-0.0080109756220309476</v>
       </c>
     </row>
     <row r="19">
@@ -2435,112 +2321,106 @@
         <v>43</v>
       </c>
       <c r="B19">
-        <v>-0.013338457624871319</v>
+        <v>0.19475512354932451</v>
       </c>
       <c r="C19">
-        <v>-3.5571747157914926e-05</v>
+        <v>3.3585706080962048e-07</v>
       </c>
       <c r="D19">
-        <v>2.9768829863696834e-06</v>
+        <v>-1.9174180004394734e-05</v>
       </c>
       <c r="E19">
-        <v>-7.6404521593637758e-09</v>
+        <v>7.8675240484065185e-05</v>
       </c>
       <c r="F19">
-        <v>0.00014961023123421049</v>
+        <v>3.3185996693455404e-05</v>
       </c>
       <c r="G19">
-        <v>5.7560987659392487e-05</v>
+        <v>0.00013915368209563547</v>
       </c>
       <c r="H19">
-        <v>2.5215092514105841e-06</v>
+        <v>0.00013130352291067067</v>
       </c>
       <c r="I19">
-        <v>-4.3118920600893561e-05</v>
+        <v>9.1079901964059986e-05</v>
       </c>
       <c r="J19">
-        <v>-3.0715747977917837e-05</v>
+        <v>6.999213058396495e-05</v>
       </c>
       <c r="K19">
-        <v>3.9338056891625398e-06</v>
+        <v>0.00063230654186255972</v>
       </c>
       <c r="L19">
-        <v>6.9006974218798443e-05</v>
+        <v>0.00047289903568890847</v>
       </c>
       <c r="M19">
-        <v>5.5124142924785216e-05</v>
+        <v>-0.00021872529679949171</v>
       </c>
       <c r="N19">
-        <v>0.00021035101059134161</v>
+        <v>-2.4394818592365961e-05</v>
       </c>
       <c r="O19">
-        <v>8.225903245233162e-05</v>
+        <v>2.4679496354268625e-05</v>
       </c>
       <c r="P19">
-        <v>-3.0651886088650264e-05</v>
+        <v>-0.00011777917643881022</v>
       </c>
       <c r="Q19">
-        <v>0.00017401398144694147</v>
+        <v>-0.00019017400239543304</v>
       </c>
       <c r="R19">
-        <v>0.006880229585386052</v>
+        <v>-0.00015611331133342095</v>
       </c>
       <c r="S19">
-        <v>0.0071263396898190792</v>
+        <v>-0.00021038681129576778</v>
       </c>
       <c r="T19">
-        <v>0.0074399238777659513</v>
+        <v>0.0010828886397138773</v>
       </c>
       <c r="U19">
-        <v>0.0072870594713744987</v>
+        <v>0.00095411326157021029</v>
       </c>
       <c r="V19">
-        <v>-0.00016190740334869234</v>
+        <v>0.0009969685137757589</v>
       </c>
       <c r="W19">
-        <v>1.0578835977466308e-05</v>
+        <v>0.0010934520904993467</v>
       </c>
       <c r="X19">
-        <v>-5.859065101626159e-05</v>
+        <v>-9.7975365989235442e-05</v>
       </c>
       <c r="Y19">
-        <v>-1.6522378890875856e-05</v>
+        <v>6.9257082614885125e-06</v>
       </c>
       <c r="Z19">
-        <v>-1.5519833150295023e-05</v>
+        <v>5.8451861510897723e-05</v>
       </c>
       <c r="AA19">
-        <v>-4.5184850812885835e-05</v>
+        <v>5.2488330671794366e-05</v>
       </c>
       <c r="AB19">
-        <v>0.00047455826863080416</v>
+        <v>2.1032802931347859e-05</v>
       </c>
       <c r="AC19">
-        <v>0.00045515397205222151</v>
+        <v>3.3098360869946624e-05</v>
       </c>
       <c r="AD19">
-        <v>0.00044579472625172131</v>
+        <v>2.1061296049569659e-05</v>
       </c>
       <c r="AE19">
-        <v>0.00037203166613365528</v>
+        <v>0.00011004290423317754</v>
       </c>
       <c r="AF19">
-        <v>0.0004470645319115639</v>
+        <v>-3.1269371662587711e-06</v>
       </c>
       <c r="AG19">
-        <v>0.00046032666736534544</v>
+        <v>-0.00013761921847101522</v>
       </c>
       <c r="AH19">
-        <v>2.9048955028014134e-06</v>
+        <v>-5.2297174353573331e-05</v>
       </c>
       <c r="AI19">
-        <v>6.6076337071089772e-05</v>
-      </c>
-      <c r="AJ19">
-        <v>2.7281207194245795e-05</v>
-      </c>
-      <c r="AK19">
-        <v>-0.0078956453265367523</v>
+        <v>-0.00073223072105569578</v>
       </c>
     </row>
     <row r="20">
@@ -2548,112 +2428,106 @@
         <v>44</v>
       </c>
       <c r="B20">
-        <v>-0.04264819766323568</v>
+        <v>0.079518653485038435</v>
       </c>
       <c r="C20">
-        <v>-8.4545928728930157e-05</v>
+        <v>3.897800193710734e-05</v>
       </c>
       <c r="D20">
-        <v>1.0292432767799328e-05</v>
+        <v>-3.2793598063826689e-05</v>
       </c>
       <c r="E20">
-        <v>-6.533851256180072e-08</v>
+        <v>9.0123156531705896e-05</v>
       </c>
       <c r="F20">
-        <v>0.00038255499253252179</v>
+        <v>4.759201680919038e-05</v>
       </c>
       <c r="G20">
-        <v>0.00010408204210283025</v>
+        <v>0.00021119581025745267</v>
       </c>
       <c r="H20">
-        <v>8.7750778236801545e-06</v>
+        <v>0.00014664378215088975</v>
       </c>
       <c r="I20">
-        <v>5.4137266248193631e-05</v>
+        <v>0.00022175602752184205</v>
       </c>
       <c r="J20">
-        <v>3.2143550216585069e-05</v>
+        <v>7.925130788153387e-05</v>
       </c>
       <c r="K20">
-        <v>5.6008102751753256e-06</v>
+        <v>0.0032118980277105877</v>
       </c>
       <c r="L20">
-        <v>4.574616360110851e-05</v>
+        <v>0.0026454966364136681</v>
       </c>
       <c r="M20">
-        <v>0.00019182119029518847</v>
+        <v>-0.00055939481065233362</v>
       </c>
       <c r="N20">
-        <v>0.00037251560686469925</v>
+        <v>0.00014571898141819267</v>
       </c>
       <c r="O20">
-        <v>7.6712840879963147e-05</v>
+        <v>0.00018782629432656083</v>
       </c>
       <c r="P20">
-        <v>2.876497494133594e-05</v>
+        <v>0.00038688893363880315</v>
       </c>
       <c r="Q20">
-        <v>0.00024760958492600247</v>
+        <v>-2.4202738745484134e-07</v>
       </c>
       <c r="R20">
-        <v>0.0068631250994986778</v>
+        <v>6.7493561899841393e-05</v>
       </c>
       <c r="S20">
-        <v>0.0071392658714457963</v>
+        <v>0.00017642226562673922</v>
       </c>
       <c r="T20">
-        <v>0.0072870594713744987</v>
+        <v>0.00095411326157021029</v>
       </c>
       <c r="U20">
-        <v>0.0078871029018913099</v>
+        <v>0.0035249377378211919</v>
       </c>
       <c r="V20">
-        <v>-0.00020871349241464665</v>
+        <v>0.0033561089904270564</v>
       </c>
       <c r="W20">
-        <v>9.6452086689876541e-05</v>
+        <v>0.0036402634101280343</v>
       </c>
       <c r="X20">
-        <v>7.7192051089696942e-05</v>
+        <v>-0.0002085859767480611</v>
       </c>
       <c r="Y20">
-        <v>0.00015214063173027079</v>
+        <v>2.5943844974372215e-05</v>
       </c>
       <c r="Z20">
-        <v>-1.4993509390343136e-05</v>
+        <v>2.768071263798029e-05</v>
       </c>
       <c r="AA20">
-        <v>-2.1733090131611501e-05</v>
+        <v>-2.6550282929700686e-05</v>
       </c>
       <c r="AB20">
-        <v>0.00055392495136093352</v>
+        <v>-3.9589942205490092e-05</v>
       </c>
       <c r="AC20">
-        <v>0.00050832725165993794</v>
+        <v>4.6144882518512828e-06</v>
       </c>
       <c r="AD20">
-        <v>0.00050851898057002048</v>
+        <v>0.0001070700554739681</v>
       </c>
       <c r="AE20">
-        <v>0.00044167620340231171</v>
+        <v>7.5686072508696781e-05</v>
       </c>
       <c r="AF20">
-        <v>0.00054349859132573459</v>
+        <v>4.5265732748416096e-06</v>
       </c>
       <c r="AG20">
-        <v>0.00037321764746299301</v>
+        <v>-2.3809894667179386e-05</v>
       </c>
       <c r="AH20">
-        <v>4.8929705299049164e-06</v>
+        <v>-6.8373762652340847e-05</v>
       </c>
       <c r="AI20">
-        <v>6.6273869017443449e-05</v>
-      </c>
-      <c r="AJ20">
-        <v>7.7407651909492357e-05</v>
-      </c>
-      <c r="AK20">
-        <v>-0.0084047649127244502</v>
+        <v>-0.0036109294228694145</v>
       </c>
     </row>
     <row r="21">
@@ -2661,112 +2535,106 @@
         <v>45</v>
       </c>
       <c r="B21">
-        <v>0.18587288408909039</v>
+        <v>0.20038459830311944</v>
       </c>
       <c r="C21">
-        <v>-1.5333079626743306e-06</v>
+        <v>-1.429762836629479e-06</v>
       </c>
       <c r="D21">
-        <v>5.478910716750254e-06</v>
+        <v>0.00034904637853419248</v>
       </c>
       <c r="E21">
-        <v>-5.131731462441057e-08</v>
+        <v>0.00023564401616686876</v>
       </c>
       <c r="F21">
-        <v>4.2393983027296228e-05</v>
+        <v>6.0529809378991268e-05</v>
       </c>
       <c r="G21">
-        <v>7.6936626433448784e-05</v>
+        <v>0.00054653907747107444</v>
       </c>
       <c r="H21">
-        <v>2.5072607670293513e-05</v>
+        <v>0.00051188472275484316</v>
       </c>
       <c r="I21">
-        <v>0.00011977695022078335</v>
+        <v>0.0003513849927976253</v>
       </c>
       <c r="J21">
-        <v>0.00011960556855189529</v>
+        <v>0.0004394237064820612</v>
       </c>
       <c r="K21">
-        <v>9.7996192177115843e-05</v>
+        <v>0.0036789130441664463</v>
       </c>
       <c r="L21">
-        <v>5.2687433501897525e-05</v>
+        <v>0.0030849932598246382</v>
       </c>
       <c r="M21">
-        <v>0.0006513196185803673</v>
+        <v>-0.00045654085313738161</v>
       </c>
       <c r="N21">
-        <v>0.00047851206798052014</v>
+        <v>0.00024170927075665868</v>
       </c>
       <c r="O21">
-        <v>-0.00020577290392620511</v>
+        <v>0.00029188576739535427</v>
       </c>
       <c r="P21">
-        <v>-1.9320896881787098e-05</v>
+        <v>0.00055400873771308933</v>
       </c>
       <c r="Q21">
-        <v>3.0141678541860193e-05</v>
+        <v>-2.6207257167606968e-05</v>
       </c>
       <c r="R21">
-        <v>-0.00011630626322391521</v>
+        <v>-1.1335263924642028e-05</v>
       </c>
       <c r="S21">
-        <v>-0.00019814679312695627</v>
+        <v>0.00013642230501540332</v>
       </c>
       <c r="T21">
-        <v>-0.00016190740334869234</v>
+        <v>0.0009969685137757589</v>
       </c>
       <c r="U21">
-        <v>-0.00020871349241464665</v>
+        <v>0.0033561089904270564</v>
       </c>
       <c r="V21">
-        <v>0.0010879734232769349</v>
+        <v>0.0044746450417367783</v>
       </c>
       <c r="W21">
-        <v>0.00096492220489102559</v>
+        <v>0.0042381389294276536</v>
       </c>
       <c r="X21">
-        <v>0.0010060107628910462</v>
+        <v>-0.00021322219030547236</v>
       </c>
       <c r="Y21">
-        <v>0.0010986902141187286</v>
+        <v>2.7666029659508765e-05</v>
       </c>
       <c r="Z21">
-        <v>-9.7735378788608415e-05</v>
+        <v>8.6603241043895548e-05</v>
       </c>
       <c r="AA21">
-        <v>8.430203632331238e-06</v>
+        <v>1.9365119552465504e-06</v>
       </c>
       <c r="AB21">
-        <v>6.2215016927632811e-05</v>
+        <v>3.0966175405273098e-05</v>
       </c>
       <c r="AC21">
-        <v>5.551159091172304e-05</v>
+        <v>7.6567174047375945e-05</v>
       </c>
       <c r="AD21">
-        <v>2.5427207967291783e-05</v>
+        <v>0.00018787443626774088</v>
       </c>
       <c r="AE21">
-        <v>3.5370838212990833e-05</v>
+        <v>0.00020760721124195796</v>
       </c>
       <c r="AF21">
-        <v>2.186656129644343e-05</v>
+        <v>9.0116810501175454e-06</v>
       </c>
       <c r="AG21">
-        <v>0.00011343594944440005</v>
+        <v>9.8761563418469159e-05</v>
       </c>
       <c r="AH21">
-        <v>-3.2051049512609733e-06</v>
+        <v>-0.00010339082551956988</v>
       </c>
       <c r="AI21">
-        <v>-0.00014341427858625163</v>
-      </c>
-      <c r="AJ21">
-        <v>-5.5734186276285567e-05</v>
-      </c>
-      <c r="AK21">
-        <v>-0.00087039852192216031</v>
+        <v>-0.0044241714089441721</v>
       </c>
     </row>
     <row r="22">
@@ -2774,112 +2642,106 @@
         <v>46</v>
       </c>
       <c r="B22">
-        <v>0.060779790579179357</v>
+        <v>0.23388741978217065</v>
       </c>
       <c r="C22">
-        <v>1.7320127798754005e-05</v>
+        <v>-5.9422502834602001e-05</v>
       </c>
       <c r="D22">
-        <v>3.6238612205948006e-06</v>
+        <v>0.00080519745304555952</v>
       </c>
       <c r="E22">
-        <v>-8.4522838499709036e-08</v>
+        <v>0.00072939579332476838</v>
       </c>
       <c r="F22">
-        <v>6.7013509459798448e-05</v>
+        <v>0.00035402050081689601</v>
       </c>
       <c r="G22">
-        <v>0.000130512544865558</v>
+        <v>0.0012059413454082234</v>
       </c>
       <c r="H22">
-        <v>2.7925235297103024e-05</v>
+        <v>0.001063574258902799</v>
       </c>
       <c r="I22">
-        <v>0.00018705243795518194</v>
+        <v>0.000769543349896985</v>
       </c>
       <c r="J22">
-        <v>0.00011896340925752569</v>
+        <v>0.00077552129634346251</v>
       </c>
       <c r="K22">
-        <v>0.00021082050307295311</v>
+        <v>0.0039392190568509015</v>
       </c>
       <c r="L22">
-        <v>3.737803418578595e-06</v>
+        <v>0.0033259568499667243</v>
       </c>
       <c r="M22">
-        <v>0.0031556052964034076</v>
+        <v>-0.00033281241228975955</v>
       </c>
       <c r="N22">
-        <v>0.0027092356933511616</v>
+        <v>0.00043867877034087726</v>
       </c>
       <c r="O22">
-        <v>-0.00054620077739307054</v>
+        <v>0.00050573604431693045</v>
       </c>
       <c r="P22">
-        <v>0.00015476411292640716</v>
+        <v>0.00046371833807942004</v>
       </c>
       <c r="Q22">
-        <v>0.00021945842890863947</v>
+        <v>1.6812808064698651e-05</v>
       </c>
       <c r="R22">
-        <v>0.00037061157523519354</v>
+        <v>5.8702360032054837e-05</v>
       </c>
       <c r="S22">
-        <v>-1.7942532772350067e-05</v>
+        <v>0.00025997622043381517</v>
       </c>
       <c r="T22">
-        <v>1.0578835977466308e-05</v>
+        <v>0.0010934520904993467</v>
       </c>
       <c r="U22">
-        <v>9.6452086689876541e-05</v>
+        <v>0.0036402634101280343</v>
       </c>
       <c r="V22">
-        <v>0.00096492220489102559</v>
+        <v>0.0042381389294276536</v>
       </c>
       <c r="W22">
-        <v>0.0035235765768407623</v>
+        <v>0.0054224935541577687</v>
       </c>
       <c r="X22">
-        <v>0.0033564437282770543</v>
+        <v>-0.00025246361274046842</v>
       </c>
       <c r="Y22">
-        <v>0.0036511541137874536</v>
+        <v>2.9979686537174189e-05</v>
       </c>
       <c r="Z22">
-        <v>-0.00020362293739623115</v>
+        <v>0.00016191570019673729</v>
       </c>
       <c r="AA22">
-        <v>3.5515039328621321e-05</v>
+        <v>2.6869125629069759e-05</v>
       </c>
       <c r="AB22">
-        <v>4.9105307281538564e-05</v>
+        <v>5.4205815082350884e-05</v>
       </c>
       <c r="AC22">
-        <v>-4.7251357243268712e-06</v>
+        <v>0.00013184405026467035</v>
       </c>
       <c r="AD22">
-        <v>-1.8605951851966268e-05</v>
+        <v>0.00019495295271682251</v>
       </c>
       <c r="AE22">
-        <v>2.2304809881174177e-05</v>
+        <v>0.00014314395619293653</v>
       </c>
       <c r="AF22">
-        <v>0.00011837024832619996</v>
+        <v>1.1770680230066018e-05</v>
       </c>
       <c r="AG22">
-        <v>8.2314725543089447e-05</v>
+        <v>-0.00017259147849396899</v>
       </c>
       <c r="AH22">
-        <v>6.2405451611873328e-06</v>
+        <v>-0.00014225457160009481</v>
       </c>
       <c r="AI22">
-        <v>-3.4047526304822797e-05</v>
-      </c>
-      <c r="AJ22">
-        <v>-5.7130189632925753e-05</v>
-      </c>
-      <c r="AK22">
-        <v>-0.0035894863773359397</v>
+        <v>-0.0053221193019862469</v>
       </c>
     </row>
     <row r="23">
@@ -2887,112 +2749,106 @@
         <v>47</v>
       </c>
       <c r="B23">
-        <v>0.17599427622298103</v>
+        <v>0.01736585391862102</v>
       </c>
       <c r="C23">
-        <v>-2.7578672969093225e-05</v>
+        <v>-4.802813257907438e-07</v>
       </c>
       <c r="D23">
-        <v>7.3128771778003263e-06</v>
+        <v>-7.8230614138234162e-06</v>
       </c>
       <c r="E23">
-        <v>-1.126472656274382e-07</v>
+        <v>-3.1864712784610305e-05</v>
       </c>
       <c r="F23">
-        <v>0.00041790608657136272</v>
+        <v>-1.1239453734116289e-05</v>
       </c>
       <c r="G23">
-        <v>0.00027336396351494187</v>
+        <v>-4.7557013707125948e-05</v>
       </c>
       <c r="H23">
-        <v>4.9524922024530302e-05</v>
+        <v>-2.6566527801927502e-05</v>
       </c>
       <c r="I23">
-        <v>0.0004913479309294731</v>
+        <v>-3.6324449322708719e-05</v>
       </c>
       <c r="J23">
-        <v>0.00048695453163207381</v>
+        <v>-3.8749522387691831e-05</v>
       </c>
       <c r="K23">
-        <v>0.00034669342221652424</v>
+        <v>-0.00016679003225496483</v>
       </c>
       <c r="L23">
-        <v>0.00036019533200513454</v>
+        <v>-0.0001492195673697877</v>
       </c>
       <c r="M23">
-        <v>0.0036333819257838018</v>
+        <v>1.3508018690001934e-05</v>
       </c>
       <c r="N23">
-        <v>0.0031294106327237835</v>
+        <v>-8.9450452029444165e-06</v>
       </c>
       <c r="O23">
-        <v>-0.00044372109775907888</v>
+        <v>-1.0285577321125531e-05</v>
       </c>
       <c r="P23">
-        <v>0.0002500355632349666</v>
+        <v>-2.9039404761879379e-05</v>
       </c>
       <c r="Q23">
-        <v>0.00032337329010795313</v>
+        <v>-1.5446679067544567e-05</v>
       </c>
       <c r="R23">
-        <v>0.00053355947791007205</v>
+        <v>-1.4914311524460619e-05</v>
       </c>
       <c r="S23">
-        <v>-4.2471438949593342e-05</v>
+        <v>-1.2964826891340041e-05</v>
       </c>
       <c r="T23">
-        <v>-5.859065101626159e-05</v>
+        <v>-9.7975365989235442e-05</v>
       </c>
       <c r="U23">
-        <v>7.7192051089696942e-05</v>
+        <v>-0.0002085859767480611</v>
       </c>
       <c r="V23">
-        <v>0.0010060107628910462</v>
+        <v>-0.00021322219030547236</v>
       </c>
       <c r="W23">
-        <v>0.0033564437282770543</v>
+        <v>-0.00025246361274046842</v>
       </c>
       <c r="X23">
-        <v>0.0044514737926923311</v>
+        <v>3.5907221896566375e-05</v>
       </c>
       <c r="Y23">
-        <v>0.0042274158152500524</v>
+        <v>-5.0879498333561162e-06</v>
       </c>
       <c r="Z23">
-        <v>-0.0002080005552566935</v>
+        <v>-1.4893099836860317e-05</v>
       </c>
       <c r="AA23">
-        <v>3.8055925120422164e-05</v>
+        <v>-1.3096336156970693e-05</v>
       </c>
       <c r="AB23">
-        <v>0.000109941145362372</v>
+        <v>-7.4033122276246515e-06</v>
       </c>
       <c r="AC23">
-        <v>2.3099686328289723e-05</v>
+        <v>-1.2136815108224061e-05</v>
       </c>
       <c r="AD23">
-        <v>5.238172533216694e-05</v>
+        <v>-8.7635720959443405e-06</v>
       </c>
       <c r="AE23">
-        <v>9.3594557088700053e-05</v>
+        <v>-1.5430911525350005e-05</v>
       </c>
       <c r="AF23">
-        <v>0.00020361227965020592</v>
+        <v>1.9760107536395215e-06</v>
       </c>
       <c r="AG23">
-        <v>0.00021554429213088209</v>
+        <v>3.0246414570963748e-05</v>
       </c>
       <c r="AH23">
-        <v>1.0351104190018683e-05</v>
+        <v>-4.9263320160389701e-06</v>
       </c>
       <c r="AI23">
-        <v>9.7645302096884337e-05</v>
-      </c>
-      <c r="AJ23">
-        <v>-8.5620284228440056e-05</v>
-      </c>
-      <c r="AK23">
-        <v>-0.0044935850989067851</v>
+        <v>0.00018792114322453663</v>
       </c>
     </row>
     <row r="24">
@@ -3000,112 +2856,106 @@
         <v>48</v>
       </c>
       <c r="B24">
-        <v>0.19730644786845025</v>
+        <v>3.892237300748834</v>
       </c>
       <c r="C24">
-        <v>-9.7140136555206414e-05</v>
+        <v>-3.1834493471115892e-05</v>
       </c>
       <c r="D24">
-        <v>-6.051814695894758e-06</v>
+        <v>0.00033228372241895826</v>
       </c>
       <c r="E24">
-        <v>-1.690835330445087e-08</v>
+        <v>-6.7136134926304263e-05</v>
       </c>
       <c r="F24">
-        <v>0.00082093055223320935</v>
+        <v>-4.883454486433441e-05</v>
       </c>
       <c r="G24">
-        <v>0.0007647872838871736</v>
+        <v>0.00012877618346038923</v>
       </c>
       <c r="H24">
-        <v>0.00031935560965139686</v>
+        <v>-1.8494888706545559e-05</v>
       </c>
       <c r="I24">
-        <v>0.0010978483904407641</v>
+        <v>-8.8974886706919552e-05</v>
       </c>
       <c r="J24">
-        <v>0.0010174882548330177</v>
+        <v>-2.3845104977733469e-05</v>
       </c>
       <c r="K24">
-        <v>0.00071294432274992669</v>
+        <v>3.7762544182087083e-05</v>
       </c>
       <c r="L24">
-        <v>0.00063382182572373994</v>
+        <v>4.2739638244125274e-05</v>
       </c>
       <c r="M24">
-        <v>0.0038086350141968688</v>
+        <v>3.3516023083526297e-06</v>
       </c>
       <c r="N24">
-        <v>0.0034072040684542042</v>
+        <v>2.5349901746122248e-06</v>
       </c>
       <c r="O24">
-        <v>-0.00033472777077171392</v>
+        <v>1.0451598659236535e-05</v>
       </c>
       <c r="P24">
-        <v>0.0004489876661003785</v>
+        <v>-0.00011733515753141401</v>
       </c>
       <c r="Q24">
-        <v>0.00055503397386503595</v>
+        <v>-2.0611295039211402e-05</v>
       </c>
       <c r="R24">
-        <v>0.00043500993381972563</v>
+        <v>-2.791809035572186e-05</v>
       </c>
       <c r="S24">
-        <v>-2.8065318577845389e-06</v>
+        <v>1.2286128425974523e-06</v>
       </c>
       <c r="T24">
-        <v>-1.6522378890875856e-05</v>
+        <v>6.9257082614885125e-06</v>
       </c>
       <c r="U24">
-        <v>0.00015214063173027079</v>
+        <v>2.5943844974372215e-05</v>
       </c>
       <c r="V24">
-        <v>0.0010986902141187286</v>
+        <v>2.7666029659508765e-05</v>
       </c>
       <c r="W24">
-        <v>0.0036511541137874536</v>
+        <v>2.9979686537174189e-05</v>
       </c>
       <c r="X24">
-        <v>0.0042274158152500524</v>
+        <v>-5.0879498333561162e-06</v>
       </c>
       <c r="Y24">
-        <v>0.0054436772202071226</v>
+        <v>0.00046673961194149469</v>
       </c>
       <c r="Z24">
-        <v>-0.0002447574363151083</v>
+        <v>-1.3656190882247636e-05</v>
       </c>
       <c r="AA24">
-        <v>4.5752712847904001e-05</v>
+        <v>2.3027779609006551e-05</v>
       </c>
       <c r="AB24">
-        <v>0.00018971010605313291</v>
+        <v>-1.2590197192875486e-05</v>
       </c>
       <c r="AC24">
-        <v>4.8850147306897605e-05</v>
+        <v>-5.4273072590255015e-06</v>
       </c>
       <c r="AD24">
-        <v>7.2796011310754822e-05</v>
+        <v>5.0475275273062659e-06</v>
       </c>
       <c r="AE24">
-        <v>0.00014541651187611679</v>
+        <v>-4.6852151554368798e-05</v>
       </c>
       <c r="AF24">
-        <v>0.00021085587420886527</v>
+        <v>-1.5188203201894497e-07</v>
       </c>
       <c r="AG24">
-        <v>0.00014886355641468603</v>
+        <v>-0.00010559568546626718</v>
       </c>
       <c r="AH24">
-        <v>1.4633362057436353e-05</v>
+        <v>2.8898995698168813e-05</v>
       </c>
       <c r="AI24">
-        <v>-0.00017670710869012625</v>
-      </c>
-      <c r="AJ24">
-        <v>-0.00011658928202047648</v>
-      </c>
-      <c r="AK24">
-        <v>-0.0049899018761898149</v>
+        <v>-0.00018355116897700159</v>
       </c>
     </row>
     <row r="25">
@@ -3113,112 +2963,106 @@
         <v>49</v>
       </c>
       <c r="B25">
-        <v>0.014239308773784565</v>
+        <v>0.094379236628785945</v>
       </c>
       <c r="C25">
-        <v>-1.3032057519368863e-06</v>
+        <v>-8.1085924364915341e-05</v>
       </c>
       <c r="D25">
-        <v>-1.005130469697827e-06</v>
+        <v>0.00014280146279554637</v>
       </c>
       <c r="E25">
-        <v>6.8760027504605691e-09</v>
+        <v>0.00010394145986337652</v>
       </c>
       <c r="F25">
-        <v>-2.9380921477202878e-05</v>
+        <v>0.00011191749201079561</v>
       </c>
       <c r="G25">
-        <v>-2.9295868871452031e-05</v>
+        <v>0.00020423090026065174</v>
       </c>
       <c r="H25">
-        <v>-8.9246904624852345e-06</v>
+        <v>0.00022190153581250639</v>
       </c>
       <c r="I25">
-        <v>-4.522272122790604e-05</v>
+        <v>5.285445932202786e-05</v>
       </c>
       <c r="J25">
-        <v>-2.4016397220903199e-05</v>
+        <v>0.00014993704661024967</v>
       </c>
       <c r="K25">
-        <v>-3.8092029488725583e-05</v>
+        <v>0.00018681899800963376</v>
       </c>
       <c r="L25">
-        <v>-3.9087122093091754e-05</v>
+        <v>4.4432803402145657e-05</v>
       </c>
       <c r="M25">
-        <v>-0.00016792801303399941</v>
+        <v>5.3753552470530829e-06</v>
       </c>
       <c r="N25">
-        <v>-0.00014091800407097161</v>
+        <v>3.176840152891992e-05</v>
       </c>
       <c r="O25">
-        <v>1.1142088365938665e-05</v>
+        <v>7.8399976348818355e-05</v>
       </c>
       <c r="P25">
-        <v>-8.7127622993345505e-06</v>
+        <v>0.00011420262847560651</v>
       </c>
       <c r="Q25">
-        <v>-8.1337547318097298e-06</v>
+        <v>0.00039977578339571874</v>
       </c>
       <c r="R25">
-        <v>-2.6951325317340401e-05</v>
+        <v>0.00042834881384021077</v>
       </c>
       <c r="S25">
-        <v>-1.3604001049854248e-05</v>
+        <v>0.00050815612522661473</v>
       </c>
       <c r="T25">
-        <v>-1.5519833150295023e-05</v>
+        <v>5.8451861510897723e-05</v>
       </c>
       <c r="U25">
-        <v>-1.4993509390343136e-05</v>
+        <v>2.768071263798029e-05</v>
       </c>
       <c r="V25">
-        <v>-9.7735378788608415e-05</v>
+        <v>8.6603241043895548e-05</v>
       </c>
       <c r="W25">
-        <v>-0.00020362293739623115</v>
+        <v>0.00016191570019673729</v>
       </c>
       <c r="X25">
-        <v>-0.0002080005552566935</v>
+        <v>-1.4893099836860317e-05</v>
       </c>
       <c r="Y25">
-        <v>-0.0002447574363151083</v>
+        <v>-1.3656190882247636e-05</v>
       </c>
       <c r="Z25">
-        <v>3.572969261520134e-05</v>
+        <v>0.0030697965617201852</v>
       </c>
       <c r="AA25">
-        <v>-4.6243367574907948e-06</v>
+        <v>0.0024179089040784613</v>
       </c>
       <c r="AB25">
-        <v>-1.6342250942130411e-05</v>
+        <v>0.002404550751804479</v>
       </c>
       <c r="AC25">
-        <v>-1.5099728936074261e-05</v>
+        <v>0.0024220989664617064</v>
       </c>
       <c r="AD25">
-        <v>-8.9277565666271954e-06</v>
+        <v>0.0024195156018215242</v>
       </c>
       <c r="AE25">
-        <v>-1.3549173748914008e-05</v>
+        <v>0.0024034528561093405</v>
       </c>
       <c r="AF25">
-        <v>-9.7813632305206431e-06</v>
+        <v>4.3270358777724812e-06</v>
       </c>
       <c r="AG25">
-        <v>-1.7717223407969519e-05</v>
+        <v>-8.9653440550173033e-05</v>
       </c>
       <c r="AH25">
-        <v>2.0838513120365381e-06</v>
+        <v>-7.5214449039279706e-05</v>
       </c>
       <c r="AI25">
-        <v>3.0127887298176141e-05</v>
-      </c>
-      <c r="AJ25">
-        <v>-5.5428478897691602e-06</v>
-      </c>
-      <c r="AK25">
-        <v>0.00021091908774728004</v>
+        <v>-0.0030368046871220981</v>
       </c>
     </row>
     <row r="26">
@@ -3226,112 +3070,106 @@
         <v>50</v>
       </c>
       <c r="B26">
-        <v>3.8787235130671189</v>
+        <v>0.12294840072921695</v>
       </c>
       <c r="C26">
-        <v>-3.7841443168210034e-05</v>
+        <v>-8.7021960423897996e-05</v>
       </c>
       <c r="D26">
-        <v>-2.1263051652331842e-06</v>
+        <v>0.0010716454027064866</v>
       </c>
       <c r="E26">
-        <v>6.422796339319445e-09</v>
+        <v>8.770373819365785e-05</v>
       </c>
       <c r="F26">
-        <v>0.00035992754909626565</v>
+        <v>7.3842847933200395e-06</v>
       </c>
       <c r="G26">
-        <v>-5.4323734239563628e-05</v>
+        <v>6.1444208924456853e-05</v>
       </c>
       <c r="H26">
-        <v>-4.9655501839485723e-05</v>
+        <v>0.00014698745143087479</v>
       </c>
       <c r="I26">
-        <v>8.0340995526613057e-05</v>
+        <v>3.2123447875525299e-05</v>
       </c>
       <c r="J26">
-        <v>-1.9662175965197534e-05</v>
+        <v>0.00012300481935884349</v>
       </c>
       <c r="K26">
-        <v>-9.5348212475492803e-05</v>
+        <v>0.00010292825587060895</v>
       </c>
       <c r="L26">
-        <v>-4.1284254635589463e-05</v>
+        <v>-5.0739540888786183e-05</v>
       </c>
       <c r="M26">
-        <v>2.3582936305882834e-05</v>
+        <v>-4.7040608925575636e-05</v>
       </c>
       <c r="N26">
-        <v>6.7132284963779482e-05</v>
+        <v>1.4427976619051325e-05</v>
       </c>
       <c r="O26">
-        <v>-3.6176184143933189e-07</v>
+        <v>8.0597869771119454e-05</v>
       </c>
       <c r="P26">
-        <v>3.181593351948706e-06</v>
+        <v>0.00016597672273013959</v>
       </c>
       <c r="Q26">
-        <v>1.7334835094153639e-05</v>
+        <v>0.00039619269341183844</v>
       </c>
       <c r="R26">
-        <v>-0.00012142235918183677</v>
+        <v>0.00038964786848787094</v>
       </c>
       <c r="S26">
-        <v>-2.7502158129465463e-05</v>
+        <v>0.00043808842808900489</v>
       </c>
       <c r="T26">
-        <v>-4.5184850812885835e-05</v>
+        <v>5.2488330671794366e-05</v>
       </c>
       <c r="U26">
-        <v>-2.1733090131611501e-05</v>
+        <v>-2.6550282929700686e-05</v>
       </c>
       <c r="V26">
-        <v>8.430203632331238e-06</v>
+        <v>1.9365119552465504e-06</v>
       </c>
       <c r="W26">
-        <v>3.5515039328621321e-05</v>
+        <v>2.6869125629069759e-05</v>
       </c>
       <c r="X26">
-        <v>3.8055925120422164e-05</v>
+        <v>-1.3096336156970693e-05</v>
       </c>
       <c r="Y26">
-        <v>4.5752712847904001e-05</v>
+        <v>2.3027779609006551e-05</v>
       </c>
       <c r="Z26">
-        <v>-4.6243367574907948e-06</v>
+        <v>0.0024179089040784613</v>
       </c>
       <c r="AA26">
-        <v>0.0004698381381528199</v>
+        <v>0.0031027946331042924</v>
       </c>
       <c r="AB26">
-        <v>-9.5157637410631557e-06</v>
+        <v>0.0023978483286616562</v>
       </c>
       <c r="AC26">
-        <v>2.7938140835760225e-05</v>
+        <v>0.002409357967163568</v>
       </c>
       <c r="AD26">
-        <v>-8.4700965027039316e-06</v>
+        <v>0.0024111185307734502</v>
       </c>
       <c r="AE26">
-        <v>-2.3695392562908703e-06</v>
+        <v>0.0024006466571823933</v>
       </c>
       <c r="AF26">
-        <v>9.4052218660299923e-06</v>
+        <v>5.2611654468122114e-06</v>
       </c>
       <c r="AG26">
-        <v>-4.6754991388016934e-05</v>
+        <v>-8.5541095288291539e-05</v>
       </c>
       <c r="AH26">
-        <v>3.237116744580379e-07</v>
+        <v>-1.6356704670957467e-05</v>
       </c>
       <c r="AI26">
-        <v>-0.00010533869536918442</v>
-      </c>
-      <c r="AJ26">
-        <v>3.1083917251401773e-05</v>
-      </c>
-      <c r="AK26">
-        <v>-0.0001100793555372636</v>
+        <v>-0.0029087018043451578</v>
       </c>
     </row>
     <row r="27">
@@ -3339,112 +3177,106 @@
         <v>51</v>
       </c>
       <c r="B27">
-        <v>0.077787627733398201</v>
+        <v>-0.042363738032216963</v>
       </c>
       <c r="C27">
-        <v>-8.3220926574514197e-05</v>
+        <v>-9.2596972208624484e-05</v>
       </c>
       <c r="D27">
-        <v>-4.9021878271057989e-06</v>
+        <v>0.0007563371623317567</v>
       </c>
       <c r="E27">
-        <v>4.9290414321812228e-08</v>
+        <v>0.00010743254938749445</v>
       </c>
       <c r="F27">
-        <v>0.00017089336480977861</v>
+        <v>5.2590944147562577e-05</v>
       </c>
       <c r="G27">
-        <v>0.00010552169516705925</v>
+        <v>0.0001231085885548299</v>
       </c>
       <c r="H27">
-        <v>0.00010618260158602776</v>
+        <v>0.00017526084095628117</v>
       </c>
       <c r="I27">
-        <v>0.00019839081252925948</v>
+        <v>5.362024703079349e-05</v>
       </c>
       <c r="J27">
-        <v>0.00023229934460498262</v>
+        <v>7.6264365752959753e-05</v>
       </c>
       <c r="K27">
-        <v>4.9044470238045592e-05</v>
+        <v>7.9016028483066278e-05</v>
       </c>
       <c r="L27">
-        <v>0.00015320647609406166</v>
+        <v>-2.6403228015850705e-05</v>
       </c>
       <c r="M27">
-        <v>0.0001770860584250889</v>
+        <v>2.4527032191439961e-05</v>
       </c>
       <c r="N27">
-        <v>5.0297396159034759e-05</v>
+        <v>4.8685890455250794e-06</v>
       </c>
       <c r="O27">
-        <v>5.7726246558616754e-06</v>
+        <v>0.00010319506017073969</v>
       </c>
       <c r="P27">
-        <v>4.0226663270417082e-05</v>
+        <v>0.00016024217855355183</v>
       </c>
       <c r="Q27">
-        <v>8.0581684497851988e-05</v>
+        <v>0.00039999263156205271</v>
       </c>
       <c r="R27">
-        <v>0.00015721225935875181</v>
+        <v>0.00039390262233660652</v>
       </c>
       <c r="S27">
-        <v>0.00043792243425426741</v>
+        <v>0.00045272675287770861</v>
       </c>
       <c r="T27">
-        <v>0.00047455826863080416</v>
+        <v>2.1032802931347859e-05</v>
       </c>
       <c r="U27">
-        <v>0.00055392495136093352</v>
+        <v>-3.9589942205490092e-05</v>
       </c>
       <c r="V27">
-        <v>6.2215016927632811e-05</v>
+        <v>3.0966175405273098e-05</v>
       </c>
       <c r="W27">
-        <v>4.9105307281538564e-05</v>
+        <v>5.4205815082350884e-05</v>
       </c>
       <c r="X27">
-        <v>0.000109941145362372</v>
+        <v>-7.4033122276246515e-06</v>
       </c>
       <c r="Y27">
-        <v>0.00018971010605313291</v>
+        <v>-1.2590197192875486e-05</v>
       </c>
       <c r="Z27">
-        <v>-1.6342250942130411e-05</v>
+        <v>0.002404550751804479</v>
       </c>
       <c r="AA27">
-        <v>-9.5157637410631557e-06</v>
+        <v>0.0023978483286616562</v>
       </c>
       <c r="AB27">
-        <v>0.0031191578122552349</v>
+        <v>0.0029016948845160947</v>
       </c>
       <c r="AC27">
-        <v>0.0024615492144343292</v>
+        <v>0.0023941358533534473</v>
       </c>
       <c r="AD27">
-        <v>0.0024488437454076809</v>
+        <v>0.002393188555904899</v>
       </c>
       <c r="AE27">
-        <v>0.0024653027195969237</v>
+        <v>0.0023926236367021038</v>
       </c>
       <c r="AF27">
-        <v>0.0024650856877057167</v>
+        <v>2.0155216062572577e-06</v>
       </c>
       <c r="AG27">
-        <v>0.0024491287077466947</v>
+        <v>-6.419983764488252e-05</v>
       </c>
       <c r="AH27">
-        <v>4.6315409095330833e-06</v>
+        <v>-9.5198216619427263e-05</v>
       </c>
       <c r="AI27">
-        <v>-0.00010663134530288594</v>
-      </c>
-      <c r="AJ27">
-        <v>-7.4617209358636568e-05</v>
-      </c>
-      <c r="AK27">
-        <v>-0.0030391536449426407</v>
+        <v>-0.0028667674330144039</v>
       </c>
     </row>
     <row r="28">
@@ -3452,112 +3284,106 @@
         <v>52</v>
       </c>
       <c r="B28">
-        <v>0.10214527809118833</v>
+        <v>0.05751555787790158</v>
       </c>
       <c r="C28">
-        <v>-8.906949029818085e-05</v>
+        <v>-0.00010856841590938738</v>
       </c>
       <c r="D28">
-        <v>-1.9514781448637993e-07</v>
+        <v>0.00013931877986970488</v>
       </c>
       <c r="E28">
-        <v>7.2420227277417834e-09</v>
+        <v>4.3360577271745913e-05</v>
       </c>
       <c r="F28">
-        <v>0.0010396622006849535</v>
+        <v>-2.1056099340477884e-05</v>
       </c>
       <c r="G28">
-        <v>8.4368794715609105e-05</v>
+        <v>6.6073099431141315e-05</v>
       </c>
       <c r="H28">
-        <v>-2.5287817091834003e-06</v>
+        <v>9.9242546054492892e-05</v>
       </c>
       <c r="I28">
-        <v>0.00011279705654526346</v>
+        <v>-1.5459636173135441e-05</v>
       </c>
       <c r="J28">
-        <v>0.00015046715161416485</v>
+        <v>7.7531048207134723e-05</v>
       </c>
       <c r="K28">
-        <v>3.0487672599616676e-05</v>
+        <v>0.0001535077105833311</v>
       </c>
       <c r="L28">
-        <v>0.00012705031902480557</v>
+        <v>2.9783468960469656e-05</v>
       </c>
       <c r="M28">
-        <v>0.00012066737429660291</v>
+        <v>-2.7358458102672961e-05</v>
       </c>
       <c r="N28">
-        <v>-3.4870515197211495e-05</v>
+        <v>1.6549667470975769e-05</v>
       </c>
       <c r="O28">
-        <v>-4.2572121139827388e-05</v>
+        <v>1.7201678399737103e-05</v>
       </c>
       <c r="P28">
-        <v>2.1456531395724183e-05</v>
+        <v>0.00011097867444821892</v>
       </c>
       <c r="Q28">
-        <v>8.3807967486456704e-05</v>
+        <v>0.00032778991844844511</v>
       </c>
       <c r="R28">
-        <v>0.00022045493845321632</v>
+        <v>0.00031836766960773727</v>
       </c>
       <c r="S28">
-        <v>0.00044953031904174882</v>
+        <v>0.00038264462745451165</v>
       </c>
       <c r="T28">
-        <v>0.00045515397205222151</v>
+        <v>3.3098360869946624e-05</v>
       </c>
       <c r="U28">
-        <v>0.00050832725165993794</v>
+        <v>4.6144882518512828e-06</v>
       </c>
       <c r="V28">
-        <v>5.551159091172304e-05</v>
+        <v>7.6567174047375945e-05</v>
       </c>
       <c r="W28">
-        <v>-4.7251357243268712e-06</v>
+        <v>0.00013184405026467035</v>
       </c>
       <c r="X28">
-        <v>2.3099686328289723e-05</v>
+        <v>-1.2136815108224061e-05</v>
       </c>
       <c r="Y28">
-        <v>4.8850147306897605e-05</v>
+        <v>-5.4273072590255015e-06</v>
       </c>
       <c r="Z28">
-        <v>-1.5099728936074261e-05</v>
+        <v>0.0024220989664617064</v>
       </c>
       <c r="AA28">
-        <v>2.7938140835760225e-05</v>
+        <v>0.002409357967163568</v>
       </c>
       <c r="AB28">
-        <v>0.0024615492144343292</v>
+        <v>0.0023941358533534473</v>
       </c>
       <c r="AC28">
-        <v>0.0031617186933199136</v>
+        <v>0.0029680040026244256</v>
       </c>
       <c r="AD28">
-        <v>0.0024431470469142647</v>
+        <v>0.0024122865124234327</v>
       </c>
       <c r="AE28">
-        <v>0.002451786944779519</v>
+        <v>0.0024099257746925127</v>
       </c>
       <c r="AF28">
-        <v>0.002456123938966397</v>
+        <v>5.4268485730809757e-06</v>
       </c>
       <c r="AG28">
-        <v>0.0024444506879656787</v>
+        <v>-7.3490856489324399e-05</v>
       </c>
       <c r="AH28">
-        <v>5.06704063144684e-06</v>
+        <v>-6.1148263188881189e-05</v>
       </c>
       <c r="AI28">
-        <v>-0.00010368989030267979</v>
-      </c>
-      <c r="AJ28">
-        <v>-1.616832719370789e-05</v>
-      </c>
-      <c r="AK28">
-        <v>-0.0030386505253575426</v>
+        <v>-0.0028181773427799263</v>
       </c>
     </row>
     <row r="29">
@@ -3565,112 +3391,106 @@
         <v>53</v>
       </c>
       <c r="B29">
-        <v>-0.056508206108460045</v>
+        <v>-0.072941401664601224</v>
       </c>
       <c r="C29">
-        <v>-9.2826737795602955e-05</v>
+        <v>-6.3819334106375331e-05</v>
       </c>
       <c r="D29">
-        <v>6.1513538738070233e-07</v>
+        <v>0.00013819997115470237</v>
       </c>
       <c r="E29">
-        <v>-2.7174720676790462e-09</v>
+        <v>6.5902518832273212e-05</v>
       </c>
       <c r="F29">
-        <v>0.00072293055582634642</v>
+        <v>-5.3059972264982548e-06</v>
       </c>
       <c r="G29">
-        <v>0.00010134094841438446</v>
+        <v>2.2334027506154791e-05</v>
       </c>
       <c r="H29">
-        <v>3.6201780308259225e-05</v>
+        <v>0.00011251699848729887</v>
       </c>
       <c r="I29">
-        <v>0.00012739588607572666</v>
+        <v>3.2777159819301132e-05</v>
       </c>
       <c r="J29">
-        <v>0.00017382373752403732</v>
+        <v>0.00016385404757253771</v>
       </c>
       <c r="K29">
-        <v>4.9970620505085557e-05</v>
+        <v>0.00035701943319050699</v>
       </c>
       <c r="L29">
-        <v>7.0737092000580518e-05</v>
+        <v>0.00011865440852693141</v>
       </c>
       <c r="M29">
-        <v>9.3938644631497929e-05</v>
+        <v>-7.4634030212139476e-05</v>
       </c>
       <c r="N29">
-        <v>-1.1278162757271618e-05</v>
+        <v>1.0462524298719981e-05</v>
       </c>
       <c r="O29">
-        <v>3.0913068517185124e-05</v>
+        <v>6.7471731706362253e-05</v>
       </c>
       <c r="P29">
-        <v>1.1429507838074302e-05</v>
+        <v>0.00021100525375209183</v>
       </c>
       <c r="Q29">
-        <v>0.00010132380066673349</v>
+        <v>0.00040526383753041113</v>
       </c>
       <c r="R29">
-        <v>0.00021139810342213176</v>
+        <v>0.00039693324408751564</v>
       </c>
       <c r="S29">
-        <v>0.00044366328659484807</v>
+        <v>0.00049446962267037727</v>
       </c>
       <c r="T29">
-        <v>0.00044579472625172131</v>
+        <v>2.1061296049569659e-05</v>
       </c>
       <c r="U29">
-        <v>0.00050851898057002048</v>
+        <v>0.0001070700554739681</v>
       </c>
       <c r="V29">
-        <v>2.5427207967291783e-05</v>
+        <v>0.00018787443626774088</v>
       </c>
       <c r="W29">
-        <v>-1.8605951851966268e-05</v>
+        <v>0.00019495295271682251</v>
       </c>
       <c r="X29">
-        <v>5.238172533216694e-05</v>
+        <v>-8.7635720959443405e-06</v>
       </c>
       <c r="Y29">
-        <v>7.2796011310754822e-05</v>
+        <v>5.0475275273062659e-06</v>
       </c>
       <c r="Z29">
-        <v>-8.9277565666271954e-06</v>
+        <v>0.0024195156018215242</v>
       </c>
       <c r="AA29">
-        <v>-8.4700965027039316e-06</v>
+        <v>0.0024111185307734502</v>
       </c>
       <c r="AB29">
-        <v>0.0024488437454076809</v>
+        <v>0.002393188555904899</v>
       </c>
       <c r="AC29">
-        <v>0.0024431470469142647</v>
+        <v>0.0024122865124234327</v>
       </c>
       <c r="AD29">
-        <v>0.0029521486895823226</v>
+        <v>0.0027931079009252111</v>
       </c>
       <c r="AE29">
-        <v>0.0024387267736864955</v>
+        <v>0.0024091875765934519</v>
       </c>
       <c r="AF29">
-        <v>0.0024389757691829321</v>
+        <v>8.473941459985273e-07</v>
       </c>
       <c r="AG29">
-        <v>0.0024379177749221988</v>
+        <v>5.9676148105947688e-05</v>
       </c>
       <c r="AH29">
-        <v>1.9600508353146852e-06</v>
+        <v>-3.4783355698563088e-05</v>
       </c>
       <c r="AI29">
-        <v>-8.5239957407083709e-05</v>
-      </c>
-      <c r="AJ29">
-        <v>-0.00010133362225287065</v>
-      </c>
-      <c r="AK29">
-        <v>-0.0029955110811089739</v>
+        <v>-0.0030305872269813412</v>
       </c>
     </row>
     <row r="30">
@@ -3678,112 +3498,106 @@
         <v>54</v>
       </c>
       <c r="B30">
-        <v>0.043341630929584853</v>
+        <v>0.065751712427960879</v>
       </c>
       <c r="C30">
-        <v>-0.00010770278311922061</v>
+        <v>-4.7641209485684455e-06</v>
       </c>
       <c r="D30">
-        <v>-1.4172083583867813e-06</v>
+        <v>2.6842920995643992e-05</v>
       </c>
       <c r="E30">
-        <v>2.3275186937323524e-08</v>
+        <v>-1.1316323787113696e-05</v>
       </c>
       <c r="F30">
-        <v>0.00014512559808635612</v>
+        <v>-7.2812817573096904e-05</v>
       </c>
       <c r="G30">
-        <v>3.1844229894414759e-05</v>
+        <v>-3.5116145501650625e-05</v>
       </c>
       <c r="H30">
-        <v>-3.4557675597660662e-05</v>
+        <v>-6.6641415073845887e-06</v>
       </c>
       <c r="I30">
-        <v>6.2411795254526141e-05</v>
+        <v>2.4805335383795338e-05</v>
       </c>
       <c r="J30">
-        <v>9.8726304086698682e-05</v>
+        <v>1.1865457425506851e-05</v>
       </c>
       <c r="K30">
-        <v>-1.9916388888269491e-05</v>
+        <v>0.0002187728275894843</v>
       </c>
       <c r="L30">
-        <v>7.975825688759635e-05</v>
+        <v>-5.003866963365614e-05</v>
       </c>
       <c r="M30">
-        <v>0.00016406673375481216</v>
+        <v>-0.00015014202061696563</v>
       </c>
       <c r="N30">
-        <v>2.8744723553628723e-05</v>
+        <v>-2.3821879086441338e-05</v>
       </c>
       <c r="O30">
-        <v>-2.4403755522718325e-05</v>
+        <v>1.4188838300472849e-05</v>
       </c>
       <c r="P30">
-        <v>2.3669353205774937e-05</v>
+        <v>0.00039010103324478698</v>
       </c>
       <c r="Q30">
-        <v>1.3751992204978332e-05</v>
+        <v>0.00037619705005900988</v>
       </c>
       <c r="R30">
-        <v>0.00015404135002411445</v>
+        <v>0.00041366543595435884</v>
       </c>
       <c r="S30">
-        <v>0.00036860541209909198</v>
+        <v>0.00032125317013082764</v>
       </c>
       <c r="T30">
-        <v>0.00037203166613365528</v>
+        <v>0.00011004290423317754</v>
       </c>
       <c r="U30">
-        <v>0.00044167620340231171</v>
+        <v>7.5686072508696781e-05</v>
       </c>
       <c r="V30">
-        <v>3.5370838212990833e-05</v>
+        <v>0.00020760721124195796</v>
       </c>
       <c r="W30">
-        <v>2.2304809881174177e-05</v>
+        <v>0.00014314395619293653</v>
       </c>
       <c r="X30">
-        <v>9.3594557088700053e-05</v>
+        <v>-1.5430911525350005e-05</v>
       </c>
       <c r="Y30">
-        <v>0.00014541651187611679</v>
+        <v>-4.6852151554368798e-05</v>
       </c>
       <c r="Z30">
-        <v>-1.3549173748914008e-05</v>
+        <v>0.0024034528561093405</v>
       </c>
       <c r="AA30">
-        <v>-2.3695392562908703e-06</v>
+        <v>0.0024006466571823933</v>
       </c>
       <c r="AB30">
-        <v>0.0024653027195969237</v>
+        <v>0.0023926236367021038</v>
       </c>
       <c r="AC30">
-        <v>0.002451786944779519</v>
+        <v>0.0024099257746925127</v>
       </c>
       <c r="AD30">
-        <v>0.0024387267736864955</v>
+        <v>0.0024091875765934519</v>
       </c>
       <c r="AE30">
-        <v>0.0030162686506356477</v>
+        <v>0.0030251089773792807</v>
       </c>
       <c r="AF30">
-        <v>0.0024576626423326664</v>
+        <v>2.9194340006780237e-06</v>
       </c>
       <c r="AG30">
-        <v>0.0024568943830358997</v>
+        <v>-4.3658362118767502e-06</v>
       </c>
       <c r="AH30">
-        <v>5.1927534039564299e-06</v>
+        <v>-9.5541077437662171e-05</v>
       </c>
       <c r="AI30">
-        <v>-8.9430173679340159e-05</v>
-      </c>
-      <c r="AJ30">
-        <v>-6.4100404898649859e-05</v>
-      </c>
-      <c r="AK30">
-        <v>-0.0029049788151290796</v>
+        <v>-0.0028833015366855784</v>
       </c>
     </row>
     <row r="31">
@@ -3791,112 +3605,106 @@
         <v>55</v>
       </c>
       <c r="B31">
-        <v>-0.088320160860836272</v>
+        <v>0.001711011159776669</v>
       </c>
       <c r="C31">
-        <v>-6.848526538045293e-05</v>
+        <v>-1.9497710287320405e-06</v>
       </c>
       <c r="D31">
-        <v>-5.3222697295533773e-07</v>
+        <v>-8.510155342639439e-06</v>
       </c>
       <c r="E31">
-        <v>4.869925171155404e-09</v>
+        <v>5.5397297790903439e-06</v>
       </c>
       <c r="F31">
-        <v>0.00014004760693710243</v>
+        <v>2.3800320149084932e-06</v>
       </c>
       <c r="G31">
-        <v>6.3109637921800286e-05</v>
+        <v>1.0130120580751479e-05</v>
       </c>
       <c r="H31">
-        <v>-2.8034532334489664e-05</v>
+        <v>1.4003597577924943e-05</v>
       </c>
       <c r="I31">
-        <v>3.0199903768108759e-05</v>
+        <v>2.8167527087327672e-06</v>
       </c>
       <c r="J31">
-        <v>0.00010976484539881637</v>
+        <v>2.2537754202507757e-06</v>
       </c>
       <c r="K31">
-        <v>2.3812120986320905e-05</v>
+        <v>-3.2565980408890923e-07</v>
       </c>
       <c r="L31">
-        <v>0.00016117107222544724</v>
+        <v>1.0516857342269178e-05</v>
       </c>
       <c r="M31">
-        <v>0.00035967883933484685</v>
+        <v>1.4859872921433072e-05</v>
       </c>
       <c r="N31">
-        <v>0.00012682828905954903</v>
+        <v>5.616813985184142e-06</v>
       </c>
       <c r="O31">
-        <v>-7.0864633063615599e-05</v>
+        <v>9.5812939870465262e-06</v>
       </c>
       <c r="P31">
-        <v>1.8138429968336334e-05</v>
+        <v>5.7254640730687004e-06</v>
       </c>
       <c r="Q31">
-        <v>6.7733099180269083e-05</v>
+        <v>-2.857098044788532e-07</v>
       </c>
       <c r="R31">
-        <v>0.00026289074750658766</v>
+        <v>3.6208117601797146e-06</v>
       </c>
       <c r="S31">
-        <v>0.00045108047264597604</v>
+        <v>6.4351374456237591e-06</v>
       </c>
       <c r="T31">
-        <v>0.0004470645319115639</v>
+        <v>-3.1269371662587711e-06</v>
       </c>
       <c r="U31">
-        <v>0.00054349859132573459</v>
+        <v>4.5265732748416096e-06</v>
       </c>
       <c r="V31">
-        <v>2.186656129644343e-05</v>
+        <v>9.0116810501175454e-06</v>
       </c>
       <c r="W31">
-        <v>0.00011837024832619996</v>
+        <v>1.1770680230066018e-05</v>
       </c>
       <c r="X31">
-        <v>0.00020361227965020592</v>
+        <v>1.9760107536395215e-06</v>
       </c>
       <c r="Y31">
-        <v>0.00021085587420886527</v>
+        <v>-1.5188203201894497e-07</v>
       </c>
       <c r="Z31">
-        <v>-9.7813632305206431e-06</v>
+        <v>4.3270358777724812e-06</v>
       </c>
       <c r="AA31">
-        <v>9.4052218660299923e-06</v>
+        <v>5.2611654468122114e-06</v>
       </c>
       <c r="AB31">
-        <v>0.0024650856877057167</v>
+        <v>2.0155216062572577e-06</v>
       </c>
       <c r="AC31">
-        <v>0.002456123938966397</v>
+        <v>5.4268485730809757e-06</v>
       </c>
       <c r="AD31">
-        <v>0.0024389757691829321</v>
+        <v>8.473941459985273e-07</v>
       </c>
       <c r="AE31">
-        <v>0.0024576626423326664</v>
+        <v>2.9194340006780237e-06</v>
       </c>
       <c r="AF31">
-        <v>0.0028360734200607602</v>
+        <v>4.7593550376573534e-06</v>
       </c>
       <c r="AG31">
-        <v>0.002455569014236571</v>
+        <v>-7.1751980030202551e-06</v>
       </c>
       <c r="AH31">
-        <v>1.112915820024626e-06</v>
+        <v>-1.3480168463238869e-05</v>
       </c>
       <c r="AI31">
-        <v>4.4512379639054592e-05</v>
-      </c>
-      <c r="AJ31">
-        <v>-3.4834226891073935e-05</v>
-      </c>
-      <c r="AK31">
-        <v>-0.0031186835463261585</v>
+        <v>-0.00011321363707010669</v>
       </c>
     </row>
     <row r="32">
@@ -3904,112 +3712,106 @@
         <v>56</v>
       </c>
       <c r="B32">
-        <v>0.065431214866320711</v>
+        <v>-0.15251988705998118</v>
       </c>
       <c r="C32">
-        <v>2.2275491929254512e-06</v>
+        <v>8.2682461790918376e-05</v>
       </c>
       <c r="D32">
-        <v>-3.0054686833840975e-06</v>
+        <v>5.4247913094004809e-05</v>
       </c>
       <c r="E32">
-        <v>4.6013643849496761e-08</v>
+        <v>-3.4781742681625188e-05</v>
       </c>
       <c r="F32">
-        <v>2.1591697983216096e-05</v>
+        <v>0.00011273175229523135</v>
       </c>
       <c r="G32">
-        <v>-1.6876315326658318e-05</v>
+        <v>-0.00013755789499182453</v>
       </c>
       <c r="H32">
-        <v>-6.975746189792013e-05</v>
+        <v>-8.6778641401065969e-05</v>
       </c>
       <c r="I32">
-        <v>-4.7522259414865033e-05</v>
+        <v>4.6806591355737746e-06</v>
       </c>
       <c r="J32">
-        <v>1.6276962793432672e-05</v>
+        <v>0.00015386211925594567</v>
       </c>
       <c r="K32">
-        <v>3.5794081858431996e-05</v>
+        <v>0.00037063543131517608</v>
       </c>
       <c r="L32">
-        <v>4.7937875782734567e-05</v>
+        <v>5.5955232594965317e-05</v>
       </c>
       <c r="M32">
-        <v>0.00021698156621521262</v>
+        <v>-0.00030833222323535297</v>
       </c>
       <c r="N32">
-        <v>-8.0194557288379138e-05</v>
+        <v>-9.8069252881486258e-05</v>
       </c>
       <c r="O32">
-        <v>-0.00014196893536984535</v>
+        <v>-8.9809283282528017e-05</v>
       </c>
       <c r="P32">
-        <v>-1.8294509765440727e-05</v>
+        <v>1.2088203191898579e-05</v>
       </c>
       <c r="Q32">
-        <v>6.9540725960201121e-07</v>
+        <v>4.3779515320177889e-05</v>
       </c>
       <c r="R32">
-        <v>0.0004219850881182784</v>
+        <v>4.5946337358625244e-05</v>
       </c>
       <c r="S32">
-        <v>0.00040657107945525444</v>
+        <v>4.3708144531398943e-05</v>
       </c>
       <c r="T32">
-        <v>0.00046032666736534544</v>
+        <v>-0.00013761921847101522</v>
       </c>
       <c r="U32">
-        <v>0.00037321764746299301</v>
+        <v>-2.3809894667179386e-05</v>
       </c>
       <c r="V32">
-        <v>0.00011343594944440005</v>
+        <v>9.8761563418469159e-05</v>
       </c>
       <c r="W32">
-        <v>8.2314725543089447e-05</v>
+        <v>-0.00017259147849396899</v>
       </c>
       <c r="X32">
-        <v>0.00021554429213088209</v>
+        <v>3.0246414570963748e-05</v>
       </c>
       <c r="Y32">
-        <v>0.00014886355641468603</v>
+        <v>-0.00010559568546626718</v>
       </c>
       <c r="Z32">
-        <v>-1.7717223407969519e-05</v>
+        <v>-8.9653440550173033e-05</v>
       </c>
       <c r="AA32">
-        <v>-4.6754991388016934e-05</v>
+        <v>-8.5541095288291539e-05</v>
       </c>
       <c r="AB32">
-        <v>0.0024491287077466947</v>
+        <v>-6.419983764488252e-05</v>
       </c>
       <c r="AC32">
-        <v>0.0024444506879656787</v>
+        <v>-7.3490856489324399e-05</v>
       </c>
       <c r="AD32">
-        <v>0.0024379177749221988</v>
+        <v>5.9676148105947688e-05</v>
       </c>
       <c r="AE32">
-        <v>0.0024568943830358997</v>
+        <v>-4.3658362118767502e-06</v>
       </c>
       <c r="AF32">
-        <v>0.002455569014236571</v>
+        <v>-7.1751980030202551e-06</v>
       </c>
       <c r="AG32">
-        <v>0.0030746667522620849</v>
+        <v>0.0021902531402251324</v>
       </c>
       <c r="AH32">
-        <v>2.6586276749018822e-06</v>
+        <v>0.00014619121712923053</v>
       </c>
       <c r="AI32">
-        <v>-1.8214574711171352e-05</v>
-      </c>
-      <c r="AJ32">
-        <v>-9.8878405566171735e-05</v>
-      </c>
-      <c r="AK32">
-        <v>-0.0029429837293659545</v>
+        <v>7.4687898885440079e-06</v>
       </c>
     </row>
     <row r="33">
@@ -4017,112 +3819,106 @@
         <v>57</v>
       </c>
       <c r="B33">
-        <v>-0.00028612342360396305</v>
+        <v>-0.045878343329260198</v>
       </c>
       <c r="C33">
-        <v>-2.7855725170312608e-06</v>
+        <v>1.3097791130418853e-05</v>
       </c>
       <c r="D33">
-        <v>-6.7275357072985575e-07</v>
+        <v>0.0013306349657106415</v>
       </c>
       <c r="E33">
-        <v>4.5830711267215435e-09</v>
+        <v>2.948272168971347e-05</v>
       </c>
       <c r="F33">
-        <v>-1.0575696445527265e-05</v>
+        <v>7.0103091909831813e-05</v>
       </c>
       <c r="G33">
-        <v>6.8023772104693964e-06</v>
+        <v>7.9445070357428687e-05</v>
       </c>
       <c r="H33">
-        <v>2.6249090092077162e-06</v>
+        <v>6.0970632979302688e-05</v>
       </c>
       <c r="I33">
-        <v>7.3389126967648348e-06</v>
+        <v>3.7243755954839588e-05</v>
       </c>
       <c r="J33">
-        <v>1.3921870275758492e-05</v>
+        <v>-2.3520691061540422e-05</v>
       </c>
       <c r="K33">
-        <v>9.1424478038541258e-07</v>
+        <v>-9.4744370399680016e-05</v>
       </c>
       <c r="L33">
-        <v>-5.6423937115830138e-07</v>
+        <v>-2.7635679663996337e-05</v>
       </c>
       <c r="M33">
-        <v>-3.6083818067304883e-06</v>
+        <v>-4.2100416755658121e-05</v>
       </c>
       <c r="N33">
-        <v>1.4011853674495702e-05</v>
+        <v>-3.6525377833204319e-05</v>
       </c>
       <c r="O33">
-        <v>1.3672779687304104e-05</v>
+        <v>-7.0967816654567714e-05</v>
       </c>
       <c r="P33">
-        <v>5.9739552814932e-06</v>
+        <v>-4.9005125978268584e-05</v>
       </c>
       <c r="Q33">
-        <v>1.118153308104632e-05</v>
+        <v>2.3744716712641081e-05</v>
       </c>
       <c r="R33">
-        <v>6.3090179502545336e-06</v>
+        <v>2.3263439245871376e-05</v>
       </c>
       <c r="S33">
-        <v>3.9528066487977713e-07</v>
+        <v>7.8244783439976838e-05</v>
       </c>
       <c r="T33">
-        <v>2.9048955028014134e-06</v>
+        <v>-5.2297174353573331e-05</v>
       </c>
       <c r="U33">
-        <v>4.8929705299049164e-06</v>
+        <v>-6.8373762652340847e-05</v>
       </c>
       <c r="V33">
-        <v>-3.2051049512609733e-06</v>
+        <v>-0.00010339082551956988</v>
       </c>
       <c r="W33">
-        <v>6.2405451611873328e-06</v>
+        <v>-0.00014225457160009481</v>
       </c>
       <c r="X33">
-        <v>1.0351104190018683e-05</v>
+        <v>-4.9263320160389701e-06</v>
       </c>
       <c r="Y33">
-        <v>1.4633362057436353e-05</v>
+        <v>2.8898995698168813e-05</v>
       </c>
       <c r="Z33">
-        <v>2.0838513120365381e-06</v>
+        <v>-7.5214449039279706e-05</v>
       </c>
       <c r="AA33">
-        <v>3.237116744580379e-07</v>
+        <v>-1.6356704670957467e-05</v>
       </c>
       <c r="AB33">
-        <v>4.6315409095330833e-06</v>
+        <v>-9.5198216619427263e-05</v>
       </c>
       <c r="AC33">
-        <v>5.06704063144684e-06</v>
+        <v>-6.1148263188881189e-05</v>
       </c>
       <c r="AD33">
-        <v>1.9600508353146852e-06</v>
+        <v>-3.4783355698563088e-05</v>
       </c>
       <c r="AE33">
-        <v>5.1927534039564299e-06</v>
+        <v>-9.5541077437662171e-05</v>
       </c>
       <c r="AF33">
-        <v>1.112915820024626e-06</v>
+        <v>-1.3480168463238869e-05</v>
       </c>
       <c r="AG33">
-        <v>2.6586276749018822e-06</v>
+        <v>0.00014619121712923053</v>
       </c>
       <c r="AH33">
-        <v>4.8363452685978054e-06</v>
+        <v>0.0024010981295976529</v>
       </c>
       <c r="AI33">
-        <v>-7.6858596764321785e-06</v>
-      </c>
-      <c r="AJ33">
-        <v>-1.3276019498263992e-05</v>
-      </c>
-      <c r="AK33">
-        <v>-9.5414755969491113e-05</v>
+        <v>0.00024089133971755663</v>
       </c>
     </row>
     <row r="34">
@@ -4130,338 +3926,106 @@
         <v>58</v>
       </c>
       <c r="B34">
-        <v>-0.15034503538462818</v>
+        <v>-1.5822168062419928</v>
       </c>
       <c r="C34">
-        <v>8.915465808709844e-05</v>
+        <v>-7.2034827626274e-05</v>
       </c>
       <c r="D34">
-        <v>-5.6633420541665563e-06</v>
+        <v>-0.0029610538351407139</v>
       </c>
       <c r="E34">
-        <v>6.6863409455461351e-08</v>
+        <v>-0.0024047977311919084</v>
       </c>
       <c r="F34">
-        <v>-1.0610707155621259e-05</v>
+        <v>-0.0020326920215607788</v>
       </c>
       <c r="G34">
-        <v>-4.2492166427976746e-05</v>
+        <v>-0.0029729672163784247</v>
       </c>
       <c r="H34">
-        <v>0.00012237409901647987</v>
+        <v>-0.0028559799727096713</v>
       </c>
       <c r="I34">
-        <v>-2.5280771717804598e-05</v>
+        <v>-0.0024133870012868893</v>
       </c>
       <c r="J34">
-        <v>-6.9409204249576764e-05</v>
+        <v>-0.002582096142993707</v>
       </c>
       <c r="K34">
-        <v>2.2814609825895851e-06</v>
+        <v>-0.0040142065628919503</v>
       </c>
       <c r="L34">
-        <v>0.00018715727023934812</v>
+        <v>-0.0036131444182356887</v>
       </c>
       <c r="M34">
-        <v>0.00035750766520286238</v>
+        <v>-0.00015965131485163437</v>
       </c>
       <c r="N34">
-        <v>2.2514017574319558e-05</v>
+        <v>-0.00082028153442178608</v>
       </c>
       <c r="O34">
-        <v>-0.00032039198444023365</v>
+        <v>-0.0011770786664807337</v>
       </c>
       <c r="P34">
-        <v>-9.9376228560866013e-05</v>
+        <v>-0.007646923409067169</v>
       </c>
       <c r="Q34">
-        <v>-9.6747092675855922e-05</v>
+        <v>-0.0074153616530795467</v>
       </c>
       <c r="R34">
-        <v>3.2992963550648041e-05</v>
+        <v>-0.0076541926183776501</v>
       </c>
       <c r="S34">
-        <v>6.2750748413151203e-05</v>
+        <v>-0.0080109756220309476</v>
       </c>
       <c r="T34">
-        <v>6.6076337071089772e-05</v>
+        <v>-0.00073223072105569578</v>
       </c>
       <c r="U34">
-        <v>6.6273869017443449e-05</v>
+        <v>-0.0036109294228694145</v>
       </c>
       <c r="V34">
-        <v>-0.00014341427858625163</v>
+        <v>-0.0044241714089441721</v>
       </c>
       <c r="W34">
-        <v>-3.4047526304822797e-05</v>
+        <v>-0.0053221193019862469</v>
       </c>
       <c r="X34">
-        <v>9.7645302096884337e-05</v>
+        <v>0.00018792114322453663</v>
       </c>
       <c r="Y34">
-        <v>-0.00017670710869012625</v>
+        <v>-0.00018355116897700159</v>
       </c>
       <c r="Z34">
-        <v>3.0127887298176141e-05</v>
+        <v>-0.0030368046871220981</v>
       </c>
       <c r="AA34">
-        <v>-0.00010533869536918442</v>
+        <v>-0.0029087018043451578</v>
       </c>
       <c r="AB34">
-        <v>-0.00010663134530288594</v>
+        <v>-0.0028667674330144039</v>
       </c>
       <c r="AC34">
-        <v>-0.00010368989030267979</v>
+        <v>-0.0028181773427799263</v>
       </c>
       <c r="AD34">
-        <v>-8.5239957407083709e-05</v>
+        <v>-0.0030305872269813412</v>
       </c>
       <c r="AE34">
-        <v>-8.9430173679340159e-05</v>
+        <v>-0.0028833015366855784</v>
       </c>
       <c r="AF34">
-        <v>4.4512379639054592e-05</v>
+        <v>-0.00011321363707010669</v>
       </c>
       <c r="AG34">
-        <v>-1.8214574711171352e-05</v>
+        <v>7.4687898885440079e-06</v>
       </c>
       <c r="AH34">
-        <v>-7.6858596764321785e-06</v>
+        <v>0.00024089133971755663</v>
       </c>
       <c r="AI34">
-        <v>0.0022137049556604062</v>
-      </c>
-      <c r="AJ34">
-        <v>0.0001443201995180632</v>
-      </c>
-      <c r="AK34">
-        <v>0.00012343758506881501</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35">
-        <v>-0.054715726299834171</v>
-      </c>
-      <c r="C35">
-        <v>1.1057416584411131e-05</v>
-      </c>
-      <c r="D35">
-        <v>-1.003814833831166e-05</v>
-      </c>
-      <c r="E35">
-        <v>8.9041164065659396e-08</v>
-      </c>
-      <c r="F35">
-        <v>0.0013384388536105847</v>
-      </c>
-      <c r="G35">
-        <v>4.1329387394248513e-05</v>
-      </c>
-      <c r="H35">
-        <v>8.4058184719090962e-05</v>
-      </c>
-      <c r="I35">
-        <v>0.00012367372499727611</v>
-      </c>
-      <c r="J35">
-        <v>7.8782802852043641e-05</v>
-      </c>
-      <c r="K35">
-        <v>3.2271928767388684e-05</v>
-      </c>
-      <c r="L35">
-        <v>-2.0544762476647953e-05</v>
-      </c>
-      <c r="M35">
-        <v>-0.00014043889582977332</v>
-      </c>
-      <c r="N35">
-        <v>-1.7625645102796765e-05</v>
-      </c>
-      <c r="O35">
-        <v>-5.052634472419023e-05</v>
-      </c>
-      <c r="P35">
-        <v>-3.6944388681503179e-05</v>
-      </c>
-      <c r="Q35">
-        <v>-6.6631928615452647e-05</v>
-      </c>
-      <c r="R35">
-        <v>-3.3360425697209761e-05</v>
-      </c>
-      <c r="S35">
-        <v>3.6761823225330524e-05</v>
-      </c>
-      <c r="T35">
-        <v>2.7281207194245795e-05</v>
-      </c>
-      <c r="U35">
-        <v>7.7407651909492357e-05</v>
-      </c>
-      <c r="V35">
-        <v>-5.5734186276285567e-05</v>
-      </c>
-      <c r="W35">
-        <v>-5.7130189632925753e-05</v>
-      </c>
-      <c r="X35">
-        <v>-8.5620284228440056e-05</v>
-      </c>
-      <c r="Y35">
-        <v>-0.00011658928202047648</v>
-      </c>
-      <c r="Z35">
-        <v>-5.5428478897691602e-06</v>
-      </c>
-      <c r="AA35">
-        <v>3.1083917251401773e-05</v>
-      </c>
-      <c r="AB35">
-        <v>-7.4617209358636568e-05</v>
-      </c>
-      <c r="AC35">
-        <v>-1.616832719370789e-05</v>
-      </c>
-      <c r="AD35">
-        <v>-0.00010133362225287065</v>
-      </c>
-      <c r="AE35">
-        <v>-6.4100404898649859e-05</v>
-      </c>
-      <c r="AF35">
-        <v>-3.4834226891073935e-05</v>
-      </c>
-      <c r="AG35">
-        <v>-9.8878405566171735e-05</v>
-      </c>
-      <c r="AH35">
-        <v>-1.3276019498263992e-05</v>
-      </c>
-      <c r="AI35">
-        <v>0.0001443201995180632</v>
-      </c>
-      <c r="AJ35">
-        <v>0.0024491015669465288</v>
-      </c>
-      <c r="AK35">
-        <v>0.0004677202747141088</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36">
-        <v>-1.6843882547400635</v>
-      </c>
-      <c r="C36">
-        <v>-0.00018429143249133056</v>
-      </c>
-      <c r="D36">
-        <v>-0.00030416812978090462</v>
-      </c>
-      <c r="E36">
-        <v>2.7310916419036542e-06</v>
-      </c>
-      <c r="F36">
-        <v>-0.0036321204845852118</v>
-      </c>
-      <c r="G36">
-        <v>-0.0024305356388305312</v>
-      </c>
-      <c r="H36">
-        <v>-0.001846817251595371</v>
-      </c>
-      <c r="I36">
-        <v>-0.0029056184140483078</v>
-      </c>
-      <c r="J36">
-        <v>-0.0026564637035712568</v>
-      </c>
-      <c r="K36">
-        <v>-0.0030800114156639652</v>
-      </c>
-      <c r="L36">
-        <v>-0.0027188541205461492</v>
-      </c>
-      <c r="M36">
-        <v>-0.005378962444420857</v>
-      </c>
-      <c r="N36">
-        <v>-0.0037281263337097595</v>
-      </c>
-      <c r="O36">
-        <v>-0.00059337538449408516</v>
-      </c>
-      <c r="P36">
-        <v>-0.00088759852567903456</v>
-      </c>
-      <c r="Q36">
-        <v>-0.0010156987188927886</v>
-      </c>
-      <c r="R36">
-        <v>-0.0082142232681731674</v>
-      </c>
-      <c r="S36">
-        <v>-0.0075311980341891197</v>
-      </c>
-      <c r="T36">
-        <v>-0.0078956453265367523</v>
-      </c>
-      <c r="U36">
-        <v>-0.0084047649127244502</v>
-      </c>
-      <c r="V36">
-        <v>-0.00087039852192216031</v>
-      </c>
-      <c r="W36">
-        <v>-0.0035894863773359397</v>
-      </c>
-      <c r="X36">
-        <v>-0.0044935850989067851</v>
-      </c>
-      <c r="Y36">
-        <v>-0.0049899018761898149</v>
-      </c>
-      <c r="Z36">
-        <v>0.00021091908774728004</v>
-      </c>
-      <c r="AA36">
-        <v>-0.0001100793555372636</v>
-      </c>
-      <c r="AB36">
-        <v>-0.0030391536449426407</v>
-      </c>
-      <c r="AC36">
-        <v>-0.0030386505253575426</v>
-      </c>
-      <c r="AD36">
-        <v>-0.0029955110811089739</v>
-      </c>
-      <c r="AE36">
-        <v>-0.0029049788151290796</v>
-      </c>
-      <c r="AF36">
-        <v>-0.0031186835463261585</v>
-      </c>
-      <c r="AG36">
-        <v>-0.0029429837293659545</v>
-      </c>
-      <c r="AH36">
-        <v>-9.5414755969491113e-05</v>
-      </c>
-      <c r="AI36">
-        <v>0.00012343758506881501</v>
-      </c>
-      <c r="AJ36">
-        <v>0.0004677202747141088</v>
-      </c>
-      <c r="AK36">
-        <v>0.027541038141718505</v>
+        <v>0.019747248539181292</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_home_ownership.xlsx
+++ b/input/ES/reg_home_ownership.xlsx
@@ -508,100 +508,100 @@
         <v>0.00044992553030662381</v>
       </c>
       <c r="D2">
-        <v>8.5196106026390415e-05</v>
+        <v>8.5196106026389927e-05</v>
       </c>
       <c r="E2">
-        <v>-6.2828630875756437e-05</v>
+        <v>-6.2828630875756355e-05</v>
       </c>
       <c r="F2">
-        <v>-8.4565668852782602e-06</v>
+        <v>-8.4565668852783889e-06</v>
       </c>
       <c r="G2">
-        <v>-0.00010843423021864615</v>
+        <v>-0.00010843423021864604</v>
       </c>
       <c r="H2">
-        <v>-0.00010596516053969346</v>
+        <v>-0.00010596516053969373</v>
       </c>
       <c r="I2">
-        <v>0.00011732840928461018</v>
+        <v>0.00011732840928460902</v>
       </c>
       <c r="J2">
-        <v>0.00018803916794095022</v>
+        <v>0.00018803916794095035</v>
       </c>
       <c r="K2">
-        <v>5.1197771764598007e-06</v>
+        <v>5.1197771764612237e-06</v>
       </c>
       <c r="L2">
-        <v>-4.2400694082288633e-05</v>
+        <v>-4.2400694082287739e-05</v>
       </c>
       <c r="M2">
-        <v>-6.0906119824910346e-05</v>
+        <v>-6.0906119824910264e-05</v>
       </c>
       <c r="N2">
-        <v>-3.361322185230121e-05</v>
+        <v>-3.3613221852301075e-05</v>
       </c>
       <c r="O2">
-        <v>-4.8211227158035332e-05</v>
+        <v>-4.8211227158035095e-05</v>
       </c>
       <c r="P2">
-        <v>0.00015964187899656531</v>
+        <v>0.00015964187899656515</v>
       </c>
       <c r="Q2">
-        <v>-2.9367506558327801e-05</v>
+        <v>-2.9367506558323816e-05</v>
       </c>
       <c r="R2">
-        <v>-5.3783345333062307e-05</v>
+        <v>-5.3783345333062239e-05</v>
       </c>
       <c r="S2">
-        <v>-0.00011313088460214999</v>
+        <v>-0.00011313088460214739</v>
       </c>
       <c r="T2">
-        <v>3.3585706080962048e-07</v>
+        <v>3.3585706081016427e-07</v>
       </c>
       <c r="U2">
-        <v>3.897800193710734e-05</v>
+        <v>3.8978001937107882e-05</v>
       </c>
       <c r="V2">
-        <v>-1.429762836629479e-06</v>
+        <v>-1.4297628366294248e-06</v>
       </c>
       <c r="W2">
-        <v>-5.9422502834602001e-05</v>
+        <v>-5.9422502834600118e-05</v>
       </c>
       <c r="X2">
-        <v>-4.802813257907438e-07</v>
+        <v>-4.8028132579072198e-07</v>
       </c>
       <c r="Y2">
-        <v>-3.1834493471115892e-05</v>
+        <v>-3.1834493471115865e-05</v>
       </c>
       <c r="Z2">
-        <v>-8.1085924364915341e-05</v>
+        <v>-8.1085924364914826e-05</v>
       </c>
       <c r="AA2">
-        <v>-8.7021960423897996e-05</v>
+        <v>-8.7021960423897508e-05</v>
       </c>
       <c r="AB2">
-        <v>-9.2596972208624484e-05</v>
+        <v>-9.2596972208624809e-05</v>
       </c>
       <c r="AC2">
-        <v>-0.00010856841590938738</v>
+        <v>-0.00010856841590938695</v>
       </c>
       <c r="AD2">
-        <v>-6.3819334106375331e-05</v>
+        <v>-6.3819334106375602e-05</v>
       </c>
       <c r="AE2">
-        <v>-4.7641209485684455e-06</v>
+        <v>-4.7641209485679661e-06</v>
       </c>
       <c r="AF2">
-        <v>-1.9497710287320405e-06</v>
+        <v>-1.9497710287320125e-06</v>
       </c>
       <c r="AG2">
-        <v>8.2682461790918376e-05</v>
+        <v>8.2682461790918268e-05</v>
       </c>
       <c r="AH2">
-        <v>1.3097791130418853e-05</v>
+        <v>1.3097791130418568e-05</v>
       </c>
       <c r="AI2">
-        <v>-7.2034827626274e-05</v>
+        <v>-7.2034827626278066e-05</v>
       </c>
     </row>
     <row r="3">
@@ -612,103 +612,103 @@
         <v>0.12681895963208956</v>
       </c>
       <c r="C3">
-        <v>8.5196106026390415e-05</v>
+        <v>8.5196106026389927e-05</v>
       </c>
       <c r="D3">
         <v>0.15220756463936075</v>
       </c>
       <c r="E3">
-        <v>0.002084396923760304</v>
+        <v>0.0020843969237603283</v>
       </c>
       <c r="F3">
-        <v>0.0016882452590596976</v>
+        <v>0.0016882452590597011</v>
       </c>
       <c r="G3">
-        <v>0.0024417879512849943</v>
+        <v>0.0024417879512850195</v>
       </c>
       <c r="H3">
-        <v>0.0021134510801234059</v>
+        <v>0.0021134510801234241</v>
       </c>
       <c r="I3">
-        <v>0.0019828406336588871</v>
+        <v>0.0019828406336589123</v>
       </c>
       <c r="J3">
-        <v>0.0020871683533679178</v>
+        <v>0.0020871683533679438</v>
       </c>
       <c r="K3">
-        <v>-2.0115308488022473e-05</v>
+        <v>-2.0115308488016619e-05</v>
       </c>
       <c r="L3">
-        <v>0.0001862923207223158</v>
+        <v>0.0001862923207223358</v>
       </c>
       <c r="M3">
-        <v>0.00027309987750996157</v>
+        <v>0.00027309987750996309</v>
       </c>
       <c r="N3">
-        <v>3.415495757352156e-05</v>
+        <v>3.4154957573525626e-05</v>
       </c>
       <c r="O3">
-        <v>0.00017304750110305124</v>
+        <v>0.00017304750110305598</v>
       </c>
       <c r="P3">
-        <v>0.00024098226622748672</v>
+        <v>0.00024098226622749843</v>
       </c>
       <c r="Q3">
-        <v>0.0002049088881617481</v>
+        <v>0.00020490888816182367</v>
       </c>
       <c r="R3">
-        <v>0.00013961429365073885</v>
+        <v>0.00013961429365074959</v>
       </c>
       <c r="S3">
-        <v>0.00035347518107974138</v>
+        <v>0.00035347518107978909</v>
       </c>
       <c r="T3">
-        <v>-1.9174180004394734e-05</v>
+        <v>-1.9174180004385085e-05</v>
       </c>
       <c r="U3">
-        <v>-3.2793598063826689e-05</v>
+        <v>-3.2793598063814329e-05</v>
       </c>
       <c r="V3">
-        <v>0.00034904637853419248</v>
+        <v>0.00034904637853420397</v>
       </c>
       <c r="W3">
-        <v>0.00080519745304555952</v>
+        <v>0.000805197453045594</v>
       </c>
       <c r="X3">
-        <v>-7.8230614138234162e-06</v>
+        <v>-7.8230614138232163e-06</v>
       </c>
       <c r="Y3">
-        <v>0.00033228372241895826</v>
+        <v>0.00033228372241895908</v>
       </c>
       <c r="Z3">
-        <v>0.00014280146279554637</v>
+        <v>0.00014280146279555895</v>
       </c>
       <c r="AA3">
-        <v>0.0010716454027064866</v>
+        <v>0.0010716454027064983</v>
       </c>
       <c r="AB3">
-        <v>0.0007563371623317567</v>
+        <v>0.0007563371623317696</v>
       </c>
       <c r="AC3">
-        <v>0.00013931877986970488</v>
+        <v>0.00013931877986971463</v>
       </c>
       <c r="AD3">
-        <v>0.00013819997115470237</v>
+        <v>0.0001381999711547124</v>
       </c>
       <c r="AE3">
-        <v>2.6842920995643992e-05</v>
+        <v>2.6842920995656433e-05</v>
       </c>
       <c r="AF3">
-        <v>-8.510155342639439e-06</v>
+        <v>-8.510155342638653e-06</v>
       </c>
       <c r="AG3">
-        <v>5.4247913094004809e-05</v>
+        <v>5.4247913094002641e-05</v>
       </c>
       <c r="AH3">
-        <v>0.0013306349657106415</v>
+        <v>0.0013306349657106369</v>
       </c>
       <c r="AI3">
-        <v>-0.0029610538351407139</v>
+        <v>-0.0029610538351408063</v>
       </c>
     </row>
     <row r="4">
@@ -719,103 +719,103 @@
         <v>0.03595234274131201</v>
       </c>
       <c r="C4">
-        <v>-6.2828630875756437e-05</v>
+        <v>-6.2828630875756355e-05</v>
       </c>
       <c r="D4">
-        <v>0.002084396923760304</v>
+        <v>0.0020843969237603283</v>
       </c>
       <c r="E4">
-        <v>0.0026441163376976526</v>
+        <v>0.0026441163376976738</v>
       </c>
       <c r="F4">
-        <v>0.0018128197573376338</v>
+        <v>0.0018128197573376375</v>
       </c>
       <c r="G4">
-        <v>0.0020642741812237952</v>
+        <v>0.0020642741812238186</v>
       </c>
       <c r="H4">
-        <v>0.0020977832497201653</v>
+        <v>0.0020977832497201827</v>
       </c>
       <c r="I4">
-        <v>0.0021085718188296109</v>
+        <v>0.0021085718188296331</v>
       </c>
       <c r="J4">
-        <v>0.0021090443932507389</v>
+        <v>0.0021090443932507631</v>
       </c>
       <c r="K4">
-        <v>1.4118593225045939e-05</v>
+        <v>1.4118593225052661e-05</v>
       </c>
       <c r="L4">
-        <v>-9.3260023870279937e-05</v>
+        <v>-9.3260023870260489e-05</v>
       </c>
       <c r="M4">
-        <v>0.00011537275032906199</v>
+        <v>0.00011537275032906373</v>
       </c>
       <c r="N4">
-        <v>0.00013157663846053444</v>
+        <v>0.00013157663846053829</v>
       </c>
       <c r="O4">
-        <v>9.2101658019669966e-05</v>
+        <v>9.2101658019674547e-05</v>
       </c>
       <c r="P4">
-        <v>0.00025685583857601392</v>
+        <v>0.00025685583857602715</v>
       </c>
       <c r="Q4">
-        <v>7.6911989027215739e-05</v>
+        <v>7.6911989027287839e-05</v>
       </c>
       <c r="R4">
-        <v>5.8410909162380639e-05</v>
+        <v>5.8410909162392619e-05</v>
       </c>
       <c r="S4">
-        <v>0.00011723908016807649</v>
+        <v>0.00011723908016812289</v>
       </c>
       <c r="T4">
-        <v>7.8675240484065185e-05</v>
+        <v>7.8675240484074415e-05</v>
       </c>
       <c r="U4">
-        <v>9.0123156531705896e-05</v>
+        <v>9.0123156531717605e-05</v>
       </c>
       <c r="V4">
-        <v>0.00023564401616686876</v>
+        <v>0.00023564401616688263</v>
       </c>
       <c r="W4">
-        <v>0.00072939579332476838</v>
+        <v>0.0007293957933247996</v>
       </c>
       <c r="X4">
-        <v>-3.1864712784610305e-05</v>
+        <v>-3.1864712784610176e-05</v>
       </c>
       <c r="Y4">
-        <v>-6.7136134926304263e-05</v>
+        <v>-6.7136134926303558e-05</v>
       </c>
       <c r="Z4">
-        <v>0.00010394145986337652</v>
+        <v>0.00010394145986338931</v>
       </c>
       <c r="AA4">
-        <v>8.770373819365785e-05</v>
+        <v>8.7703738193669126e-05</v>
       </c>
       <c r="AB4">
-        <v>0.00010743254938749445</v>
+        <v>0.00010743254938750703</v>
       </c>
       <c r="AC4">
-        <v>4.3360577271745913e-05</v>
+        <v>4.3360577271755454e-05</v>
       </c>
       <c r="AD4">
-        <v>6.5902518832273212e-05</v>
+        <v>6.5902518832282645e-05</v>
       </c>
       <c r="AE4">
-        <v>-1.1316323787113696e-05</v>
+        <v>-1.1316323787101472e-05</v>
       </c>
       <c r="AF4">
-        <v>5.5397297790903439e-06</v>
+        <v>5.5397297790910622e-06</v>
       </c>
       <c r="AG4">
-        <v>-3.4781742681625188e-05</v>
+        <v>-3.478174268162779e-05</v>
       </c>
       <c r="AH4">
-        <v>2.948272168971347e-05</v>
+        <v>2.9482721689708916e-05</v>
       </c>
       <c r="AI4">
-        <v>-0.0024047977311919084</v>
+        <v>-0.0024047977311919999</v>
       </c>
     </row>
     <row r="5">
@@ -826,103 +826,103 @@
         <v>-0.076810395035844345</v>
       </c>
       <c r="C5">
-        <v>-8.4565668852782602e-06</v>
+        <v>-8.4565668852783889e-06</v>
       </c>
       <c r="D5">
-        <v>0.0016882452590596976</v>
+        <v>0.0016882452590597011</v>
       </c>
       <c r="E5">
-        <v>0.0018128197573376338</v>
+        <v>0.0018128197573376375</v>
       </c>
       <c r="F5">
-        <v>0.0028941737281210798</v>
+        <v>0.0028941737281210829</v>
       </c>
       <c r="G5">
-        <v>0.0018612724534218567</v>
+        <v>0.0018612724534218779</v>
       </c>
       <c r="H5">
-        <v>0.0018492289694546063</v>
+        <v>0.0018492289694546213</v>
       </c>
       <c r="I5">
-        <v>0.001802882282930145</v>
+        <v>0.001802882282930165</v>
       </c>
       <c r="J5">
-        <v>0.0017667256002488313</v>
+        <v>0.0017667256002488528</v>
       </c>
       <c r="K5">
-        <v>0.0001037959055400241</v>
+        <v>0.00010379590554003039</v>
       </c>
       <c r="L5">
-        <v>9.6185840505532403e-05</v>
+        <v>9.6185840505550211e-05</v>
       </c>
       <c r="M5">
-        <v>8.1680466308312917e-05</v>
+        <v>8.1680466308314218e-05</v>
       </c>
       <c r="N5">
-        <v>0.00012419560983464682</v>
+        <v>0.00012419560983465032</v>
       </c>
       <c r="O5">
-        <v>0.00011222399271491033</v>
+        <v>0.00011222399271491425</v>
       </c>
       <c r="P5">
-        <v>2.6036874602798177e-05</v>
+        <v>2.6036874602808802e-05</v>
       </c>
       <c r="Q5">
-        <v>3.0606587825475549e-05</v>
+        <v>3.0606587825537783e-05</v>
       </c>
       <c r="R5">
-        <v>-5.2813169843047366e-06</v>
+        <v>-5.2813169842945993e-06</v>
       </c>
       <c r="S5">
-        <v>2.2049062175248733e-05</v>
+        <v>2.2049062175289933e-05</v>
       </c>
       <c r="T5">
-        <v>3.3185996693455404e-05</v>
+        <v>3.3185996693463644e-05</v>
       </c>
       <c r="U5">
-        <v>4.759201680919038e-05</v>
+        <v>4.7592016809201655e-05</v>
       </c>
       <c r="V5">
-        <v>6.0529809378991268e-05</v>
+        <v>6.0529809379003194e-05</v>
       </c>
       <c r="W5">
-        <v>0.00035402050081689601</v>
+        <v>0.00035402050081692485</v>
       </c>
       <c r="X5">
-        <v>-1.1239453734116289e-05</v>
+        <v>-1.1239453734116243e-05</v>
       </c>
       <c r="Y5">
-        <v>-4.883454486433441e-05</v>
+        <v>-4.883454486433376e-05</v>
       </c>
       <c r="Z5">
-        <v>0.00011191749201079561</v>
+        <v>0.00011191749201080623</v>
       </c>
       <c r="AA5">
-        <v>7.3842847933200395e-06</v>
+        <v>7.3842847933297973e-06</v>
       </c>
       <c r="AB5">
-        <v>5.2590944147562577e-05</v>
+        <v>5.2590944147573203e-05</v>
       </c>
       <c r="AC5">
-        <v>-2.1056099340477884e-05</v>
+        <v>-2.1056099340469427e-05</v>
       </c>
       <c r="AD5">
-        <v>-5.3059972264982548e-06</v>
+        <v>-5.3059972264900691e-06</v>
       </c>
       <c r="AE5">
-        <v>-7.2812817573096904e-05</v>
+        <v>-7.2812817573086278e-05</v>
       </c>
       <c r="AF5">
-        <v>2.3800320149084932e-06</v>
+        <v>2.3800320149091234e-06</v>
       </c>
       <c r="AG5">
-        <v>0.00011273175229523135</v>
+        <v>0.00011273175229523005</v>
       </c>
       <c r="AH5">
-        <v>7.0103091909831813e-05</v>
+        <v>7.0103091909827909e-05</v>
       </c>
       <c r="AI5">
-        <v>-0.0020326920215607788</v>
+        <v>-0.0020326920215608581</v>
       </c>
     </row>
     <row r="6">
@@ -933,103 +933,103 @@
         <v>0.16250526351603703</v>
       </c>
       <c r="C6">
-        <v>-0.00010843423021864615</v>
+        <v>-0.00010843423021864604</v>
       </c>
       <c r="D6">
-        <v>0.0024417879512849943</v>
+        <v>0.0024417879512850195</v>
       </c>
       <c r="E6">
-        <v>0.0020642741812237952</v>
+        <v>0.0020642741812238186</v>
       </c>
       <c r="F6">
-        <v>0.0018612724534218567</v>
+        <v>0.0018612724534218779</v>
       </c>
       <c r="G6">
-        <v>0.057488003405249427</v>
+        <v>0.057488003405249455</v>
       </c>
       <c r="H6">
-        <v>0.0022753072320950917</v>
+        <v>0.0022753072320951104</v>
       </c>
       <c r="I6">
-        <v>0.001991292999147447</v>
+        <v>0.0019912929991474718</v>
       </c>
       <c r="J6">
-        <v>0.0021086397979223183</v>
+        <v>0.0021086397979223448</v>
       </c>
       <c r="K6">
-        <v>0.000499162153585417</v>
+        <v>0.0004991621535854222</v>
       </c>
       <c r="L6">
-        <v>0.00044981848966821586</v>
+        <v>0.00044981848966823651</v>
       </c>
       <c r="M6">
-        <v>0.00018633283427474867</v>
+        <v>0.0001863328342747504</v>
       </c>
       <c r="N6">
-        <v>0.00027573964584833103</v>
+        <v>0.00027573964584833504</v>
       </c>
       <c r="O6">
-        <v>0.00028512265825970701</v>
+        <v>0.00028512265825971189</v>
       </c>
       <c r="P6">
-        <v>-5.3984468993179338e-05</v>
+        <v>-5.398446899316687e-05</v>
       </c>
       <c r="Q6">
-        <v>6.9483088424569491e-05</v>
+        <v>6.9483088424646795e-05</v>
       </c>
       <c r="R6">
-        <v>-4.2746946247138073e-05</v>
+        <v>-4.2746946247127664e-05</v>
       </c>
       <c r="S6">
-        <v>0.0001053769319945768</v>
+        <v>0.00010537693199462651</v>
       </c>
       <c r="T6">
-        <v>0.00013915368209563547</v>
+        <v>0.00013915368209564504</v>
       </c>
       <c r="U6">
-        <v>0.00021119581025745267</v>
+        <v>0.00021119581025746525</v>
       </c>
       <c r="V6">
-        <v>0.00054653907747107444</v>
+        <v>0.00054653907747108572</v>
       </c>
       <c r="W6">
-        <v>0.0012059413454082234</v>
+        <v>0.0012059413454082583</v>
       </c>
       <c r="X6">
-        <v>-4.7557013707125948e-05</v>
+        <v>-4.7557013707125826e-05</v>
       </c>
       <c r="Y6">
-        <v>0.00012877618346038923</v>
+        <v>0.00012877618346038988</v>
       </c>
       <c r="Z6">
-        <v>0.00020423090026065174</v>
+        <v>0.00020423090026066562</v>
       </c>
       <c r="AA6">
-        <v>6.1444208924456853e-05</v>
+        <v>6.1444208924468779e-05</v>
       </c>
       <c r="AB6">
-        <v>0.0001231085885548299</v>
+        <v>0.00012310858855484356</v>
       </c>
       <c r="AC6">
-        <v>6.6073099431141315e-05</v>
+        <v>6.6073099431151507e-05</v>
       </c>
       <c r="AD6">
-        <v>2.2334027506154791e-05</v>
+        <v>2.233402750616547e-05</v>
       </c>
       <c r="AE6">
-        <v>-3.5116145501650625e-05</v>
+        <v>-3.5116145501637398e-05</v>
       </c>
       <c r="AF6">
-        <v>1.0130120580751479e-05</v>
+        <v>1.0130120580752258e-05</v>
       </c>
       <c r="AG6">
-        <v>-0.00013755789499182453</v>
+        <v>-0.00013755789499182583</v>
       </c>
       <c r="AH6">
-        <v>7.9445070357428687e-05</v>
+        <v>7.94450703574237e-05</v>
       </c>
       <c r="AI6">
-        <v>-0.0029729672163784247</v>
+        <v>-0.0029729672163785214</v>
       </c>
     </row>
     <row r="7">
@@ -1040,103 +1040,103 @@
         <v>-0.22492068207238639</v>
       </c>
       <c r="C7">
-        <v>-0.00010596516053969346</v>
+        <v>-0.00010596516053969373</v>
       </c>
       <c r="D7">
-        <v>0.0021134510801234059</v>
+        <v>0.0021134510801234241</v>
       </c>
       <c r="E7">
-        <v>0.0020977832497201653</v>
+        <v>0.0020977832497201827</v>
       </c>
       <c r="F7">
-        <v>0.0018492289694546063</v>
+        <v>0.0018492289694546213</v>
       </c>
       <c r="G7">
-        <v>0.0022753072320950917</v>
+        <v>0.0022753072320951104</v>
       </c>
       <c r="H7">
-        <v>0.0031113177501820512</v>
+        <v>0.0031113177501820698</v>
       </c>
       <c r="I7">
-        <v>0.0020203654061571332</v>
+        <v>0.0020203654061571588</v>
       </c>
       <c r="J7">
-        <v>0.0021083988136712008</v>
+        <v>0.0021083988136712272</v>
       </c>
       <c r="K7">
-        <v>0.00039531652231036374</v>
+        <v>0.00039531652231037046</v>
       </c>
       <c r="L7">
-        <v>0.00038087372306953724</v>
+        <v>0.00038087372306955822</v>
       </c>
       <c r="M7">
-        <v>0.00011825463761074928</v>
+        <v>0.00011825463761075037</v>
       </c>
       <c r="N7">
-        <v>0.00016660764644241399</v>
+        <v>0.000166607646442418</v>
       </c>
       <c r="O7">
-        <v>0.00010625670043667456</v>
+        <v>0.00010625670043667934</v>
       </c>
       <c r="P7">
-        <v>2.4952126135451978e-05</v>
+        <v>2.4952126135464555e-05</v>
       </c>
       <c r="Q7">
-        <v>1.6276286501519304e-06</v>
+        <v>1.6276286502292341e-06</v>
       </c>
       <c r="R7">
-        <v>-3.8034219591053182e-05</v>
+        <v>-3.8034219591042448e-05</v>
       </c>
       <c r="S7">
-        <v>3.104761253483148e-05</v>
+        <v>3.1047612534881083e-05</v>
       </c>
       <c r="T7">
-        <v>0.00013130352291067067</v>
+        <v>0.0001313035229106804</v>
       </c>
       <c r="U7">
-        <v>0.00014664378215088975</v>
+        <v>0.00014664378215090254</v>
       </c>
       <c r="V7">
-        <v>0.00051188472275484316</v>
+        <v>0.00051188472275485487</v>
       </c>
       <c r="W7">
-        <v>0.001063574258902799</v>
+        <v>0.0010635742589028341</v>
       </c>
       <c r="X7">
-        <v>-2.6566527801927502e-05</v>
+        <v>-2.6566527801927329e-05</v>
       </c>
       <c r="Y7">
-        <v>-1.8494888706545559e-05</v>
+        <v>-1.8494888706544908e-05</v>
       </c>
       <c r="Z7">
-        <v>0.00022190153581250639</v>
+        <v>0.00022190153581251983</v>
       </c>
       <c r="AA7">
-        <v>0.00014698745143087479</v>
+        <v>0.00014698745143088671</v>
       </c>
       <c r="AB7">
-        <v>0.00017526084095628117</v>
+        <v>0.00017526084095629484</v>
       </c>
       <c r="AC7">
-        <v>9.9242546054492892e-05</v>
+        <v>9.9242546054503084e-05</v>
       </c>
       <c r="AD7">
-        <v>0.00011251699848729887</v>
+        <v>0.00011251699848730922</v>
       </c>
       <c r="AE7">
-        <v>-6.6641415073845887e-06</v>
+        <v>-6.664141507371497e-06</v>
       </c>
       <c r="AF7">
-        <v>1.4003597577924943e-05</v>
+        <v>1.4003597577925736e-05</v>
       </c>
       <c r="AG7">
-        <v>-8.6778641401065969e-05</v>
+        <v>-8.677864140106727e-05</v>
       </c>
       <c r="AH7">
-        <v>6.0970632979302688e-05</v>
+        <v>6.0970632979297701e-05</v>
       </c>
       <c r="AI7">
-        <v>-0.0028559799727096713</v>
+        <v>-0.0028559799727097693</v>
       </c>
     </row>
     <row r="8">
@@ -1147,103 +1147,103 @@
         <v>-0.1529704486597758</v>
       </c>
       <c r="C8">
-        <v>0.00011732840928461018</v>
+        <v>0.00011732840928460902</v>
       </c>
       <c r="D8">
-        <v>0.0019828406336588871</v>
+        <v>0.0019828406336589123</v>
       </c>
       <c r="E8">
-        <v>0.0021085718188296109</v>
+        <v>0.0021085718188296331</v>
       </c>
       <c r="F8">
-        <v>0.001802882282930145</v>
+        <v>0.001802882282930165</v>
       </c>
       <c r="G8">
-        <v>0.001991292999147447</v>
+        <v>0.0019912929991474718</v>
       </c>
       <c r="H8">
-        <v>0.0020203654061571332</v>
+        <v>0.0020203654061571588</v>
       </c>
       <c r="I8">
-        <v>0.0023630518918623398</v>
+        <v>0.0023630518918623623</v>
       </c>
       <c r="J8">
-        <v>0.0021630154235348737</v>
+        <v>0.0021630154235348989</v>
       </c>
       <c r="K8">
-        <v>-9.6477412201960693e-05</v>
+        <v>-9.6477412201952453e-05</v>
       </c>
       <c r="L8">
-        <v>-6.2624319062020188e-05</v>
+        <v>-6.2624319062000184e-05</v>
       </c>
       <c r="M8">
-        <v>8.9623365210410788e-05</v>
+        <v>8.9623365210411872e-05</v>
       </c>
       <c r="N8">
-        <v>0.00012382017728425647</v>
+        <v>0.00012382017728426056</v>
       </c>
       <c r="O8">
-        <v>0.00012507577302552488</v>
+        <v>0.00012507577302552959</v>
       </c>
       <c r="P8">
-        <v>0.00012121079140615248</v>
+        <v>0.0001212107914061668</v>
       </c>
       <c r="Q8">
-        <v>-5.1614434372137608e-06</v>
+        <v>-5.1614434371389508e-06</v>
       </c>
       <c r="R8">
-        <v>-2.4039909615055483e-05</v>
+        <v>-2.4039909615042798e-05</v>
       </c>
       <c r="S8">
-        <v>-3.7246413668003554e-05</v>
+        <v>-3.7246413667954385e-05</v>
       </c>
       <c r="T8">
-        <v>9.1079901964059986e-05</v>
+        <v>9.1079901964069663e-05</v>
       </c>
       <c r="U8">
-        <v>0.00022175602752184205</v>
+        <v>0.00022175602752185462</v>
       </c>
       <c r="V8">
-        <v>0.0003513849927976253</v>
+        <v>0.00035138499279763918</v>
       </c>
       <c r="W8">
-        <v>0.000769543349896985</v>
+        <v>0.00076954334989701731</v>
       </c>
       <c r="X8">
-        <v>-3.6324449322708719e-05</v>
+        <v>-3.6324449322708611e-05</v>
       </c>
       <c r="Y8">
-        <v>-8.8974886706919552e-05</v>
+        <v>-8.8974886706918684e-05</v>
       </c>
       <c r="Z8">
-        <v>5.285445932202786e-05</v>
+        <v>5.2854459322041088e-05</v>
       </c>
       <c r="AA8">
-        <v>3.2123447875525299e-05</v>
+        <v>3.2123447875537442e-05</v>
       </c>
       <c r="AB8">
-        <v>5.362024703079349e-05</v>
+        <v>5.3620247030806501e-05</v>
       </c>
       <c r="AC8">
-        <v>-1.5459636173135441e-05</v>
+        <v>-1.54596361731259e-05</v>
       </c>
       <c r="AD8">
-        <v>3.2777159819301132e-05</v>
+        <v>3.2777159819310836e-05</v>
       </c>
       <c r="AE8">
-        <v>2.4805335383795338e-05</v>
+        <v>2.4805335383808186e-05</v>
       </c>
       <c r="AF8">
-        <v>2.8167527087327672e-06</v>
+        <v>2.8167527087335329e-06</v>
       </c>
       <c r="AG8">
-        <v>4.6806591355737746e-06</v>
+        <v>4.6806591355711726e-06</v>
       </c>
       <c r="AH8">
-        <v>3.7243755954839588e-05</v>
+        <v>3.7243755954834818e-05</v>
       </c>
       <c r="AI8">
-        <v>-0.0024133870012868893</v>
+        <v>-0.0024133870012869878</v>
       </c>
     </row>
     <row r="9">
@@ -1254,103 +1254,103 @@
         <v>-0.36025040732867963</v>
       </c>
       <c r="C9">
-        <v>0.00018803916794095022</v>
+        <v>0.00018803916794095035</v>
       </c>
       <c r="D9">
-        <v>0.0020871683533679178</v>
+        <v>0.0020871683533679438</v>
       </c>
       <c r="E9">
-        <v>0.0021090443932507389</v>
+        <v>0.0021090443932507631</v>
       </c>
       <c r="F9">
-        <v>0.0017667256002488313</v>
+        <v>0.0017667256002488528</v>
       </c>
       <c r="G9">
-        <v>0.0021086397979223183</v>
+        <v>0.0021086397979223448</v>
       </c>
       <c r="H9">
-        <v>0.0021083988136712008</v>
+        <v>0.0021083988136712272</v>
       </c>
       <c r="I9">
-        <v>0.0021630154235348737</v>
+        <v>0.0021630154235348989</v>
       </c>
       <c r="J9">
-        <v>0.0042791945053281084</v>
+        <v>0.0042791945053281336</v>
       </c>
       <c r="K9">
-        <v>0.00017945082029095587</v>
+        <v>0.00017945082029096368</v>
       </c>
       <c r="L9">
-        <v>4.5283576011172862e-05</v>
+        <v>4.528357601119441e-05</v>
       </c>
       <c r="M9">
-        <v>4.9604585912203271e-05</v>
+        <v>4.9604585912205439e-05</v>
       </c>
       <c r="N9">
-        <v>4.7138664410984951e-05</v>
+        <v>4.7138664410989125e-05</v>
       </c>
       <c r="O9">
-        <v>5.7869774781328644e-05</v>
+        <v>5.7869774781333665e-05</v>
       </c>
       <c r="P9">
-        <v>0.00020041402999989547</v>
+        <v>0.00020041402999990848</v>
       </c>
       <c r="Q9">
-        <v>6.3657106405295766e-05</v>
+        <v>6.3657106405375671e-05</v>
       </c>
       <c r="R9">
-        <v>-1.090278735531964e-05</v>
+        <v>-1.0902787355308852e-05</v>
       </c>
       <c r="S9">
-        <v>-6.0940037529625996e-05</v>
+        <v>-6.0940037529575038e-05</v>
       </c>
       <c r="T9">
-        <v>6.999213058396495e-05</v>
+        <v>6.999213058397506e-05</v>
       </c>
       <c r="U9">
-        <v>7.925130788153387e-05</v>
+        <v>7.9251307881547098e-05</v>
       </c>
       <c r="V9">
-        <v>0.0004394237064820612</v>
+        <v>0.00043942370648207335</v>
       </c>
       <c r="W9">
-        <v>0.00077552129634346251</v>
+        <v>0.00077552129634349829</v>
       </c>
       <c r="X9">
-        <v>-3.8749522387691831e-05</v>
+        <v>-3.8749522387691655e-05</v>
       </c>
       <c r="Y9">
-        <v>-2.3845104977733469e-05</v>
+        <v>-2.384510497773271e-05</v>
       </c>
       <c r="Z9">
-        <v>0.00014993704661024967</v>
+        <v>0.00014993704661026355</v>
       </c>
       <c r="AA9">
-        <v>0.00012300481935884349</v>
+        <v>0.00012300481935885563</v>
       </c>
       <c r="AB9">
-        <v>7.6264365752959753e-05</v>
+        <v>7.6264365752973414e-05</v>
       </c>
       <c r="AC9">
-        <v>7.7531048207134723e-05</v>
+        <v>7.7531048207145131e-05</v>
       </c>
       <c r="AD9">
-        <v>0.00016385404757253771</v>
+        <v>0.00016385404757254807</v>
       </c>
       <c r="AE9">
-        <v>1.1865457425506851e-05</v>
+        <v>1.1865457425520377e-05</v>
       </c>
       <c r="AF9">
-        <v>2.2537754202507757e-06</v>
+        <v>2.2537754202515888e-06</v>
       </c>
       <c r="AG9">
-        <v>0.00015386211925594567</v>
+        <v>0.00015386211925594393</v>
       </c>
       <c r="AH9">
-        <v>-2.3520691061540422e-05</v>
+        <v>-2.3520691061545192e-05</v>
       </c>
       <c r="AI9">
-        <v>-0.002582096142993707</v>
+        <v>-0.0025820961429938089</v>
       </c>
     </row>
     <row r="10">
@@ -1361,103 +1361,103 @@
         <v>0.15737459156980077</v>
       </c>
       <c r="C10">
-        <v>5.1197771764598007e-06</v>
+        <v>5.1197771764612237e-06</v>
       </c>
       <c r="D10">
-        <v>-2.0115308488022473e-05</v>
+        <v>-2.0115308488016619e-05</v>
       </c>
       <c r="E10">
-        <v>1.4118593225045939e-05</v>
+        <v>1.4118593225052661e-05</v>
       </c>
       <c r="F10">
-        <v>0.0001037959055400241</v>
+        <v>0.00010379590554003039</v>
       </c>
       <c r="G10">
-        <v>0.000499162153585417</v>
+        <v>0.0004991621535854222</v>
       </c>
       <c r="H10">
-        <v>0.00039531652231036374</v>
+        <v>0.00039531652231037046</v>
       </c>
       <c r="I10">
-        <v>-9.6477412201960693e-05</v>
+        <v>-9.6477412201952453e-05</v>
       </c>
       <c r="J10">
-        <v>0.00017945082029095587</v>
+        <v>0.00017945082029096368</v>
       </c>
       <c r="K10">
-        <v>0.0074102080942152846</v>
+        <v>0.0074102080942152811</v>
       </c>
       <c r="L10">
-        <v>0.0032290788500811763</v>
+        <v>0.0032290788500811923</v>
       </c>
       <c r="M10">
-        <v>-0.0040853893661426562</v>
+        <v>-0.0040853893661426553</v>
       </c>
       <c r="N10">
-        <v>7.6384446146617079e-05</v>
+        <v>7.6384446146619085e-05</v>
       </c>
       <c r="O10">
-        <v>0.00017008274704562862</v>
+        <v>0.00017008274704563168</v>
       </c>
       <c r="P10">
-        <v>0.00034860485841903114</v>
+        <v>0.00034860485841902724</v>
       </c>
       <c r="Q10">
-        <v>9.7647707584599822e-05</v>
+        <v>9.7647707584657718e-05</v>
       </c>
       <c r="R10">
-        <v>6.1269581888890234e-05</v>
+        <v>6.1269581888881127e-05</v>
       </c>
       <c r="S10">
-        <v>0.00016744100269595696</v>
+        <v>0.00016744100269598612</v>
       </c>
       <c r="T10">
-        <v>0.00063230654186255972</v>
+        <v>0.00063230654186256547</v>
       </c>
       <c r="U10">
-        <v>0.0032118980277105877</v>
+        <v>0.0032118980277105924</v>
       </c>
       <c r="V10">
-        <v>0.0036789130441664463</v>
+        <v>0.0036789130441664351</v>
       </c>
       <c r="W10">
-        <v>0.0039392190568509015</v>
+        <v>0.0039392190568509327</v>
       </c>
       <c r="X10">
-        <v>-0.00016679003225496483</v>
+        <v>-0.00016679003225496437</v>
       </c>
       <c r="Y10">
-        <v>3.7762544182087083e-05</v>
+        <v>3.7762544182086649e-05</v>
       </c>
       <c r="Z10">
-        <v>0.00018681899800963376</v>
+        <v>0.0001868189980096433</v>
       </c>
       <c r="AA10">
-        <v>0.00010292825587060895</v>
+        <v>0.00010292825587061589</v>
       </c>
       <c r="AB10">
-        <v>7.9016028483066278e-05</v>
+        <v>7.9016028483075602e-05</v>
       </c>
       <c r="AC10">
-        <v>0.0001535077105833311</v>
+        <v>0.00015350771058333999</v>
       </c>
       <c r="AD10">
-        <v>0.00035701943319050699</v>
+        <v>0.00035701943319051686</v>
       </c>
       <c r="AE10">
-        <v>0.0002187728275894843</v>
+        <v>0.00021877282758949387</v>
       </c>
       <c r="AF10">
-        <v>-3.2565980408890923e-07</v>
+        <v>-3.2565980408828582e-07</v>
       </c>
       <c r="AG10">
-        <v>0.00037063543131517608</v>
+        <v>0.00037063543131517695</v>
       </c>
       <c r="AH10">
-        <v>-9.4744370399680016e-05</v>
+        <v>-9.4744370399683486e-05</v>
       </c>
       <c r="AI10">
-        <v>-0.0040142065628919503</v>
+        <v>-0.0040142065628920171</v>
       </c>
     </row>
     <row r="11">
@@ -1468,103 +1468,103 @@
         <v>0.083971588068680172</v>
       </c>
       <c r="C11">
-        <v>-4.2400694082288633e-05</v>
+        <v>-4.2400694082287739e-05</v>
       </c>
       <c r="D11">
-        <v>0.0001862923207223158</v>
+        <v>0.0001862923207223358</v>
       </c>
       <c r="E11">
-        <v>-9.3260023870279937e-05</v>
+        <v>-9.3260023870260489e-05</v>
       </c>
       <c r="F11">
-        <v>9.6185840505532403e-05</v>
+        <v>9.6185840505550211e-05</v>
       </c>
       <c r="G11">
-        <v>0.00044981848966821586</v>
+        <v>0.00044981848966823651</v>
       </c>
       <c r="H11">
-        <v>0.00038087372306953724</v>
+        <v>0.00038087372306955822</v>
       </c>
       <c r="I11">
-        <v>-6.2624319062020188e-05</v>
+        <v>-6.2624319062000184e-05</v>
       </c>
       <c r="J11">
-        <v>4.5283576011172862e-05</v>
+        <v>4.528357601119441e-05</v>
       </c>
       <c r="K11">
-        <v>0.0032290788500811763</v>
+        <v>0.0032290788500811923</v>
       </c>
       <c r="L11">
-        <v>0.0031002153941946968</v>
+        <v>0.0031002153941947137</v>
       </c>
       <c r="M11">
-        <v>-0.00041434020189945052</v>
+        <v>-0.00041434020189944922</v>
       </c>
       <c r="N11">
-        <v>0.00015482852411966399</v>
+        <v>0.00015482852411966605</v>
       </c>
       <c r="O11">
-        <v>8.2149596255874971e-05</v>
+        <v>8.21495962558784e-05</v>
       </c>
       <c r="P11">
-        <v>0.00030185717532583457</v>
+        <v>0.0003018571753258311</v>
       </c>
       <c r="Q11">
-        <v>0.00017023512700279297</v>
+        <v>0.00017023512700285585</v>
       </c>
       <c r="R11">
-        <v>0.00028235702247508392</v>
+        <v>0.00028235702247507617</v>
       </c>
       <c r="S11">
-        <v>0.00047732123564773365</v>
+        <v>0.00047732123564776666</v>
       </c>
       <c r="T11">
-        <v>0.00047289903568890847</v>
+        <v>0.00047289903568891465</v>
       </c>
       <c r="U11">
-        <v>0.0026454966364136681</v>
+        <v>0.002645496636413675</v>
       </c>
       <c r="V11">
-        <v>0.0030849932598246382</v>
+        <v>0.0030849932598246296</v>
       </c>
       <c r="W11">
-        <v>0.0033259568499667243</v>
+        <v>0.003325956849966759</v>
       </c>
       <c r="X11">
-        <v>-0.0001492195673697877</v>
+        <v>-0.00014921956736978716</v>
       </c>
       <c r="Y11">
-        <v>4.2739638244125274e-05</v>
+        <v>4.2739638244124894e-05</v>
       </c>
       <c r="Z11">
-        <v>4.4432803402145657e-05</v>
+        <v>4.4432803402155632e-05</v>
       </c>
       <c r="AA11">
-        <v>-5.0739540888786183e-05</v>
+        <v>-5.0739540888778811e-05</v>
       </c>
       <c r="AB11">
-        <v>-2.6403228015850705e-05</v>
+        <v>-2.6403228015840947e-05</v>
       </c>
       <c r="AC11">
-        <v>2.9783468960469656e-05</v>
+        <v>2.9783468960480498e-05</v>
       </c>
       <c r="AD11">
-        <v>0.00011865440852693141</v>
+        <v>0.00011865440852694214</v>
       </c>
       <c r="AE11">
-        <v>-5.003866963365614e-05</v>
+        <v>-5.0038669633645488e-05</v>
       </c>
       <c r="AF11">
-        <v>1.0516857342269178e-05</v>
+        <v>1.0516857342269856e-05</v>
       </c>
       <c r="AG11">
         <v>5.5955232594965317e-05</v>
       </c>
       <c r="AH11">
-        <v>-2.7635679663996337e-05</v>
+        <v>-2.7635679664000023e-05</v>
       </c>
       <c r="AI11">
-        <v>-0.0036131444182356887</v>
+        <v>-0.0036131444182357572</v>
       </c>
     </row>
     <row r="12">
@@ -1575,103 +1575,103 @@
         <v>-0.05101015186102266</v>
       </c>
       <c r="C12">
-        <v>-6.0906119824910346e-05</v>
+        <v>-6.0906119824910264e-05</v>
       </c>
       <c r="D12">
-        <v>0.00027309987750996157</v>
+        <v>0.00027309987750996309</v>
       </c>
       <c r="E12">
-        <v>0.00011537275032906199</v>
+        <v>0.00011537275032906373</v>
       </c>
       <c r="F12">
-        <v>8.1680466308312917e-05</v>
+        <v>8.1680466308314218e-05</v>
       </c>
       <c r="G12">
-        <v>0.00018633283427474867</v>
+        <v>0.0001863328342747504</v>
       </c>
       <c r="H12">
-        <v>0.00011825463761074928</v>
+        <v>0.00011825463761075037</v>
       </c>
       <c r="I12">
-        <v>8.9623365210410788e-05</v>
+        <v>8.9623365210411872e-05</v>
       </c>
       <c r="J12">
-        <v>4.9604585912203271e-05</v>
+        <v>4.9604585912205439e-05</v>
       </c>
       <c r="K12">
-        <v>-0.0040853893661426562</v>
+        <v>-0.0040853893661426553</v>
       </c>
       <c r="L12">
-        <v>-0.00041434020189945052</v>
+        <v>-0.00041434020189944922</v>
       </c>
       <c r="M12">
         <v>0.0056550742588793567</v>
       </c>
       <c r="N12">
-        <v>0.00053972298045773537</v>
+        <v>0.00053972298045773558</v>
       </c>
       <c r="O12">
-        <v>0.00041312332789258054</v>
+        <v>0.00041312332789258098</v>
       </c>
       <c r="P12">
-        <v>0.00015702916722206293</v>
+        <v>0.0001570291672220638</v>
       </c>
       <c r="Q12">
-        <v>8.1640007173089296e-05</v>
+        <v>8.1640007173097549e-05</v>
       </c>
       <c r="R12">
-        <v>8.659241108307745e-05</v>
+        <v>8.659241108307806e-05</v>
       </c>
       <c r="S12">
-        <v>7.2625568124505723e-05</v>
+        <v>7.2625568124509883e-05</v>
       </c>
       <c r="T12">
-        <v>-0.00021872529679949171</v>
+        <v>-0.00021872529679949068</v>
       </c>
       <c r="U12">
-        <v>-0.00055939481065233362</v>
+        <v>-0.00055939481065233254</v>
       </c>
       <c r="V12">
-        <v>-0.00045654085313738161</v>
+        <v>-0.00045654085313738102</v>
       </c>
       <c r="W12">
-        <v>-0.00033281241228975955</v>
+        <v>-0.00033281241228975544</v>
       </c>
       <c r="X12">
-        <v>1.3508018690001934e-05</v>
+        <v>1.3508018690001983e-05</v>
       </c>
       <c r="Y12">
-        <v>3.3516023083526297e-06</v>
+        <v>3.3516023083527584e-06</v>
       </c>
       <c r="Z12">
-        <v>5.3753552470530829e-06</v>
+        <v>5.3753552470534624e-06</v>
       </c>
       <c r="AA12">
-        <v>-4.7040608925575636e-05</v>
+        <v>-4.7040608925574498e-05</v>
       </c>
       <c r="AB12">
-        <v>2.4527032191439961e-05</v>
+        <v>2.4527032191441208e-05</v>
       </c>
       <c r="AC12">
-        <v>-2.7358458102672961e-05</v>
+        <v>-2.7358458102671876e-05</v>
       </c>
       <c r="AD12">
-        <v>-7.4634030212139476e-05</v>
+        <v>-7.4634030212138337e-05</v>
       </c>
       <c r="AE12">
-        <v>-0.00015014202061696563</v>
+        <v>-0.00015014202061696452</v>
       </c>
       <c r="AF12">
-        <v>1.4859872921433072e-05</v>
+        <v>1.4859872921433194e-05</v>
       </c>
       <c r="AG12">
-        <v>-0.00030833222323535297</v>
+        <v>-0.0003083322232353533</v>
       </c>
       <c r="AH12">
-        <v>-4.2100416755658121e-05</v>
+        <v>-4.2100416755658744e-05</v>
       </c>
       <c r="AI12">
-        <v>-0.00015965131485163437</v>
+        <v>-0.00015965131485163692</v>
       </c>
     </row>
     <row r="13">
@@ -1682,103 +1682,103 @@
         <v>-0.080449105696533005</v>
       </c>
       <c r="C13">
-        <v>-3.361322185230121e-05</v>
+        <v>-3.3613221852301075e-05</v>
       </c>
       <c r="D13">
-        <v>3.415495757352156e-05</v>
+        <v>3.4154957573525626e-05</v>
       </c>
       <c r="E13">
-        <v>0.00013157663846053444</v>
+        <v>0.00013157663846053829</v>
       </c>
       <c r="F13">
-        <v>0.00012419560983464682</v>
+        <v>0.00012419560983465032</v>
       </c>
       <c r="G13">
-        <v>0.00027573964584833103</v>
+        <v>0.00027573964584833504</v>
       </c>
       <c r="H13">
-        <v>0.00016660764644241399</v>
+        <v>0.000166607646442418</v>
       </c>
       <c r="I13">
-        <v>0.00012382017728425647</v>
+        <v>0.00012382017728426056</v>
       </c>
       <c r="J13">
-        <v>4.7138664410984951e-05</v>
+        <v>4.7138664410989125e-05</v>
       </c>
       <c r="K13">
-        <v>7.6384446146617079e-05</v>
+        <v>7.6384446146619085e-05</v>
       </c>
       <c r="L13">
-        <v>0.00015482852411966399</v>
+        <v>0.00015482852411966605</v>
       </c>
       <c r="M13">
-        <v>0.00053972298045773537</v>
+        <v>0.00053972298045773558</v>
       </c>
       <c r="N13">
-        <v>0.00085714983948552209</v>
+        <v>0.00085714983948552241</v>
       </c>
       <c r="O13">
-        <v>0.00042212863405599837</v>
+        <v>0.00042212863405599924</v>
       </c>
       <c r="P13">
-        <v>0.00023414186729393713</v>
+        <v>0.0002341418672939381</v>
       </c>
       <c r="Q13">
-        <v>3.9947432961129814e-05</v>
+        <v>3.994743296114258e-05</v>
       </c>
       <c r="R13">
-        <v>-1.9673944736484721e-05</v>
+        <v>-1.967394473648407e-05</v>
       </c>
       <c r="S13">
-        <v>4.0788415143500092e-05</v>
+        <v>4.0788415143506556e-05</v>
       </c>
       <c r="T13">
-        <v>-2.4394818592365961e-05</v>
+        <v>-2.4394818592364416e-05</v>
       </c>
       <c r="U13">
-        <v>0.00014571898141819267</v>
+        <v>0.00014571898141819425</v>
       </c>
       <c r="V13">
-        <v>0.00024170927075665868</v>
+        <v>0.00024170927075665923</v>
       </c>
       <c r="W13">
-        <v>0.00043867877034087726</v>
+        <v>0.00043867877034088393</v>
       </c>
       <c r="X13">
-        <v>-8.9450452029444165e-06</v>
+        <v>-8.94504520294432e-06</v>
       </c>
       <c r="Y13">
-        <v>2.5349901746122248e-06</v>
+        <v>2.5349901746123875e-06</v>
       </c>
       <c r="Z13">
-        <v>3.176840152891992e-05</v>
+        <v>3.176840152892095e-05</v>
       </c>
       <c r="AA13">
-        <v>1.4427976619051325e-05</v>
+        <v>1.4427976619053114e-05</v>
       </c>
       <c r="AB13">
-        <v>4.8685890455250794e-06</v>
+        <v>4.8685890455269767e-06</v>
       </c>
       <c r="AC13">
-        <v>1.6549667470975769e-05</v>
+        <v>1.6549667470977449e-05</v>
       </c>
       <c r="AD13">
-        <v>1.0462524298719981e-05</v>
+        <v>1.0462524298721825e-05</v>
       </c>
       <c r="AE13">
-        <v>-2.3821879086441338e-05</v>
+        <v>-2.3821879086439562e-05</v>
       </c>
       <c r="AF13">
-        <v>5.616813985184142e-06</v>
+        <v>5.6168139851843385e-06</v>
       </c>
       <c r="AG13">
-        <v>-9.8069252881486258e-05</v>
+        <v>-9.8069252881486746e-05</v>
       </c>
       <c r="AH13">
-        <v>-3.6525377833204319e-05</v>
+        <v>-3.6525377833205295e-05</v>
       </c>
       <c r="AI13">
-        <v>-0.00082028153442178608</v>
+        <v>-0.00082028153442179996</v>
       </c>
     </row>
     <row r="14">
@@ -1789,103 +1789,103 @@
         <v>-0.028886584725227402</v>
       </c>
       <c r="C14">
-        <v>-4.8211227158035332e-05</v>
+        <v>-4.8211227158035095e-05</v>
       </c>
       <c r="D14">
-        <v>0.00017304750110305124</v>
+        <v>0.00017304750110305598</v>
       </c>
       <c r="E14">
-        <v>9.2101658019669966e-05</v>
+        <v>9.2101658019674547e-05</v>
       </c>
       <c r="F14">
-        <v>0.00011222399271491033</v>
+        <v>0.00011222399271491425</v>
       </c>
       <c r="G14">
-        <v>0.00028512265825970701</v>
+        <v>0.00028512265825971189</v>
       </c>
       <c r="H14">
-        <v>0.00010625670043667456</v>
+        <v>0.00010625670043667934</v>
       </c>
       <c r="I14">
-        <v>0.00012507577302552488</v>
+        <v>0.00012507577302552959</v>
       </c>
       <c r="J14">
-        <v>5.7869774781328644e-05</v>
+        <v>5.7869774781333665e-05</v>
       </c>
       <c r="K14">
-        <v>0.00017008274704562862</v>
+        <v>0.00017008274704563168</v>
       </c>
       <c r="L14">
-        <v>8.2149596255874971e-05</v>
+        <v>8.21495962558784e-05</v>
       </c>
       <c r="M14">
-        <v>0.00041312332789258054</v>
+        <v>0.00041312332789258098</v>
       </c>
       <c r="N14">
-        <v>0.00042212863405599837</v>
+        <v>0.00042212863405599924</v>
       </c>
       <c r="O14">
-        <v>0.00078169302244828506</v>
+        <v>0.00078169302244828637</v>
       </c>
       <c r="P14">
-        <v>3.2044993063426854e-05</v>
+        <v>3.2044993063428642e-05</v>
       </c>
       <c r="Q14">
-        <v>0.00012321554516546714</v>
+        <v>0.00012321554516548573</v>
       </c>
       <c r="R14">
-        <v>0.00021635474993374584</v>
+        <v>0.0002163547499337467</v>
       </c>
       <c r="S14">
-        <v>0.00031014633916723653</v>
+        <v>0.00031014633916724515</v>
       </c>
       <c r="T14">
-        <v>2.4679496354268625e-05</v>
+        <v>2.4679496354270889e-05</v>
       </c>
       <c r="U14">
-        <v>0.00018782629432656083</v>
+        <v>0.00018782629432656311</v>
       </c>
       <c r="V14">
-        <v>0.00029188576739535427</v>
+        <v>0.00029188576739535514</v>
       </c>
       <c r="W14">
-        <v>0.00050573604431693045</v>
+        <v>0.00050573604431693945</v>
       </c>
       <c r="X14">
-        <v>-1.0285577321125531e-05</v>
+        <v>-1.0285577321125419e-05</v>
       </c>
       <c r="Y14">
-        <v>1.0451598659236535e-05</v>
+        <v>1.0451598659236752e-05</v>
       </c>
       <c r="Z14">
-        <v>7.8399976348818355e-05</v>
+        <v>7.8399976348820632e-05</v>
       </c>
       <c r="AA14">
-        <v>8.0597869771119454e-05</v>
+        <v>8.0597869771121947e-05</v>
       </c>
       <c r="AB14">
-        <v>0.00010319506017073969</v>
+        <v>0.0001031950601707424</v>
       </c>
       <c r="AC14">
-        <v>1.7201678399737103e-05</v>
+        <v>1.7201678399739488e-05</v>
       </c>
       <c r="AD14">
-        <v>6.7471731706362253e-05</v>
+        <v>6.7471731706364855e-05</v>
       </c>
       <c r="AE14">
-        <v>1.4188838300472849e-05</v>
+        <v>1.4188838300475437e-05</v>
       </c>
       <c r="AF14">
-        <v>9.5812939870465262e-06</v>
+        <v>9.5812939870467515e-06</v>
       </c>
       <c r="AG14">
-        <v>-8.9809283282528017e-05</v>
+        <v>-8.9809283282528667e-05</v>
       </c>
       <c r="AH14">
-        <v>-7.0967816654567714e-05</v>
+        <v>-7.0967816654568961e-05</v>
       </c>
       <c r="AI14">
-        <v>-0.0011770786664807337</v>
+        <v>-0.0011770786664807545</v>
       </c>
     </row>
     <row r="15">
@@ -1896,103 +1896,103 @@
         <v>-0.11485641027320445</v>
       </c>
       <c r="C15">
-        <v>0.00015964187899656531</v>
+        <v>0.00015964187899656515</v>
       </c>
       <c r="D15">
-        <v>0.00024098226622748672</v>
+        <v>0.00024098226622749843</v>
       </c>
       <c r="E15">
-        <v>0.00025685583857601392</v>
+        <v>0.00025685583857602715</v>
       </c>
       <c r="F15">
-        <v>2.6036874602798177e-05</v>
+        <v>2.6036874602808802e-05</v>
       </c>
       <c r="G15">
-        <v>-5.3984468993179338e-05</v>
+        <v>-5.398446899316687e-05</v>
       </c>
       <c r="H15">
-        <v>2.4952126135451978e-05</v>
+        <v>2.4952126135464555e-05</v>
       </c>
       <c r="I15">
-        <v>0.00012121079140615248</v>
+        <v>0.0001212107914061668</v>
       </c>
       <c r="J15">
-        <v>0.00020041402999989547</v>
+        <v>0.00020041402999990848</v>
       </c>
       <c r="K15">
-        <v>0.00034860485841903114</v>
+        <v>0.00034860485841902724</v>
       </c>
       <c r="L15">
-        <v>0.00030185717532583457</v>
+        <v>0.0003018571753258311</v>
       </c>
       <c r="M15">
-        <v>0.00015702916722206293</v>
+        <v>0.0001570291672220638</v>
       </c>
       <c r="N15">
-        <v>0.00023414186729393713</v>
+        <v>0.0002341418672939381</v>
       </c>
       <c r="O15">
-        <v>3.2044993063426854e-05</v>
+        <v>3.2044993063428642e-05</v>
       </c>
       <c r="P15">
-        <v>0.009426341629225508</v>
+        <v>0.0094263416292255289</v>
       </c>
       <c r="Q15">
-        <v>0.0068137726272689426</v>
+        <v>0.0068137726272691195</v>
       </c>
       <c r="R15">
-        <v>0.0067577625961099744</v>
+        <v>0.0067577625961099935</v>
       </c>
       <c r="S15">
-        <v>0.0067408136400644997</v>
+        <v>0.0067408136400645769</v>
       </c>
       <c r="T15">
-        <v>-0.00011777917643881022</v>
+        <v>-0.00011777917643879086</v>
       </c>
       <c r="U15">
-        <v>0.00038688893363880315</v>
+        <v>0.00038688893363882744</v>
       </c>
       <c r="V15">
-        <v>0.00055400873771308933</v>
+        <v>0.00055400873771309887</v>
       </c>
       <c r="W15">
-        <v>0.00046371833807942004</v>
+        <v>0.00046371833807950721</v>
       </c>
       <c r="X15">
-        <v>-2.9039404761879379e-05</v>
+        <v>-2.9039404761877563e-05</v>
       </c>
       <c r="Y15">
-        <v>-0.00011733515753141401</v>
+        <v>-0.00011733515753141271</v>
       </c>
       <c r="Z15">
-        <v>0.00011420262847560651</v>
+        <v>0.00011420262847562559</v>
       </c>
       <c r="AA15">
-        <v>0.00016597672273013959</v>
+        <v>0.00016597672273016388</v>
       </c>
       <c r="AB15">
-        <v>0.00016024217855355183</v>
+        <v>0.00016024217855357525</v>
       </c>
       <c r="AC15">
-        <v>0.00011097867444821892</v>
+        <v>0.00011097867444824234</v>
       </c>
       <c r="AD15">
-        <v>0.00021100525375209183</v>
+        <v>0.00021100525375211568</v>
       </c>
       <c r="AE15">
-        <v>0.00039010103324478698</v>
+        <v>0.0003901010332448111</v>
       </c>
       <c r="AF15">
-        <v>5.7254640730687004e-06</v>
+        <v>5.7254640730701912e-06</v>
       </c>
       <c r="AG15">
-        <v>1.2088203191898579e-05</v>
+        <v>1.2088203191894242e-05</v>
       </c>
       <c r="AH15">
-        <v>-4.9005125978268584e-05</v>
+        <v>-4.9005125978278993e-05</v>
       </c>
       <c r="AI15">
-        <v>-0.007646923409067169</v>
+        <v>-0.0076469234090673632</v>
       </c>
     </row>
     <row r="16">
@@ -2003,103 +2003,103 @@
         <v>-0.099438391666721845</v>
       </c>
       <c r="C16">
-        <v>-2.9367506558327801e-05</v>
+        <v>-2.9367506558323816e-05</v>
       </c>
       <c r="D16">
-        <v>0.0002049088881617481</v>
+        <v>0.00020490888816182367</v>
       </c>
       <c r="E16">
-        <v>7.6911989027215739e-05</v>
+        <v>7.6911989027287839e-05</v>
       </c>
       <c r="F16">
-        <v>3.0606587825475549e-05</v>
+        <v>3.0606587825537783e-05</v>
       </c>
       <c r="G16">
-        <v>6.9483088424569491e-05</v>
+        <v>6.9483088424646795e-05</v>
       </c>
       <c r="H16">
-        <v>1.6276286501519304e-06</v>
+        <v>1.6276286502292341e-06</v>
       </c>
       <c r="I16">
-        <v>-5.1614434372137608e-06</v>
+        <v>-5.1614434371389508e-06</v>
       </c>
       <c r="J16">
-        <v>6.3657106405295766e-05</v>
+        <v>6.3657106405375671e-05</v>
       </c>
       <c r="K16">
-        <v>9.7647707584599822e-05</v>
+        <v>9.7647707584657718e-05</v>
       </c>
       <c r="L16">
-        <v>0.00017023512700279297</v>
+        <v>0.00017023512700285585</v>
       </c>
       <c r="M16">
-        <v>8.1640007173089296e-05</v>
+        <v>8.1640007173097549e-05</v>
       </c>
       <c r="N16">
-        <v>3.9947432961129814e-05</v>
+        <v>3.994743296114258e-05</v>
       </c>
       <c r="O16">
-        <v>0.00012321554516546714</v>
+        <v>0.00012321554516548573</v>
       </c>
       <c r="P16">
-        <v>0.0068137726272689426</v>
+        <v>0.0068137726272691195</v>
       </c>
       <c r="Q16">
-        <v>0.0073181904543887701</v>
+        <v>0.0073181904543889479</v>
       </c>
       <c r="R16">
-        <v>0.0069913547073796947</v>
+        <v>0.0069913547073797138</v>
       </c>
       <c r="S16">
-        <v>0.0070188449262131893</v>
+        <v>0.0070188449262132691</v>
       </c>
       <c r="T16">
-        <v>-0.00019017400239543304</v>
+        <v>-0.00019017400239541336</v>
       </c>
       <c r="U16">
-        <v>-2.4202738745484134e-07</v>
+        <v>-2.4202738742925417e-07</v>
       </c>
       <c r="V16">
-        <v>-2.6207257167606968e-05</v>
+        <v>-2.6207257167597427e-05</v>
       </c>
       <c r="W16">
-        <v>1.6812808064698651e-05</v>
+        <v>1.6812808064787556e-05</v>
       </c>
       <c r="X16">
-        <v>-1.5446679067544567e-05</v>
+        <v>-1.5446679067542744e-05</v>
       </c>
       <c r="Y16">
-        <v>-2.0611295039211402e-05</v>
+        <v>-2.0611295039210317e-05</v>
       </c>
       <c r="Z16">
-        <v>0.00039977578339571874</v>
+        <v>0.00039977578339573782</v>
       </c>
       <c r="AA16">
-        <v>0.00039619269341183844</v>
+        <v>0.00039619269341186359</v>
       </c>
       <c r="AB16">
-        <v>0.00039999263156205271</v>
+        <v>0.00039999263156207613</v>
       </c>
       <c r="AC16">
-        <v>0.00032778991844844511</v>
+        <v>0.00032778991844847026</v>
       </c>
       <c r="AD16">
-        <v>0.00040526383753041113</v>
+        <v>0.00040526383753043585</v>
       </c>
       <c r="AE16">
-        <v>0.00037619705005900988</v>
+        <v>0.00037619705005903449</v>
       </c>
       <c r="AF16">
-        <v>-2.857098044788532e-07</v>
+        <v>-2.8570980447728111e-07</v>
       </c>
       <c r="AG16">
-        <v>4.3779515320177889e-05</v>
+        <v>4.3779515320172685e-05</v>
       </c>
       <c r="AH16">
-        <v>2.3744716712641081e-05</v>
+        <v>2.3744716712629371e-05</v>
       </c>
       <c r="AI16">
-        <v>-0.0074153616530795467</v>
+        <v>-0.0074153616530797445</v>
       </c>
     </row>
     <row r="17">
@@ -2110,103 +2110,103 @@
         <v>-0.083042836433586745</v>
       </c>
       <c r="C17">
-        <v>-5.3783345333062307e-05</v>
+        <v>-5.3783345333062239e-05</v>
       </c>
       <c r="D17">
-        <v>0.00013961429365073885</v>
+        <v>0.00013961429365074959</v>
       </c>
       <c r="E17">
-        <v>5.8410909162380639e-05</v>
+        <v>5.8410909162392619e-05</v>
       </c>
       <c r="F17">
-        <v>-5.2813169843047366e-06</v>
+        <v>-5.2813169842945993e-06</v>
       </c>
       <c r="G17">
-        <v>-4.2746946247138073e-05</v>
+        <v>-4.2746946247127664e-05</v>
       </c>
       <c r="H17">
-        <v>-3.8034219591053182e-05</v>
+        <v>-3.8034219591042448e-05</v>
       </c>
       <c r="I17">
-        <v>-2.4039909615055483e-05</v>
+        <v>-2.4039909615042798e-05</v>
       </c>
       <c r="J17">
-        <v>-1.090278735531964e-05</v>
+        <v>-1.0902787355308852e-05</v>
       </c>
       <c r="K17">
-        <v>6.1269581888890234e-05</v>
+        <v>6.1269581888881127e-05</v>
       </c>
       <c r="L17">
-        <v>0.00028235702247508392</v>
+        <v>0.00028235702247507617</v>
       </c>
       <c r="M17">
-        <v>8.659241108307745e-05</v>
+        <v>8.659241108307806e-05</v>
       </c>
       <c r="N17">
-        <v>-1.9673944736484721e-05</v>
+        <v>-1.967394473648407e-05</v>
       </c>
       <c r="O17">
-        <v>0.00021635474993374584</v>
+        <v>0.0002163547499337467</v>
       </c>
       <c r="P17">
-        <v>0.0067577625961099744</v>
+        <v>0.0067577625961099935</v>
       </c>
       <c r="Q17">
-        <v>0.0069913547073796947</v>
+        <v>0.0069913547073797138</v>
       </c>
       <c r="R17">
-        <v>0.0072937728143594328</v>
+        <v>0.0072937728143594536</v>
       </c>
       <c r="S17">
-        <v>0.0071502877158113286</v>
+        <v>0.0071502877158114101</v>
       </c>
       <c r="T17">
-        <v>-0.00015611331133342095</v>
+        <v>-0.00015611331133340083</v>
       </c>
       <c r="U17">
-        <v>6.7493561899841393e-05</v>
+        <v>6.7493561899867414e-05</v>
       </c>
       <c r="V17">
-        <v>-1.1335263924642028e-05</v>
+        <v>-1.1335263924633354e-05</v>
       </c>
       <c r="W17">
-        <v>5.8702360032054837e-05</v>
+        <v>5.870236003214591e-05</v>
       </c>
       <c r="X17">
-        <v>-1.4914311524460619e-05</v>
+        <v>-1.4914311524458736e-05</v>
       </c>
       <c r="Y17">
-        <v>-2.791809035572186e-05</v>
+        <v>-2.7918090355720342e-05</v>
       </c>
       <c r="Z17">
-        <v>0.00042834881384021077</v>
+        <v>0.00042834881384023072</v>
       </c>
       <c r="AA17">
-        <v>0.00038964786848787094</v>
+        <v>0.00038964786848789609</v>
       </c>
       <c r="AB17">
-        <v>0.00039390262233660652</v>
+        <v>0.00039390262233663341</v>
       </c>
       <c r="AC17">
-        <v>0.00031836766960773727</v>
+        <v>0.00031836766960776329</v>
       </c>
       <c r="AD17">
-        <v>0.00039693324408751564</v>
+        <v>0.00039693324408754101</v>
       </c>
       <c r="AE17">
-        <v>0.00041366543595435884</v>
+        <v>0.0004136654359543841</v>
       </c>
       <c r="AF17">
-        <v>3.6208117601797146e-06</v>
+        <v>3.6208117601813138e-06</v>
       </c>
       <c r="AG17">
-        <v>4.5946337358625244e-05</v>
+        <v>4.594633735862351e-05</v>
       </c>
       <c r="AH17">
-        <v>2.3263439245871376e-05</v>
+        <v>2.3263439245859233e-05</v>
       </c>
       <c r="AI17">
-        <v>-0.0076541926183776501</v>
+        <v>-0.007654192618377853</v>
       </c>
     </row>
     <row r="18">
@@ -2217,103 +2217,103 @@
         <v>-0.13606630682082815</v>
       </c>
       <c r="C18">
-        <v>-0.00011313088460214999</v>
+        <v>-0.00011313088460214739</v>
       </c>
       <c r="D18">
-        <v>0.00035347518107974138</v>
+        <v>0.00035347518107978909</v>
       </c>
       <c r="E18">
-        <v>0.00011723908016807649</v>
+        <v>0.00011723908016812289</v>
       </c>
       <c r="F18">
-        <v>2.2049062175248733e-05</v>
+        <v>2.2049062175289933e-05</v>
       </c>
       <c r="G18">
-        <v>0.0001053769319945768</v>
+        <v>0.00010537693199462651</v>
       </c>
       <c r="H18">
-        <v>3.104761253483148e-05</v>
+        <v>3.1047612534881083e-05</v>
       </c>
       <c r="I18">
-        <v>-3.7246413668003554e-05</v>
+        <v>-3.7246413667954385e-05</v>
       </c>
       <c r="J18">
-        <v>-6.0940037529625996e-05</v>
+        <v>-6.0940037529575038e-05</v>
       </c>
       <c r="K18">
-        <v>0.00016744100269595696</v>
+        <v>0.00016744100269598612</v>
       </c>
       <c r="L18">
-        <v>0.00047732123564773365</v>
+        <v>0.00047732123564776666</v>
       </c>
       <c r="M18">
-        <v>7.2625568124505723e-05</v>
+        <v>7.2625568124509883e-05</v>
       </c>
       <c r="N18">
-        <v>4.0788415143500092e-05</v>
+        <v>4.0788415143506556e-05</v>
       </c>
       <c r="O18">
-        <v>0.00031014633916723653</v>
+        <v>0.00031014633916724515</v>
       </c>
       <c r="P18">
-        <v>0.0067408136400644997</v>
+        <v>0.0067408136400645769</v>
       </c>
       <c r="Q18">
-        <v>0.0070188449262131893</v>
+        <v>0.0070188449262132691</v>
       </c>
       <c r="R18">
-        <v>0.0071502877158113286</v>
+        <v>0.0071502877158114101</v>
       </c>
       <c r="S18">
-        <v>0.0077670221172790868</v>
+        <v>0.0077670221172791675</v>
       </c>
       <c r="T18">
-        <v>-0.00021038681129576778</v>
+        <v>-0.00021038681129574739</v>
       </c>
       <c r="U18">
-        <v>0.00017642226562673922</v>
+        <v>0.0001764222656267648</v>
       </c>
       <c r="V18">
-        <v>0.00013642230501540332</v>
+        <v>0.00013642230501541286</v>
       </c>
       <c r="W18">
-        <v>0.00025997622043381517</v>
+        <v>0.00025997622043390668</v>
       </c>
       <c r="X18">
-        <v>-1.2964826891340041e-05</v>
+        <v>-1.2964826891338069e-05</v>
       </c>
       <c r="Y18">
-        <v>1.2286128425974523e-06</v>
+        <v>1.2286128425987534e-06</v>
       </c>
       <c r="Z18">
-        <v>0.00050815612522661473</v>
+        <v>0.00050815612522663554</v>
       </c>
       <c r="AA18">
-        <v>0.00043808842808900489</v>
+        <v>0.00043808842808903178</v>
       </c>
       <c r="AB18">
-        <v>0.00045272675287770861</v>
+        <v>0.00045272675287773376</v>
       </c>
       <c r="AC18">
-        <v>0.00038264462745451165</v>
+        <v>0.00038264462745453767</v>
       </c>
       <c r="AD18">
-        <v>0.00049446962267037727</v>
+        <v>0.00049446962267040286</v>
       </c>
       <c r="AE18">
-        <v>0.00032125317013082764</v>
+        <v>0.0003212531701308536</v>
       </c>
       <c r="AF18">
-        <v>6.4351374456237591e-06</v>
+        <v>6.4351374456253854e-06</v>
       </c>
       <c r="AG18">
-        <v>4.3708144531398943e-05</v>
+        <v>4.3708144531393739e-05</v>
       </c>
       <c r="AH18">
-        <v>7.8244783439976838e-05</v>
+        <v>7.8244783439965129e-05</v>
       </c>
       <c r="AI18">
-        <v>-0.0080109756220309476</v>
+        <v>-0.0080109756220311541</v>
       </c>
     </row>
     <row r="19">
@@ -2324,103 +2324,103 @@
         <v>0.19475512354932451</v>
       </c>
       <c r="C19">
-        <v>3.3585706080962048e-07</v>
+        <v>3.3585706081016427e-07</v>
       </c>
       <c r="D19">
-        <v>-1.9174180004394734e-05</v>
+        <v>-1.9174180004385085e-05</v>
       </c>
       <c r="E19">
-        <v>7.8675240484065185e-05</v>
+        <v>7.8675240484074415e-05</v>
       </c>
       <c r="F19">
-        <v>3.3185996693455404e-05</v>
+        <v>3.3185996693463644e-05</v>
       </c>
       <c r="G19">
-        <v>0.00013915368209563547</v>
+        <v>0.00013915368209564504</v>
       </c>
       <c r="H19">
-        <v>0.00013130352291067067</v>
+        <v>0.0001313035229106804</v>
       </c>
       <c r="I19">
-        <v>9.1079901964059986e-05</v>
+        <v>9.1079901964069663e-05</v>
       </c>
       <c r="J19">
-        <v>6.999213058396495e-05</v>
+        <v>6.999213058397506e-05</v>
       </c>
       <c r="K19">
-        <v>0.00063230654186255972</v>
+        <v>0.00063230654186256547</v>
       </c>
       <c r="L19">
-        <v>0.00047289903568890847</v>
+        <v>0.00047289903568891465</v>
       </c>
       <c r="M19">
-        <v>-0.00021872529679949171</v>
+        <v>-0.00021872529679949068</v>
       </c>
       <c r="N19">
-        <v>-2.4394818592365961e-05</v>
+        <v>-2.4394818592364416e-05</v>
       </c>
       <c r="O19">
-        <v>2.4679496354268625e-05</v>
+        <v>2.4679496354270889e-05</v>
       </c>
       <c r="P19">
-        <v>-0.00011777917643881022</v>
+        <v>-0.00011777917643879086</v>
       </c>
       <c r="Q19">
-        <v>-0.00019017400239543304</v>
+        <v>-0.00019017400239541336</v>
       </c>
       <c r="R19">
-        <v>-0.00015611331133342095</v>
+        <v>-0.00015611331133340083</v>
       </c>
       <c r="S19">
-        <v>-0.00021038681129576778</v>
+        <v>-0.00021038681129574739</v>
       </c>
       <c r="T19">
-        <v>0.0010828886397138773</v>
+        <v>0.0010828886397138793</v>
       </c>
       <c r="U19">
-        <v>0.00095411326157021029</v>
+        <v>0.00095411326157021181</v>
       </c>
       <c r="V19">
-        <v>0.0009969685137757589</v>
+        <v>0.00099696851377575717</v>
       </c>
       <c r="W19">
-        <v>0.0010934520904993467</v>
+        <v>0.0010934520904993556</v>
       </c>
       <c r="X19">
-        <v>-9.7975365989235442e-05</v>
+        <v>-9.7975365989235293e-05</v>
       </c>
       <c r="Y19">
-        <v>6.9257082614885125e-06</v>
+        <v>6.9257082614884854e-06</v>
       </c>
       <c r="Z19">
-        <v>5.8451861510897723e-05</v>
+        <v>5.8451861510900867e-05</v>
       </c>
       <c r="AA19">
-        <v>5.2488330671794366e-05</v>
+        <v>5.2488330671796534e-05</v>
       </c>
       <c r="AB19">
-        <v>2.1032802931347859e-05</v>
+        <v>2.1032802931350678e-05</v>
       </c>
       <c r="AC19">
-        <v>3.3098360869946624e-05</v>
+        <v>3.3098360869949768e-05</v>
       </c>
       <c r="AD19">
-        <v>2.1061296049569659e-05</v>
+        <v>2.1061296049572695e-05</v>
       </c>
       <c r="AE19">
-        <v>0.00011004290423317754</v>
+        <v>0.0001100429042331806</v>
       </c>
       <c r="AF19">
-        <v>-3.1269371662587711e-06</v>
+        <v>-3.1269371662585882e-06</v>
       </c>
       <c r="AG19">
-        <v>-0.00013761921847101522</v>
+        <v>-0.00013761921847101533</v>
       </c>
       <c r="AH19">
-        <v>-5.2297174353573331e-05</v>
+        <v>-5.2297174353574253e-05</v>
       </c>
       <c r="AI19">
-        <v>-0.00073223072105569578</v>
+        <v>-0.00073223072105571747</v>
       </c>
     </row>
     <row r="20">
@@ -2431,103 +2431,103 @@
         <v>0.079518653485038435</v>
       </c>
       <c r="C20">
-        <v>3.897800193710734e-05</v>
+        <v>3.8978001937107882e-05</v>
       </c>
       <c r="D20">
-        <v>-3.2793598063826689e-05</v>
+        <v>-3.2793598063814329e-05</v>
       </c>
       <c r="E20">
-        <v>9.0123156531705896e-05</v>
+        <v>9.0123156531717605e-05</v>
       </c>
       <c r="F20">
-        <v>4.759201680919038e-05</v>
+        <v>4.7592016809201655e-05</v>
       </c>
       <c r="G20">
-        <v>0.00021119581025745267</v>
+        <v>0.00021119581025746525</v>
       </c>
       <c r="H20">
-        <v>0.00014664378215088975</v>
+        <v>0.00014664378215090254</v>
       </c>
       <c r="I20">
-        <v>0.00022175602752184205</v>
+        <v>0.00022175602752185462</v>
       </c>
       <c r="J20">
-        <v>7.925130788153387e-05</v>
+        <v>7.9251307881547098e-05</v>
       </c>
       <c r="K20">
-        <v>0.0032118980277105877</v>
+        <v>0.0032118980277105924</v>
       </c>
       <c r="L20">
-        <v>0.0026454966364136681</v>
+        <v>0.002645496636413675</v>
       </c>
       <c r="M20">
-        <v>-0.00055939481065233362</v>
+        <v>-0.00055939481065233254</v>
       </c>
       <c r="N20">
-        <v>0.00014571898141819267</v>
+        <v>0.00014571898141819425</v>
       </c>
       <c r="O20">
-        <v>0.00018782629432656083</v>
+        <v>0.00018782629432656311</v>
       </c>
       <c r="P20">
-        <v>0.00038688893363880315</v>
+        <v>0.00038688893363882744</v>
       </c>
       <c r="Q20">
-        <v>-2.4202738745484134e-07</v>
+        <v>-2.4202738742925417e-07</v>
       </c>
       <c r="R20">
-        <v>6.7493561899841393e-05</v>
+        <v>6.7493561899867414e-05</v>
       </c>
       <c r="S20">
-        <v>0.00017642226562673922</v>
+        <v>0.0001764222656267648</v>
       </c>
       <c r="T20">
-        <v>0.00095411326157021029</v>
+        <v>0.00095411326157021181</v>
       </c>
       <c r="U20">
-        <v>0.0035249377378211919</v>
+        <v>0.0035249377378211962</v>
       </c>
       <c r="V20">
-        <v>0.0033561089904270564</v>
+        <v>0.0033561089904270485</v>
       </c>
       <c r="W20">
-        <v>0.0036402634101280343</v>
+        <v>0.0036402634101280655</v>
       </c>
       <c r="X20">
-        <v>-0.0002085859767480611</v>
+        <v>-0.00020858597674806067</v>
       </c>
       <c r="Y20">
-        <v>2.5943844974372215e-05</v>
+        <v>2.5943844974371945e-05</v>
       </c>
       <c r="Z20">
-        <v>2.768071263798029e-05</v>
+        <v>2.7680712637990265e-05</v>
       </c>
       <c r="AA20">
-        <v>-2.6550282929700686e-05</v>
+        <v>-2.6550282929693313e-05</v>
       </c>
       <c r="AB20">
-        <v>-3.9589942205490092e-05</v>
+        <v>-3.9589942205481418e-05</v>
       </c>
       <c r="AC20">
-        <v>4.6144882518512828e-06</v>
+        <v>4.6144882518608238e-06</v>
       </c>
       <c r="AD20">
-        <v>0.0001070700554739681</v>
+        <v>0.00010707005547397802</v>
       </c>
       <c r="AE20">
-        <v>7.5686072508696781e-05</v>
+        <v>7.5686072508706647e-05</v>
       </c>
       <c r="AF20">
-        <v>4.5265732748416096e-06</v>
+        <v>4.5265732748422195e-06</v>
       </c>
       <c r="AG20">
-        <v>-2.3809894667179386e-05</v>
+        <v>-2.3809894667178953e-05</v>
       </c>
       <c r="AH20">
-        <v>-6.8373762652340847e-05</v>
+        <v>-6.83737626523441e-05</v>
       </c>
       <c r="AI20">
-        <v>-0.0036109294228694145</v>
+        <v>-0.0036109294228694813</v>
       </c>
     </row>
     <row r="21">
@@ -2538,103 +2538,103 @@
         <v>0.20038459830311944</v>
       </c>
       <c r="C21">
-        <v>-1.429762836629479e-06</v>
+        <v>-1.4297628366294248e-06</v>
       </c>
       <c r="D21">
-        <v>0.00034904637853419248</v>
+        <v>0.00034904637853420397</v>
       </c>
       <c r="E21">
-        <v>0.00023564401616686876</v>
+        <v>0.00023564401616688263</v>
       </c>
       <c r="F21">
-        <v>6.0529809378991268e-05</v>
+        <v>6.0529809379003194e-05</v>
       </c>
       <c r="G21">
-        <v>0.00054653907747107444</v>
+        <v>0.00054653907747108572</v>
       </c>
       <c r="H21">
-        <v>0.00051188472275484316</v>
+        <v>0.00051188472275485487</v>
       </c>
       <c r="I21">
-        <v>0.0003513849927976253</v>
+        <v>0.00035138499279763918</v>
       </c>
       <c r="J21">
-        <v>0.0004394237064820612</v>
+        <v>0.00043942370648207335</v>
       </c>
       <c r="K21">
-        <v>0.0036789130441664463</v>
+        <v>0.0036789130441664351</v>
       </c>
       <c r="L21">
-        <v>0.0030849932598246382</v>
+        <v>0.0030849932598246296</v>
       </c>
       <c r="M21">
-        <v>-0.00045654085313738161</v>
+        <v>-0.00045654085313738102</v>
       </c>
       <c r="N21">
-        <v>0.00024170927075665868</v>
+        <v>0.00024170927075665923</v>
       </c>
       <c r="O21">
-        <v>0.00029188576739535427</v>
+        <v>0.00029188576739535514</v>
       </c>
       <c r="P21">
-        <v>0.00055400873771308933</v>
+        <v>0.00055400873771309887</v>
       </c>
       <c r="Q21">
-        <v>-2.6207257167606968e-05</v>
+        <v>-2.6207257167597427e-05</v>
       </c>
       <c r="R21">
-        <v>-1.1335263924642028e-05</v>
+        <v>-1.1335263924633354e-05</v>
       </c>
       <c r="S21">
-        <v>0.00013642230501540332</v>
+        <v>0.00013642230501541286</v>
       </c>
       <c r="T21">
-        <v>0.0009969685137757589</v>
+        <v>0.00099696851377575717</v>
       </c>
       <c r="U21">
-        <v>0.0033561089904270564</v>
+        <v>0.0033561089904270485</v>
       </c>
       <c r="V21">
-        <v>0.0044746450417367783</v>
+        <v>0.0044746450417367679</v>
       </c>
       <c r="W21">
-        <v>0.0042381389294276536</v>
+        <v>0.0042381389294276935</v>
       </c>
       <c r="X21">
-        <v>-0.00021322219030547236</v>
+        <v>-0.00021322219030547171</v>
       </c>
       <c r="Y21">
-        <v>2.7666029659508765e-05</v>
+        <v>2.7666029659508548e-05</v>
       </c>
       <c r="Z21">
-        <v>8.6603241043895548e-05</v>
+        <v>8.6603241043908558e-05</v>
       </c>
       <c r="AA21">
-        <v>1.9365119552465504e-06</v>
+        <v>1.9365119552565251e-06</v>
       </c>
       <c r="AB21">
-        <v>3.0966175405273098e-05</v>
+        <v>3.0966175405284808e-05</v>
       </c>
       <c r="AC21">
-        <v>7.6567174047375945e-05</v>
+        <v>7.6567174047388088e-05</v>
       </c>
       <c r="AD21">
-        <v>0.00018787443626774088</v>
+        <v>0.00018787443626775379</v>
       </c>
       <c r="AE21">
-        <v>0.00020760721124195796</v>
+        <v>0.00020760721124197113</v>
       </c>
       <c r="AF21">
-        <v>9.0116810501175454e-06</v>
+        <v>9.0116810501183992e-06</v>
       </c>
       <c r="AG21">
         <v>9.8761563418469159e-05</v>
       </c>
       <c r="AH21">
-        <v>-0.00010339082551956988</v>
+        <v>-0.00010339082551957465</v>
       </c>
       <c r="AI21">
-        <v>-0.0044241714089441721</v>
+        <v>-0.0044241714089442597</v>
       </c>
     </row>
     <row r="22">
@@ -2645,103 +2645,103 @@
         <v>0.23388741978217065</v>
       </c>
       <c r="C22">
-        <v>-5.9422502834602001e-05</v>
+        <v>-5.9422502834600118e-05</v>
       </c>
       <c r="D22">
-        <v>0.00080519745304555952</v>
+        <v>0.000805197453045594</v>
       </c>
       <c r="E22">
-        <v>0.00072939579332476838</v>
+        <v>0.0007293957933247996</v>
       </c>
       <c r="F22">
-        <v>0.00035402050081689601</v>
+        <v>0.00035402050081692485</v>
       </c>
       <c r="G22">
-        <v>0.0012059413454082234</v>
+        <v>0.0012059413454082583</v>
       </c>
       <c r="H22">
-        <v>0.001063574258902799</v>
+        <v>0.0010635742589028341</v>
       </c>
       <c r="I22">
-        <v>0.000769543349896985</v>
+        <v>0.00076954334989701731</v>
       </c>
       <c r="J22">
-        <v>0.00077552129634346251</v>
+        <v>0.00077552129634349829</v>
       </c>
       <c r="K22">
-        <v>0.0039392190568509015</v>
+        <v>0.0039392190568509327</v>
       </c>
       <c r="L22">
-        <v>0.0033259568499667243</v>
+        <v>0.003325956849966759</v>
       </c>
       <c r="M22">
-        <v>-0.00033281241228975955</v>
+        <v>-0.00033281241228975544</v>
       </c>
       <c r="N22">
-        <v>0.00043867877034087726</v>
+        <v>0.00043867877034088393</v>
       </c>
       <c r="O22">
-        <v>0.00050573604431693045</v>
+        <v>0.00050573604431693945</v>
       </c>
       <c r="P22">
-        <v>0.00046371833807942004</v>
+        <v>0.00046371833807950721</v>
       </c>
       <c r="Q22">
-        <v>1.6812808064698651e-05</v>
+        <v>1.6812808064787556e-05</v>
       </c>
       <c r="R22">
-        <v>5.8702360032054837e-05</v>
+        <v>5.870236003214591e-05</v>
       </c>
       <c r="S22">
-        <v>0.00025997622043381517</v>
+        <v>0.00025997622043390668</v>
       </c>
       <c r="T22">
-        <v>0.0010934520904993467</v>
+        <v>0.0010934520904993556</v>
       </c>
       <c r="U22">
-        <v>0.0036402634101280343</v>
+        <v>0.0036402634101280655</v>
       </c>
       <c r="V22">
-        <v>0.0042381389294276536</v>
+        <v>0.0042381389294276935</v>
       </c>
       <c r="W22">
-        <v>0.0054224935541577687</v>
+        <v>0.005422493554157819</v>
       </c>
       <c r="X22">
-        <v>-0.00025246361274046842</v>
+        <v>-0.00025246361274046782</v>
       </c>
       <c r="Y22">
-        <v>2.9979686537174189e-05</v>
+        <v>2.9979686537174081e-05</v>
       </c>
       <c r="Z22">
-        <v>0.00016191570019673729</v>
+        <v>0.00016191570019675463</v>
       </c>
       <c r="AA22">
-        <v>2.6869125629069759e-05</v>
+        <v>2.6869125629082336e-05</v>
       </c>
       <c r="AB22">
-        <v>5.4205815082350884e-05</v>
+        <v>5.4205815082366497e-05</v>
       </c>
       <c r="AC22">
-        <v>0.00013184405026467035</v>
+        <v>0.0001318440502646864</v>
       </c>
       <c r="AD22">
-        <v>0.00019495295271682251</v>
+        <v>0.00019495295271683931</v>
       </c>
       <c r="AE22">
-        <v>0.00014314395619293653</v>
+        <v>0.00014314395619295401</v>
       </c>
       <c r="AF22">
-        <v>1.1770680230066018e-05</v>
+        <v>1.1770680230067129e-05</v>
       </c>
       <c r="AG22">
-        <v>-0.00017259147849396899</v>
+        <v>-0.00017259147849397072</v>
       </c>
       <c r="AH22">
-        <v>-0.00014225457160009481</v>
+        <v>-0.00014225457160010066</v>
       </c>
       <c r="AI22">
-        <v>-0.0053221193019862469</v>
+        <v>-0.0053221193019863666</v>
       </c>
     </row>
     <row r="23">
@@ -2752,103 +2752,103 @@
         <v>0.01736585391862102</v>
       </c>
       <c r="C23">
-        <v>-4.802813257907438e-07</v>
+        <v>-4.8028132579072198e-07</v>
       </c>
       <c r="D23">
-        <v>-7.8230614138234162e-06</v>
+        <v>-7.8230614138232163e-06</v>
       </c>
       <c r="E23">
-        <v>-3.1864712784610305e-05</v>
+        <v>-3.1864712784610176e-05</v>
       </c>
       <c r="F23">
-        <v>-1.1239453734116289e-05</v>
+        <v>-1.1239453734116243e-05</v>
       </c>
       <c r="G23">
-        <v>-4.7557013707125948e-05</v>
+        <v>-4.7557013707125826e-05</v>
       </c>
       <c r="H23">
-        <v>-2.6566527801927502e-05</v>
+        <v>-2.6566527801927329e-05</v>
       </c>
       <c r="I23">
-        <v>-3.6324449322708719e-05</v>
+        <v>-3.6324449322708611e-05</v>
       </c>
       <c r="J23">
-        <v>-3.8749522387691831e-05</v>
+        <v>-3.8749522387691655e-05</v>
       </c>
       <c r="K23">
-        <v>-0.00016679003225496483</v>
+        <v>-0.00016679003225496437</v>
       </c>
       <c r="L23">
-        <v>-0.0001492195673697877</v>
+        <v>-0.00014921956736978716</v>
       </c>
       <c r="M23">
-        <v>1.3508018690001934e-05</v>
+        <v>1.3508018690001983e-05</v>
       </c>
       <c r="N23">
-        <v>-8.9450452029444165e-06</v>
+        <v>-8.94504520294432e-06</v>
       </c>
       <c r="O23">
-        <v>-1.0285577321125531e-05</v>
+        <v>-1.0285577321125419e-05</v>
       </c>
       <c r="P23">
-        <v>-2.9039404761879379e-05</v>
+        <v>-2.9039404761877563e-05</v>
       </c>
       <c r="Q23">
-        <v>-1.5446679067544567e-05</v>
+        <v>-1.5446679067542744e-05</v>
       </c>
       <c r="R23">
-        <v>-1.4914311524460619e-05</v>
+        <v>-1.4914311524458736e-05</v>
       </c>
       <c r="S23">
-        <v>-1.2964826891340041e-05</v>
+        <v>-1.2964826891338069e-05</v>
       </c>
       <c r="T23">
-        <v>-9.7975365989235442e-05</v>
+        <v>-9.7975365989235293e-05</v>
       </c>
       <c r="U23">
-        <v>-0.0002085859767480611</v>
+        <v>-0.00020858597674806067</v>
       </c>
       <c r="V23">
-        <v>-0.00021322219030547236</v>
+        <v>-0.00021322219030547171</v>
       </c>
       <c r="W23">
-        <v>-0.00025246361274046842</v>
+        <v>-0.00025246361274046782</v>
       </c>
       <c r="X23">
-        <v>3.5907221896566375e-05</v>
+        <v>3.5907221896566362e-05</v>
       </c>
       <c r="Y23">
-        <v>-5.0879498333561162e-06</v>
+        <v>-5.0879498333560857e-06</v>
       </c>
       <c r="Z23">
-        <v>-1.4893099836860317e-05</v>
+        <v>-1.4893099836860914e-05</v>
       </c>
       <c r="AA23">
-        <v>-1.3096336156970693e-05</v>
+        <v>-1.3096336156971045e-05</v>
       </c>
       <c r="AB23">
-        <v>-7.4033122276246515e-06</v>
+        <v>-7.4033122276251123e-06</v>
       </c>
       <c r="AC23">
-        <v>-1.2136815108224061e-05</v>
+        <v>-1.2136815108224671e-05</v>
       </c>
       <c r="AD23">
-        <v>-8.7635720959443405e-06</v>
+        <v>-8.7635720959448961e-06</v>
       </c>
       <c r="AE23">
-        <v>-1.5430911525350005e-05</v>
+        <v>-1.5430911525350564e-05</v>
       </c>
       <c r="AF23">
-        <v>1.9760107536395215e-06</v>
+        <v>1.9760107536394927e-06</v>
       </c>
       <c r="AG23">
-        <v>3.0246414570963748e-05</v>
+        <v>3.0246414570963667e-05</v>
       </c>
       <c r="AH23">
-        <v>-4.9263320160389701e-06</v>
+        <v>-4.9263320160388346e-06</v>
       </c>
       <c r="AI23">
-        <v>0.00018792114322453663</v>
+        <v>0.0001879211432245401</v>
       </c>
     </row>
     <row r="24">
@@ -2859,103 +2859,103 @@
         <v>3.892237300748834</v>
       </c>
       <c r="C24">
-        <v>-3.1834493471115892e-05</v>
+        <v>-3.1834493471115865e-05</v>
       </c>
       <c r="D24">
-        <v>0.00033228372241895826</v>
+        <v>0.00033228372241895908</v>
       </c>
       <c r="E24">
-        <v>-6.7136134926304263e-05</v>
+        <v>-6.7136134926303558e-05</v>
       </c>
       <c r="F24">
-        <v>-4.883454486433441e-05</v>
+        <v>-4.883454486433376e-05</v>
       </c>
       <c r="G24">
-        <v>0.00012877618346038923</v>
+        <v>0.00012877618346038988</v>
       </c>
       <c r="H24">
-        <v>-1.8494888706545559e-05</v>
+        <v>-1.8494888706544908e-05</v>
       </c>
       <c r="I24">
-        <v>-8.8974886706919552e-05</v>
+        <v>-8.8974886706918684e-05</v>
       </c>
       <c r="J24">
-        <v>-2.3845104977733469e-05</v>
+        <v>-2.384510497773271e-05</v>
       </c>
       <c r="K24">
-        <v>3.7762544182087083e-05</v>
+        <v>3.7762544182086649e-05</v>
       </c>
       <c r="L24">
-        <v>4.2739638244125274e-05</v>
+        <v>4.2739638244124894e-05</v>
       </c>
       <c r="M24">
-        <v>3.3516023083526297e-06</v>
+        <v>3.3516023083527584e-06</v>
       </c>
       <c r="N24">
-        <v>2.5349901746122248e-06</v>
+        <v>2.5349901746123875e-06</v>
       </c>
       <c r="O24">
-        <v>1.0451598659236535e-05</v>
+        <v>1.0451598659236752e-05</v>
       </c>
       <c r="P24">
-        <v>-0.00011733515753141401</v>
+        <v>-0.00011733515753141271</v>
       </c>
       <c r="Q24">
-        <v>-2.0611295039211402e-05</v>
+        <v>-2.0611295039210317e-05</v>
       </c>
       <c r="R24">
-        <v>-2.791809035572186e-05</v>
+        <v>-2.7918090355720342e-05</v>
       </c>
       <c r="S24">
-        <v>1.2286128425974523e-06</v>
+        <v>1.2286128425987534e-06</v>
       </c>
       <c r="T24">
-        <v>6.9257082614885125e-06</v>
+        <v>6.9257082614884854e-06</v>
       </c>
       <c r="U24">
-        <v>2.5943844974372215e-05</v>
+        <v>2.5943844974371945e-05</v>
       </c>
       <c r="V24">
-        <v>2.7666029659508765e-05</v>
+        <v>2.7666029659508548e-05</v>
       </c>
       <c r="W24">
-        <v>2.9979686537174189e-05</v>
+        <v>2.9979686537174081e-05</v>
       </c>
       <c r="X24">
-        <v>-5.0879498333561162e-06</v>
+        <v>-5.0879498333560857e-06</v>
       </c>
       <c r="Y24">
         <v>0.00046673961194149469</v>
       </c>
       <c r="Z24">
-        <v>-1.3656190882247636e-05</v>
+        <v>-1.3656190882247501e-05</v>
       </c>
       <c r="AA24">
-        <v>2.3027779609006551e-05</v>
+        <v>2.3027779609006741e-05</v>
       </c>
       <c r="AB24">
-        <v>-1.2590197192875486e-05</v>
+        <v>-1.2590197192875337e-05</v>
       </c>
       <c r="AC24">
-        <v>-5.4273072590255015e-06</v>
+        <v>-5.4273072590252304e-06</v>
       </c>
       <c r="AD24">
-        <v>5.0475275273062659e-06</v>
+        <v>5.0475275273064929e-06</v>
       </c>
       <c r="AE24">
-        <v>-4.6852151554368798e-05</v>
+        <v>-4.6852151554368649e-05</v>
       </c>
       <c r="AF24">
-        <v>-1.5188203201894497e-07</v>
+        <v>-1.5188203201892972e-07</v>
       </c>
       <c r="AG24">
-        <v>-0.00010559568546626718</v>
+        <v>-0.00010559568546626726</v>
       </c>
       <c r="AH24">
-        <v>2.8898995698168813e-05</v>
+        <v>2.8898995698168637e-05</v>
       </c>
       <c r="AI24">
-        <v>-0.00018355116897700159</v>
+        <v>-0.00018355116897699833</v>
       </c>
     </row>
     <row r="25">
@@ -2966,103 +2966,103 @@
         <v>0.094379236628785945</v>
       </c>
       <c r="C25">
-        <v>-8.1085924364915341e-05</v>
+        <v>-8.1085924364914826e-05</v>
       </c>
       <c r="D25">
-        <v>0.00014280146279554637</v>
+        <v>0.00014280146279555895</v>
       </c>
       <c r="E25">
-        <v>0.00010394145986337652</v>
+        <v>0.00010394145986338931</v>
       </c>
       <c r="F25">
-        <v>0.00011191749201079561</v>
+        <v>0.00011191749201080623</v>
       </c>
       <c r="G25">
-        <v>0.00020423090026065174</v>
+        <v>0.00020423090026066562</v>
       </c>
       <c r="H25">
-        <v>0.00022190153581250639</v>
+        <v>0.00022190153581251983</v>
       </c>
       <c r="I25">
-        <v>5.285445932202786e-05</v>
+        <v>5.2854459322041088e-05</v>
       </c>
       <c r="J25">
-        <v>0.00014993704661024967</v>
+        <v>0.00014993704661026355</v>
       </c>
       <c r="K25">
-        <v>0.00018681899800963376</v>
+        <v>0.0001868189980096433</v>
       </c>
       <c r="L25">
-        <v>4.4432803402145657e-05</v>
+        <v>4.4432803402155632e-05</v>
       </c>
       <c r="M25">
-        <v>5.3753552470530829e-06</v>
+        <v>5.3753552470534624e-06</v>
       </c>
       <c r="N25">
-        <v>3.176840152891992e-05</v>
+        <v>3.176840152892095e-05</v>
       </c>
       <c r="O25">
-        <v>7.8399976348818355e-05</v>
+        <v>7.8399976348820632e-05</v>
       </c>
       <c r="P25">
-        <v>0.00011420262847560651</v>
+        <v>0.00011420262847562559</v>
       </c>
       <c r="Q25">
-        <v>0.00039977578339571874</v>
+        <v>0.00039977578339573782</v>
       </c>
       <c r="R25">
-        <v>0.00042834881384021077</v>
+        <v>0.00042834881384023072</v>
       </c>
       <c r="S25">
-        <v>0.00050815612522661473</v>
+        <v>0.00050815612522663554</v>
       </c>
       <c r="T25">
-        <v>5.8451861510897723e-05</v>
+        <v>5.8451861510900867e-05</v>
       </c>
       <c r="U25">
-        <v>2.768071263798029e-05</v>
+        <v>2.7680712637990265e-05</v>
       </c>
       <c r="V25">
-        <v>8.6603241043895548e-05</v>
+        <v>8.6603241043908558e-05</v>
       </c>
       <c r="W25">
-        <v>0.00016191570019673729</v>
+        <v>0.00016191570019675463</v>
       </c>
       <c r="X25">
-        <v>-1.4893099836860317e-05</v>
+        <v>-1.4893099836860914e-05</v>
       </c>
       <c r="Y25">
-        <v>-1.3656190882247636e-05</v>
+        <v>-1.3656190882247501e-05</v>
       </c>
       <c r="Z25">
-        <v>0.0030697965617201852</v>
+        <v>0.00306979656172019</v>
       </c>
       <c r="AA25">
-        <v>0.0024179089040784613</v>
+        <v>0.0024179089040784673</v>
       </c>
       <c r="AB25">
-        <v>0.002404550751804479</v>
+        <v>0.0024045507518044842</v>
       </c>
       <c r="AC25">
-        <v>0.0024220989664617064</v>
+        <v>0.002422098966461712</v>
       </c>
       <c r="AD25">
-        <v>0.0024195156018215242</v>
+        <v>0.0024195156018215289</v>
       </c>
       <c r="AE25">
-        <v>0.0024034528561093405</v>
+        <v>0.0024034528561093466</v>
       </c>
       <c r="AF25">
-        <v>4.3270358777724812e-06</v>
+        <v>4.3270358777728335e-06</v>
       </c>
       <c r="AG25">
-        <v>-8.9653440550173033e-05</v>
+        <v>-8.9653440550173901e-05</v>
       </c>
       <c r="AH25">
-        <v>-7.5214449039279706e-05</v>
+        <v>-7.5214449039282634e-05</v>
       </c>
       <c r="AI25">
-        <v>-0.0030368046871220981</v>
+        <v>-0.0030368046871221436</v>
       </c>
     </row>
     <row r="26">
@@ -3073,103 +3073,103 @@
         <v>0.12294840072921695</v>
       </c>
       <c r="C26">
-        <v>-8.7021960423897996e-05</v>
+        <v>-8.7021960423897508e-05</v>
       </c>
       <c r="D26">
-        <v>0.0010716454027064866</v>
+        <v>0.0010716454027064983</v>
       </c>
       <c r="E26">
-        <v>8.770373819365785e-05</v>
+        <v>8.7703738193669126e-05</v>
       </c>
       <c r="F26">
-        <v>7.3842847933200395e-06</v>
+        <v>7.3842847933297973e-06</v>
       </c>
       <c r="G26">
-        <v>6.1444208924456853e-05</v>
+        <v>6.1444208924468779e-05</v>
       </c>
       <c r="H26">
-        <v>0.00014698745143087479</v>
+        <v>0.00014698745143088671</v>
       </c>
       <c r="I26">
-        <v>3.2123447875525299e-05</v>
+        <v>3.2123447875537442e-05</v>
       </c>
       <c r="J26">
-        <v>0.00012300481935884349</v>
+        <v>0.00012300481935885563</v>
       </c>
       <c r="K26">
-        <v>0.00010292825587060895</v>
+        <v>0.00010292825587061589</v>
       </c>
       <c r="L26">
-        <v>-5.0739540888786183e-05</v>
+        <v>-5.0739540888778811e-05</v>
       </c>
       <c r="M26">
-        <v>-4.7040608925575636e-05</v>
+        <v>-4.7040608925574498e-05</v>
       </c>
       <c r="N26">
-        <v>1.4427976619051325e-05</v>
+        <v>1.4427976619053114e-05</v>
       </c>
       <c r="O26">
-        <v>8.0597869771119454e-05</v>
+        <v>8.0597869771121947e-05</v>
       </c>
       <c r="P26">
-        <v>0.00016597672273013959</v>
+        <v>0.00016597672273016388</v>
       </c>
       <c r="Q26">
-        <v>0.00039619269341183844</v>
+        <v>0.00039619269341186359</v>
       </c>
       <c r="R26">
-        <v>0.00038964786848787094</v>
+        <v>0.00038964786848789609</v>
       </c>
       <c r="S26">
-        <v>0.00043808842808900489</v>
+        <v>0.00043808842808903178</v>
       </c>
       <c r="T26">
-        <v>5.2488330671794366e-05</v>
+        <v>5.2488330671796534e-05</v>
       </c>
       <c r="U26">
-        <v>-2.6550282929700686e-05</v>
+        <v>-2.6550282929693313e-05</v>
       </c>
       <c r="V26">
-        <v>1.9365119552465504e-06</v>
+        <v>1.9365119552565251e-06</v>
       </c>
       <c r="W26">
-        <v>2.6869125629069759e-05</v>
+        <v>2.6869125629082336e-05</v>
       </c>
       <c r="X26">
-        <v>-1.3096336156970693e-05</v>
+        <v>-1.3096336156971045e-05</v>
       </c>
       <c r="Y26">
-        <v>2.3027779609006551e-05</v>
+        <v>2.3027779609006741e-05</v>
       </c>
       <c r="Z26">
-        <v>0.0024179089040784613</v>
+        <v>0.0024179089040784673</v>
       </c>
       <c r="AA26">
-        <v>0.0031027946331042924</v>
+        <v>0.0031027946331042976</v>
       </c>
       <c r="AB26">
-        <v>0.0023978483286616562</v>
+        <v>0.0023978483286616614</v>
       </c>
       <c r="AC26">
-        <v>0.002409357967163568</v>
+        <v>0.0024093579671635732</v>
       </c>
       <c r="AD26">
-        <v>0.0024111185307734502</v>
+        <v>0.002411118530773455</v>
       </c>
       <c r="AE26">
-        <v>0.0024006466571823933</v>
+        <v>0.0024006466571823981</v>
       </c>
       <c r="AF26">
-        <v>5.2611654468122114e-06</v>
+        <v>5.2611654468125231e-06</v>
       </c>
       <c r="AG26">
-        <v>-8.5541095288291539e-05</v>
+        <v>-8.554109528829219e-05</v>
       </c>
       <c r="AH26">
-        <v>-1.6356704670957467e-05</v>
+        <v>-1.6356704670960178e-05</v>
       </c>
       <c r="AI26">
-        <v>-0.0029087018043451578</v>
+        <v>-0.0029087018043451977</v>
       </c>
     </row>
     <row r="27">
@@ -3180,103 +3180,103 @@
         <v>-0.042363738032216963</v>
       </c>
       <c r="C27">
-        <v>-9.2596972208624484e-05</v>
+        <v>-9.2596972208624809e-05</v>
       </c>
       <c r="D27">
-        <v>0.0007563371623317567</v>
+        <v>0.0007563371623317696</v>
       </c>
       <c r="E27">
-        <v>0.00010743254938749445</v>
+        <v>0.00010743254938750703</v>
       </c>
       <c r="F27">
-        <v>5.2590944147562577e-05</v>
+        <v>5.2590944147573203e-05</v>
       </c>
       <c r="G27">
-        <v>0.0001231085885548299</v>
+        <v>0.00012310858855484356</v>
       </c>
       <c r="H27">
-        <v>0.00017526084095628117</v>
+        <v>0.00017526084095629484</v>
       </c>
       <c r="I27">
-        <v>5.362024703079349e-05</v>
+        <v>5.3620247030806501e-05</v>
       </c>
       <c r="J27">
-        <v>7.6264365752959753e-05</v>
+        <v>7.6264365752973414e-05</v>
       </c>
       <c r="K27">
-        <v>7.9016028483066278e-05</v>
+        <v>7.9016028483075602e-05</v>
       </c>
       <c r="L27">
-        <v>-2.6403228015850705e-05</v>
+        <v>-2.6403228015840947e-05</v>
       </c>
       <c r="M27">
-        <v>2.4527032191439961e-05</v>
+        <v>2.4527032191441208e-05</v>
       </c>
       <c r="N27">
-        <v>4.8685890455250794e-06</v>
+        <v>4.8685890455269767e-06</v>
       </c>
       <c r="O27">
-        <v>0.00010319506017073969</v>
+        <v>0.0001031950601707424</v>
       </c>
       <c r="P27">
-        <v>0.00016024217855355183</v>
+        <v>0.00016024217855357525</v>
       </c>
       <c r="Q27">
-        <v>0.00039999263156205271</v>
+        <v>0.00039999263156207613</v>
       </c>
       <c r="R27">
-        <v>0.00039390262233660652</v>
+        <v>0.00039390262233663341</v>
       </c>
       <c r="S27">
-        <v>0.00045272675287770861</v>
+        <v>0.00045272675287773376</v>
       </c>
       <c r="T27">
-        <v>2.1032802931347859e-05</v>
+        <v>2.1032802931350678e-05</v>
       </c>
       <c r="U27">
-        <v>-3.9589942205490092e-05</v>
+        <v>-3.9589942205481418e-05</v>
       </c>
       <c r="V27">
-        <v>3.0966175405273098e-05</v>
+        <v>3.0966175405284808e-05</v>
       </c>
       <c r="W27">
-        <v>5.4205815082350884e-05</v>
+        <v>5.4205815082366497e-05</v>
       </c>
       <c r="X27">
-        <v>-7.4033122276246515e-06</v>
+        <v>-7.4033122276251123e-06</v>
       </c>
       <c r="Y27">
-        <v>-1.2590197192875486e-05</v>
+        <v>-1.2590197192875337e-05</v>
       </c>
       <c r="Z27">
-        <v>0.002404550751804479</v>
+        <v>0.0024045507518044842</v>
       </c>
       <c r="AA27">
-        <v>0.0023978483286616562</v>
+        <v>0.0023978483286616614</v>
       </c>
       <c r="AB27">
-        <v>0.0029016948845160947</v>
+        <v>0.0029016948845160995</v>
       </c>
       <c r="AC27">
-        <v>0.0023941358533534473</v>
+        <v>0.0023941358533534521</v>
       </c>
       <c r="AD27">
-        <v>0.002393188555904899</v>
+        <v>0.0023931885559049038</v>
       </c>
       <c r="AE27">
-        <v>0.0023926236367021038</v>
+        <v>0.002392623636702109</v>
       </c>
       <c r="AF27">
-        <v>2.0155216062572577e-06</v>
+        <v>2.0155216062575626e-06</v>
       </c>
       <c r="AG27">
-        <v>-6.419983764488252e-05</v>
+        <v>-6.419983764488317e-05</v>
       </c>
       <c r="AH27">
-        <v>-9.5198216619427263e-05</v>
+        <v>-9.5198216619429973e-05</v>
       </c>
       <c r="AI27">
-        <v>-0.0028667674330144039</v>
+        <v>-0.0028667674330144456</v>
       </c>
     </row>
     <row r="28">
@@ -3287,103 +3287,103 @@
         <v>0.05751555787790158</v>
       </c>
       <c r="C28">
-        <v>-0.00010856841590938738</v>
+        <v>-0.00010856841590938695</v>
       </c>
       <c r="D28">
-        <v>0.00013931877986970488</v>
+        <v>0.00013931877986971463</v>
       </c>
       <c r="E28">
-        <v>4.3360577271745913e-05</v>
+        <v>4.3360577271755454e-05</v>
       </c>
       <c r="F28">
-        <v>-2.1056099340477884e-05</v>
+        <v>-2.1056099340469427e-05</v>
       </c>
       <c r="G28">
-        <v>6.6073099431141315e-05</v>
+        <v>6.6073099431151507e-05</v>
       </c>
       <c r="H28">
-        <v>9.9242546054492892e-05</v>
+        <v>9.9242546054503084e-05</v>
       </c>
       <c r="I28">
-        <v>-1.5459636173135441e-05</v>
+        <v>-1.54596361731259e-05</v>
       </c>
       <c r="J28">
-        <v>7.7531048207134723e-05</v>
+        <v>7.7531048207145131e-05</v>
       </c>
       <c r="K28">
-        <v>0.0001535077105833311</v>
+        <v>0.00015350771058333999</v>
       </c>
       <c r="L28">
-        <v>2.9783468960469656e-05</v>
+        <v>2.9783468960480498e-05</v>
       </c>
       <c r="M28">
-        <v>-2.7358458102672961e-05</v>
+        <v>-2.7358458102671876e-05</v>
       </c>
       <c r="N28">
-        <v>1.6549667470975769e-05</v>
+        <v>1.6549667470977449e-05</v>
       </c>
       <c r="O28">
-        <v>1.7201678399737103e-05</v>
+        <v>1.7201678399739488e-05</v>
       </c>
       <c r="P28">
-        <v>0.00011097867444821892</v>
+        <v>0.00011097867444824234</v>
       </c>
       <c r="Q28">
-        <v>0.00032778991844844511</v>
+        <v>0.00032778991844847026</v>
       </c>
       <c r="R28">
-        <v>0.00031836766960773727</v>
+        <v>0.00031836766960776329</v>
       </c>
       <c r="S28">
-        <v>0.00038264462745451165</v>
+        <v>0.00038264462745453767</v>
       </c>
       <c r="T28">
-        <v>3.3098360869946624e-05</v>
+        <v>3.3098360869949768e-05</v>
       </c>
       <c r="U28">
-        <v>4.6144882518512828e-06</v>
+        <v>4.6144882518608238e-06</v>
       </c>
       <c r="V28">
-        <v>7.6567174047375945e-05</v>
+        <v>7.6567174047388088e-05</v>
       </c>
       <c r="W28">
-        <v>0.00013184405026467035</v>
+        <v>0.0001318440502646864</v>
       </c>
       <c r="X28">
-        <v>-1.2136815108224061e-05</v>
+        <v>-1.2136815108224671e-05</v>
       </c>
       <c r="Y28">
-        <v>-5.4273072590255015e-06</v>
+        <v>-5.4273072590252304e-06</v>
       </c>
       <c r="Z28">
-        <v>0.0024220989664617064</v>
+        <v>0.002422098966461712</v>
       </c>
       <c r="AA28">
-        <v>0.002409357967163568</v>
+        <v>0.0024093579671635732</v>
       </c>
       <c r="AB28">
-        <v>0.0023941358533534473</v>
+        <v>0.0023941358533534521</v>
       </c>
       <c r="AC28">
-        <v>0.0029680040026244256</v>
+        <v>0.0029680040026244308</v>
       </c>
       <c r="AD28">
-        <v>0.0024122865124234327</v>
+        <v>0.0024122865124234379</v>
       </c>
       <c r="AE28">
-        <v>0.0024099257746925127</v>
+        <v>0.0024099257746925183</v>
       </c>
       <c r="AF28">
-        <v>5.4268485730809757e-06</v>
+        <v>5.4268485730813349e-06</v>
       </c>
       <c r="AG28">
-        <v>-7.3490856489324399e-05</v>
+        <v>-7.3490856489324833e-05</v>
       </c>
       <c r="AH28">
-        <v>-6.1148263188881189e-05</v>
+        <v>-6.1148263188884225e-05</v>
       </c>
       <c r="AI28">
-        <v>-0.0028181773427799263</v>
+        <v>-0.0028181773427799692</v>
       </c>
     </row>
     <row r="29">
@@ -3394,103 +3394,103 @@
         <v>-0.072941401664601224</v>
       </c>
       <c r="C29">
-        <v>-6.3819334106375331e-05</v>
+        <v>-6.3819334106375602e-05</v>
       </c>
       <c r="D29">
-        <v>0.00013819997115470237</v>
+        <v>0.0001381999711547124</v>
       </c>
       <c r="E29">
-        <v>6.5902518832273212e-05</v>
+        <v>6.5902518832282645e-05</v>
       </c>
       <c r="F29">
-        <v>-5.3059972264982548e-06</v>
+        <v>-5.3059972264900691e-06</v>
       </c>
       <c r="G29">
-        <v>2.2334027506154791e-05</v>
+        <v>2.233402750616547e-05</v>
       </c>
       <c r="H29">
-        <v>0.00011251699848729887</v>
+        <v>0.00011251699848730922</v>
       </c>
       <c r="I29">
-        <v>3.2777159819301132e-05</v>
+        <v>3.2777159819310836e-05</v>
       </c>
       <c r="J29">
-        <v>0.00016385404757253771</v>
+        <v>0.00016385404757254807</v>
       </c>
       <c r="K29">
-        <v>0.00035701943319050699</v>
+        <v>0.00035701943319051686</v>
       </c>
       <c r="L29">
-        <v>0.00011865440852693141</v>
+        <v>0.00011865440852694214</v>
       </c>
       <c r="M29">
-        <v>-7.4634030212139476e-05</v>
+        <v>-7.4634030212138337e-05</v>
       </c>
       <c r="N29">
-        <v>1.0462524298719981e-05</v>
+        <v>1.0462524298721825e-05</v>
       </c>
       <c r="O29">
-        <v>6.7471731706362253e-05</v>
+        <v>6.7471731706364855e-05</v>
       </c>
       <c r="P29">
-        <v>0.00021100525375209183</v>
+        <v>0.00021100525375211568</v>
       </c>
       <c r="Q29">
-        <v>0.00040526383753041113</v>
+        <v>0.00040526383753043585</v>
       </c>
       <c r="R29">
-        <v>0.00039693324408751564</v>
+        <v>0.00039693324408754101</v>
       </c>
       <c r="S29">
-        <v>0.00049446962267037727</v>
+        <v>0.00049446962267040286</v>
       </c>
       <c r="T29">
-        <v>2.1061296049569659e-05</v>
+        <v>2.1061296049572695e-05</v>
       </c>
       <c r="U29">
-        <v>0.0001070700554739681</v>
+        <v>0.00010707005547397802</v>
       </c>
       <c r="V29">
-        <v>0.00018787443626774088</v>
+        <v>0.00018787443626775379</v>
       </c>
       <c r="W29">
-        <v>0.00019495295271682251</v>
+        <v>0.00019495295271683931</v>
       </c>
       <c r="X29">
-        <v>-8.7635720959443405e-06</v>
+        <v>-8.7635720959448961e-06</v>
       </c>
       <c r="Y29">
-        <v>5.0475275273062659e-06</v>
+        <v>5.0475275273064929e-06</v>
       </c>
       <c r="Z29">
-        <v>0.0024195156018215242</v>
+        <v>0.0024195156018215289</v>
       </c>
       <c r="AA29">
-        <v>0.0024111185307734502</v>
+        <v>0.002411118530773455</v>
       </c>
       <c r="AB29">
-        <v>0.002393188555904899</v>
+        <v>0.0023931885559049038</v>
       </c>
       <c r="AC29">
-        <v>0.0024122865124234327</v>
+        <v>0.0024122865124234379</v>
       </c>
       <c r="AD29">
-        <v>0.0027931079009252111</v>
+        <v>0.0027931079009252159</v>
       </c>
       <c r="AE29">
-        <v>0.0024091875765934519</v>
+        <v>0.0024091875765934576</v>
       </c>
       <c r="AF29">
-        <v>8.473941459985273e-07</v>
+        <v>8.4739414599884578e-07</v>
       </c>
       <c r="AG29">
-        <v>5.9676148105947688e-05</v>
+        <v>5.9676148105947038e-05</v>
       </c>
       <c r="AH29">
-        <v>-3.4783355698563088e-05</v>
+        <v>-3.4783355698565798e-05</v>
       </c>
       <c r="AI29">
-        <v>-0.0030305872269813412</v>
+        <v>-0.003030587226981382</v>
       </c>
     </row>
     <row r="30">
@@ -3501,103 +3501,103 @@
         <v>0.065751712427960879</v>
       </c>
       <c r="C30">
-        <v>-4.7641209485684455e-06</v>
+        <v>-4.7641209485679661e-06</v>
       </c>
       <c r="D30">
-        <v>2.6842920995643992e-05</v>
+        <v>2.6842920995656433e-05</v>
       </c>
       <c r="E30">
-        <v>-1.1316323787113696e-05</v>
+        <v>-1.1316323787101472e-05</v>
       </c>
       <c r="F30">
-        <v>-7.2812817573096904e-05</v>
+        <v>-7.2812817573086278e-05</v>
       </c>
       <c r="G30">
-        <v>-3.5116145501650625e-05</v>
+        <v>-3.5116145501637398e-05</v>
       </c>
       <c r="H30">
-        <v>-6.6641415073845887e-06</v>
+        <v>-6.664141507371497e-06</v>
       </c>
       <c r="I30">
-        <v>2.4805335383795338e-05</v>
+        <v>2.4805335383808186e-05</v>
       </c>
       <c r="J30">
-        <v>1.1865457425506851e-05</v>
+        <v>1.1865457425520377e-05</v>
       </c>
       <c r="K30">
-        <v>0.0002187728275894843</v>
+        <v>0.00021877282758949387</v>
       </c>
       <c r="L30">
-        <v>-5.003866963365614e-05</v>
+        <v>-5.0038669633645488e-05</v>
       </c>
       <c r="M30">
-        <v>-0.00015014202061696563</v>
+        <v>-0.00015014202061696452</v>
       </c>
       <c r="N30">
-        <v>-2.3821879086441338e-05</v>
+        <v>-2.3821879086439562e-05</v>
       </c>
       <c r="O30">
-        <v>1.4188838300472849e-05</v>
+        <v>1.4188838300475437e-05</v>
       </c>
       <c r="P30">
-        <v>0.00039010103324478698</v>
+        <v>0.0003901010332448111</v>
       </c>
       <c r="Q30">
-        <v>0.00037619705005900988</v>
+        <v>0.00037619705005903449</v>
       </c>
       <c r="R30">
-        <v>0.00041366543595435884</v>
+        <v>0.0004136654359543841</v>
       </c>
       <c r="S30">
-        <v>0.00032125317013082764</v>
+        <v>0.0003212531701308536</v>
       </c>
       <c r="T30">
-        <v>0.00011004290423317754</v>
+        <v>0.0001100429042331806</v>
       </c>
       <c r="U30">
-        <v>7.5686072508696781e-05</v>
+        <v>7.5686072508706647e-05</v>
       </c>
       <c r="V30">
-        <v>0.00020760721124195796</v>
+        <v>0.00020760721124197113</v>
       </c>
       <c r="W30">
-        <v>0.00014314395619293653</v>
+        <v>0.00014314395619295401</v>
       </c>
       <c r="X30">
-        <v>-1.5430911525350005e-05</v>
+        <v>-1.5430911525350564e-05</v>
       </c>
       <c r="Y30">
-        <v>-4.6852151554368798e-05</v>
+        <v>-4.6852151554368649e-05</v>
       </c>
       <c r="Z30">
-        <v>0.0024034528561093405</v>
+        <v>0.0024034528561093466</v>
       </c>
       <c r="AA30">
-        <v>0.0024006466571823933</v>
+        <v>0.0024006466571823981</v>
       </c>
       <c r="AB30">
-        <v>0.0023926236367021038</v>
+        <v>0.002392623636702109</v>
       </c>
       <c r="AC30">
-        <v>0.0024099257746925127</v>
+        <v>0.0024099257746925183</v>
       </c>
       <c r="AD30">
-        <v>0.0024091875765934519</v>
+        <v>0.0024091875765934576</v>
       </c>
       <c r="AE30">
-        <v>0.0030251089773792807</v>
+        <v>0.0030251089773792855</v>
       </c>
       <c r="AF30">
-        <v>2.9194340006780237e-06</v>
+        <v>2.9194340006783489e-06</v>
       </c>
       <c r="AG30">
-        <v>-4.3658362118767502e-06</v>
+        <v>-4.3658362118780512e-06</v>
       </c>
       <c r="AH30">
-        <v>-9.5541077437662171e-05</v>
+        <v>-9.5541077437664881e-05</v>
       </c>
       <c r="AI30">
-        <v>-0.0028833015366855784</v>
+        <v>-0.00288330153668562</v>
       </c>
     </row>
     <row r="31">
@@ -3608,103 +3608,103 @@
         <v>0.001711011159776669</v>
       </c>
       <c r="C31">
-        <v>-1.9497710287320405e-06</v>
+        <v>-1.9497710287320125e-06</v>
       </c>
       <c r="D31">
-        <v>-8.510155342639439e-06</v>
+        <v>-8.510155342638653e-06</v>
       </c>
       <c r="E31">
-        <v>5.5397297790903439e-06</v>
+        <v>5.5397297790910622e-06</v>
       </c>
       <c r="F31">
-        <v>2.3800320149084932e-06</v>
+        <v>2.3800320149091234e-06</v>
       </c>
       <c r="G31">
-        <v>1.0130120580751479e-05</v>
+        <v>1.0130120580752258e-05</v>
       </c>
       <c r="H31">
-        <v>1.4003597577924943e-05</v>
+        <v>1.4003597577925736e-05</v>
       </c>
       <c r="I31">
-        <v>2.8167527087327672e-06</v>
+        <v>2.8167527087335329e-06</v>
       </c>
       <c r="J31">
-        <v>2.2537754202507757e-06</v>
+        <v>2.2537754202515888e-06</v>
       </c>
       <c r="K31">
-        <v>-3.2565980408890923e-07</v>
+        <v>-3.2565980408828582e-07</v>
       </c>
       <c r="L31">
-        <v>1.0516857342269178e-05</v>
+        <v>1.0516857342269856e-05</v>
       </c>
       <c r="M31">
-        <v>1.4859872921433072e-05</v>
+        <v>1.4859872921433194e-05</v>
       </c>
       <c r="N31">
-        <v>5.616813985184142e-06</v>
+        <v>5.6168139851843385e-06</v>
       </c>
       <c r="O31">
-        <v>9.5812939870465262e-06</v>
+        <v>9.5812939870467515e-06</v>
       </c>
       <c r="P31">
-        <v>5.7254640730687004e-06</v>
+        <v>5.7254640730701912e-06</v>
       </c>
       <c r="Q31">
-        <v>-2.857098044788532e-07</v>
+        <v>-2.8570980447728111e-07</v>
       </c>
       <c r="R31">
-        <v>3.6208117601797146e-06</v>
+        <v>3.6208117601813138e-06</v>
       </c>
       <c r="S31">
-        <v>6.4351374456237591e-06</v>
+        <v>6.4351374456253854e-06</v>
       </c>
       <c r="T31">
-        <v>-3.1269371662587711e-06</v>
+        <v>-3.1269371662585882e-06</v>
       </c>
       <c r="U31">
-        <v>4.5265732748416096e-06</v>
+        <v>4.5265732748422195e-06</v>
       </c>
       <c r="V31">
-        <v>9.0116810501175454e-06</v>
+        <v>9.0116810501183992e-06</v>
       </c>
       <c r="W31">
-        <v>1.1770680230066018e-05</v>
+        <v>1.1770680230067129e-05</v>
       </c>
       <c r="X31">
-        <v>1.9760107536395215e-06</v>
+        <v>1.9760107536394927e-06</v>
       </c>
       <c r="Y31">
-        <v>-1.5188203201894497e-07</v>
+        <v>-1.5188203201892972e-07</v>
       </c>
       <c r="Z31">
-        <v>4.3270358777724812e-06</v>
+        <v>4.3270358777728335e-06</v>
       </c>
       <c r="AA31">
-        <v>5.2611654468122114e-06</v>
+        <v>5.2611654468125231e-06</v>
       </c>
       <c r="AB31">
-        <v>2.0155216062572577e-06</v>
+        <v>2.0155216062575626e-06</v>
       </c>
       <c r="AC31">
-        <v>5.4268485730809757e-06</v>
+        <v>5.4268485730813349e-06</v>
       </c>
       <c r="AD31">
-        <v>8.473941459985273e-07</v>
+        <v>8.4739414599884578e-07</v>
       </c>
       <c r="AE31">
-        <v>2.9194340006780237e-06</v>
+        <v>2.9194340006783489e-06</v>
       </c>
       <c r="AF31">
-        <v>4.7593550376573534e-06</v>
+        <v>4.7593550376573975e-06</v>
       </c>
       <c r="AG31">
-        <v>-7.1751980030202551e-06</v>
+        <v>-7.1751980030204448e-06</v>
       </c>
       <c r="AH31">
-        <v>-1.3480168463238869e-05</v>
+        <v>-1.3480168463239126e-05</v>
       </c>
       <c r="AI31">
-        <v>-0.00011321363707010669</v>
+        <v>-0.00011321363707010979</v>
       </c>
     </row>
     <row r="32">
@@ -3715,103 +3715,103 @@
         <v>-0.15251988705998118</v>
       </c>
       <c r="C32">
-        <v>8.2682461790918376e-05</v>
+        <v>8.2682461790918268e-05</v>
       </c>
       <c r="D32">
-        <v>5.4247913094004809e-05</v>
+        <v>5.4247913094002641e-05</v>
       </c>
       <c r="E32">
-        <v>-3.4781742681625188e-05</v>
+        <v>-3.478174268162779e-05</v>
       </c>
       <c r="F32">
-        <v>0.00011273175229523135</v>
+        <v>0.00011273175229523005</v>
       </c>
       <c r="G32">
-        <v>-0.00013755789499182453</v>
+        <v>-0.00013755789499182583</v>
       </c>
       <c r="H32">
-        <v>-8.6778641401065969e-05</v>
+        <v>-8.677864140106727e-05</v>
       </c>
       <c r="I32">
-        <v>4.6806591355737746e-06</v>
+        <v>4.6806591355711726e-06</v>
       </c>
       <c r="J32">
-        <v>0.00015386211925594567</v>
+        <v>0.00015386211925594393</v>
       </c>
       <c r="K32">
-        <v>0.00037063543131517608</v>
+        <v>0.00037063543131517695</v>
       </c>
       <c r="L32">
         <v>5.5955232594965317e-05</v>
       </c>
       <c r="M32">
-        <v>-0.00030833222323535297</v>
+        <v>-0.0003083322232353533</v>
       </c>
       <c r="N32">
-        <v>-9.8069252881486258e-05</v>
+        <v>-9.8069252881486746e-05</v>
       </c>
       <c r="O32">
-        <v>-8.9809283282528017e-05</v>
+        <v>-8.9809283282528667e-05</v>
       </c>
       <c r="P32">
-        <v>1.2088203191898579e-05</v>
+        <v>1.2088203191894242e-05</v>
       </c>
       <c r="Q32">
-        <v>4.3779515320177889e-05</v>
+        <v>4.3779515320172685e-05</v>
       </c>
       <c r="R32">
-        <v>4.5946337358625244e-05</v>
+        <v>4.594633735862351e-05</v>
       </c>
       <c r="S32">
-        <v>4.3708144531398943e-05</v>
+        <v>4.3708144531393739e-05</v>
       </c>
       <c r="T32">
-        <v>-0.00013761921847101522</v>
+        <v>-0.00013761921847101533</v>
       </c>
       <c r="U32">
-        <v>-2.3809894667179386e-05</v>
+        <v>-2.3809894667178953e-05</v>
       </c>
       <c r="V32">
         <v>9.8761563418469159e-05</v>
       </c>
       <c r="W32">
-        <v>-0.00017259147849396899</v>
+        <v>-0.00017259147849397072</v>
       </c>
       <c r="X32">
-        <v>3.0246414570963748e-05</v>
+        <v>3.0246414570963667e-05</v>
       </c>
       <c r="Y32">
-        <v>-0.00010559568546626718</v>
+        <v>-0.00010559568546626726</v>
       </c>
       <c r="Z32">
-        <v>-8.9653440550173033e-05</v>
+        <v>-8.9653440550173901e-05</v>
       </c>
       <c r="AA32">
-        <v>-8.5541095288291539e-05</v>
+        <v>-8.554109528829219e-05</v>
       </c>
       <c r="AB32">
-        <v>-6.419983764488252e-05</v>
+        <v>-6.419983764488317e-05</v>
       </c>
       <c r="AC32">
-        <v>-7.3490856489324399e-05</v>
+        <v>-7.3490856489324833e-05</v>
       </c>
       <c r="AD32">
-        <v>5.9676148105947688e-05</v>
+        <v>5.9676148105947038e-05</v>
       </c>
       <c r="AE32">
-        <v>-4.3658362118767502e-06</v>
+        <v>-4.3658362118780512e-06</v>
       </c>
       <c r="AF32">
-        <v>-7.1751980030202551e-06</v>
+        <v>-7.1751980030204448e-06</v>
       </c>
       <c r="AG32">
-        <v>0.0021902531402251324</v>
+        <v>0.0021902531402251328</v>
       </c>
       <c r="AH32">
-        <v>0.00014619121712923053</v>
+        <v>0.00014619121712923123</v>
       </c>
       <c r="AI32">
-        <v>7.4687898885440079e-06</v>
+        <v>7.4687898885519226e-06</v>
       </c>
     </row>
     <row r="33">
@@ -3822,103 +3822,103 @@
         <v>-0.045878343329260198</v>
       </c>
       <c r="C33">
-        <v>1.3097791130418853e-05</v>
+        <v>1.3097791130418568e-05</v>
       </c>
       <c r="D33">
-        <v>0.0013306349657106415</v>
+        <v>0.0013306349657106369</v>
       </c>
       <c r="E33">
-        <v>2.948272168971347e-05</v>
+        <v>2.9482721689708916e-05</v>
       </c>
       <c r="F33">
-        <v>7.0103091909831813e-05</v>
+        <v>7.0103091909827909e-05</v>
       </c>
       <c r="G33">
-        <v>7.9445070357428687e-05</v>
+        <v>7.94450703574237e-05</v>
       </c>
       <c r="H33">
-        <v>6.0970632979302688e-05</v>
+        <v>6.0970632979297701e-05</v>
       </c>
       <c r="I33">
-        <v>3.7243755954839588e-05</v>
+        <v>3.7243755954834818e-05</v>
       </c>
       <c r="J33">
-        <v>-2.3520691061540422e-05</v>
+        <v>-2.3520691061545192e-05</v>
       </c>
       <c r="K33">
-        <v>-9.4744370399680016e-05</v>
+        <v>-9.4744370399683486e-05</v>
       </c>
       <c r="L33">
-        <v>-2.7635679663996337e-05</v>
+        <v>-2.7635679664000023e-05</v>
       </c>
       <c r="M33">
-        <v>-4.2100416755658121e-05</v>
+        <v>-4.2100416755658744e-05</v>
       </c>
       <c r="N33">
-        <v>-3.6525377833204319e-05</v>
+        <v>-3.6525377833205295e-05</v>
       </c>
       <c r="O33">
-        <v>-7.0967816654567714e-05</v>
+        <v>-7.0967816654568961e-05</v>
       </c>
       <c r="P33">
-        <v>-4.9005125978268584e-05</v>
+        <v>-4.9005125978278993e-05</v>
       </c>
       <c r="Q33">
-        <v>2.3744716712641081e-05</v>
+        <v>2.3744716712629371e-05</v>
       </c>
       <c r="R33">
-        <v>2.3263439245871376e-05</v>
+        <v>2.3263439245859233e-05</v>
       </c>
       <c r="S33">
-        <v>7.8244783439976838e-05</v>
+        <v>7.8244783439965129e-05</v>
       </c>
       <c r="T33">
-        <v>-5.2297174353573331e-05</v>
+        <v>-5.2297174353574253e-05</v>
       </c>
       <c r="U33">
-        <v>-6.8373762652340847e-05</v>
+        <v>-6.83737626523441e-05</v>
       </c>
       <c r="V33">
-        <v>-0.00010339082551956988</v>
+        <v>-0.00010339082551957465</v>
       </c>
       <c r="W33">
-        <v>-0.00014225457160009481</v>
+        <v>-0.00014225457160010066</v>
       </c>
       <c r="X33">
-        <v>-4.9263320160389701e-06</v>
+        <v>-4.9263320160388346e-06</v>
       </c>
       <c r="Y33">
-        <v>2.8898995698168813e-05</v>
+        <v>2.8898995698168637e-05</v>
       </c>
       <c r="Z33">
-        <v>-7.5214449039279706e-05</v>
+        <v>-7.5214449039282634e-05</v>
       </c>
       <c r="AA33">
-        <v>-1.6356704670957467e-05</v>
+        <v>-1.6356704670960178e-05</v>
       </c>
       <c r="AB33">
-        <v>-9.5198216619427263e-05</v>
+        <v>-9.5198216619429973e-05</v>
       </c>
       <c r="AC33">
-        <v>-6.1148263188881189e-05</v>
+        <v>-6.1148263188884225e-05</v>
       </c>
       <c r="AD33">
-        <v>-3.4783355698563088e-05</v>
+        <v>-3.4783355698565798e-05</v>
       </c>
       <c r="AE33">
-        <v>-9.5541077437662171e-05</v>
+        <v>-9.5541077437664881e-05</v>
       </c>
       <c r="AF33">
-        <v>-1.3480168463238869e-05</v>
+        <v>-1.3480168463239126e-05</v>
       </c>
       <c r="AG33">
-        <v>0.00014619121712923053</v>
+        <v>0.00014619121712923123</v>
       </c>
       <c r="AH33">
-        <v>0.0024010981295976529</v>
+        <v>0.0024010981295976537</v>
       </c>
       <c r="AI33">
-        <v>0.00024089133971755663</v>
+        <v>0.00024089133971756486</v>
       </c>
     </row>
     <row r="34">
@@ -3929,103 +3929,103 @@
         <v>-1.5822168062419928</v>
       </c>
       <c r="C34">
-        <v>-7.2034827626274e-05</v>
+        <v>-7.2034827626278066e-05</v>
       </c>
       <c r="D34">
-        <v>-0.0029610538351407139</v>
+        <v>-0.0029610538351408063</v>
       </c>
       <c r="E34">
-        <v>-0.0024047977311919084</v>
+        <v>-0.0024047977311919999</v>
       </c>
       <c r="F34">
-        <v>-0.0020326920215607788</v>
+        <v>-0.0020326920215608581</v>
       </c>
       <c r="G34">
-        <v>-0.0029729672163784247</v>
+        <v>-0.0029729672163785214</v>
       </c>
       <c r="H34">
-        <v>-0.0028559799727096713</v>
+        <v>-0.0028559799727097693</v>
       </c>
       <c r="I34">
-        <v>-0.0024133870012868893</v>
+        <v>-0.0024133870012869878</v>
       </c>
       <c r="J34">
-        <v>-0.002582096142993707</v>
+        <v>-0.0025820961429938089</v>
       </c>
       <c r="K34">
-        <v>-0.0040142065628919503</v>
+        <v>-0.0040142065628920171</v>
       </c>
       <c r="L34">
-        <v>-0.0036131444182356887</v>
+        <v>-0.0036131444182357572</v>
       </c>
       <c r="M34">
-        <v>-0.00015965131485163437</v>
+        <v>-0.00015965131485163692</v>
       </c>
       <c r="N34">
-        <v>-0.00082028153442178608</v>
+        <v>-0.00082028153442179996</v>
       </c>
       <c r="O34">
-        <v>-0.0011770786664807337</v>
+        <v>-0.0011770786664807545</v>
       </c>
       <c r="P34">
-        <v>-0.007646923409067169</v>
+        <v>-0.0076469234090673632</v>
       </c>
       <c r="Q34">
-        <v>-0.0074153616530795467</v>
+        <v>-0.0074153616530797445</v>
       </c>
       <c r="R34">
-        <v>-0.0076541926183776501</v>
+        <v>-0.007654192618377853</v>
       </c>
       <c r="S34">
-        <v>-0.0080109756220309476</v>
+        <v>-0.0080109756220311541</v>
       </c>
       <c r="T34">
-        <v>-0.00073223072105569578</v>
+        <v>-0.00073223072105571747</v>
       </c>
       <c r="U34">
-        <v>-0.0036109294228694145</v>
+        <v>-0.0036109294228694813</v>
       </c>
       <c r="V34">
-        <v>-0.0044241714089441721</v>
+        <v>-0.0044241714089442597</v>
       </c>
       <c r="W34">
-        <v>-0.0053221193019862469</v>
+        <v>-0.0053221193019863666</v>
       </c>
       <c r="X34">
-        <v>0.00018792114322453663</v>
+        <v>0.0001879211432245401</v>
       </c>
       <c r="Y34">
-        <v>-0.00018355116897700159</v>
+        <v>-0.00018355116897699833</v>
       </c>
       <c r="Z34">
-        <v>-0.0030368046871220981</v>
+        <v>-0.0030368046871221436</v>
       </c>
       <c r="AA34">
-        <v>-0.0029087018043451578</v>
+        <v>-0.0029087018043451977</v>
       </c>
       <c r="AB34">
-        <v>-0.0028667674330144039</v>
+        <v>-0.0028667674330144456</v>
       </c>
       <c r="AC34">
-        <v>-0.0028181773427799263</v>
+        <v>-0.0028181773427799692</v>
       </c>
       <c r="AD34">
-        <v>-0.0030305872269813412</v>
+        <v>-0.003030587226981382</v>
       </c>
       <c r="AE34">
-        <v>-0.0028833015366855784</v>
+        <v>-0.00288330153668562</v>
       </c>
       <c r="AF34">
-        <v>-0.00011321363707010669</v>
+        <v>-0.00011321363707010979</v>
       </c>
       <c r="AG34">
-        <v>7.4687898885440079e-06</v>
+        <v>7.4687898885519226e-06</v>
       </c>
       <c r="AH34">
-        <v>0.00024089133971755663</v>
+        <v>0.00024089133971756486</v>
       </c>
       <c r="AI34">
-        <v>0.019747248539181292</v>
+        <v>0.019747248539181771</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_home_ownership.xlsx
+++ b/input/ES/reg_home_ownership.xlsx
@@ -41,7 +41,7 @@
     <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
   </si>
   <si>
-    <t>15 June 2016 AK</t>
+    <t>07 Oct. 2026 AK</t>
   </si>
   <si>
     <t>Description:</t>
@@ -62,7 +62,7 @@
     <t>Goodnessoffit</t>
   </si>
   <si>
-    <t>HO1 - Home ownership</t>
+    <t>HO1 - Own home</t>
   </si>
   <si>
     <t>Pseudo R-squared</t>
@@ -305,7 +305,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -344,40 +344,34 @@
       <c r="F3"/>
     </row>
     <row r="4">
-      <c r="B4"/>
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>0.82462702602528459</v>
+      </c>
       <c r="C4"/>
       <c r="D4"/>
-      <c r="F4"/>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>34533.017929957103</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5">
-        <v>0.82462702602528459</v>
+        <v>178084</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>34533.017929957103</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6">
-        <v>178084</v>
-      </c>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6">
         <v>-21085708.007565789</v>
       </c>
     </row>
@@ -508,100 +502,100 @@
         <v>0.00044992553030662381</v>
       </c>
       <c r="D2">
-        <v>8.5196106026389927e-05</v>
+        <v>8.5196106026389222e-05</v>
       </c>
       <c r="E2">
-        <v>-6.2828630875756355e-05</v>
+        <v>-6.2828630875756857e-05</v>
       </c>
       <c r="F2">
-        <v>-8.4565668852783889e-06</v>
+        <v>-8.4565668852784262e-06</v>
       </c>
       <c r="G2">
-        <v>-0.00010843423021864604</v>
+        <v>-0.00010843423021864664</v>
       </c>
       <c r="H2">
-        <v>-0.00010596516053969373</v>
+        <v>-0.00010596516053969427</v>
       </c>
       <c r="I2">
-        <v>0.00011732840928460902</v>
+        <v>0.00011732840928460846</v>
       </c>
       <c r="J2">
-        <v>0.00018803916794095035</v>
+        <v>0.00018803916794094986</v>
       </c>
       <c r="K2">
-        <v>5.1197771764612237e-06</v>
+        <v>5.1197771764612373e-06</v>
       </c>
       <c r="L2">
-        <v>-4.2400694082287739e-05</v>
+        <v>-4.2400694082288742e-05</v>
       </c>
       <c r="M2">
-        <v>-6.0906119824910264e-05</v>
+        <v>-6.09061198249104e-05</v>
       </c>
       <c r="N2">
-        <v>-3.3613221852301075e-05</v>
+        <v>-3.3613221852301197e-05</v>
       </c>
       <c r="O2">
-        <v>-4.8211227158035095e-05</v>
+        <v>-4.8211227158035352e-05</v>
       </c>
       <c r="P2">
-        <v>0.00015964187899656515</v>
+        <v>0.0001596418789965655</v>
       </c>
       <c r="Q2">
-        <v>-2.9367506558323816e-05</v>
+        <v>-2.9367506558325781e-05</v>
       </c>
       <c r="R2">
-        <v>-5.3783345333062239e-05</v>
+        <v>-5.3783345333062266e-05</v>
       </c>
       <c r="S2">
-        <v>-0.00011313088460214739</v>
+        <v>-0.00011313088460214937</v>
       </c>
       <c r="T2">
-        <v>3.3585706081016427e-07</v>
+        <v>3.3585706081015749e-07</v>
       </c>
       <c r="U2">
-        <v>3.8978001937107882e-05</v>
+        <v>3.897800193710734e-05</v>
       </c>
       <c r="V2">
-        <v>-1.4297628366294248e-06</v>
+        <v>-1.4297628366304819e-06</v>
       </c>
       <c r="W2">
-        <v>-5.9422502834600118e-05</v>
+        <v>-5.9422502834600836e-05</v>
       </c>
       <c r="X2">
-        <v>-4.8028132579072198e-07</v>
+        <v>-4.802813257906881e-07</v>
       </c>
       <c r="Y2">
-        <v>-3.1834493471115865e-05</v>
+        <v>-3.1834493471115879e-05</v>
       </c>
       <c r="Z2">
-        <v>-8.1085924364914826e-05</v>
+        <v>-8.108592436491526e-05</v>
       </c>
       <c r="AA2">
-        <v>-8.7021960423897508e-05</v>
+        <v>-8.7021960423897996e-05</v>
       </c>
       <c r="AB2">
-        <v>-9.2596972208624809e-05</v>
+        <v>-9.2596972208625297e-05</v>
       </c>
       <c r="AC2">
-        <v>-0.00010856841590938695</v>
+        <v>-0.00010856841590938744</v>
       </c>
       <c r="AD2">
-        <v>-6.3819334106375602e-05</v>
+        <v>-6.381933410637609e-05</v>
       </c>
       <c r="AE2">
-        <v>-4.7641209485679661e-06</v>
+        <v>-4.7641209485683879e-06</v>
       </c>
       <c r="AF2">
-        <v>-1.9497710287320125e-06</v>
+        <v>-1.9497710287320363e-06</v>
       </c>
       <c r="AG2">
         <v>8.2682461790918268e-05</v>
       </c>
       <c r="AH2">
-        <v>1.3097791130418568e-05</v>
+        <v>1.3097791130418758e-05</v>
       </c>
       <c r="AI2">
-        <v>-7.2034827626278066e-05</v>
+        <v>-7.2034827626273621e-05</v>
       </c>
     </row>
     <row r="3">
@@ -612,103 +606,103 @@
         <v>0.12681895963208956</v>
       </c>
       <c r="C3">
-        <v>8.5196106026389927e-05</v>
+        <v>8.5196106026389222e-05</v>
       </c>
       <c r="D3">
         <v>0.15220756463936075</v>
       </c>
       <c r="E3">
-        <v>0.0020843969237603283</v>
+        <v>0.0020843969237603218</v>
       </c>
       <c r="F3">
-        <v>0.0016882452590597011</v>
+        <v>0.0016882452590597013</v>
       </c>
       <c r="G3">
-        <v>0.0024417879512850195</v>
+        <v>0.0024417879512850134</v>
       </c>
       <c r="H3">
-        <v>0.0021134510801234241</v>
+        <v>0.002113451080123418</v>
       </c>
       <c r="I3">
-        <v>0.0019828406336589123</v>
+        <v>0.0019828406336589058</v>
       </c>
       <c r="J3">
-        <v>0.0020871683533679438</v>
+        <v>0.0020871683533679373</v>
       </c>
       <c r="K3">
-        <v>-2.0115308488016619e-05</v>
+        <v>-2.0115308488016835e-05</v>
       </c>
       <c r="L3">
-        <v>0.0001862923207223358</v>
+        <v>0.00018629232072232181</v>
       </c>
       <c r="M3">
-        <v>0.00027309987750996309</v>
+        <v>0.00027309987750996243</v>
       </c>
       <c r="N3">
-        <v>3.4154957573525626e-05</v>
+        <v>3.4154957573523891e-05</v>
       </c>
       <c r="O3">
-        <v>0.00017304750110305598</v>
+        <v>0.00017304750110305238</v>
       </c>
       <c r="P3">
-        <v>0.00024098226622749843</v>
+        <v>0.00024098226622749647</v>
       </c>
       <c r="Q3">
-        <v>0.00020490888816182367</v>
+        <v>0.00020490888816179624</v>
       </c>
       <c r="R3">
-        <v>0.00013961429365074959</v>
+        <v>0.00013961429365074899</v>
       </c>
       <c r="S3">
-        <v>0.00035347518107978909</v>
+        <v>0.00035347518107976144</v>
       </c>
       <c r="T3">
-        <v>-1.9174180004385085e-05</v>
+        <v>-1.9174180004385329e-05</v>
       </c>
       <c r="U3">
-        <v>-3.2793598063814329e-05</v>
+        <v>-3.2793598063820834e-05</v>
       </c>
       <c r="V3">
-        <v>0.00034904637853420397</v>
+        <v>0.00034904637853419075</v>
       </c>
       <c r="W3">
-        <v>0.000805197453045594</v>
+        <v>0.0008051974530455799</v>
       </c>
       <c r="X3">
-        <v>-7.8230614138232163e-06</v>
+        <v>-7.8230614138227945e-06</v>
       </c>
       <c r="Y3">
-        <v>0.00033228372241895908</v>
+        <v>0.00033228372241895859</v>
       </c>
       <c r="Z3">
-        <v>0.00014280146279555895</v>
+        <v>0.00014280146279555439</v>
       </c>
       <c r="AA3">
-        <v>0.0010716454027064983</v>
+        <v>0.0010716454027064914</v>
       </c>
       <c r="AB3">
-        <v>0.0007563371623317696</v>
+        <v>0.00075633716233176255</v>
       </c>
       <c r="AC3">
-        <v>0.00013931877986971463</v>
+        <v>0.00013931877986970748</v>
       </c>
       <c r="AD3">
-        <v>0.0001381999711547124</v>
+        <v>0.00013819997115470568</v>
       </c>
       <c r="AE3">
-        <v>2.6842920995656433e-05</v>
+        <v>2.6842920995652259e-05</v>
       </c>
       <c r="AF3">
-        <v>-8.510155342638653e-06</v>
+        <v>-8.5101553426391137e-06</v>
       </c>
       <c r="AG3">
-        <v>5.4247913094002641e-05</v>
+        <v>5.4247913094003508e-05</v>
       </c>
       <c r="AH3">
-        <v>0.0013306349657106369</v>
+        <v>0.0013306349657106393</v>
       </c>
       <c r="AI3">
-        <v>-0.0029610538351408063</v>
+        <v>-0.0029610538351407534</v>
       </c>
     </row>
     <row r="4">
@@ -719,103 +713,103 @@
         <v>0.03595234274131201</v>
       </c>
       <c r="C4">
-        <v>-6.2828630875756355e-05</v>
+        <v>-6.2828630875756857e-05</v>
       </c>
       <c r="D4">
-        <v>0.0020843969237603283</v>
+        <v>0.0020843969237603218</v>
       </c>
       <c r="E4">
-        <v>0.0026441163376976738</v>
+        <v>0.0026441163376976682</v>
       </c>
       <c r="F4">
-        <v>0.0018128197573376375</v>
+        <v>0.0018128197573376377</v>
       </c>
       <c r="G4">
-        <v>0.0020642741812238186</v>
+        <v>0.0020642741812238129</v>
       </c>
       <c r="H4">
-        <v>0.0020977832497201827</v>
+        <v>0.002097783249720177</v>
       </c>
       <c r="I4">
-        <v>0.0021085718188296331</v>
+        <v>0.0021085718188296279</v>
       </c>
       <c r="J4">
-        <v>0.0021090443932507631</v>
+        <v>0.0021090443932507575</v>
       </c>
       <c r="K4">
-        <v>1.4118593225052661e-05</v>
+        <v>1.4118593225053095e-05</v>
       </c>
       <c r="L4">
-        <v>-9.3260023870260489e-05</v>
+        <v>-9.3260023870271819e-05</v>
       </c>
       <c r="M4">
-        <v>0.00011537275032906373</v>
+        <v>0.00011537275032906286</v>
       </c>
       <c r="N4">
-        <v>0.00013157663846053829</v>
+        <v>0.00013157663846053686</v>
       </c>
       <c r="O4">
-        <v>9.2101658019674547e-05</v>
+        <v>9.2101658019671362e-05</v>
       </c>
       <c r="P4">
-        <v>0.00025685583857602715</v>
+        <v>0.00025685583857602736</v>
       </c>
       <c r="Q4">
-        <v>7.6911989027287839e-05</v>
+        <v>7.6911989027264745e-05</v>
       </c>
       <c r="R4">
-        <v>5.8410909162392619e-05</v>
+        <v>5.8410909162393053e-05</v>
       </c>
       <c r="S4">
-        <v>0.00011723908016812289</v>
+        <v>0.00011723908016810012</v>
       </c>
       <c r="T4">
-        <v>7.8675240484074415e-05</v>
+        <v>7.867524048407455e-05</v>
       </c>
       <c r="U4">
-        <v>9.0123156531717605e-05</v>
+        <v>9.0123156531713268e-05</v>
       </c>
       <c r="V4">
-        <v>0.00023564401616688263</v>
+        <v>0.00023564401616687136</v>
       </c>
       <c r="W4">
-        <v>0.0007293957933247996</v>
+        <v>0.00072939579332478789</v>
       </c>
       <c r="X4">
-        <v>-3.1864712784610176e-05</v>
+        <v>-3.186471278460981e-05</v>
       </c>
       <c r="Y4">
-        <v>-6.7136134926303558e-05</v>
+        <v>-6.7136134926303937e-05</v>
       </c>
       <c r="Z4">
-        <v>0.00010394145986338931</v>
+        <v>0.00010394145986338584</v>
       </c>
       <c r="AA4">
-        <v>8.7703738193669126e-05</v>
+        <v>8.7703738193663271e-05</v>
       </c>
       <c r="AB4">
-        <v>0.00010743254938750703</v>
+        <v>0.00010743254938750139</v>
       </c>
       <c r="AC4">
-        <v>4.3360577271755454e-05</v>
+        <v>4.3360577271749599e-05</v>
       </c>
       <c r="AD4">
-        <v>6.5902518832282645e-05</v>
+        <v>6.590251883227679e-05</v>
       </c>
       <c r="AE4">
-        <v>-1.1316323787101472e-05</v>
+        <v>-1.1316323787104453e-05</v>
       </c>
       <c r="AF4">
-        <v>5.5397297790910622e-06</v>
+        <v>5.5397297790906963e-06</v>
       </c>
       <c r="AG4">
-        <v>-3.478174268162779e-05</v>
+        <v>-3.4781742681626923e-05</v>
       </c>
       <c r="AH4">
-        <v>2.9482721689708916e-05</v>
+        <v>2.9482721689711084e-05</v>
       </c>
       <c r="AI4">
-        <v>-0.0024047977311919999</v>
+        <v>-0.0024047977311919557</v>
       </c>
     </row>
     <row r="5">
@@ -826,103 +820,103 @@
         <v>-0.076810395035844345</v>
       </c>
       <c r="C5">
-        <v>-8.4565668852783889e-06</v>
+        <v>-8.4565668852784262e-06</v>
       </c>
       <c r="D5">
-        <v>0.0016882452590597011</v>
+        <v>0.0016882452590597013</v>
       </c>
       <c r="E5">
-        <v>0.0018128197573376375</v>
+        <v>0.0018128197573376377</v>
       </c>
       <c r="F5">
         <v>0.0028941737281210829</v>
       </c>
       <c r="G5">
-        <v>0.0018612724534218779</v>
+        <v>0.0018612724534218727</v>
       </c>
       <c r="H5">
-        <v>0.0018492289694546213</v>
+        <v>0.0018492289694546165</v>
       </c>
       <c r="I5">
-        <v>0.001802882282930165</v>
+        <v>0.00180288228293016</v>
       </c>
       <c r="J5">
-        <v>0.0017667256002488528</v>
+        <v>0.0017667256002488478</v>
       </c>
       <c r="K5">
-        <v>0.00010379590554003039</v>
+        <v>0.00010379590554003061</v>
       </c>
       <c r="L5">
-        <v>9.6185840505550211e-05</v>
+        <v>9.6185840505540101e-05</v>
       </c>
       <c r="M5">
-        <v>8.1680466308314218e-05</v>
+        <v>8.1680466308313568e-05</v>
       </c>
       <c r="N5">
-        <v>0.00012419560983465032</v>
+        <v>0.00012419560983464905</v>
       </c>
       <c r="O5">
-        <v>0.00011222399271491425</v>
+        <v>0.00011222399271491151</v>
       </c>
       <c r="P5">
         <v>2.6036874602808802e-05</v>
       </c>
       <c r="Q5">
-        <v>3.0606587825537783e-05</v>
+        <v>3.0606587825516966e-05</v>
       </c>
       <c r="R5">
-        <v>-5.2813169842945993e-06</v>
+        <v>-5.2813169842943824e-06</v>
       </c>
       <c r="S5">
-        <v>2.2049062175289933e-05</v>
+        <v>2.2049062175269008e-05</v>
       </c>
       <c r="T5">
-        <v>3.3185996693463644e-05</v>
+        <v>3.318599669346378e-05</v>
       </c>
       <c r="U5">
-        <v>4.7592016809201655e-05</v>
+        <v>4.7592016809197427e-05</v>
       </c>
       <c r="V5">
-        <v>6.0529809379003194e-05</v>
+        <v>6.0529809378992785e-05</v>
       </c>
       <c r="W5">
-        <v>0.00035402050081692485</v>
+        <v>0.00035402050081691455</v>
       </c>
       <c r="X5">
-        <v>-1.1239453734116243e-05</v>
+        <v>-1.1239453734115928e-05</v>
       </c>
       <c r="Y5">
-        <v>-4.883454486433376e-05</v>
+        <v>-4.8834544864334085e-05</v>
       </c>
       <c r="Z5">
-        <v>0.00011191749201080623</v>
+        <v>0.00011191749201080342</v>
       </c>
       <c r="AA5">
-        <v>7.3842847933297973e-06</v>
+        <v>7.3842847933245932e-06</v>
       </c>
       <c r="AB5">
-        <v>5.2590944147573203e-05</v>
+        <v>5.2590944147567998e-05</v>
       </c>
       <c r="AC5">
-        <v>-2.1056099340469427e-05</v>
+        <v>-2.1056099340474848e-05</v>
       </c>
       <c r="AD5">
-        <v>-5.3059972264900691e-06</v>
+        <v>-5.3059972264953275e-06</v>
       </c>
       <c r="AE5">
-        <v>-7.2812817573086278e-05</v>
+        <v>-7.2812817573089097e-05</v>
       </c>
       <c r="AF5">
-        <v>2.3800320149091234e-06</v>
+        <v>2.3800320149087914e-06</v>
       </c>
       <c r="AG5">
-        <v>0.00011273175229523005</v>
+        <v>0.00011273175229523048</v>
       </c>
       <c r="AH5">
-        <v>7.0103091909827909e-05</v>
+        <v>7.0103091909829969e-05</v>
       </c>
       <c r="AI5">
-        <v>-0.0020326920215608581</v>
+        <v>-0.0020326920215608178</v>
       </c>
     </row>
     <row r="6">
@@ -933,103 +927,103 @@
         <v>0.16250526351603703</v>
       </c>
       <c r="C6">
-        <v>-0.00010843423021864604</v>
+        <v>-0.00010843423021864664</v>
       </c>
       <c r="D6">
-        <v>0.0024417879512850195</v>
+        <v>0.0024417879512850134</v>
       </c>
       <c r="E6">
-        <v>0.0020642741812238186</v>
+        <v>0.0020642741812238129</v>
       </c>
       <c r="F6">
-        <v>0.0018612724534218779</v>
+        <v>0.0018612724534218727</v>
       </c>
       <c r="G6">
-        <v>0.057488003405249455</v>
+        <v>0.057488003405249448</v>
       </c>
       <c r="H6">
-        <v>0.0022753072320951104</v>
+        <v>0.0022753072320951043</v>
       </c>
       <c r="I6">
-        <v>0.0019912929991474718</v>
+        <v>0.0019912929991474653</v>
       </c>
       <c r="J6">
-        <v>0.0021086397979223448</v>
+        <v>0.0021086397979223378</v>
       </c>
       <c r="K6">
         <v>0.0004991621535854222</v>
       </c>
       <c r="L6">
-        <v>0.00044981848966823651</v>
+        <v>0.00044981848966822236</v>
       </c>
       <c r="M6">
-        <v>0.0001863328342747504</v>
+        <v>0.00018633283427474954</v>
       </c>
       <c r="N6">
-        <v>0.00027573964584833504</v>
+        <v>0.00027573964584833331</v>
       </c>
       <c r="O6">
-        <v>0.00028512265825971189</v>
+        <v>0.0002851226582597082</v>
       </c>
       <c r="P6">
-        <v>-5.398446899316687e-05</v>
+        <v>-5.3984468993169255e-05</v>
       </c>
       <c r="Q6">
-        <v>6.9483088424646795e-05</v>
+        <v>6.9483088424618714e-05</v>
       </c>
       <c r="R6">
-        <v>-4.2746946247127664e-05</v>
+        <v>-4.2746946247128749e-05</v>
       </c>
       <c r="S6">
-        <v>0.00010537693199462651</v>
+        <v>0.00010537693199459762</v>
       </c>
       <c r="T6">
-        <v>0.00013915368209564504</v>
+        <v>0.00013915368209564482</v>
       </c>
       <c r="U6">
-        <v>0.00021119581025746525</v>
+        <v>0.00021119581025745874</v>
       </c>
       <c r="V6">
-        <v>0.00054653907747108572</v>
+        <v>0.00054653907747107293</v>
       </c>
       <c r="W6">
-        <v>0.0012059413454082583</v>
+        <v>0.0012059413454082453</v>
       </c>
       <c r="X6">
-        <v>-4.7557013707125826e-05</v>
+        <v>-4.7557013707125406e-05</v>
       </c>
       <c r="Y6">
-        <v>0.00012877618346038988</v>
+        <v>0.00012877618346038934</v>
       </c>
       <c r="Z6">
-        <v>0.00020423090026066562</v>
+        <v>0.00020423090026066106</v>
       </c>
       <c r="AA6">
-        <v>6.1444208924468779e-05</v>
+        <v>6.1444208924462274e-05</v>
       </c>
       <c r="AB6">
-        <v>0.00012310858855484356</v>
+        <v>0.00012310858855483641</v>
       </c>
       <c r="AC6">
-        <v>6.6073099431151507e-05</v>
+        <v>6.6073099431144568e-05</v>
       </c>
       <c r="AD6">
-        <v>2.233402750616547e-05</v>
+        <v>2.2334027506158748e-05</v>
       </c>
       <c r="AE6">
-        <v>-3.5116145501637398e-05</v>
+        <v>-3.5116145501641518e-05</v>
       </c>
       <c r="AF6">
-        <v>1.0130120580752258e-05</v>
+        <v>1.0130120580751824e-05</v>
       </c>
       <c r="AG6">
-        <v>-0.00013755789499182583</v>
+        <v>-0.00013755789499182497</v>
       </c>
       <c r="AH6">
-        <v>7.94450703574237e-05</v>
+        <v>7.9445070357426519e-05</v>
       </c>
       <c r="AI6">
-        <v>-0.0029729672163785214</v>
+        <v>-0.0029729672163784711</v>
       </c>
     </row>
     <row r="7">
@@ -1040,103 +1034,103 @@
         <v>-0.22492068207238639</v>
       </c>
       <c r="C7">
-        <v>-0.00010596516053969373</v>
+        <v>-0.00010596516053969427</v>
       </c>
       <c r="D7">
-        <v>0.0021134510801234241</v>
+        <v>0.002113451080123418</v>
       </c>
       <c r="E7">
-        <v>0.0020977832497201827</v>
+        <v>0.002097783249720177</v>
       </c>
       <c r="F7">
-        <v>0.0018492289694546213</v>
+        <v>0.0018492289694546165</v>
       </c>
       <c r="G7">
-        <v>0.0022753072320951104</v>
+        <v>0.0022753072320951043</v>
       </c>
       <c r="H7">
-        <v>0.0031113177501820698</v>
+        <v>0.0031113177501820629</v>
       </c>
       <c r="I7">
-        <v>0.0020203654061571588</v>
+        <v>0.0020203654061571527</v>
       </c>
       <c r="J7">
-        <v>0.0021083988136712272</v>
+        <v>0.0021083988136712212</v>
       </c>
       <c r="K7">
-        <v>0.00039531652231037046</v>
+        <v>0.00039531652231037089</v>
       </c>
       <c r="L7">
-        <v>0.00038087372306955822</v>
+        <v>0.00038087372306954515</v>
       </c>
       <c r="M7">
-        <v>0.00011825463761075037</v>
+        <v>0.0001182546376107495</v>
       </c>
       <c r="N7">
-        <v>0.000166607646442418</v>
+        <v>0.00016660764644241635</v>
       </c>
       <c r="O7">
-        <v>0.00010625670043667934</v>
+        <v>0.00010625670043667587</v>
       </c>
       <c r="P7">
-        <v>2.4952126135464555e-05</v>
+        <v>2.495212613546423e-05</v>
       </c>
       <c r="Q7">
-        <v>1.6276286502292341e-06</v>
+        <v>1.6276286502025627e-06</v>
       </c>
       <c r="R7">
-        <v>-3.8034219591042448e-05</v>
+        <v>-3.8034219591042339e-05</v>
       </c>
       <c r="S7">
-        <v>3.1047612534881083e-05</v>
+        <v>3.1047612534853815e-05</v>
       </c>
       <c r="T7">
-        <v>0.0001313035229106804</v>
+        <v>0.00013130352291068056</v>
       </c>
       <c r="U7">
-        <v>0.00014664378215090254</v>
+        <v>0.00014664378215089647</v>
       </c>
       <c r="V7">
-        <v>0.00051188472275485487</v>
+        <v>0.0005118847227548423</v>
       </c>
       <c r="W7">
-        <v>0.0010635742589028341</v>
+        <v>0.0010635742589028211</v>
       </c>
       <c r="X7">
-        <v>-2.6566527801927329e-05</v>
+        <v>-2.6566527801926923e-05</v>
       </c>
       <c r="Y7">
-        <v>-1.8494888706544908e-05</v>
+        <v>-1.8494888706545396e-05</v>
       </c>
       <c r="Z7">
-        <v>0.00022190153581251983</v>
+        <v>0.00022190153581251528</v>
       </c>
       <c r="AA7">
-        <v>0.00014698745143088671</v>
+        <v>0.00014698745143088021</v>
       </c>
       <c r="AB7">
-        <v>0.00017526084095629484</v>
+        <v>0.00017526084095628811</v>
       </c>
       <c r="AC7">
-        <v>9.9242546054503084e-05</v>
+        <v>9.9242546054496145e-05</v>
       </c>
       <c r="AD7">
-        <v>0.00011251699848730922</v>
+        <v>0.00011251699848730256</v>
       </c>
       <c r="AE7">
-        <v>-6.664141507371497e-06</v>
+        <v>-6.6641415073755085e-06</v>
       </c>
       <c r="AF7">
-        <v>1.4003597577925736e-05</v>
+        <v>1.4003597577925309e-05</v>
       </c>
       <c r="AG7">
-        <v>-8.677864140106727e-05</v>
+        <v>-8.6778641401066403e-05</v>
       </c>
       <c r="AH7">
-        <v>6.0970632979297701e-05</v>
+        <v>6.0970632979300519e-05</v>
       </c>
       <c r="AI7">
-        <v>-0.0028559799727097693</v>
+        <v>-0.0028559799727097212</v>
       </c>
     </row>
     <row r="8">
@@ -1147,103 +1141,103 @@
         <v>-0.1529704486597758</v>
       </c>
       <c r="C8">
-        <v>0.00011732840928460902</v>
+        <v>0.00011732840928460846</v>
       </c>
       <c r="D8">
-        <v>0.0019828406336589123</v>
+        <v>0.0019828406336589058</v>
       </c>
       <c r="E8">
-        <v>0.0021085718188296331</v>
+        <v>0.0021085718188296279</v>
       </c>
       <c r="F8">
-        <v>0.001802882282930165</v>
+        <v>0.00180288228293016</v>
       </c>
       <c r="G8">
-        <v>0.0019912929991474718</v>
+        <v>0.0019912929991474653</v>
       </c>
       <c r="H8">
-        <v>0.0020203654061571588</v>
+        <v>0.0020203654061571527</v>
       </c>
       <c r="I8">
-        <v>0.0023630518918623623</v>
+        <v>0.0023630518918623567</v>
       </c>
       <c r="J8">
-        <v>0.0021630154235348989</v>
+        <v>0.0021630154235348933</v>
       </c>
       <c r="K8">
-        <v>-9.6477412201952453e-05</v>
+        <v>-9.6477412201952236e-05</v>
       </c>
       <c r="L8">
-        <v>-6.2624319062000184e-05</v>
+        <v>-6.2624319062011893e-05</v>
       </c>
       <c r="M8">
-        <v>8.9623365210411872e-05</v>
+        <v>8.9623365210411222e-05</v>
       </c>
       <c r="N8">
-        <v>0.00012382017728426056</v>
+        <v>0.00012382017728425907</v>
       </c>
       <c r="O8">
-        <v>0.00012507577302552959</v>
+        <v>0.00012507577302552645</v>
       </c>
       <c r="P8">
-        <v>0.0001212107914061668</v>
+        <v>0.00012121079140616701</v>
       </c>
       <c r="Q8">
-        <v>-5.1614434371389508e-06</v>
+        <v>-5.1614434371626949e-06</v>
       </c>
       <c r="R8">
-        <v>-2.4039909615042798e-05</v>
+        <v>-2.4039909615042364e-05</v>
       </c>
       <c r="S8">
-        <v>-3.7246413667954385e-05</v>
+        <v>-3.7246413667977967e-05</v>
       </c>
       <c r="T8">
-        <v>9.1079901964069663e-05</v>
+        <v>9.1079901964069798e-05</v>
       </c>
       <c r="U8">
-        <v>0.00022175602752185462</v>
+        <v>0.00022175602752184942</v>
       </c>
       <c r="V8">
-        <v>0.00035138499279763918</v>
+        <v>0.0003513849927976279</v>
       </c>
       <c r="W8">
-        <v>0.00076954334989701731</v>
+        <v>0.00076954334989700539</v>
       </c>
       <c r="X8">
-        <v>-3.6324449322708611e-05</v>
+        <v>-3.6324449322708231e-05</v>
       </c>
       <c r="Y8">
-        <v>-8.8974886706918684e-05</v>
+        <v>-8.8974886706919064e-05</v>
       </c>
       <c r="Z8">
-        <v>5.2854459322041088e-05</v>
+        <v>5.2854459322038052e-05</v>
       </c>
       <c r="AA8">
-        <v>3.2123447875537442e-05</v>
+        <v>3.2123447875531371e-05</v>
       </c>
       <c r="AB8">
-        <v>5.3620247030806501e-05</v>
+        <v>5.3620247030800646e-05</v>
       </c>
       <c r="AC8">
-        <v>-1.54596361731259e-05</v>
+        <v>-1.5459636173131754e-05</v>
       </c>
       <c r="AD8">
-        <v>3.2777159819310836e-05</v>
+        <v>3.2777159819304764e-05</v>
       </c>
       <c r="AE8">
-        <v>2.4805335383808186e-05</v>
+        <v>2.4805335383805286e-05</v>
       </c>
       <c r="AF8">
-        <v>2.8167527087335329e-06</v>
+        <v>2.816752708733167e-06</v>
       </c>
       <c r="AG8">
-        <v>4.6806591355711726e-06</v>
+        <v>4.6806591355720399e-06</v>
       </c>
       <c r="AH8">
-        <v>3.7243755954834818e-05</v>
+        <v>3.7243755954837095e-05</v>
       </c>
       <c r="AI8">
-        <v>-0.0024133870012869878</v>
+        <v>-0.0024133870012869427</v>
       </c>
     </row>
     <row r="9">
@@ -1254,103 +1248,103 @@
         <v>-0.36025040732867963</v>
       </c>
       <c r="C9">
-        <v>0.00018803916794095035</v>
+        <v>0.00018803916794094986</v>
       </c>
       <c r="D9">
-        <v>0.0020871683533679438</v>
+        <v>0.0020871683533679373</v>
       </c>
       <c r="E9">
-        <v>0.0021090443932507631</v>
+        <v>0.0021090443932507575</v>
       </c>
       <c r="F9">
-        <v>0.0017667256002488528</v>
+        <v>0.0017667256002488478</v>
       </c>
       <c r="G9">
-        <v>0.0021086397979223448</v>
+        <v>0.0021086397979223378</v>
       </c>
       <c r="H9">
-        <v>0.0021083988136712272</v>
+        <v>0.0021083988136712212</v>
       </c>
       <c r="I9">
-        <v>0.0021630154235348989</v>
+        <v>0.0021630154235348933</v>
       </c>
       <c r="J9">
-        <v>0.0042791945053281336</v>
+        <v>0.0042791945053281275</v>
       </c>
       <c r="K9">
-        <v>0.00017945082029096368</v>
+        <v>0.0001794508202909639</v>
       </c>
       <c r="L9">
-        <v>4.528357601119441e-05</v>
+        <v>4.5283576011180776e-05</v>
       </c>
       <c r="M9">
-        <v>4.9604585912205439e-05</v>
+        <v>4.9604585912204355e-05</v>
       </c>
       <c r="N9">
-        <v>4.7138664410989125e-05</v>
+        <v>4.7138664410987336e-05</v>
       </c>
       <c r="O9">
-        <v>5.7869774781333665e-05</v>
+        <v>5.7869774781330013e-05</v>
       </c>
       <c r="P9">
-        <v>0.00020041402999990848</v>
+        <v>0.00020041402999990804</v>
       </c>
       <c r="Q9">
-        <v>6.3657106405375671e-05</v>
+        <v>6.365710640534759e-05</v>
       </c>
       <c r="R9">
-        <v>-1.0902787355308852e-05</v>
+        <v>-1.0902787355308798e-05</v>
       </c>
       <c r="S9">
-        <v>-6.0940037529575038e-05</v>
+        <v>-6.0940037529603553e-05</v>
       </c>
       <c r="T9">
-        <v>6.999213058397506e-05</v>
+        <v>6.9992130583975169e-05</v>
       </c>
       <c r="U9">
-        <v>7.9251307881547098e-05</v>
+        <v>7.9251307881541026e-05</v>
       </c>
       <c r="V9">
-        <v>0.00043942370648207335</v>
+        <v>0.00043942370648206034</v>
       </c>
       <c r="W9">
-        <v>0.00077552129634349829</v>
+        <v>0.00077552129634348398</v>
       </c>
       <c r="X9">
-        <v>-3.8749522387691655e-05</v>
+        <v>-3.8749522387691228e-05</v>
       </c>
       <c r="Y9">
-        <v>-2.384510497773271e-05</v>
+        <v>-2.3845104977733252e-05</v>
       </c>
       <c r="Z9">
-        <v>0.00014993704661026355</v>
+        <v>0.00014993704661025922</v>
       </c>
       <c r="AA9">
-        <v>0.00012300481935885563</v>
+        <v>0.00012300481935884869</v>
       </c>
       <c r="AB9">
-        <v>7.6264365752973414e-05</v>
+        <v>7.6264365752966258e-05</v>
       </c>
       <c r="AC9">
-        <v>7.7531048207145131e-05</v>
+        <v>7.7531048207137758e-05</v>
       </c>
       <c r="AD9">
-        <v>0.00016385404757254807</v>
+        <v>0.00016385404757254108</v>
       </c>
       <c r="AE9">
-        <v>1.1865457425520377e-05</v>
+        <v>1.1865457425516121e-05</v>
       </c>
       <c r="AF9">
-        <v>2.2537754202515888e-06</v>
+        <v>2.2537754202511416e-06</v>
       </c>
       <c r="AG9">
-        <v>0.00015386211925594393</v>
+        <v>0.0001538621192559448</v>
       </c>
       <c r="AH9">
-        <v>-2.3520691061545192e-05</v>
+        <v>-2.352069106154259e-05</v>
       </c>
       <c r="AI9">
-        <v>-0.0025820961429938089</v>
+        <v>-0.0025820961429937582</v>
       </c>
     </row>
     <row r="10">
@@ -1361,103 +1355,103 @@
         <v>0.15737459156980077</v>
       </c>
       <c r="C10">
-        <v>5.1197771764612237e-06</v>
+        <v>5.1197771764612373e-06</v>
       </c>
       <c r="D10">
-        <v>-2.0115308488016619e-05</v>
+        <v>-2.0115308488016835e-05</v>
       </c>
       <c r="E10">
-        <v>1.4118593225052661e-05</v>
+        <v>1.4118593225053095e-05</v>
       </c>
       <c r="F10">
-        <v>0.00010379590554003039</v>
+        <v>0.00010379590554003061</v>
       </c>
       <c r="G10">
         <v>0.0004991621535854222</v>
       </c>
       <c r="H10">
-        <v>0.00039531652231037046</v>
+        <v>0.00039531652231037089</v>
       </c>
       <c r="I10">
-        <v>-9.6477412201952453e-05</v>
+        <v>-9.6477412201952236e-05</v>
       </c>
       <c r="J10">
-        <v>0.00017945082029096368</v>
+        <v>0.0001794508202909639</v>
       </c>
       <c r="K10">
         <v>0.0074102080942152811</v>
       </c>
       <c r="L10">
-        <v>0.0032290788500811923</v>
+        <v>0.0032290788500811771</v>
       </c>
       <c r="M10">
-        <v>-0.0040853893661426553</v>
+        <v>-0.0040853893661426562</v>
       </c>
       <c r="N10">
-        <v>7.6384446146619085e-05</v>
+        <v>7.6384446146617133e-05</v>
       </c>
       <c r="O10">
-        <v>0.00017008274704563168</v>
+        <v>0.00017008274704562781</v>
       </c>
       <c r="P10">
-        <v>0.00034860485841902724</v>
+        <v>0.000348604858419019</v>
       </c>
       <c r="Q10">
-        <v>9.7647707584657718e-05</v>
+        <v>9.764770758462194e-05</v>
       </c>
       <c r="R10">
-        <v>6.1269581888881127e-05</v>
+        <v>6.1269581888877332e-05</v>
       </c>
       <c r="S10">
-        <v>0.00016744100269598612</v>
+        <v>0.0001674410026959479</v>
       </c>
       <c r="T10">
-        <v>0.00063230654186256547</v>
+        <v>0.0006323065418625659</v>
       </c>
       <c r="U10">
-        <v>0.0032118980277105924</v>
+        <v>0.0032118980277105851</v>
       </c>
       <c r="V10">
-        <v>0.0036789130441664351</v>
+        <v>0.0036789130441664238</v>
       </c>
       <c r="W10">
-        <v>0.0039392190568509327</v>
+        <v>0.003939219056850918</v>
       </c>
       <c r="X10">
-        <v>-0.00016679003225496437</v>
+        <v>-0.00016679003225496402</v>
       </c>
       <c r="Y10">
-        <v>3.7762544182086649e-05</v>
+        <v>3.7762544182085836e-05</v>
       </c>
       <c r="Z10">
-        <v>0.0001868189980096433</v>
+        <v>0.00018681899800963549</v>
       </c>
       <c r="AA10">
-        <v>0.00010292825587061589</v>
+        <v>0.00010292825587060982</v>
       </c>
       <c r="AB10">
-        <v>7.9016028483075602e-05</v>
+        <v>7.9016028483066495e-05</v>
       </c>
       <c r="AC10">
-        <v>0.00015350771058333999</v>
+        <v>0.00015350771058333153</v>
       </c>
       <c r="AD10">
-        <v>0.00035701943319051686</v>
+        <v>0.00035701943319050916</v>
       </c>
       <c r="AE10">
-        <v>0.00021877282758949387</v>
+        <v>0.00021877282758948503</v>
       </c>
       <c r="AF10">
-        <v>-3.2565980408828582e-07</v>
+        <v>-3.2565980408889568e-07</v>
       </c>
       <c r="AG10">
-        <v>0.00037063543131517695</v>
+        <v>0.00037063543131517782</v>
       </c>
       <c r="AH10">
-        <v>-9.4744370399683486e-05</v>
+        <v>-9.4744370399680233e-05</v>
       </c>
       <c r="AI10">
-        <v>-0.0040142065628920171</v>
+        <v>-0.0040142065628919693</v>
       </c>
     </row>
     <row r="11">
@@ -1468,103 +1462,103 @@
         <v>0.083971588068680172</v>
       </c>
       <c r="C11">
-        <v>-4.2400694082287739e-05</v>
+        <v>-4.2400694082288742e-05</v>
       </c>
       <c r="D11">
-        <v>0.0001862923207223358</v>
+        <v>0.00018629232072232181</v>
       </c>
       <c r="E11">
-        <v>-9.3260023870260489e-05</v>
+        <v>-9.3260023870271819e-05</v>
       </c>
       <c r="F11">
-        <v>9.6185840505550211e-05</v>
+        <v>9.6185840505540101e-05</v>
       </c>
       <c r="G11">
-        <v>0.00044981848966823651</v>
+        <v>0.00044981848966822236</v>
       </c>
       <c r="H11">
-        <v>0.00038087372306955822</v>
+        <v>0.00038087372306954515</v>
       </c>
       <c r="I11">
-        <v>-6.2624319062000184e-05</v>
+        <v>-6.2624319062011893e-05</v>
       </c>
       <c r="J11">
-        <v>4.528357601119441e-05</v>
+        <v>4.5283576011180776e-05</v>
       </c>
       <c r="K11">
-        <v>0.0032290788500811923</v>
+        <v>0.0032290788500811771</v>
       </c>
       <c r="L11">
-        <v>0.0031002153941947137</v>
+        <v>0.0031002153941946972</v>
       </c>
       <c r="M11">
-        <v>-0.00041434020189944922</v>
+        <v>-0.00041434020189945009</v>
       </c>
       <c r="N11">
-        <v>0.00015482852411966605</v>
+        <v>0.00015482852411966399</v>
       </c>
       <c r="O11">
-        <v>8.21495962558784e-05</v>
+        <v>8.2149596255874253e-05</v>
       </c>
       <c r="P11">
-        <v>0.0003018571753258311</v>
+        <v>0.00030185717532582807</v>
       </c>
       <c r="Q11">
-        <v>0.00017023512700285585</v>
+        <v>0.00017023512700282094</v>
       </c>
       <c r="R11">
-        <v>0.00028235702247507617</v>
+        <v>0.00028235702247507449</v>
       </c>
       <c r="S11">
-        <v>0.00047732123564776666</v>
+        <v>0.00047732123564772492</v>
       </c>
       <c r="T11">
-        <v>0.00047289903568891465</v>
+        <v>0.00047289903568891475</v>
       </c>
       <c r="U11">
-        <v>0.002645496636413675</v>
+        <v>0.0026454966364136663</v>
       </c>
       <c r="V11">
-        <v>0.0030849932598246296</v>
+        <v>0.0030849932598246165</v>
       </c>
       <c r="W11">
-        <v>0.003325956849966759</v>
+        <v>0.0033259568499667417</v>
       </c>
       <c r="X11">
-        <v>-0.00014921956736978716</v>
+        <v>-0.00014921956736978667</v>
       </c>
       <c r="Y11">
-        <v>4.2739638244124894e-05</v>
+        <v>4.2739638244123918e-05</v>
       </c>
       <c r="Z11">
-        <v>4.4432803402155632e-05</v>
+        <v>4.4432803402147392e-05</v>
       </c>
       <c r="AA11">
-        <v>-5.0739540888778811e-05</v>
+        <v>-5.0739540888785316e-05</v>
       </c>
       <c r="AB11">
-        <v>-2.6403228015840947e-05</v>
+        <v>-2.6403228015850272e-05</v>
       </c>
       <c r="AC11">
-        <v>2.9783468960480498e-05</v>
+        <v>2.9783468960470957e-05</v>
       </c>
       <c r="AD11">
-        <v>0.00011865440852694214</v>
+        <v>0.00011865440852693368</v>
       </c>
       <c r="AE11">
-        <v>-5.0038669633645488e-05</v>
+        <v>-5.0038669633654487e-05</v>
       </c>
       <c r="AF11">
-        <v>1.0516857342269856e-05</v>
+        <v>1.0516857342269273e-05</v>
       </c>
       <c r="AG11">
-        <v>5.5955232594965317e-05</v>
+        <v>5.5955232594966618e-05</v>
       </c>
       <c r="AH11">
-        <v>-2.7635679664000023e-05</v>
+        <v>-2.7635679663996771e-05</v>
       </c>
       <c r="AI11">
-        <v>-0.0036131444182357572</v>
+        <v>-0.0036131444182357165</v>
       </c>
     </row>
     <row r="12">
@@ -1575,103 +1569,103 @@
         <v>-0.05101015186102266</v>
       </c>
       <c r="C12">
-        <v>-6.0906119824910264e-05</v>
+        <v>-6.09061198249104e-05</v>
       </c>
       <c r="D12">
-        <v>0.00027309987750996309</v>
+        <v>0.00027309987750996243</v>
       </c>
       <c r="E12">
-        <v>0.00011537275032906373</v>
+        <v>0.00011537275032906286</v>
       </c>
       <c r="F12">
-        <v>8.1680466308314218e-05</v>
+        <v>8.1680466308313568e-05</v>
       </c>
       <c r="G12">
-        <v>0.0001863328342747504</v>
+        <v>0.00018633283427474954</v>
       </c>
       <c r="H12">
-        <v>0.00011825463761075037</v>
+        <v>0.0001182546376107495</v>
       </c>
       <c r="I12">
-        <v>8.9623365210411872e-05</v>
+        <v>8.9623365210411222e-05</v>
       </c>
       <c r="J12">
-        <v>4.9604585912205439e-05</v>
+        <v>4.9604585912204355e-05</v>
       </c>
       <c r="K12">
-        <v>-0.0040853893661426553</v>
+        <v>-0.0040853893661426562</v>
       </c>
       <c r="L12">
-        <v>-0.00041434020189944922</v>
+        <v>-0.00041434020189945009</v>
       </c>
       <c r="M12">
         <v>0.0056550742588793567</v>
       </c>
       <c r="N12">
-        <v>0.00053972298045773558</v>
+        <v>0.00053972298045773537</v>
       </c>
       <c r="O12">
-        <v>0.00041312332789258098</v>
+        <v>0.0004131233278925806</v>
       </c>
       <c r="P12">
-        <v>0.0001570291672220638</v>
+        <v>0.00015702916722206596</v>
       </c>
       <c r="Q12">
-        <v>8.1640007173097549e-05</v>
+        <v>8.1640007173097834e-05</v>
       </c>
       <c r="R12">
-        <v>8.659241108307806e-05</v>
+        <v>8.6592411083080201e-05</v>
       </c>
       <c r="S12">
-        <v>7.2625568124509883e-05</v>
+        <v>7.2625568124506603e-05</v>
       </c>
       <c r="T12">
-        <v>-0.00021872529679949068</v>
+        <v>-0.00021872529679949106</v>
       </c>
       <c r="U12">
-        <v>-0.00055939481065233254</v>
+        <v>-0.00055939481065233319</v>
       </c>
       <c r="V12">
-        <v>-0.00045654085313738102</v>
+        <v>-0.00045654085313738275</v>
       </c>
       <c r="W12">
-        <v>-0.00033281241228975544</v>
+        <v>-0.00033281241228975722</v>
       </c>
       <c r="X12">
-        <v>1.3508018690001983e-05</v>
+        <v>1.3508018690002081e-05</v>
       </c>
       <c r="Y12">
-        <v>3.3516023083527584e-06</v>
+        <v>3.3516023083526975e-06</v>
       </c>
       <c r="Z12">
-        <v>5.3753552470534624e-06</v>
+        <v>5.375355247053354e-06</v>
       </c>
       <c r="AA12">
-        <v>-4.7040608925574498e-05</v>
+        <v>-4.7040608925575419e-05</v>
       </c>
       <c r="AB12">
-        <v>2.4527032191441208e-05</v>
+        <v>2.4527032191440829e-05</v>
       </c>
       <c r="AC12">
-        <v>-2.7358458102671876e-05</v>
+        <v>-2.7358458102672744e-05</v>
       </c>
       <c r="AD12">
-        <v>-7.4634030212138337e-05</v>
+        <v>-7.4634030212139259e-05</v>
       </c>
       <c r="AE12">
-        <v>-0.00015014202061696452</v>
+        <v>-0.00015014202061696492</v>
       </c>
       <c r="AF12">
-        <v>1.4859872921433194e-05</v>
+        <v>1.485987292143316e-05</v>
       </c>
       <c r="AG12">
-        <v>-0.0003083322232353533</v>
+        <v>-0.00030833222323535335</v>
       </c>
       <c r="AH12">
-        <v>-4.2100416755658744e-05</v>
+        <v>-4.2100416755658582e-05</v>
       </c>
       <c r="AI12">
-        <v>-0.00015965131485163692</v>
+        <v>-0.00015965131485164451</v>
       </c>
     </row>
     <row r="13">
@@ -1682,103 +1676,103 @@
         <v>-0.080449105696533005</v>
       </c>
       <c r="C13">
-        <v>-3.3613221852301075e-05</v>
+        <v>-3.3613221852301197e-05</v>
       </c>
       <c r="D13">
-        <v>3.4154957573525626e-05</v>
+        <v>3.4154957573523891e-05</v>
       </c>
       <c r="E13">
-        <v>0.00013157663846053829</v>
+        <v>0.00013157663846053686</v>
       </c>
       <c r="F13">
-        <v>0.00012419560983465032</v>
+        <v>0.00012419560983464905</v>
       </c>
       <c r="G13">
-        <v>0.00027573964584833504</v>
+        <v>0.00027573964584833331</v>
       </c>
       <c r="H13">
-        <v>0.000166607646442418</v>
+        <v>0.00016660764644241635</v>
       </c>
       <c r="I13">
-        <v>0.00012382017728426056</v>
+        <v>0.00012382017728425907</v>
       </c>
       <c r="J13">
-        <v>4.7138664410989125e-05</v>
+        <v>4.7138664410987336e-05</v>
       </c>
       <c r="K13">
-        <v>7.6384446146619085e-05</v>
+        <v>7.6384446146617133e-05</v>
       </c>
       <c r="L13">
-        <v>0.00015482852411966605</v>
+        <v>0.00015482852411966399</v>
       </c>
       <c r="M13">
-        <v>0.00053972298045773558</v>
+        <v>0.00053972298045773537</v>
       </c>
       <c r="N13">
-        <v>0.00085714983948552241</v>
+        <v>0.00085714983948552209</v>
       </c>
       <c r="O13">
-        <v>0.00042212863405599924</v>
+        <v>0.00042212863405599848</v>
       </c>
       <c r="P13">
-        <v>0.0002341418672939381</v>
+        <v>0.00023414186729393588</v>
       </c>
       <c r="Q13">
-        <v>3.994743296114258e-05</v>
+        <v>3.9947432961136997e-05</v>
       </c>
       <c r="R13">
-        <v>-1.967394473648407e-05</v>
+        <v>-1.9673944736483975e-05</v>
       </c>
       <c r="S13">
-        <v>4.0788415143506556e-05</v>
+        <v>4.0788415143500742e-05</v>
       </c>
       <c r="T13">
-        <v>-2.4394818592364416e-05</v>
+        <v>-2.4394818592364429e-05</v>
       </c>
       <c r="U13">
-        <v>0.00014571898141819425</v>
+        <v>0.00014571898141819284</v>
       </c>
       <c r="V13">
-        <v>0.00024170927075665923</v>
+        <v>0.0002417092707566563</v>
       </c>
       <c r="W13">
-        <v>0.00043867877034088393</v>
+        <v>0.00043867877034088062</v>
       </c>
       <c r="X13">
-        <v>-8.94504520294432e-06</v>
+        <v>-8.9450452029442691e-06</v>
       </c>
       <c r="Y13">
-        <v>2.5349901746123875e-06</v>
+        <v>2.5349901746122384e-06</v>
       </c>
       <c r="Z13">
-        <v>3.176840152892095e-05</v>
+        <v>3.1768401528920246e-05</v>
       </c>
       <c r="AA13">
-        <v>1.4427976619053114e-05</v>
+        <v>1.442797661905165e-05</v>
       </c>
       <c r="AB13">
-        <v>4.8685890455269767e-06</v>
+        <v>4.8685890455255673e-06</v>
       </c>
       <c r="AC13">
-        <v>1.6549667470977449e-05</v>
+        <v>1.654966747097604e-05</v>
       </c>
       <c r="AD13">
-        <v>1.0462524298721825e-05</v>
+        <v>1.0462524298720361e-05</v>
       </c>
       <c r="AE13">
-        <v>-2.3821879086439562e-05</v>
+        <v>-2.3821879086440985e-05</v>
       </c>
       <c r="AF13">
-        <v>5.6168139851843385e-06</v>
+        <v>5.6168139851841725e-06</v>
       </c>
       <c r="AG13">
-        <v>-9.8069252881486746e-05</v>
+        <v>-9.8069252881486529e-05</v>
       </c>
       <c r="AH13">
-        <v>-3.6525377833205295e-05</v>
+        <v>-3.6525377833204617e-05</v>
       </c>
       <c r="AI13">
-        <v>-0.00082028153442179996</v>
+        <v>-0.00082028153442178955</v>
       </c>
     </row>
     <row r="14">
@@ -1789,103 +1783,103 @@
         <v>-0.028886584725227402</v>
       </c>
       <c r="C14">
-        <v>-4.8211227158035095e-05</v>
+        <v>-4.8211227158035352e-05</v>
       </c>
       <c r="D14">
-        <v>0.00017304750110305598</v>
+        <v>0.00017304750110305238</v>
       </c>
       <c r="E14">
-        <v>9.2101658019674547e-05</v>
+        <v>9.2101658019671362e-05</v>
       </c>
       <c r="F14">
-        <v>0.00011222399271491425</v>
+        <v>0.00011222399271491151</v>
       </c>
       <c r="G14">
-        <v>0.00028512265825971189</v>
+        <v>0.0002851226582597082</v>
       </c>
       <c r="H14">
-        <v>0.00010625670043667934</v>
+        <v>0.00010625670043667587</v>
       </c>
       <c r="I14">
-        <v>0.00012507577302552959</v>
+        <v>0.00012507577302552645</v>
       </c>
       <c r="J14">
-        <v>5.7869774781333665e-05</v>
+        <v>5.7869774781330013e-05</v>
       </c>
       <c r="K14">
-        <v>0.00017008274704563168</v>
+        <v>0.00017008274704562781</v>
       </c>
       <c r="L14">
-        <v>8.21495962558784e-05</v>
+        <v>8.2149596255874253e-05</v>
       </c>
       <c r="M14">
-        <v>0.00041312332789258098</v>
+        <v>0.0004131233278925806</v>
       </c>
       <c r="N14">
-        <v>0.00042212863405599924</v>
+        <v>0.00042212863405599848</v>
       </c>
       <c r="O14">
-        <v>0.00078169302244828637</v>
+        <v>0.00078169302244828528</v>
       </c>
       <c r="P14">
-        <v>3.2044993063428642e-05</v>
+        <v>3.2044993063424143e-05</v>
       </c>
       <c r="Q14">
-        <v>0.00012321554516548573</v>
+        <v>0.00012321554516547755</v>
       </c>
       <c r="R14">
-        <v>0.0002163547499337467</v>
+        <v>0.00021635474993374665</v>
       </c>
       <c r="S14">
-        <v>0.00031014633916724515</v>
+        <v>0.00031014633916723712</v>
       </c>
       <c r="T14">
-        <v>2.4679496354270889e-05</v>
+        <v>2.4679496354270875e-05</v>
       </c>
       <c r="U14">
-        <v>0.00018782629432656311</v>
+        <v>0.00018782629432656116</v>
       </c>
       <c r="V14">
-        <v>0.00029188576739535514</v>
+        <v>0.00029188576739535123</v>
       </c>
       <c r="W14">
-        <v>0.00050573604431693945</v>
+        <v>0.0005057360443169349</v>
       </c>
       <c r="X14">
-        <v>-1.0285577321125419e-05</v>
+        <v>-1.0285577321125307e-05</v>
       </c>
       <c r="Y14">
-        <v>1.0451598659236752e-05</v>
+        <v>1.0451598659236589e-05</v>
       </c>
       <c r="Z14">
-        <v>7.8399976348820632e-05</v>
+        <v>7.8399976348818789e-05</v>
       </c>
       <c r="AA14">
-        <v>8.0597869771121947e-05</v>
+        <v>8.0597869771119887e-05</v>
       </c>
       <c r="AB14">
-        <v>0.0001031950601707424</v>
+        <v>0.00010319506017074034</v>
       </c>
       <c r="AC14">
-        <v>1.7201678399739488e-05</v>
+        <v>1.7201678399737428e-05</v>
       </c>
       <c r="AD14">
-        <v>6.7471731706364855e-05</v>
+        <v>6.7471731706362795e-05</v>
       </c>
       <c r="AE14">
-        <v>1.4188838300475437e-05</v>
+        <v>1.4188838300473384e-05</v>
       </c>
       <c r="AF14">
-        <v>9.5812939870467515e-06</v>
+        <v>9.5812939870465787e-06</v>
       </c>
       <c r="AG14">
-        <v>-8.9809283282528667e-05</v>
+        <v>-8.9809283282528234e-05</v>
       </c>
       <c r="AH14">
-        <v>-7.0967816654568961e-05</v>
+        <v>-7.0967816654568094e-05</v>
       </c>
       <c r="AI14">
-        <v>-0.0011770786664807545</v>
+        <v>-0.0011770786664807391</v>
       </c>
     </row>
     <row r="15">
@@ -1896,103 +1890,103 @@
         <v>-0.11485641027320445</v>
       </c>
       <c r="C15">
-        <v>0.00015964187899656515</v>
+        <v>0.0001596418789965655</v>
       </c>
       <c r="D15">
-        <v>0.00024098226622749843</v>
+        <v>0.00024098226622749647</v>
       </c>
       <c r="E15">
-        <v>0.00025685583857602715</v>
+        <v>0.00025685583857602736</v>
       </c>
       <c r="F15">
         <v>2.6036874602808802e-05</v>
       </c>
       <c r="G15">
-        <v>-5.398446899316687e-05</v>
+        <v>-5.3984468993169255e-05</v>
       </c>
       <c r="H15">
-        <v>2.4952126135464555e-05</v>
+        <v>2.495212613546423e-05</v>
       </c>
       <c r="I15">
-        <v>0.0001212107914061668</v>
+        <v>0.00012121079140616701</v>
       </c>
       <c r="J15">
-        <v>0.00020041402999990848</v>
+        <v>0.00020041402999990804</v>
       </c>
       <c r="K15">
-        <v>0.00034860485841902724</v>
+        <v>0.000348604858419019</v>
       </c>
       <c r="L15">
-        <v>0.0003018571753258311</v>
+        <v>0.00030185717532582807</v>
       </c>
       <c r="M15">
-        <v>0.0001570291672220638</v>
+        <v>0.00015702916722206596</v>
       </c>
       <c r="N15">
-        <v>0.0002341418672939381</v>
+        <v>0.00023414186729393588</v>
       </c>
       <c r="O15">
-        <v>3.2044993063428642e-05</v>
+        <v>3.2044993063424143e-05</v>
       </c>
       <c r="P15">
         <v>0.0094263416292255289</v>
       </c>
       <c r="Q15">
-        <v>0.0068137726272691195</v>
+        <v>0.0068137726272690415</v>
       </c>
       <c r="R15">
         <v>0.0067577625961099935</v>
       </c>
       <c r="S15">
-        <v>0.0067408136400645769</v>
+        <v>0.0067408136400644997</v>
       </c>
       <c r="T15">
-        <v>-0.00011777917643879086</v>
+        <v>-0.0001177791764387907</v>
       </c>
       <c r="U15">
-        <v>0.00038688893363882744</v>
+        <v>0.00038688893363880836</v>
       </c>
       <c r="V15">
-        <v>0.00055400873771309887</v>
+        <v>0.00055400873771305984</v>
       </c>
       <c r="W15">
-        <v>0.00046371833807950721</v>
+        <v>0.0004637183380794491</v>
       </c>
       <c r="X15">
-        <v>-2.9039404761877563e-05</v>
+        <v>-2.9039404761876357e-05</v>
       </c>
       <c r="Y15">
-        <v>-0.00011733515753141271</v>
+        <v>-0.00011733515753141379</v>
       </c>
       <c r="Z15">
-        <v>0.00011420262847562559</v>
+        <v>0.00011420262847560651</v>
       </c>
       <c r="AA15">
-        <v>0.00016597672273016388</v>
+        <v>0.0001659767227301448</v>
       </c>
       <c r="AB15">
-        <v>0.00016024217855357525</v>
+        <v>0.00016024217855355617</v>
       </c>
       <c r="AC15">
-        <v>0.00011097867444824234</v>
+        <v>0.00011097867444822412</v>
       </c>
       <c r="AD15">
-        <v>0.00021100525375211568</v>
+        <v>0.00021100525375209638</v>
       </c>
       <c r="AE15">
-        <v>0.0003901010332448111</v>
+        <v>0.00039010103324479181</v>
       </c>
       <c r="AF15">
-        <v>5.7254640730701912e-06</v>
+        <v>5.7254640730689985e-06</v>
       </c>
       <c r="AG15">
-        <v>1.2088203191894242e-05</v>
+        <v>1.2088203191896844e-05</v>
       </c>
       <c r="AH15">
-        <v>-4.9005125978278993e-05</v>
+        <v>-4.9005125978272054e-05</v>
       </c>
       <c r="AI15">
-        <v>-0.0076469234090673632</v>
+        <v>-0.0076469234090672089</v>
       </c>
     </row>
     <row r="16">
@@ -2003,103 +1997,103 @@
         <v>-0.099438391666721845</v>
       </c>
       <c r="C16">
-        <v>-2.9367506558323816e-05</v>
+        <v>-2.9367506558325781e-05</v>
       </c>
       <c r="D16">
-        <v>0.00020490888816182367</v>
+        <v>0.00020490888816179624</v>
       </c>
       <c r="E16">
-        <v>7.6911989027287839e-05</v>
+        <v>7.6911989027264745e-05</v>
       </c>
       <c r="F16">
-        <v>3.0606587825537783e-05</v>
+        <v>3.0606587825516966e-05</v>
       </c>
       <c r="G16">
-        <v>6.9483088424646795e-05</v>
+        <v>6.9483088424618714e-05</v>
       </c>
       <c r="H16">
-        <v>1.6276286502292341e-06</v>
+        <v>1.6276286502025627e-06</v>
       </c>
       <c r="I16">
-        <v>-5.1614434371389508e-06</v>
+        <v>-5.1614434371626949e-06</v>
       </c>
       <c r="J16">
-        <v>6.3657106405375671e-05</v>
+        <v>6.365710640534759e-05</v>
       </c>
       <c r="K16">
-        <v>9.7647707584657718e-05</v>
+        <v>9.764770758462194e-05</v>
       </c>
       <c r="L16">
-        <v>0.00017023512700285585</v>
+        <v>0.00017023512700282094</v>
       </c>
       <c r="M16">
-        <v>8.1640007173097549e-05</v>
+        <v>8.1640007173097834e-05</v>
       </c>
       <c r="N16">
-        <v>3.994743296114258e-05</v>
+        <v>3.9947432961136997e-05</v>
       </c>
       <c r="O16">
-        <v>0.00012321554516548573</v>
+        <v>0.00012321554516547755</v>
       </c>
       <c r="P16">
-        <v>0.0068137726272691195</v>
+        <v>0.0068137726272690415</v>
       </c>
       <c r="Q16">
-        <v>0.0073181904543889479</v>
+        <v>0.007318190454388869</v>
       </c>
       <c r="R16">
         <v>0.0069913547073797138</v>
       </c>
       <c r="S16">
-        <v>0.0070188449262132691</v>
+        <v>0.0070188449262131901</v>
       </c>
       <c r="T16">
-        <v>-0.00019017400239541336</v>
+        <v>-0.00019017400239541331</v>
       </c>
       <c r="U16">
-        <v>-2.4202738742925417e-07</v>
+        <v>-2.4202738744876981e-07</v>
       </c>
       <c r="V16">
-        <v>-2.6207257167597427e-05</v>
+        <v>-2.6207257167636458e-05</v>
       </c>
       <c r="W16">
-        <v>1.6812808064787556e-05</v>
+        <v>1.6812808064727708e-05</v>
       </c>
       <c r="X16">
-        <v>-1.5446679067542744e-05</v>
+        <v>-1.5446679067541518e-05</v>
       </c>
       <c r="Y16">
-        <v>-2.0611295039210317e-05</v>
+        <v>-2.0611295039211185e-05</v>
       </c>
       <c r="Z16">
-        <v>0.00039977578339573782</v>
+        <v>0.00039977578339571874</v>
       </c>
       <c r="AA16">
-        <v>0.00039619269341186359</v>
+        <v>0.00039619269341184364</v>
       </c>
       <c r="AB16">
-        <v>0.00039999263156207613</v>
+        <v>0.00039999263156205705</v>
       </c>
       <c r="AC16">
-        <v>0.00032778991844847026</v>
+        <v>0.00032778991844845031</v>
       </c>
       <c r="AD16">
-        <v>0.00040526383753043585</v>
+        <v>0.00040526383753041611</v>
       </c>
       <c r="AE16">
-        <v>0.00037619705005903449</v>
+        <v>0.00037619705005901481</v>
       </c>
       <c r="AF16">
-        <v>-2.8570980447728111e-07</v>
+        <v>-2.8570980447852794e-07</v>
       </c>
       <c r="AG16">
-        <v>4.3779515320172685e-05</v>
+        <v>4.3779515320176154e-05</v>
       </c>
       <c r="AH16">
-        <v>2.3744716712629371e-05</v>
+        <v>2.3744716712636744e-05</v>
       </c>
       <c r="AI16">
-        <v>-0.0074153616530797445</v>
+        <v>-0.0074153616530795857</v>
       </c>
     </row>
     <row r="17">
@@ -2110,43 +2104,43 @@
         <v>-0.083042836433586745</v>
       </c>
       <c r="C17">
-        <v>-5.3783345333062239e-05</v>
+        <v>-5.3783345333062266e-05</v>
       </c>
       <c r="D17">
-        <v>0.00013961429365074959</v>
+        <v>0.00013961429365074899</v>
       </c>
       <c r="E17">
-        <v>5.8410909162392619e-05</v>
+        <v>5.8410909162393053e-05</v>
       </c>
       <c r="F17">
-        <v>-5.2813169842945993e-06</v>
+        <v>-5.2813169842943824e-06</v>
       </c>
       <c r="G17">
-        <v>-4.2746946247127664e-05</v>
+        <v>-4.2746946247128749e-05</v>
       </c>
       <c r="H17">
-        <v>-3.8034219591042448e-05</v>
+        <v>-3.8034219591042339e-05</v>
       </c>
       <c r="I17">
-        <v>-2.4039909615042798e-05</v>
+        <v>-2.4039909615042364e-05</v>
       </c>
       <c r="J17">
-        <v>-1.0902787355308852e-05</v>
+        <v>-1.0902787355308798e-05</v>
       </c>
       <c r="K17">
-        <v>6.1269581888881127e-05</v>
+        <v>6.1269581888877332e-05</v>
       </c>
       <c r="L17">
-        <v>0.00028235702247507617</v>
+        <v>0.00028235702247507449</v>
       </c>
       <c r="M17">
-        <v>8.659241108307806e-05</v>
+        <v>8.6592411083080201e-05</v>
       </c>
       <c r="N17">
-        <v>-1.967394473648407e-05</v>
+        <v>-1.9673944736483975e-05</v>
       </c>
       <c r="O17">
-        <v>0.0002163547499337467</v>
+        <v>0.00021635474993374665</v>
       </c>
       <c r="P17">
         <v>0.0067577625961099935</v>
@@ -2158,55 +2152,55 @@
         <v>0.0072937728143594536</v>
       </c>
       <c r="S17">
-        <v>0.0071502877158114101</v>
+        <v>0.0071502877158113294</v>
       </c>
       <c r="T17">
-        <v>-0.00015611331133340083</v>
+        <v>-0.00015611331133340078</v>
       </c>
       <c r="U17">
-        <v>6.7493561899867414e-05</v>
+        <v>6.7493561899847031e-05</v>
       </c>
       <c r="V17">
-        <v>-1.1335263924633354e-05</v>
+        <v>-1.133526392467412e-05</v>
       </c>
       <c r="W17">
-        <v>5.870236003214591e-05</v>
+        <v>5.8702360032085194e-05</v>
       </c>
       <c r="X17">
-        <v>-1.4914311524458736e-05</v>
+        <v>-1.4914311524457475e-05</v>
       </c>
       <c r="Y17">
-        <v>-2.7918090355720342e-05</v>
+        <v>-2.7918090355721426e-05</v>
       </c>
       <c r="Z17">
-        <v>0.00042834881384023072</v>
+        <v>0.00042834881384021077</v>
       </c>
       <c r="AA17">
-        <v>0.00038964786848789609</v>
+        <v>0.00038964786848787614</v>
       </c>
       <c r="AB17">
-        <v>0.00039390262233663341</v>
+        <v>0.00039390262233661259</v>
       </c>
       <c r="AC17">
-        <v>0.00031836766960776329</v>
+        <v>0.00031836766960774247</v>
       </c>
       <c r="AD17">
-        <v>0.00039693324408754101</v>
+        <v>0.00039693324408752063</v>
       </c>
       <c r="AE17">
-        <v>0.0004136654359543841</v>
+        <v>0.00041366543595436388</v>
       </c>
       <c r="AF17">
-        <v>3.6208117601813138e-06</v>
+        <v>3.6208117601800398e-06</v>
       </c>
       <c r="AG17">
-        <v>4.594633735862351e-05</v>
+        <v>4.5946337358625244e-05</v>
       </c>
       <c r="AH17">
-        <v>2.3263439245859233e-05</v>
+        <v>2.3263439245867039e-05</v>
       </c>
       <c r="AI17">
-        <v>-0.007654192618377853</v>
+        <v>-0.00765419261837769</v>
       </c>
     </row>
     <row r="18">
@@ -2217,103 +2211,103 @@
         <v>-0.13606630682082815</v>
       </c>
       <c r="C18">
-        <v>-0.00011313088460214739</v>
+        <v>-0.00011313088460214937</v>
       </c>
       <c r="D18">
-        <v>0.00035347518107978909</v>
+        <v>0.00035347518107976144</v>
       </c>
       <c r="E18">
-        <v>0.00011723908016812289</v>
+        <v>0.00011723908016810012</v>
       </c>
       <c r="F18">
-        <v>2.2049062175289933e-05</v>
+        <v>2.2049062175269008e-05</v>
       </c>
       <c r="G18">
-        <v>0.00010537693199462651</v>
+        <v>0.00010537693199459762</v>
       </c>
       <c r="H18">
-        <v>3.1047612534881083e-05</v>
+        <v>3.1047612534853815e-05</v>
       </c>
       <c r="I18">
-        <v>-3.7246413667954385e-05</v>
+        <v>-3.7246413667977967e-05</v>
       </c>
       <c r="J18">
-        <v>-6.0940037529575038e-05</v>
+        <v>-6.0940037529603553e-05</v>
       </c>
       <c r="K18">
-        <v>0.00016744100269598612</v>
+        <v>0.0001674410026959479</v>
       </c>
       <c r="L18">
-        <v>0.00047732123564776666</v>
+        <v>0.00047732123564772492</v>
       </c>
       <c r="M18">
-        <v>7.2625568124509883e-05</v>
+        <v>7.2625568124506603e-05</v>
       </c>
       <c r="N18">
-        <v>4.0788415143506556e-05</v>
+        <v>4.0788415143500742e-05</v>
       </c>
       <c r="O18">
-        <v>0.00031014633916724515</v>
+        <v>0.00031014633916723712</v>
       </c>
       <c r="P18">
-        <v>0.0067408136400645769</v>
+        <v>0.0067408136400644997</v>
       </c>
       <c r="Q18">
-        <v>0.0070188449262132691</v>
+        <v>0.0070188449262131901</v>
       </c>
       <c r="R18">
-        <v>0.0071502877158114101</v>
+        <v>0.0071502877158113294</v>
       </c>
       <c r="S18">
-        <v>0.0077670221172791675</v>
+        <v>0.0077670221172790868</v>
       </c>
       <c r="T18">
-        <v>-0.00021038681129574739</v>
+        <v>-0.00021038681129574734</v>
       </c>
       <c r="U18">
-        <v>0.0001764222656267648</v>
+        <v>0.00017642226562674442</v>
       </c>
       <c r="V18">
-        <v>0.00013642230501541286</v>
+        <v>0.00013642230501537209</v>
       </c>
       <c r="W18">
-        <v>0.00025997622043390668</v>
+        <v>0.00025997622043384423</v>
       </c>
       <c r="X18">
-        <v>-1.2964826891338069e-05</v>
+        <v>-1.2964826891336795e-05</v>
       </c>
       <c r="Y18">
-        <v>1.2286128425987534e-06</v>
+        <v>1.2286128425976692e-06</v>
       </c>
       <c r="Z18">
-        <v>0.00050815612522663554</v>
+        <v>0.0005081561252266156</v>
       </c>
       <c r="AA18">
-        <v>0.00043808842808903178</v>
+        <v>0.00043808842808901096</v>
       </c>
       <c r="AB18">
-        <v>0.00045272675287773376</v>
+        <v>0.00045272675287771381</v>
       </c>
       <c r="AC18">
-        <v>0.00038264462745453767</v>
+        <v>0.00038264462745451686</v>
       </c>
       <c r="AD18">
-        <v>0.00049446962267040286</v>
+        <v>0.00049446962267038247</v>
       </c>
       <c r="AE18">
-        <v>0.0003212531701308536</v>
+        <v>0.00032125317013083311</v>
       </c>
       <c r="AF18">
-        <v>6.4351374456253854e-06</v>
+        <v>6.4351374456240844e-06</v>
       </c>
       <c r="AG18">
-        <v>4.3708144531393739e-05</v>
+        <v>4.3708144531397208e-05</v>
       </c>
       <c r="AH18">
-        <v>7.8244783439965129e-05</v>
+        <v>7.8244783439972935e-05</v>
       </c>
       <c r="AI18">
-        <v>-0.0080109756220311541</v>
+        <v>-0.0080109756220309893</v>
       </c>
     </row>
     <row r="19">
@@ -2324,103 +2318,103 @@
         <v>0.19475512354932451</v>
       </c>
       <c r="C19">
-        <v>3.3585706081016427e-07</v>
+        <v>3.3585706081015749e-07</v>
       </c>
       <c r="D19">
-        <v>-1.9174180004385085e-05</v>
+        <v>-1.9174180004385329e-05</v>
       </c>
       <c r="E19">
-        <v>7.8675240484074415e-05</v>
+        <v>7.867524048407455e-05</v>
       </c>
       <c r="F19">
-        <v>3.3185996693463644e-05</v>
+        <v>3.318599669346378e-05</v>
       </c>
       <c r="G19">
-        <v>0.00013915368209564504</v>
+        <v>0.00013915368209564482</v>
       </c>
       <c r="H19">
-        <v>0.0001313035229106804</v>
+        <v>0.00013130352291068056</v>
       </c>
       <c r="I19">
-        <v>9.1079901964069663e-05</v>
+        <v>9.1079901964069798e-05</v>
       </c>
       <c r="J19">
-        <v>6.999213058397506e-05</v>
+        <v>6.9992130583975169e-05</v>
       </c>
       <c r="K19">
-        <v>0.00063230654186256547</v>
+        <v>0.0006323065418625659</v>
       </c>
       <c r="L19">
-        <v>0.00047289903568891465</v>
+        <v>0.00047289903568891475</v>
       </c>
       <c r="M19">
-        <v>-0.00021872529679949068</v>
+        <v>-0.00021872529679949106</v>
       </c>
       <c r="N19">
-        <v>-2.4394818592364416e-05</v>
+        <v>-2.4394818592364429e-05</v>
       </c>
       <c r="O19">
-        <v>2.4679496354270889e-05</v>
+        <v>2.4679496354270875e-05</v>
       </c>
       <c r="P19">
-        <v>-0.00011777917643879086</v>
+        <v>-0.0001177791764387907</v>
       </c>
       <c r="Q19">
-        <v>-0.00019017400239541336</v>
+        <v>-0.00019017400239541331</v>
       </c>
       <c r="R19">
-        <v>-0.00015611331133340083</v>
+        <v>-0.00015611331133340078</v>
       </c>
       <c r="S19">
-        <v>-0.00021038681129574739</v>
+        <v>-0.00021038681129574734</v>
       </c>
       <c r="T19">
         <v>0.0010828886397138793</v>
       </c>
       <c r="U19">
-        <v>0.00095411326157021181</v>
+        <v>0.00095411326157020943</v>
       </c>
       <c r="V19">
-        <v>0.00099696851377575717</v>
+        <v>0.00099696851377575413</v>
       </c>
       <c r="W19">
-        <v>0.0010934520904993556</v>
+        <v>0.001093452090499351</v>
       </c>
       <c r="X19">
-        <v>-9.7975365989235293e-05</v>
+        <v>-9.7975365989235171e-05</v>
       </c>
       <c r="Y19">
-        <v>6.9257082614884854e-06</v>
+        <v>6.9257082614881873e-06</v>
       </c>
       <c r="Z19">
-        <v>5.8451861510900867e-05</v>
+        <v>5.8451861510898698e-05</v>
       </c>
       <c r="AA19">
-        <v>5.2488330671796534e-05</v>
+        <v>5.2488330671794691e-05</v>
       </c>
       <c r="AB19">
-        <v>2.1032802931350678e-05</v>
+        <v>2.1032802931348293e-05</v>
       </c>
       <c r="AC19">
-        <v>3.3098360869949768e-05</v>
+        <v>3.3098360869947274e-05</v>
       </c>
       <c r="AD19">
-        <v>2.1061296049572695e-05</v>
+        <v>2.1061296049570486e-05</v>
       </c>
       <c r="AE19">
-        <v>0.0001100429042331806</v>
+        <v>0.00011004290423317835</v>
       </c>
       <c r="AF19">
-        <v>-3.1269371662585882e-06</v>
+        <v>-3.1269371662587372e-06</v>
       </c>
       <c r="AG19">
-        <v>-0.00013761921847101533</v>
+        <v>-0.000137619218471015</v>
       </c>
       <c r="AH19">
-        <v>-5.2297174353574253e-05</v>
+        <v>-5.2297174353573494e-05</v>
       </c>
       <c r="AI19">
-        <v>-0.00073223072105571747</v>
+        <v>-0.00073223072105570988</v>
       </c>
     </row>
     <row r="20">
@@ -2431,103 +2425,103 @@
         <v>0.079518653485038435</v>
       </c>
       <c r="C20">
-        <v>3.8978001937107882e-05</v>
+        <v>3.897800193710734e-05</v>
       </c>
       <c r="D20">
-        <v>-3.2793598063814329e-05</v>
+        <v>-3.2793598063820834e-05</v>
       </c>
       <c r="E20">
-        <v>9.0123156531717605e-05</v>
+        <v>9.0123156531713268e-05</v>
       </c>
       <c r="F20">
-        <v>4.7592016809201655e-05</v>
+        <v>4.7592016809197427e-05</v>
       </c>
       <c r="G20">
-        <v>0.00021119581025746525</v>
+        <v>0.00021119581025745874</v>
       </c>
       <c r="H20">
-        <v>0.00014664378215090254</v>
+        <v>0.00014664378215089647</v>
       </c>
       <c r="I20">
-        <v>0.00022175602752185462</v>
+        <v>0.00022175602752184942</v>
       </c>
       <c r="J20">
-        <v>7.9251307881547098e-05</v>
+        <v>7.9251307881541026e-05</v>
       </c>
       <c r="K20">
-        <v>0.0032118980277105924</v>
+        <v>0.0032118980277105851</v>
       </c>
       <c r="L20">
-        <v>0.002645496636413675</v>
+        <v>0.0026454966364136663</v>
       </c>
       <c r="M20">
-        <v>-0.00055939481065233254</v>
+        <v>-0.00055939481065233319</v>
       </c>
       <c r="N20">
-        <v>0.00014571898141819425</v>
+        <v>0.00014571898141819284</v>
       </c>
       <c r="O20">
-        <v>0.00018782629432656311</v>
+        <v>0.00018782629432656116</v>
       </c>
       <c r="P20">
-        <v>0.00038688893363882744</v>
+        <v>0.00038688893363880836</v>
       </c>
       <c r="Q20">
-        <v>-2.4202738742925417e-07</v>
+        <v>-2.4202738744876981e-07</v>
       </c>
       <c r="R20">
-        <v>6.7493561899867414e-05</v>
+        <v>6.7493561899847031e-05</v>
       </c>
       <c r="S20">
-        <v>0.0001764222656267648</v>
+        <v>0.00017642226562674442</v>
       </c>
       <c r="T20">
-        <v>0.00095411326157021181</v>
+        <v>0.00095411326157020943</v>
       </c>
       <c r="U20">
-        <v>0.0035249377378211962</v>
+        <v>0.0035249377378211893</v>
       </c>
       <c r="V20">
-        <v>0.0033561089904270485</v>
+        <v>0.0033561089904270381</v>
       </c>
       <c r="W20">
-        <v>0.0036402634101280655</v>
+        <v>0.0036402634101280512</v>
       </c>
       <c r="X20">
-        <v>-0.00020858597674806067</v>
+        <v>-0.00020858597674806026</v>
       </c>
       <c r="Y20">
-        <v>2.5943844974371945e-05</v>
+        <v>2.5943844974371023e-05</v>
       </c>
       <c r="Z20">
-        <v>2.7680712637990265e-05</v>
+        <v>2.7680712637983326e-05</v>
       </c>
       <c r="AA20">
-        <v>-2.6550282929693313e-05</v>
+        <v>-2.6550282929699385e-05</v>
       </c>
       <c r="AB20">
-        <v>-3.9589942205481418e-05</v>
+        <v>-3.9589942205489224e-05</v>
       </c>
       <c r="AC20">
-        <v>4.6144882518608238e-06</v>
+        <v>4.6144882518525838e-06</v>
       </c>
       <c r="AD20">
-        <v>0.00010707005547397802</v>
+        <v>0.00010707005547397054</v>
       </c>
       <c r="AE20">
-        <v>7.5686072508706647e-05</v>
+        <v>7.5686072508698935e-05</v>
       </c>
       <c r="AF20">
-        <v>4.5265732748422195e-06</v>
+        <v>4.526573274841691e-06</v>
       </c>
       <c r="AG20">
-        <v>-2.3809894667178953e-05</v>
+        <v>-2.3809894667178085e-05</v>
       </c>
       <c r="AH20">
-        <v>-6.83737626523441e-05</v>
+        <v>-6.8373762652341064e-05</v>
       </c>
       <c r="AI20">
-        <v>-0.0036109294228694813</v>
+        <v>-0.0036109294228694492</v>
       </c>
     </row>
     <row r="21">
@@ -2538,103 +2532,103 @@
         <v>0.20038459830311944</v>
       </c>
       <c r="C21">
-        <v>-1.4297628366294248e-06</v>
+        <v>-1.4297628366304819e-06</v>
       </c>
       <c r="D21">
-        <v>0.00034904637853420397</v>
+        <v>0.00034904637853419075</v>
       </c>
       <c r="E21">
-        <v>0.00023564401616688263</v>
+        <v>0.00023564401616687136</v>
       </c>
       <c r="F21">
-        <v>6.0529809379003194e-05</v>
+        <v>6.0529809378992785e-05</v>
       </c>
       <c r="G21">
-        <v>0.00054653907747108572</v>
+        <v>0.00054653907747107293</v>
       </c>
       <c r="H21">
-        <v>0.00051188472275485487</v>
+        <v>0.0005118847227548423</v>
       </c>
       <c r="I21">
-        <v>0.00035138499279763918</v>
+        <v>0.0003513849927976279</v>
       </c>
       <c r="J21">
-        <v>0.00043942370648207335</v>
+        <v>0.00043942370648206034</v>
       </c>
       <c r="K21">
-        <v>0.0036789130441664351</v>
+        <v>0.0036789130441664238</v>
       </c>
       <c r="L21">
-        <v>0.0030849932598246296</v>
+        <v>0.0030849932598246165</v>
       </c>
       <c r="M21">
-        <v>-0.00045654085313738102</v>
+        <v>-0.00045654085313738275</v>
       </c>
       <c r="N21">
-        <v>0.00024170927075665923</v>
+        <v>0.0002417092707566563</v>
       </c>
       <c r="O21">
-        <v>0.00029188576739535514</v>
+        <v>0.00029188576739535123</v>
       </c>
       <c r="P21">
-        <v>0.00055400873771309887</v>
+        <v>0.00055400873771305984</v>
       </c>
       <c r="Q21">
-        <v>-2.6207257167597427e-05</v>
+        <v>-2.6207257167636458e-05</v>
       </c>
       <c r="R21">
-        <v>-1.1335263924633354e-05</v>
+        <v>-1.133526392467412e-05</v>
       </c>
       <c r="S21">
-        <v>0.00013642230501541286</v>
+        <v>0.00013642230501537209</v>
       </c>
       <c r="T21">
-        <v>0.00099696851377575717</v>
+        <v>0.00099696851377575413</v>
       </c>
       <c r="U21">
-        <v>0.0033561089904270485</v>
+        <v>0.0033561089904270381</v>
       </c>
       <c r="V21">
-        <v>0.0044746450417367679</v>
+        <v>0.004474645041736754</v>
       </c>
       <c r="W21">
-        <v>0.0042381389294276935</v>
+        <v>0.0042381389294276727</v>
       </c>
       <c r="X21">
-        <v>-0.00021322219030547171</v>
+        <v>-0.00021322219030547114</v>
       </c>
       <c r="Y21">
-        <v>2.7666029659508548e-05</v>
+        <v>2.7666029659507247e-05</v>
       </c>
       <c r="Z21">
-        <v>8.6603241043908558e-05</v>
+        <v>8.6603241043899451e-05</v>
       </c>
       <c r="AA21">
-        <v>1.9365119552565251e-06</v>
+        <v>1.9365119552478515e-06</v>
       </c>
       <c r="AB21">
-        <v>3.0966175405284808e-05</v>
+        <v>3.0966175405273966e-05</v>
       </c>
       <c r="AC21">
-        <v>7.6567174047388088e-05</v>
+        <v>7.6567174047377246e-05</v>
       </c>
       <c r="AD21">
-        <v>0.00018787443626775379</v>
+        <v>0.00018787443626774381</v>
       </c>
       <c r="AE21">
-        <v>0.00020760721124197113</v>
+        <v>0.00020760721124196092</v>
       </c>
       <c r="AF21">
-        <v>9.0116810501183992e-06</v>
+        <v>9.011681050117681e-06</v>
       </c>
       <c r="AG21">
-        <v>9.8761563418469159e-05</v>
+        <v>9.8761563418470026e-05</v>
       </c>
       <c r="AH21">
-        <v>-0.00010339082551957465</v>
+        <v>-0.00010339082551957053</v>
       </c>
       <c r="AI21">
-        <v>-0.0044241714089442597</v>
+        <v>-0.0044241714089442189</v>
       </c>
     </row>
     <row r="22">
@@ -2645,103 +2639,103 @@
         <v>0.23388741978217065</v>
       </c>
       <c r="C22">
-        <v>-5.9422502834600118e-05</v>
+        <v>-5.9422502834600836e-05</v>
       </c>
       <c r="D22">
-        <v>0.000805197453045594</v>
+        <v>0.0008051974530455799</v>
       </c>
       <c r="E22">
-        <v>0.0007293957933247996</v>
+        <v>0.00072939579332478789</v>
       </c>
       <c r="F22">
-        <v>0.00035402050081692485</v>
+        <v>0.00035402050081691455</v>
       </c>
       <c r="G22">
-        <v>0.0012059413454082583</v>
+        <v>0.0012059413454082453</v>
       </c>
       <c r="H22">
-        <v>0.0010635742589028341</v>
+        <v>0.0010635742589028211</v>
       </c>
       <c r="I22">
-        <v>0.00076954334989701731</v>
+        <v>0.00076954334989700539</v>
       </c>
       <c r="J22">
-        <v>0.00077552129634349829</v>
+        <v>0.00077552129634348398</v>
       </c>
       <c r="K22">
-        <v>0.0039392190568509327</v>
+        <v>0.003939219056850918</v>
       </c>
       <c r="L22">
-        <v>0.003325956849966759</v>
+        <v>0.0033259568499667417</v>
       </c>
       <c r="M22">
-        <v>-0.00033281241228975544</v>
+        <v>-0.00033281241228975722</v>
       </c>
       <c r="N22">
-        <v>0.00043867877034088393</v>
+        <v>0.00043867877034088062</v>
       </c>
       <c r="O22">
-        <v>0.00050573604431693945</v>
+        <v>0.0005057360443169349</v>
       </c>
       <c r="P22">
-        <v>0.00046371833807950721</v>
+        <v>0.0004637183380794491</v>
       </c>
       <c r="Q22">
-        <v>1.6812808064787556e-05</v>
+        <v>1.6812808064727708e-05</v>
       </c>
       <c r="R22">
-        <v>5.870236003214591e-05</v>
+        <v>5.8702360032085194e-05</v>
       </c>
       <c r="S22">
-        <v>0.00025997622043390668</v>
+        <v>0.00025997622043384423</v>
       </c>
       <c r="T22">
-        <v>0.0010934520904993556</v>
+        <v>0.001093452090499351</v>
       </c>
       <c r="U22">
-        <v>0.0036402634101280655</v>
+        <v>0.0036402634101280512</v>
       </c>
       <c r="V22">
-        <v>0.0042381389294276935</v>
+        <v>0.0042381389294276727</v>
       </c>
       <c r="W22">
-        <v>0.005422493554157819</v>
+        <v>0.0054224935541577965</v>
       </c>
       <c r="X22">
-        <v>-0.00025246361274046782</v>
+        <v>-0.00025246361274046711</v>
       </c>
       <c r="Y22">
-        <v>2.9979686537174081e-05</v>
+        <v>2.9979686537172671e-05</v>
       </c>
       <c r="Z22">
-        <v>0.00016191570019675463</v>
+        <v>0.00016191570019674379</v>
       </c>
       <c r="AA22">
-        <v>2.6869125629082336e-05</v>
+        <v>2.6869125629073228e-05</v>
       </c>
       <c r="AB22">
-        <v>5.4205815082366497e-05</v>
+        <v>5.4205815082355221e-05</v>
       </c>
       <c r="AC22">
-        <v>0.0001318440502646864</v>
+        <v>0.00013184405026467339</v>
       </c>
       <c r="AD22">
-        <v>0.00019495295271683931</v>
+        <v>0.00019495295271682749</v>
       </c>
       <c r="AE22">
-        <v>0.00014314395619295401</v>
+        <v>0.00014314395619294227</v>
       </c>
       <c r="AF22">
-        <v>1.1770680230067129e-05</v>
+        <v>1.1770680230066316e-05</v>
       </c>
       <c r="AG22">
-        <v>-0.00017259147849397072</v>
+        <v>-0.00017259147849396899</v>
       </c>
       <c r="AH22">
-        <v>-0.00014225457160010066</v>
+        <v>-0.00014225457160009589</v>
       </c>
       <c r="AI22">
-        <v>-0.0053221193019863666</v>
+        <v>-0.0053221193019863094</v>
       </c>
     </row>
     <row r="23">
@@ -2752,103 +2746,103 @@
         <v>0.01736585391862102</v>
       </c>
       <c r="C23">
-        <v>-4.8028132579072198e-07</v>
+        <v>-4.802813257906881e-07</v>
       </c>
       <c r="D23">
-        <v>-7.8230614138232163e-06</v>
+        <v>-7.8230614138227945e-06</v>
       </c>
       <c r="E23">
-        <v>-3.1864712784610176e-05</v>
+        <v>-3.186471278460981e-05</v>
       </c>
       <c r="F23">
-        <v>-1.1239453734116243e-05</v>
+        <v>-1.1239453734115928e-05</v>
       </c>
       <c r="G23">
-        <v>-4.7557013707125826e-05</v>
+        <v>-4.7557013707125406e-05</v>
       </c>
       <c r="H23">
-        <v>-2.6566527801927329e-05</v>
+        <v>-2.6566527801926923e-05</v>
       </c>
       <c r="I23">
-        <v>-3.6324449322708611e-05</v>
+        <v>-3.6324449322708231e-05</v>
       </c>
       <c r="J23">
-        <v>-3.8749522387691655e-05</v>
+        <v>-3.8749522387691228e-05</v>
       </c>
       <c r="K23">
-        <v>-0.00016679003225496437</v>
+        <v>-0.00016679003225496402</v>
       </c>
       <c r="L23">
-        <v>-0.00014921956736978716</v>
+        <v>-0.00014921956736978667</v>
       </c>
       <c r="M23">
-        <v>1.3508018690001983e-05</v>
+        <v>1.3508018690002081e-05</v>
       </c>
       <c r="N23">
-        <v>-8.94504520294432e-06</v>
+        <v>-8.9450452029442691e-06</v>
       </c>
       <c r="O23">
-        <v>-1.0285577321125419e-05</v>
+        <v>-1.0285577321125307e-05</v>
       </c>
       <c r="P23">
-        <v>-2.9039404761877563e-05</v>
+        <v>-2.9039404761876357e-05</v>
       </c>
       <c r="Q23">
-        <v>-1.5446679067542744e-05</v>
+        <v>-1.5446679067541518e-05</v>
       </c>
       <c r="R23">
-        <v>-1.4914311524458736e-05</v>
+        <v>-1.4914311524457475e-05</v>
       </c>
       <c r="S23">
-        <v>-1.2964826891338069e-05</v>
+        <v>-1.2964826891336795e-05</v>
       </c>
       <c r="T23">
-        <v>-9.7975365989235293e-05</v>
+        <v>-9.7975365989235171e-05</v>
       </c>
       <c r="U23">
-        <v>-0.00020858597674806067</v>
+        <v>-0.00020858597674806026</v>
       </c>
       <c r="V23">
-        <v>-0.00021322219030547171</v>
+        <v>-0.00021322219030547114</v>
       </c>
       <c r="W23">
-        <v>-0.00025246361274046782</v>
+        <v>-0.00025246361274046711</v>
       </c>
       <c r="X23">
-        <v>3.5907221896566362e-05</v>
+        <v>3.5907221896566341e-05</v>
       </c>
       <c r="Y23">
-        <v>-5.0879498333560857e-06</v>
+        <v>-5.0879498333560417e-06</v>
       </c>
       <c r="Z23">
-        <v>-1.4893099836860914e-05</v>
+        <v>-1.4893099836860561e-05</v>
       </c>
       <c r="AA23">
-        <v>-1.3096336156971045e-05</v>
+        <v>-1.3096336156970788e-05</v>
       </c>
       <c r="AB23">
-        <v>-7.4033122276251123e-06</v>
+        <v>-7.4033122276247464e-06</v>
       </c>
       <c r="AC23">
-        <v>-1.2136815108224671e-05</v>
+        <v>-1.2136815108224142e-05</v>
       </c>
       <c r="AD23">
-        <v>-8.7635720959448961e-06</v>
+        <v>-8.7635720959445454e-06</v>
       </c>
       <c r="AE23">
-        <v>-1.5430911525350564e-05</v>
+        <v>-1.5430911525350185e-05</v>
       </c>
       <c r="AF23">
-        <v>1.9760107536394927e-06</v>
+        <v>1.9760107536395181e-06</v>
       </c>
       <c r="AG23">
-        <v>3.0246414570963667e-05</v>
+        <v>3.0246414570963613e-05</v>
       </c>
       <c r="AH23">
-        <v>-4.9263320160388346e-06</v>
+        <v>-4.9263320160389769e-06</v>
       </c>
       <c r="AI23">
-        <v>0.0001879211432245401</v>
+        <v>0.00018792114322453902</v>
       </c>
     </row>
     <row r="24">
@@ -2859,103 +2853,103 @@
         <v>3.892237300748834</v>
       </c>
       <c r="C24">
-        <v>-3.1834493471115865e-05</v>
+        <v>-3.1834493471115879e-05</v>
       </c>
       <c r="D24">
-        <v>0.00033228372241895908</v>
+        <v>0.00033228372241895859</v>
       </c>
       <c r="E24">
-        <v>-6.7136134926303558e-05</v>
+        <v>-6.7136134926303937e-05</v>
       </c>
       <c r="F24">
-        <v>-4.883454486433376e-05</v>
+        <v>-4.8834544864334085e-05</v>
       </c>
       <c r="G24">
-        <v>0.00012877618346038988</v>
+        <v>0.00012877618346038934</v>
       </c>
       <c r="H24">
-        <v>-1.8494888706544908e-05</v>
+        <v>-1.8494888706545396e-05</v>
       </c>
       <c r="I24">
-        <v>-8.8974886706918684e-05</v>
+        <v>-8.8974886706919064e-05</v>
       </c>
       <c r="J24">
-        <v>-2.384510497773271e-05</v>
+        <v>-2.3845104977733252e-05</v>
       </c>
       <c r="K24">
-        <v>3.7762544182086649e-05</v>
+        <v>3.7762544182085836e-05</v>
       </c>
       <c r="L24">
-        <v>4.2739638244124894e-05</v>
+        <v>4.2739638244123918e-05</v>
       </c>
       <c r="M24">
-        <v>3.3516023083527584e-06</v>
+        <v>3.3516023083526975e-06</v>
       </c>
       <c r="N24">
-        <v>2.5349901746123875e-06</v>
+        <v>2.5349901746122384e-06</v>
       </c>
       <c r="O24">
-        <v>1.0451598659236752e-05</v>
+        <v>1.0451598659236589e-05</v>
       </c>
       <c r="P24">
-        <v>-0.00011733515753141271</v>
+        <v>-0.00011733515753141379</v>
       </c>
       <c r="Q24">
-        <v>-2.0611295039210317e-05</v>
+        <v>-2.0611295039211185e-05</v>
       </c>
       <c r="R24">
-        <v>-2.7918090355720342e-05</v>
+        <v>-2.7918090355721426e-05</v>
       </c>
       <c r="S24">
-        <v>1.2286128425987534e-06</v>
+        <v>1.2286128425976692e-06</v>
       </c>
       <c r="T24">
-        <v>6.9257082614884854e-06</v>
+        <v>6.9257082614881873e-06</v>
       </c>
       <c r="U24">
-        <v>2.5943844974371945e-05</v>
+        <v>2.5943844974371023e-05</v>
       </c>
       <c r="V24">
-        <v>2.7666029659508548e-05</v>
+        <v>2.7666029659507247e-05</v>
       </c>
       <c r="W24">
-        <v>2.9979686537174081e-05</v>
+        <v>2.9979686537172671e-05</v>
       </c>
       <c r="X24">
-        <v>-5.0879498333560857e-06</v>
+        <v>-5.0879498333560417e-06</v>
       </c>
       <c r="Y24">
-        <v>0.00046673961194149469</v>
+        <v>0.00046673961194149458</v>
       </c>
       <c r="Z24">
-        <v>-1.3656190882247501e-05</v>
+        <v>-1.3656190882248558e-05</v>
       </c>
       <c r="AA24">
-        <v>2.3027779609006741e-05</v>
+        <v>2.3027779609005738e-05</v>
       </c>
       <c r="AB24">
-        <v>-1.2590197192875337e-05</v>
+        <v>-1.2590197192876312e-05</v>
       </c>
       <c r="AC24">
-        <v>-5.4273072590252304e-06</v>
+        <v>-5.4273072590262333e-06</v>
       </c>
       <c r="AD24">
-        <v>5.0475275273064929e-06</v>
+        <v>5.0475275273061134e-06</v>
       </c>
       <c r="AE24">
-        <v>-4.6852151554368649e-05</v>
+        <v>-4.6852151554369116e-05</v>
       </c>
       <c r="AF24">
-        <v>-1.5188203201892972e-07</v>
+        <v>-1.5188203201898986e-07</v>
       </c>
       <c r="AG24">
-        <v>-0.00010559568546626726</v>
+        <v>-0.00010559568546626721</v>
       </c>
       <c r="AH24">
-        <v>2.8898995698168637e-05</v>
+        <v>2.8898995698168942e-05</v>
       </c>
       <c r="AI24">
-        <v>-0.00018355116897699833</v>
+        <v>-0.0001835511689769905</v>
       </c>
     </row>
     <row r="25">
@@ -2966,103 +2960,103 @@
         <v>0.094379236628785945</v>
       </c>
       <c r="C25">
-        <v>-8.1085924364914826e-05</v>
+        <v>-8.108592436491526e-05</v>
       </c>
       <c r="D25">
-        <v>0.00014280146279555895</v>
+        <v>0.00014280146279555439</v>
       </c>
       <c r="E25">
-        <v>0.00010394145986338931</v>
+        <v>0.00010394145986338584</v>
       </c>
       <c r="F25">
-        <v>0.00011191749201080623</v>
+        <v>0.00011191749201080342</v>
       </c>
       <c r="G25">
-        <v>0.00020423090026066562</v>
+        <v>0.00020423090026066106</v>
       </c>
       <c r="H25">
-        <v>0.00022190153581251983</v>
+        <v>0.00022190153581251528</v>
       </c>
       <c r="I25">
-        <v>5.2854459322041088e-05</v>
+        <v>5.2854459322038052e-05</v>
       </c>
       <c r="J25">
-        <v>0.00014993704661026355</v>
+        <v>0.00014993704661025922</v>
       </c>
       <c r="K25">
-        <v>0.0001868189980096433</v>
+        <v>0.00018681899800963549</v>
       </c>
       <c r="L25">
-        <v>4.4432803402155632e-05</v>
+        <v>4.4432803402147392e-05</v>
       </c>
       <c r="M25">
-        <v>5.3753552470534624e-06</v>
+        <v>5.375355247053354e-06</v>
       </c>
       <c r="N25">
-        <v>3.176840152892095e-05</v>
+        <v>3.1768401528920246e-05</v>
       </c>
       <c r="O25">
-        <v>7.8399976348820632e-05</v>
+        <v>7.8399976348818789e-05</v>
       </c>
       <c r="P25">
-        <v>0.00011420262847562559</v>
+        <v>0.00011420262847560651</v>
       </c>
       <c r="Q25">
-        <v>0.00039977578339573782</v>
+        <v>0.00039977578339571874</v>
       </c>
       <c r="R25">
-        <v>0.00042834881384023072</v>
+        <v>0.00042834881384021077</v>
       </c>
       <c r="S25">
-        <v>0.00050815612522663554</v>
+        <v>0.0005081561252266156</v>
       </c>
       <c r="T25">
-        <v>5.8451861510900867e-05</v>
+        <v>5.8451861510898698e-05</v>
       </c>
       <c r="U25">
-        <v>2.7680712637990265e-05</v>
+        <v>2.7680712637983326e-05</v>
       </c>
       <c r="V25">
-        <v>8.6603241043908558e-05</v>
+        <v>8.6603241043899451e-05</v>
       </c>
       <c r="W25">
-        <v>0.00016191570019675463</v>
+        <v>0.00016191570019674379</v>
       </c>
       <c r="X25">
-        <v>-1.4893099836860914e-05</v>
+        <v>-1.4893099836860561e-05</v>
       </c>
       <c r="Y25">
-        <v>-1.3656190882247501e-05</v>
+        <v>-1.3656190882248558e-05</v>
       </c>
       <c r="Z25">
-        <v>0.00306979656172019</v>
+        <v>0.0030697965617201856</v>
       </c>
       <c r="AA25">
-        <v>0.0024179089040784673</v>
+        <v>0.0024179089040784617</v>
       </c>
       <c r="AB25">
-        <v>0.0024045507518044842</v>
+        <v>0.002404550751804479</v>
       </c>
       <c r="AC25">
-        <v>0.002422098966461712</v>
+        <v>0.0024220989664617064</v>
       </c>
       <c r="AD25">
-        <v>0.0024195156018215289</v>
+        <v>0.0024195156018215242</v>
       </c>
       <c r="AE25">
-        <v>0.0024034528561093466</v>
+        <v>0.0024034528561093405</v>
       </c>
       <c r="AF25">
-        <v>4.3270358777728335e-06</v>
+        <v>4.3270358777724812e-06</v>
       </c>
       <c r="AG25">
-        <v>-8.9653440550173901e-05</v>
+        <v>-8.9653440550173467e-05</v>
       </c>
       <c r="AH25">
-        <v>-7.5214449039282634e-05</v>
+        <v>-7.5214449039280574e-05</v>
       </c>
       <c r="AI25">
-        <v>-0.0030368046871221436</v>
+        <v>-0.003036804687122102</v>
       </c>
     </row>
     <row r="26">
@@ -3073,103 +3067,103 @@
         <v>0.12294840072921695</v>
       </c>
       <c r="C26">
-        <v>-8.7021960423897508e-05</v>
+        <v>-8.7021960423897996e-05</v>
       </c>
       <c r="D26">
-        <v>0.0010716454027064983</v>
+        <v>0.0010716454027064914</v>
       </c>
       <c r="E26">
-        <v>8.7703738193669126e-05</v>
+        <v>8.7703738193663271e-05</v>
       </c>
       <c r="F26">
-        <v>7.3842847933297973e-06</v>
+        <v>7.3842847933245932e-06</v>
       </c>
       <c r="G26">
-        <v>6.1444208924468779e-05</v>
+        <v>6.1444208924462274e-05</v>
       </c>
       <c r="H26">
-        <v>0.00014698745143088671</v>
+        <v>0.00014698745143088021</v>
       </c>
       <c r="I26">
-        <v>3.2123447875537442e-05</v>
+        <v>3.2123447875531371e-05</v>
       </c>
       <c r="J26">
-        <v>0.00012300481935885563</v>
+        <v>0.00012300481935884869</v>
       </c>
       <c r="K26">
-        <v>0.00010292825587061589</v>
+        <v>0.00010292825587060982</v>
       </c>
       <c r="L26">
-        <v>-5.0739540888778811e-05</v>
+        <v>-5.0739540888785316e-05</v>
       </c>
       <c r="M26">
-        <v>-4.7040608925574498e-05</v>
+        <v>-4.7040608925575419e-05</v>
       </c>
       <c r="N26">
-        <v>1.4427976619053114e-05</v>
+        <v>1.442797661905165e-05</v>
       </c>
       <c r="O26">
-        <v>8.0597869771121947e-05</v>
+        <v>8.0597869771119887e-05</v>
       </c>
       <c r="P26">
-        <v>0.00016597672273016388</v>
+        <v>0.0001659767227301448</v>
       </c>
       <c r="Q26">
-        <v>0.00039619269341186359</v>
+        <v>0.00039619269341184364</v>
       </c>
       <c r="R26">
-        <v>0.00038964786848789609</v>
+        <v>0.00038964786848787614</v>
       </c>
       <c r="S26">
-        <v>0.00043808842808903178</v>
+        <v>0.00043808842808901096</v>
       </c>
       <c r="T26">
-        <v>5.2488330671796534e-05</v>
+        <v>5.2488330671794691e-05</v>
       </c>
       <c r="U26">
-        <v>-2.6550282929693313e-05</v>
+        <v>-2.6550282929699385e-05</v>
       </c>
       <c r="V26">
-        <v>1.9365119552565251e-06</v>
+        <v>1.9365119552478515e-06</v>
       </c>
       <c r="W26">
-        <v>2.6869125629082336e-05</v>
+        <v>2.6869125629073228e-05</v>
       </c>
       <c r="X26">
-        <v>-1.3096336156971045e-05</v>
+        <v>-1.3096336156970788e-05</v>
       </c>
       <c r="Y26">
-        <v>2.3027779609006741e-05</v>
+        <v>2.3027779609005738e-05</v>
       </c>
       <c r="Z26">
-        <v>0.0024179089040784673</v>
+        <v>0.0024179089040784617</v>
       </c>
       <c r="AA26">
-        <v>0.0031027946331042976</v>
+        <v>0.0031027946331042919</v>
       </c>
       <c r="AB26">
-        <v>0.0023978483286616614</v>
+        <v>0.0023978483286616558</v>
       </c>
       <c r="AC26">
-        <v>0.0024093579671635732</v>
+        <v>0.002409357967163568</v>
       </c>
       <c r="AD26">
-        <v>0.002411118530773455</v>
+        <v>0.0024111185307734502</v>
       </c>
       <c r="AE26">
-        <v>0.0024006466571823981</v>
+        <v>0.0024006466571823933</v>
       </c>
       <c r="AF26">
-        <v>5.2611654468125231e-06</v>
+        <v>5.261165446812191e-06</v>
       </c>
       <c r="AG26">
-        <v>-8.554109528829219e-05</v>
+        <v>-8.5541095288291539e-05</v>
       </c>
       <c r="AH26">
-        <v>-1.6356704670960178e-05</v>
+        <v>-1.6356704670958226e-05</v>
       </c>
       <c r="AI26">
-        <v>-0.0029087018043451977</v>
+        <v>-0.0029087018043451578</v>
       </c>
     </row>
     <row r="27">
@@ -3180,103 +3174,103 @@
         <v>-0.042363738032216963</v>
       </c>
       <c r="C27">
-        <v>-9.2596972208624809e-05</v>
+        <v>-9.2596972208625297e-05</v>
       </c>
       <c r="D27">
-        <v>0.0007563371623317696</v>
+        <v>0.00075633716233176255</v>
       </c>
       <c r="E27">
-        <v>0.00010743254938750703</v>
+        <v>0.00010743254938750139</v>
       </c>
       <c r="F27">
-        <v>5.2590944147573203e-05</v>
+        <v>5.2590944147567998e-05</v>
       </c>
       <c r="G27">
-        <v>0.00012310858855484356</v>
+        <v>0.00012310858855483641</v>
       </c>
       <c r="H27">
-        <v>0.00017526084095629484</v>
+        <v>0.00017526084095628811</v>
       </c>
       <c r="I27">
-        <v>5.3620247030806501e-05</v>
+        <v>5.3620247030800646e-05</v>
       </c>
       <c r="J27">
-        <v>7.6264365752973414e-05</v>
+        <v>7.6264365752966258e-05</v>
       </c>
       <c r="K27">
-        <v>7.9016028483075602e-05</v>
+        <v>7.9016028483066495e-05</v>
       </c>
       <c r="L27">
-        <v>-2.6403228015840947e-05</v>
+        <v>-2.6403228015850272e-05</v>
       </c>
       <c r="M27">
-        <v>2.4527032191441208e-05</v>
+        <v>2.4527032191440829e-05</v>
       </c>
       <c r="N27">
-        <v>4.8685890455269767e-06</v>
+        <v>4.8685890455255673e-06</v>
       </c>
       <c r="O27">
-        <v>0.0001031950601707424</v>
+        <v>0.00010319506017074034</v>
       </c>
       <c r="P27">
-        <v>0.00016024217855357525</v>
+        <v>0.00016024217855355617</v>
       </c>
       <c r="Q27">
-        <v>0.00039999263156207613</v>
+        <v>0.00039999263156205705</v>
       </c>
       <c r="R27">
-        <v>0.00039390262233663341</v>
+        <v>0.00039390262233661259</v>
       </c>
       <c r="S27">
-        <v>0.00045272675287773376</v>
+        <v>0.00045272675287771381</v>
       </c>
       <c r="T27">
-        <v>2.1032802931350678e-05</v>
+        <v>2.1032802931348293e-05</v>
       </c>
       <c r="U27">
-        <v>-3.9589942205481418e-05</v>
+        <v>-3.9589942205489224e-05</v>
       </c>
       <c r="V27">
-        <v>3.0966175405284808e-05</v>
+        <v>3.0966175405273966e-05</v>
       </c>
       <c r="W27">
-        <v>5.4205815082366497e-05</v>
+        <v>5.4205815082355221e-05</v>
       </c>
       <c r="X27">
-        <v>-7.4033122276251123e-06</v>
+        <v>-7.4033122276247464e-06</v>
       </c>
       <c r="Y27">
-        <v>-1.2590197192875337e-05</v>
+        <v>-1.2590197192876312e-05</v>
       </c>
       <c r="Z27">
-        <v>0.0024045507518044842</v>
+        <v>0.002404550751804479</v>
       </c>
       <c r="AA27">
-        <v>0.0023978483286616614</v>
+        <v>0.0023978483286616558</v>
       </c>
       <c r="AB27">
-        <v>0.0029016948845160995</v>
+        <v>0.0029016948845160943</v>
       </c>
       <c r="AC27">
-        <v>0.0023941358533534521</v>
+        <v>0.0023941358533534464</v>
       </c>
       <c r="AD27">
-        <v>0.0023931885559049038</v>
+        <v>0.0023931885559048986</v>
       </c>
       <c r="AE27">
-        <v>0.002392623636702109</v>
+        <v>0.0023926236367021038</v>
       </c>
       <c r="AF27">
-        <v>2.0155216062575626e-06</v>
+        <v>2.0155216062572306e-06</v>
       </c>
       <c r="AG27">
-        <v>-6.419983764488317e-05</v>
+        <v>-6.4199837644882303e-05</v>
       </c>
       <c r="AH27">
-        <v>-9.5198216619429973e-05</v>
+        <v>-9.519821661942813e-05</v>
       </c>
       <c r="AI27">
-        <v>-0.0028667674330144456</v>
+        <v>-0.0028667674330144052</v>
       </c>
     </row>
     <row r="28">
@@ -3287,103 +3281,103 @@
         <v>0.05751555787790158</v>
       </c>
       <c r="C28">
-        <v>-0.00010856841590938695</v>
+        <v>-0.00010856841590938744</v>
       </c>
       <c r="D28">
-        <v>0.00013931877986971463</v>
+        <v>0.00013931877986970748</v>
       </c>
       <c r="E28">
-        <v>4.3360577271755454e-05</v>
+        <v>4.3360577271749599e-05</v>
       </c>
       <c r="F28">
-        <v>-2.1056099340469427e-05</v>
+        <v>-2.1056099340474848e-05</v>
       </c>
       <c r="G28">
-        <v>6.6073099431151507e-05</v>
+        <v>6.6073099431144568e-05</v>
       </c>
       <c r="H28">
-        <v>9.9242546054503084e-05</v>
+        <v>9.9242546054496145e-05</v>
       </c>
       <c r="I28">
-        <v>-1.54596361731259e-05</v>
+        <v>-1.5459636173131754e-05</v>
       </c>
       <c r="J28">
-        <v>7.7531048207145131e-05</v>
+        <v>7.7531048207137758e-05</v>
       </c>
       <c r="K28">
-        <v>0.00015350771058333999</v>
+        <v>0.00015350771058333153</v>
       </c>
       <c r="L28">
-        <v>2.9783468960480498e-05</v>
+        <v>2.9783468960470957e-05</v>
       </c>
       <c r="M28">
-        <v>-2.7358458102671876e-05</v>
+        <v>-2.7358458102672744e-05</v>
       </c>
       <c r="N28">
-        <v>1.6549667470977449e-05</v>
+        <v>1.654966747097604e-05</v>
       </c>
       <c r="O28">
-        <v>1.7201678399739488e-05</v>
+        <v>1.7201678399737428e-05</v>
       </c>
       <c r="P28">
-        <v>0.00011097867444824234</v>
+        <v>0.00011097867444822412</v>
       </c>
       <c r="Q28">
-        <v>0.00032778991844847026</v>
+        <v>0.00032778991844845031</v>
       </c>
       <c r="R28">
-        <v>0.00031836766960776329</v>
+        <v>0.00031836766960774247</v>
       </c>
       <c r="S28">
-        <v>0.00038264462745453767</v>
+        <v>0.00038264462745451686</v>
       </c>
       <c r="T28">
-        <v>3.3098360869949768e-05</v>
+        <v>3.3098360869947274e-05</v>
       </c>
       <c r="U28">
-        <v>4.6144882518608238e-06</v>
+        <v>4.6144882518525838e-06</v>
       </c>
       <c r="V28">
-        <v>7.6567174047388088e-05</v>
+        <v>7.6567174047377246e-05</v>
       </c>
       <c r="W28">
-        <v>0.0001318440502646864</v>
+        <v>0.00013184405026467339</v>
       </c>
       <c r="X28">
-        <v>-1.2136815108224671e-05</v>
+        <v>-1.2136815108224142e-05</v>
       </c>
       <c r="Y28">
-        <v>-5.4273072590252304e-06</v>
+        <v>-5.4273072590262333e-06</v>
       </c>
       <c r="Z28">
-        <v>0.002422098966461712</v>
+        <v>0.0024220989664617064</v>
       </c>
       <c r="AA28">
-        <v>0.0024093579671635732</v>
+        <v>0.002409357967163568</v>
       </c>
       <c r="AB28">
-        <v>0.0023941358533534521</v>
+        <v>0.0023941358533534464</v>
       </c>
       <c r="AC28">
-        <v>0.0029680040026244308</v>
+        <v>0.0029680040026244256</v>
       </c>
       <c r="AD28">
-        <v>0.0024122865124234379</v>
+        <v>0.0024122865124234327</v>
       </c>
       <c r="AE28">
-        <v>0.0024099257746925183</v>
+        <v>0.0024099257746925127</v>
       </c>
       <c r="AF28">
-        <v>5.4268485730813349e-06</v>
+        <v>5.426848573080996e-06</v>
       </c>
       <c r="AG28">
-        <v>-7.3490856489324833e-05</v>
+        <v>-7.3490856489324399e-05</v>
       </c>
       <c r="AH28">
-        <v>-6.1148263188884225e-05</v>
+        <v>-6.1148263188882165e-05</v>
       </c>
       <c r="AI28">
-        <v>-0.0028181773427799692</v>
+        <v>-0.0028181773427799289</v>
       </c>
     </row>
     <row r="29">
@@ -3394,103 +3388,103 @@
         <v>-0.072941401664601224</v>
       </c>
       <c r="C29">
-        <v>-6.3819334106375602e-05</v>
+        <v>-6.381933410637609e-05</v>
       </c>
       <c r="D29">
-        <v>0.0001381999711547124</v>
+        <v>0.00013819997115470568</v>
       </c>
       <c r="E29">
-        <v>6.5902518832282645e-05</v>
+        <v>6.590251883227679e-05</v>
       </c>
       <c r="F29">
-        <v>-5.3059972264900691e-06</v>
+        <v>-5.3059972264953275e-06</v>
       </c>
       <c r="G29">
-        <v>2.233402750616547e-05</v>
+        <v>2.2334027506158748e-05</v>
       </c>
       <c r="H29">
-        <v>0.00011251699848730922</v>
+        <v>0.00011251699848730256</v>
       </c>
       <c r="I29">
-        <v>3.2777159819310836e-05</v>
+        <v>3.2777159819304764e-05</v>
       </c>
       <c r="J29">
-        <v>0.00016385404757254807</v>
+        <v>0.00016385404757254108</v>
       </c>
       <c r="K29">
-        <v>0.00035701943319051686</v>
+        <v>0.00035701943319050916</v>
       </c>
       <c r="L29">
-        <v>0.00011865440852694214</v>
+        <v>0.00011865440852693368</v>
       </c>
       <c r="M29">
-        <v>-7.4634030212138337e-05</v>
+        <v>-7.4634030212139259e-05</v>
       </c>
       <c r="N29">
-        <v>1.0462524298721825e-05</v>
+        <v>1.0462524298720361e-05</v>
       </c>
       <c r="O29">
-        <v>6.7471731706364855e-05</v>
+        <v>6.7471731706362795e-05</v>
       </c>
       <c r="P29">
-        <v>0.00021100525375211568</v>
+        <v>0.00021100525375209638</v>
       </c>
       <c r="Q29">
-        <v>0.00040526383753043585</v>
+        <v>0.00040526383753041611</v>
       </c>
       <c r="R29">
-        <v>0.00039693324408754101</v>
+        <v>0.00039693324408752063</v>
       </c>
       <c r="S29">
-        <v>0.00049446962267040286</v>
+        <v>0.00049446962267038247</v>
       </c>
       <c r="T29">
-        <v>2.1061296049572695e-05</v>
+        <v>2.1061296049570486e-05</v>
       </c>
       <c r="U29">
-        <v>0.00010707005547397802</v>
+        <v>0.00010707005547397054</v>
       </c>
       <c r="V29">
-        <v>0.00018787443626775379</v>
+        <v>0.00018787443626774381</v>
       </c>
       <c r="W29">
-        <v>0.00019495295271683931</v>
+        <v>0.00019495295271682749</v>
       </c>
       <c r="X29">
-        <v>-8.7635720959448961e-06</v>
+        <v>-8.7635720959445454e-06</v>
       </c>
       <c r="Y29">
-        <v>5.0475275273064929e-06</v>
+        <v>5.0475275273061134e-06</v>
       </c>
       <c r="Z29">
-        <v>0.0024195156018215289</v>
+        <v>0.0024195156018215242</v>
       </c>
       <c r="AA29">
-        <v>0.002411118530773455</v>
+        <v>0.0024111185307734502</v>
       </c>
       <c r="AB29">
-        <v>0.0023931885559049038</v>
+        <v>0.0023931885559048986</v>
       </c>
       <c r="AC29">
-        <v>0.0024122865124234379</v>
+        <v>0.0024122865124234327</v>
       </c>
       <c r="AD29">
-        <v>0.0027931079009252159</v>
+        <v>0.0027931079009252111</v>
       </c>
       <c r="AE29">
-        <v>0.0024091875765934576</v>
+        <v>0.0024091875765934519</v>
       </c>
       <c r="AF29">
-        <v>8.4739414599884578e-07</v>
+        <v>8.4739414599852052e-07</v>
       </c>
       <c r="AG29">
-        <v>5.9676148105947038e-05</v>
+        <v>5.9676148105947688e-05</v>
       </c>
       <c r="AH29">
-        <v>-3.4783355698565798e-05</v>
+        <v>-3.4783355698563847e-05</v>
       </c>
       <c r="AI29">
-        <v>-0.003030587226981382</v>
+        <v>-0.0030305872269813425</v>
       </c>
     </row>
     <row r="30">
@@ -3501,103 +3495,103 @@
         <v>0.065751712427960879</v>
       </c>
       <c r="C30">
-        <v>-4.7641209485679661e-06</v>
+        <v>-4.7641209485683879e-06</v>
       </c>
       <c r="D30">
-        <v>2.6842920995656433e-05</v>
+        <v>2.6842920995652259e-05</v>
       </c>
       <c r="E30">
-        <v>-1.1316323787101472e-05</v>
+        <v>-1.1316323787104453e-05</v>
       </c>
       <c r="F30">
-        <v>-7.2812817573086278e-05</v>
+        <v>-7.2812817573089097e-05</v>
       </c>
       <c r="G30">
-        <v>-3.5116145501637398e-05</v>
+        <v>-3.5116145501641518e-05</v>
       </c>
       <c r="H30">
-        <v>-6.664141507371497e-06</v>
+        <v>-6.6641415073755085e-06</v>
       </c>
       <c r="I30">
-        <v>2.4805335383808186e-05</v>
+        <v>2.4805335383805286e-05</v>
       </c>
       <c r="J30">
-        <v>1.1865457425520377e-05</v>
+        <v>1.1865457425516121e-05</v>
       </c>
       <c r="K30">
-        <v>0.00021877282758949387</v>
+        <v>0.00021877282758948503</v>
       </c>
       <c r="L30">
-        <v>-5.0038669633645488e-05</v>
+        <v>-5.0038669633654487e-05</v>
       </c>
       <c r="M30">
-        <v>-0.00015014202061696452</v>
+        <v>-0.00015014202061696492</v>
       </c>
       <c r="N30">
-        <v>-2.3821879086439562e-05</v>
+        <v>-2.3821879086440985e-05</v>
       </c>
       <c r="O30">
-        <v>1.4188838300475437e-05</v>
+        <v>1.4188838300473384e-05</v>
       </c>
       <c r="P30">
-        <v>0.0003901010332448111</v>
+        <v>0.00039010103324479181</v>
       </c>
       <c r="Q30">
-        <v>0.00037619705005903449</v>
+        <v>0.00037619705005901481</v>
       </c>
       <c r="R30">
-        <v>0.0004136654359543841</v>
+        <v>0.00041366543595436388</v>
       </c>
       <c r="S30">
-        <v>0.0003212531701308536</v>
+        <v>0.00032125317013083311</v>
       </c>
       <c r="T30">
-        <v>0.0001100429042331806</v>
+        <v>0.00011004290423317835</v>
       </c>
       <c r="U30">
-        <v>7.5686072508706647e-05</v>
+        <v>7.5686072508698935e-05</v>
       </c>
       <c r="V30">
-        <v>0.00020760721124197113</v>
+        <v>0.00020760721124196092</v>
       </c>
       <c r="W30">
-        <v>0.00014314395619295401</v>
+        <v>0.00014314395619294227</v>
       </c>
       <c r="X30">
-        <v>-1.5430911525350564e-05</v>
+        <v>-1.5430911525350185e-05</v>
       </c>
       <c r="Y30">
-        <v>-4.6852151554368649e-05</v>
+        <v>-4.6852151554369116e-05</v>
       </c>
       <c r="Z30">
-        <v>0.0024034528561093466</v>
+        <v>0.0024034528561093405</v>
       </c>
       <c r="AA30">
-        <v>0.0024006466571823981</v>
+        <v>0.0024006466571823933</v>
       </c>
       <c r="AB30">
-        <v>0.002392623636702109</v>
+        <v>0.0023926236367021038</v>
       </c>
       <c r="AC30">
-        <v>0.0024099257746925183</v>
+        <v>0.0024099257746925127</v>
       </c>
       <c r="AD30">
-        <v>0.0024091875765934576</v>
+        <v>0.0024091875765934519</v>
       </c>
       <c r="AE30">
-        <v>0.0030251089773792855</v>
+        <v>0.0030251089773792803</v>
       </c>
       <c r="AF30">
-        <v>2.9194340006783489e-06</v>
+        <v>2.9194340006780101e-06</v>
       </c>
       <c r="AG30">
-        <v>-4.3658362118780512e-06</v>
+        <v>-4.3658362118767502e-06</v>
       </c>
       <c r="AH30">
-        <v>-9.5541077437664881e-05</v>
+        <v>-9.554107743766293e-05</v>
       </c>
       <c r="AI30">
-        <v>-0.00288330153668562</v>
+        <v>-0.002883301536685581</v>
       </c>
     </row>
     <row r="31">
@@ -3608,103 +3602,103 @@
         <v>0.001711011159776669</v>
       </c>
       <c r="C31">
-        <v>-1.9497710287320125e-06</v>
+        <v>-1.9497710287320363e-06</v>
       </c>
       <c r="D31">
-        <v>-8.510155342638653e-06</v>
+        <v>-8.5101553426391137e-06</v>
       </c>
       <c r="E31">
-        <v>5.5397297790910622e-06</v>
+        <v>5.5397297790906963e-06</v>
       </c>
       <c r="F31">
-        <v>2.3800320149091234e-06</v>
+        <v>2.3800320149087914e-06</v>
       </c>
       <c r="G31">
-        <v>1.0130120580752258e-05</v>
+        <v>1.0130120580751824e-05</v>
       </c>
       <c r="H31">
-        <v>1.4003597577925736e-05</v>
+        <v>1.4003597577925309e-05</v>
       </c>
       <c r="I31">
-        <v>2.8167527087335329e-06</v>
+        <v>2.816752708733167e-06</v>
       </c>
       <c r="J31">
-        <v>2.2537754202515888e-06</v>
+        <v>2.2537754202511416e-06</v>
       </c>
       <c r="K31">
-        <v>-3.2565980408828582e-07</v>
+        <v>-3.2565980408889568e-07</v>
       </c>
       <c r="L31">
-        <v>1.0516857342269856e-05</v>
+        <v>1.0516857342269273e-05</v>
       </c>
       <c r="M31">
-        <v>1.4859872921433194e-05</v>
+        <v>1.485987292143316e-05</v>
       </c>
       <c r="N31">
-        <v>5.6168139851843385e-06</v>
+        <v>5.6168139851841725e-06</v>
       </c>
       <c r="O31">
-        <v>9.5812939870467515e-06</v>
+        <v>9.5812939870465787e-06</v>
       </c>
       <c r="P31">
-        <v>5.7254640730701912e-06</v>
+        <v>5.7254640730689985e-06</v>
       </c>
       <c r="Q31">
-        <v>-2.8570980447728111e-07</v>
+        <v>-2.8570980447852794e-07</v>
       </c>
       <c r="R31">
-        <v>3.6208117601813138e-06</v>
+        <v>3.6208117601800398e-06</v>
       </c>
       <c r="S31">
-        <v>6.4351374456253854e-06</v>
+        <v>6.4351374456240844e-06</v>
       </c>
       <c r="T31">
-        <v>-3.1269371662585882e-06</v>
+        <v>-3.1269371662587372e-06</v>
       </c>
       <c r="U31">
-        <v>4.5265732748422195e-06</v>
+        <v>4.526573274841691e-06</v>
       </c>
       <c r="V31">
-        <v>9.0116810501183992e-06</v>
+        <v>9.011681050117681e-06</v>
       </c>
       <c r="W31">
-        <v>1.1770680230067129e-05</v>
+        <v>1.1770680230066316e-05</v>
       </c>
       <c r="X31">
-        <v>1.9760107536394927e-06</v>
+        <v>1.9760107536395181e-06</v>
       </c>
       <c r="Y31">
-        <v>-1.5188203201892972e-07</v>
+        <v>-1.5188203201898986e-07</v>
       </c>
       <c r="Z31">
-        <v>4.3270358777728335e-06</v>
+        <v>4.3270358777724812e-06</v>
       </c>
       <c r="AA31">
-        <v>5.2611654468125231e-06</v>
+        <v>5.261165446812191e-06</v>
       </c>
       <c r="AB31">
-        <v>2.0155216062575626e-06</v>
+        <v>2.0155216062572306e-06</v>
       </c>
       <c r="AC31">
-        <v>5.4268485730813349e-06</v>
+        <v>5.426848573080996e-06</v>
       </c>
       <c r="AD31">
-        <v>8.4739414599884578e-07</v>
+        <v>8.4739414599852052e-07</v>
       </c>
       <c r="AE31">
-        <v>2.9194340006783489e-06</v>
+        <v>2.9194340006780101e-06</v>
       </c>
       <c r="AF31">
-        <v>4.7593550376573975e-06</v>
+        <v>4.7593550376573738e-06</v>
       </c>
       <c r="AG31">
-        <v>-7.1751980030204448e-06</v>
+        <v>-7.1751980030203906e-06</v>
       </c>
       <c r="AH31">
-        <v>-1.3480168463239126e-05</v>
+        <v>-1.3480168463238984e-05</v>
       </c>
       <c r="AI31">
-        <v>-0.00011321363707010979</v>
+        <v>-0.00011321363707010679</v>
       </c>
     </row>
     <row r="32">
@@ -3718,100 +3712,100 @@
         <v>8.2682461790918268e-05</v>
       </c>
       <c r="D32">
-        <v>5.4247913094002641e-05</v>
+        <v>5.4247913094003508e-05</v>
       </c>
       <c r="E32">
-        <v>-3.478174268162779e-05</v>
+        <v>-3.4781742681626923e-05</v>
       </c>
       <c r="F32">
-        <v>0.00011273175229523005</v>
+        <v>0.00011273175229523048</v>
       </c>
       <c r="G32">
-        <v>-0.00013755789499182583</v>
+        <v>-0.00013755789499182497</v>
       </c>
       <c r="H32">
-        <v>-8.677864140106727e-05</v>
+        <v>-8.6778641401066403e-05</v>
       </c>
       <c r="I32">
-        <v>4.6806591355711726e-06</v>
+        <v>4.6806591355720399e-06</v>
       </c>
       <c r="J32">
-        <v>0.00015386211925594393</v>
+        <v>0.0001538621192559448</v>
       </c>
       <c r="K32">
-        <v>0.00037063543131517695</v>
+        <v>0.00037063543131517782</v>
       </c>
       <c r="L32">
-        <v>5.5955232594965317e-05</v>
+        <v>5.5955232594966618e-05</v>
       </c>
       <c r="M32">
-        <v>-0.0003083322232353533</v>
+        <v>-0.00030833222323535335</v>
       </c>
       <c r="N32">
-        <v>-9.8069252881486746e-05</v>
+        <v>-9.8069252881486529e-05</v>
       </c>
       <c r="O32">
-        <v>-8.9809283282528667e-05</v>
+        <v>-8.9809283282528234e-05</v>
       </c>
       <c r="P32">
-        <v>1.2088203191894242e-05</v>
+        <v>1.2088203191896844e-05</v>
       </c>
       <c r="Q32">
-        <v>4.3779515320172685e-05</v>
+        <v>4.3779515320176154e-05</v>
       </c>
       <c r="R32">
-        <v>4.594633735862351e-05</v>
+        <v>4.5946337358625244e-05</v>
       </c>
       <c r="S32">
-        <v>4.3708144531393739e-05</v>
+        <v>4.3708144531397208e-05</v>
       </c>
       <c r="T32">
-        <v>-0.00013761921847101533</v>
+        <v>-0.000137619218471015</v>
       </c>
       <c r="U32">
-        <v>-2.3809894667178953e-05</v>
+        <v>-2.3809894667178085e-05</v>
       </c>
       <c r="V32">
-        <v>9.8761563418469159e-05</v>
+        <v>9.8761563418470026e-05</v>
       </c>
       <c r="W32">
-        <v>-0.00017259147849397072</v>
+        <v>-0.00017259147849396899</v>
       </c>
       <c r="X32">
-        <v>3.0246414570963667e-05</v>
+        <v>3.0246414570963613e-05</v>
       </c>
       <c r="Y32">
-        <v>-0.00010559568546626726</v>
+        <v>-0.00010559568546626721</v>
       </c>
       <c r="Z32">
-        <v>-8.9653440550173901e-05</v>
+        <v>-8.9653440550173467e-05</v>
       </c>
       <c r="AA32">
-        <v>-8.554109528829219e-05</v>
+        <v>-8.5541095288291539e-05</v>
       </c>
       <c r="AB32">
-        <v>-6.419983764488317e-05</v>
+        <v>-6.4199837644882303e-05</v>
       </c>
       <c r="AC32">
-        <v>-7.3490856489324833e-05</v>
+        <v>-7.3490856489324399e-05</v>
       </c>
       <c r="AD32">
-        <v>5.9676148105947038e-05</v>
+        <v>5.9676148105947688e-05</v>
       </c>
       <c r="AE32">
-        <v>-4.3658362118780512e-06</v>
+        <v>-4.3658362118767502e-06</v>
       </c>
       <c r="AF32">
-        <v>-7.1751980030204448e-06</v>
+        <v>-7.1751980030203906e-06</v>
       </c>
       <c r="AG32">
-        <v>0.0021902531402251328</v>
+        <v>0.0021902531402251324</v>
       </c>
       <c r="AH32">
-        <v>0.00014619121712923123</v>
+        <v>0.00014619121712923088</v>
       </c>
       <c r="AI32">
-        <v>7.4687898885519226e-06</v>
+        <v>7.4687898885448753e-06</v>
       </c>
     </row>
     <row r="33">
@@ -3822,103 +3816,103 @@
         <v>-0.045878343329260198</v>
       </c>
       <c r="C33">
-        <v>1.3097791130418568e-05</v>
+        <v>1.3097791130418758e-05</v>
       </c>
       <c r="D33">
-        <v>0.0013306349657106369</v>
+        <v>0.0013306349657106393</v>
       </c>
       <c r="E33">
-        <v>2.9482721689708916e-05</v>
+        <v>2.9482721689711084e-05</v>
       </c>
       <c r="F33">
-        <v>7.0103091909827909e-05</v>
+        <v>7.0103091909829969e-05</v>
       </c>
       <c r="G33">
-        <v>7.94450703574237e-05</v>
+        <v>7.9445070357426519e-05</v>
       </c>
       <c r="H33">
-        <v>6.0970632979297701e-05</v>
+        <v>6.0970632979300519e-05</v>
       </c>
       <c r="I33">
-        <v>3.7243755954834818e-05</v>
+        <v>3.7243755954837095e-05</v>
       </c>
       <c r="J33">
-        <v>-2.3520691061545192e-05</v>
+        <v>-2.352069106154259e-05</v>
       </c>
       <c r="K33">
-        <v>-9.4744370399683486e-05</v>
+        <v>-9.4744370399680233e-05</v>
       </c>
       <c r="L33">
-        <v>-2.7635679664000023e-05</v>
+        <v>-2.7635679663996771e-05</v>
       </c>
       <c r="M33">
-        <v>-4.2100416755658744e-05</v>
+        <v>-4.2100416755658582e-05</v>
       </c>
       <c r="N33">
-        <v>-3.6525377833205295e-05</v>
+        <v>-3.6525377833204617e-05</v>
       </c>
       <c r="O33">
-        <v>-7.0967816654568961e-05</v>
+        <v>-7.0967816654568094e-05</v>
       </c>
       <c r="P33">
-        <v>-4.9005125978278993e-05</v>
+        <v>-4.9005125978272054e-05</v>
       </c>
       <c r="Q33">
-        <v>2.3744716712629371e-05</v>
+        <v>2.3744716712636744e-05</v>
       </c>
       <c r="R33">
-        <v>2.3263439245859233e-05</v>
+        <v>2.3263439245867039e-05</v>
       </c>
       <c r="S33">
-        <v>7.8244783439965129e-05</v>
+        <v>7.8244783439972935e-05</v>
       </c>
       <c r="T33">
-        <v>-5.2297174353574253e-05</v>
+        <v>-5.2297174353573494e-05</v>
       </c>
       <c r="U33">
-        <v>-6.83737626523441e-05</v>
+        <v>-6.8373762652341064e-05</v>
       </c>
       <c r="V33">
-        <v>-0.00010339082551957465</v>
+        <v>-0.00010339082551957053</v>
       </c>
       <c r="W33">
-        <v>-0.00014225457160010066</v>
+        <v>-0.00014225457160009589</v>
       </c>
       <c r="X33">
-        <v>-4.9263320160388346e-06</v>
+        <v>-4.9263320160389769e-06</v>
       </c>
       <c r="Y33">
-        <v>2.8898995698168637e-05</v>
+        <v>2.8898995698168942e-05</v>
       </c>
       <c r="Z33">
-        <v>-7.5214449039282634e-05</v>
+        <v>-7.5214449039280574e-05</v>
       </c>
       <c r="AA33">
-        <v>-1.6356704670960178e-05</v>
+        <v>-1.6356704670958226e-05</v>
       </c>
       <c r="AB33">
-        <v>-9.5198216619429973e-05</v>
+        <v>-9.519821661942813e-05</v>
       </c>
       <c r="AC33">
-        <v>-6.1148263188884225e-05</v>
+        <v>-6.1148263188882165e-05</v>
       </c>
       <c r="AD33">
-        <v>-3.4783355698565798e-05</v>
+        <v>-3.4783355698563847e-05</v>
       </c>
       <c r="AE33">
-        <v>-9.5541077437664881e-05</v>
+        <v>-9.554107743766293e-05</v>
       </c>
       <c r="AF33">
-        <v>-1.3480168463239126e-05</v>
+        <v>-1.3480168463238984e-05</v>
       </c>
       <c r="AG33">
-        <v>0.00014619121712923123</v>
+        <v>0.00014619121712923088</v>
       </c>
       <c r="AH33">
         <v>0.0024010981295976537</v>
       </c>
       <c r="AI33">
-        <v>0.00024089133971756486</v>
+        <v>0.00024089133971756042</v>
       </c>
     </row>
     <row r="34">
@@ -3929,103 +3923,103 @@
         <v>-1.5822168062419928</v>
       </c>
       <c r="C34">
-        <v>-7.2034827626278066e-05</v>
+        <v>-7.2034827626273621e-05</v>
       </c>
       <c r="D34">
-        <v>-0.0029610538351408063</v>
+        <v>-0.0029610538351407534</v>
       </c>
       <c r="E34">
-        <v>-0.0024047977311919999</v>
+        <v>-0.0024047977311919557</v>
       </c>
       <c r="F34">
-        <v>-0.0020326920215608581</v>
+        <v>-0.0020326920215608178</v>
       </c>
       <c r="G34">
-        <v>-0.0029729672163785214</v>
+        <v>-0.0029729672163784711</v>
       </c>
       <c r="H34">
-        <v>-0.0028559799727097693</v>
+        <v>-0.0028559799727097212</v>
       </c>
       <c r="I34">
-        <v>-0.0024133870012869878</v>
+        <v>-0.0024133870012869427</v>
       </c>
       <c r="J34">
-        <v>-0.0025820961429938089</v>
+        <v>-0.0025820961429937582</v>
       </c>
       <c r="K34">
-        <v>-0.0040142065628920171</v>
+        <v>-0.0040142065628919693</v>
       </c>
       <c r="L34">
-        <v>-0.0036131444182357572</v>
+        <v>-0.0036131444182357165</v>
       </c>
       <c r="M34">
-        <v>-0.00015965131485163692</v>
+        <v>-0.00015965131485164451</v>
       </c>
       <c r="N34">
-        <v>-0.00082028153442179996</v>
+        <v>-0.00082028153442178955</v>
       </c>
       <c r="O34">
-        <v>-0.0011770786664807545</v>
+        <v>-0.0011770786664807391</v>
       </c>
       <c r="P34">
-        <v>-0.0076469234090673632</v>
+        <v>-0.0076469234090672089</v>
       </c>
       <c r="Q34">
-        <v>-0.0074153616530797445</v>
+        <v>-0.0074153616530795857</v>
       </c>
       <c r="R34">
-        <v>-0.007654192618377853</v>
+        <v>-0.00765419261837769</v>
       </c>
       <c r="S34">
-        <v>-0.0080109756220311541</v>
+        <v>-0.0080109756220309893</v>
       </c>
       <c r="T34">
-        <v>-0.00073223072105571747</v>
+        <v>-0.00073223072105570988</v>
       </c>
       <c r="U34">
-        <v>-0.0036109294228694813</v>
+        <v>-0.0036109294228694492</v>
       </c>
       <c r="V34">
-        <v>-0.0044241714089442597</v>
+        <v>-0.0044241714089442189</v>
       </c>
       <c r="W34">
-        <v>-0.0053221193019863666</v>
+        <v>-0.0053221193019863094</v>
       </c>
       <c r="X34">
-        <v>0.0001879211432245401</v>
+        <v>0.00018792114322453902</v>
       </c>
       <c r="Y34">
-        <v>-0.00018355116897699833</v>
+        <v>-0.0001835511689769905</v>
       </c>
       <c r="Z34">
-        <v>-0.0030368046871221436</v>
+        <v>-0.003036804687122102</v>
       </c>
       <c r="AA34">
-        <v>-0.0029087018043451977</v>
+        <v>-0.0029087018043451578</v>
       </c>
       <c r="AB34">
-        <v>-0.0028667674330144456</v>
+        <v>-0.0028667674330144052</v>
       </c>
       <c r="AC34">
-        <v>-0.0028181773427799692</v>
+        <v>-0.0028181773427799289</v>
       </c>
       <c r="AD34">
-        <v>-0.003030587226981382</v>
+        <v>-0.0030305872269813425</v>
       </c>
       <c r="AE34">
-        <v>-0.00288330153668562</v>
+        <v>-0.002883301536685581</v>
       </c>
       <c r="AF34">
-        <v>-0.00011321363707010979</v>
+        <v>-0.00011321363707010679</v>
       </c>
       <c r="AG34">
-        <v>7.4687898885519226e-06</v>
+        <v>7.4687898885448753e-06</v>
       </c>
       <c r="AH34">
-        <v>0.00024089133971756486</v>
+        <v>0.00024089133971756042</v>
       </c>
       <c r="AI34">
-        <v>0.019747248539181771</v>
+        <v>0.01974724853918142</v>
       </c>
     </row>
   </sheetData>
